--- a/data/50001580- CIA. RIO MINERALES.xlsx
+++ b/data/50001580- CIA. RIO MINERALES.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1346" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1346" uniqueCount="328">
   <si>
     <t>50001580- "CIA. RIO MINERALES"</t>
   </si>
@@ -221,6 +221,9 @@
   </si>
   <si>
     <t>Reserva Alabes OT4378</t>
+  </si>
+  <si>
+    <t>NATALYA ESPINOZA</t>
   </si>
   <si>
     <t>nespinoza@zitron.com</t>
@@ -2369,7 +2372,7 @@
         <v>70</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I17" s="8">
         <v>46226</v>
@@ -2393,7 +2396,7 @@
         <v>36</v>
       </c>
       <c r="P17" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q17" s="8">
         <v>46227</v>
@@ -2413,7 +2416,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B18" s="5">
         <v>46225.58096494213</v>
@@ -2423,7 +2426,7 @@
         <v>46225.61237618055</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
@@ -2432,7 +2435,7 @@
         <v>70</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I18" s="5">
         <v>46226</v>
@@ -2456,7 +2459,7 @@
         <v>36</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q18" s="5">
         <v>46227</v>
@@ -2476,7 +2479,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B19" s="8">
         <v>46225.58097109954</v>
@@ -2486,7 +2489,7 @@
         <v>46225.612370937495</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>26</v>
@@ -2495,7 +2498,7 @@
         <v>70</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I19" s="8">
         <v>46226</v>
@@ -2519,7 +2522,7 @@
         <v>36</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q19" s="8">
         <v>46227</v>
@@ -2539,7 +2542,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B20" s="5">
         <v>46225.58086628473</v>
@@ -2549,7 +2552,7 @@
         <v>46225.59619578704</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>25</v>
@@ -2573,7 +2576,7 @@
         <v>26</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P20" s="6" t="s">
         <v>26</v>
@@ -2586,7 +2589,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B21" s="8">
         <v>46225.580978240745</v>
@@ -2596,7 +2599,7 @@
         <v>46225.61247136574</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>26</v>
@@ -2605,7 +2608,7 @@
         <v>70</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I21" s="8">
         <v>46245</v>
@@ -2623,13 +2626,13 @@
         <v>26</v>
       </c>
       <c r="N21" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q21" s="8">
         <v>46246</v>
@@ -2649,7 +2652,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B22" s="5">
         <v>46225.5809840625</v>
@@ -2659,7 +2662,7 @@
         <v>46225.612467824074</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
@@ -2668,7 +2671,7 @@
         <v>70</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I22" s="5">
         <v>46245</v>
@@ -2686,13 +2689,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q22" s="5">
         <v>46246</v>
@@ -2712,7 +2715,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B23" s="8">
         <v>46225.58098827546</v>
@@ -2722,7 +2725,7 @@
         <v>46225.612464756945</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
@@ -2731,7 +2734,7 @@
         <v>70</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I23" s="8">
         <v>46245</v>
@@ -2749,13 +2752,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q23" s="8">
         <v>46246</v>
@@ -2775,7 +2778,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B24" s="5">
         <v>46225.58100011574</v>
@@ -2785,7 +2788,7 @@
         <v>46225.61246184028</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
@@ -2794,7 +2797,7 @@
         <v>70</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I24" s="5">
         <v>46245</v>
@@ -2812,13 +2815,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q24" s="5">
         <v>46246</v>
@@ -2838,7 +2841,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B25" s="8">
         <v>46225.59619364583</v>
@@ -2848,7 +2851,7 @@
         <v>46225.61245637732</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
@@ -2857,7 +2860,7 @@
         <v>70</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I25" s="8">
         <v>46231</v>
@@ -2875,13 +2878,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O25" s="9" t="s">
         <v>44</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q25" s="8">
         <v>46232</v>
@@ -2901,7 +2904,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B26" s="5">
         <v>46225.58087085648</v>
@@ -2911,7 +2914,7 @@
         <v>46225.596821886575</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>25</v>
@@ -2935,7 +2938,7 @@
         <v>26</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P26" s="6" t="s">
         <v>26</v>
@@ -2948,7 +2951,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B27" s="8">
         <v>46225.58100560185</v>
@@ -2958,16 +2961,16 @@
         <v>46225.61255763889</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I27" s="8">
         <v>46247</v>
@@ -2985,13 +2988,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q27" s="8">
         <v>46259</v>
@@ -3011,7 +3014,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B28" s="5">
         <v>46225.58101144676</v>
@@ -3021,16 +3024,16 @@
         <v>46225.61262662037</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I28" s="5">
         <v>46247</v>
@@ -3048,13 +3051,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3070,7 +3073,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B29" s="8">
         <v>46225.581017233795</v>
@@ -3080,16 +3083,16 @@
         <v>46225.61262351852</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I29" s="8">
         <v>46251</v>
@@ -3107,13 +3110,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
@@ -3129,7 +3132,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B30" s="5">
         <v>46225.58102277778</v>
@@ -3139,16 +3142,16 @@
         <v>46225.61255446759</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I30" s="5">
         <v>46247</v>
@@ -3166,10 +3169,10 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P30" s="6" t="s">
         <v>26</v>
@@ -3192,7 +3195,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B31" s="8">
         <v>46225.58102737268</v>
@@ -3202,16 +3205,16 @@
         <v>46225.61269579861</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I31" s="8">
         <v>46247</v>
@@ -3229,13 +3232,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3245,7 +3248,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B32" s="5">
         <v>46225.581032222224</v>
@@ -3255,16 +3258,16 @@
         <v>46225.612692442126</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I32" s="5">
         <v>46251</v>
@@ -3282,13 +3285,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3298,7 +3301,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B33" s="8">
         <v>46225.581037199074</v>
@@ -3308,16 +3311,16 @@
         <v>46225.61279568287</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I33" s="8">
         <v>46247</v>
@@ -3335,10 +3338,10 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P33" s="9" t="s">
         <v>26</v>
@@ -3361,7 +3364,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B34" s="5">
         <v>46225.58104158565</v>
@@ -3371,16 +3374,16 @@
         <v>46225.61298453704</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I34" s="5">
         <v>46247</v>
@@ -3398,13 +3401,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3414,7 +3417,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B35" s="8">
         <v>46225.5810464699</v>
@@ -3424,16 +3427,16 @@
         <v>46225.61298125</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I35" s="8">
         <v>46251</v>
@@ -3451,13 +3454,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
@@ -3467,7 +3470,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B36" s="5">
         <v>46225.58105121528</v>
@@ -3477,16 +3480,16 @@
         <v>46225.61316422454</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I36" s="5">
         <v>46247</v>
@@ -3504,10 +3507,10 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3530,7 +3533,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B37" s="8">
         <v>46225.58109630787</v>
@@ -3540,16 +3543,16 @@
         <v>46225.613052245375</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I37" s="8">
         <v>46247</v>
@@ -3567,13 +3570,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3583,7 +3586,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B38" s="5">
         <v>46225.58110178241</v>
@@ -3593,16 +3596,16 @@
         <v>46225.613047719904</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I38" s="5">
         <v>46258</v>
@@ -3620,13 +3623,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3636,7 +3639,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B39" s="8">
         <v>46225.58110600694</v>
@@ -3646,16 +3649,16 @@
         <v>46225.613129363424</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I39" s="8">
         <v>46289</v>
@@ -3673,13 +3676,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
@@ -3689,7 +3692,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B40" s="5">
         <v>46225.59682005787</v>
@@ -3699,16 +3702,16 @@
         <v>46225.6133383912</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I40" s="5">
         <v>46233</v>
@@ -3726,10 +3729,10 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>26</v>
@@ -3752,7 +3755,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B41" s="8">
         <v>46225.59686481481</v>
@@ -3762,16 +3765,16 @@
         <v>46225.613313634254</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I41" s="8">
         <v>46233</v>
@@ -3789,13 +3792,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
@@ -3805,7 +3808,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B42" s="5">
         <v>46225.59692966435</v>
@@ -3815,16 +3818,16 @@
         <v>46225.613310636574</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I42" s="5">
         <v>46244</v>
@@ -3842,13 +3845,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -3858,7 +3861,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B43" s="8">
         <v>46225.58111748843</v>
@@ -3868,7 +3871,7 @@
         <v>46225.589328946764</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>25</v>
@@ -3892,7 +3895,7 @@
         <v>26</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>26</v>
@@ -3905,7 +3908,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B44" s="5">
         <v>46225.58112127315</v>
@@ -3915,16 +3918,16 @@
         <v>46225.61343114583</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I44" s="5">
         <v>46230</v>
@@ -3942,13 +3945,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>62</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q44" s="5">
         <v>46234</v>
@@ -3968,7 +3971,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B45" s="8">
         <v>46225.58112643519</v>
@@ -3978,16 +3981,16 @@
         <v>46225.613428275465</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I45" s="8">
         <v>46237</v>
@@ -4005,13 +4008,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q45" s="8">
         <v>46241</v>
@@ -4031,7 +4034,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B46" s="5">
         <v>46225.58113097222</v>
@@ -4041,16 +4044,16 @@
         <v>46225.61342412037</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I46" s="5">
         <v>46244</v>
@@ -4068,13 +4071,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q46" s="5">
         <v>46244</v>
@@ -4094,7 +4097,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B47" s="8">
         <v>46225.58114445602</v>
@@ -4104,16 +4107,16 @@
         <v>46225.61347256944</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I47" s="8">
         <v>46290</v>
@@ -4131,13 +4134,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q47" s="8">
         <v>46290</v>
@@ -4157,7 +4160,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B48" s="5">
         <v>46225.58114871528</v>
@@ -4167,16 +4170,16 @@
         <v>46225.61551950232</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I48" s="5">
         <v>46290</v>
@@ -4194,13 +4197,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4210,7 +4213,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B49" s="8">
         <v>46225.58115283565</v>
@@ -4220,16 +4223,16 @@
         <v>46225.615519513885</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I49" s="8">
         <v>46290</v>
@@ -4247,13 +4250,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q49" s="9"/>
       <c r="R49" s="9"/>
@@ -4263,7 +4266,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B50" s="5">
         <v>46225.581171631944</v>
@@ -4273,7 +4276,7 @@
         <v>46225.59181146991</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>25</v>
@@ -4297,7 +4300,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4310,7 +4313,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B51" s="8">
         <v>46225.58117489584</v>
@@ -4320,16 +4323,16 @@
         <v>46225.61367097222</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I51" s="8">
         <v>46260</v>
@@ -4347,13 +4350,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q51" s="8">
         <v>46260</v>
@@ -4373,7 +4376,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B52" s="5">
         <v>46225.58118028935</v>
@@ -4383,16 +4386,16 @@
         <v>46225.613667349535</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I52" s="5">
         <v>46260</v>
@@ -4410,13 +4413,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q52" s="5">
         <v>46260</v>
@@ -4436,7 +4439,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B53" s="8">
         <v>46225.58118576389</v>
@@ -4446,16 +4449,16 @@
         <v>46225.61366387732</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I53" s="8">
         <v>46260</v>
@@ -4473,13 +4476,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q53" s="8">
         <v>46260</v>
@@ -4499,7 +4502,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B54" s="5">
         <v>46225.58119107639</v>
@@ -4509,16 +4512,16 @@
         <v>46225.61417395833</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I54" s="5">
         <v>46261</v>
@@ -4536,13 +4539,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q54" s="5">
         <v>46261</v>
@@ -4562,7 +4565,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B55" s="8">
         <v>46225.58119642361</v>
@@ -4572,16 +4575,16 @@
         <v>46225.61417104167</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I55" s="8">
         <v>46261</v>
@@ -4599,13 +4602,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q55" s="8">
         <v>46261</v>
@@ -4625,7 +4628,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B56" s="5">
         <v>46225.581201678244</v>
@@ -4635,16 +4638,16 @@
         <v>46225.61416773148</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I56" s="5">
         <v>46261</v>
@@ -4662,13 +4665,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q56" s="5">
         <v>46261</v>
@@ -4688,7 +4691,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B57" s="8">
         <v>46225.58120702546</v>
@@ -4698,7 +4701,7 @@
         <v>46225.59190644676</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>25</v>
@@ -4722,7 +4725,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P57" s="9" t="s">
         <v>26</v>
@@ -4735,7 +4738,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B58" s="5">
         <v>46225.58121010417</v>
@@ -4745,16 +4748,16 @@
         <v>46225.6142333912</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I58" s="5">
         <v>46262</v>
@@ -4772,13 +4775,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q58" s="5">
         <v>46266</v>
@@ -4798,7 +4801,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B59" s="8">
         <v>46225.581215474536</v>
@@ -4808,16 +4811,16 @@
         <v>46225.61435628472</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I59" s="8">
         <v>46267</v>
@@ -4835,13 +4838,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q59" s="8">
         <v>46273</v>
@@ -4861,7 +4864,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B60" s="5">
         <v>46225.581219618056</v>
@@ -4871,16 +4874,16 @@
         <v>46225.614318611115</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I60" s="5">
         <v>46267</v>
@@ -4898,13 +4901,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -4914,7 +4917,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B61" s="8">
         <v>46225.58123596065</v>
@@ -4924,16 +4927,16 @@
         <v>46225.61431550926</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I61" s="8">
         <v>46267</v>
@@ -4951,13 +4954,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
@@ -4967,7 +4970,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B62" s="5">
         <v>46225.58129219907</v>
@@ -4977,16 +4980,16 @@
         <v>46225.61447392361</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I62" s="5">
         <v>46274</v>
@@ -5004,13 +5007,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q62" s="5">
         <v>46274</v>
@@ -5030,7 +5033,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B63" s="8">
         <v>46225.58129802083</v>
@@ -5040,16 +5043,16 @@
         <v>46225.61443357639</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I63" s="9"/>
       <c r="J63" s="8">
@@ -5065,13 +5068,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q63" s="9"/>
       <c r="R63" s="9"/>
@@ -5081,7 +5084,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B64" s="5">
         <v>46225.581304374995</v>
@@ -5091,16 +5094,16 @@
         <v>46225.61443052083</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I64" s="6"/>
       <c r="J64" s="5">
@@ -5116,13 +5119,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5132,7 +5135,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B65" s="8">
         <v>46225.58131015046</v>
@@ -5142,7 +5145,7 @@
         <v>46225.59759329861</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>25</v>
@@ -5166,7 +5169,7 @@
         <v>26</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P65" s="9" t="s">
         <v>26</v>
@@ -5179,7 +5182,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B66" s="5">
         <v>46225.58131376158</v>
@@ -5189,16 +5192,16 @@
         <v>46225.61459215278</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I66" s="5">
         <v>46230</v>
@@ -5216,13 +5219,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O66" s="6" t="s">
         <v>69</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q66" s="5">
         <v>46231</v>
@@ -5242,7 +5245,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B67" s="8">
         <v>46225.58131929398</v>
@@ -5252,16 +5255,16 @@
         <v>46225.61459149305</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I67" s="8">
         <v>46230</v>
@@ -5279,13 +5282,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q67" s="8">
         <v>46231</v>
@@ -5305,7 +5308,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B68" s="5">
         <v>46225.58132505787</v>
@@ -5315,16 +5318,16 @@
         <v>46225.61459082176</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I68" s="5">
         <v>46230</v>
@@ -5342,13 +5345,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q68" s="5">
         <v>46231</v>
@@ -5368,7 +5371,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B69" s="8">
         <v>46225.597591134254</v>
@@ -5384,10 +5387,10 @@
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I69" s="8">
         <v>46293</v>
@@ -5405,10 +5408,10 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P69" s="9" t="s">
         <v>53</v>
@@ -5431,7 +5434,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B70" s="5">
         <v>46225.58133054398</v>
@@ -5441,7 +5444,7 @@
         <v>46225.59299179398</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>25</v>
@@ -5465,7 +5468,7 @@
         <v>26</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -5478,7 +5481,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B71" s="8">
         <v>46225.58133395833</v>
@@ -5488,7 +5491,7 @@
         <v>46225.614863599534</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
@@ -5497,7 +5500,7 @@
         <v>70</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I71" s="8">
         <v>46275</v>
@@ -5515,13 +5518,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q71" s="8">
         <v>46281</v>
@@ -5541,7 +5544,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B72" s="5">
         <v>46225.58133853009</v>
@@ -5551,7 +5554,7 @@
         <v>46225.61483068287</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5560,7 +5563,7 @@
         <v>70</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I72" s="5">
         <v>46275</v>
@@ -5578,13 +5581,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5594,7 +5597,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B73" s="8">
         <v>46225.58134314815</v>
@@ -5604,7 +5607,7 @@
         <v>46225.61482673611</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
@@ -5613,7 +5616,7 @@
         <v>70</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I73" s="8">
         <v>46275</v>
@@ -5631,13 +5634,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
@@ -5647,7 +5650,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B74" s="5">
         <v>46225.58134744213</v>
@@ -5657,7 +5660,7 @@
         <v>46225.61499751157</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5666,7 +5669,7 @@
         <v>70</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I74" s="5">
         <v>46286</v>
@@ -5684,13 +5687,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q74" s="5">
         <v>46286</v>
@@ -5710,7 +5713,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B75" s="8">
         <v>46225.581351932866</v>
@@ -5720,7 +5723,7 @@
         <v>46225.61504185185</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
@@ -5729,7 +5732,7 @@
         <v>70</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I75" s="8">
         <v>46286</v>
@@ -5747,13 +5750,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q75" s="9"/>
       <c r="R75" s="9"/>
@@ -5763,7 +5766,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B76" s="5">
         <v>46225.58135922454</v>
@@ -5773,7 +5776,7 @@
         <v>46225.615038819444</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5782,7 +5785,7 @@
         <v>70</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I76" s="5">
         <v>46286</v>
@@ -5800,13 +5803,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -5816,7 +5819,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B77" s="8">
         <v>46225.5813728588</v>
@@ -5826,7 +5829,7 @@
         <v>46225.61522760417</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
@@ -5835,7 +5838,7 @@
         <v>70</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I77" s="8">
         <v>46287</v>
@@ -5853,13 +5856,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q77" s="8">
         <v>46287</v>
@@ -5879,7 +5882,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B78" s="5">
         <v>46225.58137722222</v>
@@ -5889,7 +5892,7 @@
         <v>46225.61518142361</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -5898,7 +5901,7 @@
         <v>70</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I78" s="6"/>
       <c r="J78" s="5">
@@ -5914,13 +5917,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -5930,7 +5933,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B79" s="8">
         <v>46225.58138231482</v>
@@ -5940,7 +5943,7 @@
         <v>46225.615182291665</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
@@ -5949,7 +5952,7 @@
         <v>70</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I79" s="9"/>
       <c r="J79" s="8">
@@ -5965,13 +5968,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
@@ -5981,7 +5984,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B80" s="5">
         <v>46225.58138733797</v>
@@ -5991,7 +5994,7 @@
         <v>46225.61538164352</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6000,7 +6003,7 @@
         <v>70</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I80" s="5">
         <v>46288</v>
@@ -6018,13 +6021,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q80" s="5">
         <v>46288</v>
@@ -6044,7 +6047,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B81" s="8">
         <v>46225.58139180556</v>
@@ -6054,7 +6057,7 @@
         <v>46225.61534716435</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
@@ -6063,7 +6066,7 @@
         <v>70</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I81" s="8">
         <v>46288</v>
@@ -6081,13 +6084,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q81" s="9"/>
       <c r="R81" s="9"/>
@@ -6097,7 +6100,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B82" s="5">
         <v>46225.58139752314</v>
@@ -6107,7 +6110,7 @@
         <v>46225.615343854166</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6116,7 +6119,7 @@
         <v>70</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I82" s="5">
         <v>46288</v>
@@ -6134,13 +6137,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6150,7 +6153,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B83" s="8">
         <v>46225.58140275463</v>
@@ -6160,7 +6163,7 @@
         <v>46225.61555996528</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
@@ -6169,7 +6172,7 @@
         <v>70</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I83" s="8">
         <v>46289</v>
@@ -6187,13 +6190,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q83" s="8">
         <v>46289</v>
@@ -6213,7 +6216,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B84" s="5">
         <v>46225.581407488426</v>
@@ -6223,7 +6226,7 @@
         <v>46225.61551967592</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6232,7 +6235,7 @@
         <v>70</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I84" s="6"/>
       <c r="J84" s="5">
@@ -6248,13 +6251,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6264,7 +6267,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B85" s="8">
         <v>46225.581414988425</v>
@@ -6274,7 +6277,7 @@
         <v>46225.61552056713</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
@@ -6283,7 +6286,7 @@
         <v>70</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I85" s="9"/>
       <c r="J85" s="8">
@@ -6299,13 +6302,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q85" s="9"/>
       <c r="R85" s="9"/>
@@ -6315,7 +6318,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B86" s="5">
         <v>46225.58145953703</v>
@@ -6325,7 +6328,7 @@
         <v>46225.61568145834</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6350,13 +6353,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q86" s="5">
         <v>46293</v>
@@ -6376,7 +6379,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B87" s="8">
         <v>46225.58146568287</v>
@@ -6386,7 +6389,7 @@
         <v>46225.61568175926</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
@@ -6395,7 +6398,7 @@
         <v>70</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I87" s="8">
         <v>46293</v>
@@ -6413,13 +6416,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q87" s="9"/>
       <c r="R87" s="9"/>
@@ -6429,7 +6432,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B88" s="5">
         <v>46225.58147099537</v>
@@ -6439,7 +6442,7 @@
         <v>46225.615682592594</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6448,7 +6451,7 @@
         <v>70</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I88" s="5">
         <v>46293</v>
@@ -6466,13 +6469,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6482,7 +6485,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B89" s="8">
         <v>46225.58147606481</v>
@@ -6492,7 +6495,7 @@
         <v>46225.60367008102</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>25</v>
@@ -6516,7 +6519,7 @@
         <v>26</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P89" s="9" t="s">
         <v>26</v>
@@ -6529,7 +6532,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B90" s="5">
         <v>46225.58147990741</v>
@@ -6539,16 +6542,16 @@
         <v>46225.615814467594</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I90" s="5">
         <v>46301</v>
@@ -6566,13 +6569,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q90" s="5">
         <v>46301</v>
@@ -6592,7 +6595,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B91" s="8">
         <v>46225.58148496528</v>
@@ -6602,16 +6605,16 @@
         <v>46225.61578579861</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I91" s="9"/>
       <c r="J91" s="8">
@@ -6627,13 +6630,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q91" s="9"/>
       <c r="R91" s="9"/>
@@ -6643,7 +6646,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B92" s="5">
         <v>46225.58148953704</v>
@@ -6653,16 +6656,16 @@
         <v>46225.61578274306</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I92" s="5">
         <v>46301</v>
@@ -6680,13 +6683,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6696,7 +6699,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B93" s="8">
         <v>46225.6055390625</v>
@@ -6706,16 +6709,16 @@
         <v>46225.61577960648</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I93" s="9"/>
       <c r="J93" s="8">
@@ -6731,13 +6734,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O93" s="9" t="s">
         <v>55</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -6747,7 +6750,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B94" s="5">
         <v>46225.605553333335</v>
@@ -6757,16 +6760,16 @@
         <v>46225.61577443287</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I94" s="6"/>
       <c r="J94" s="5">
@@ -6782,13 +6785,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O94" s="6" t="s">
         <v>59</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -6798,7 +6801,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B95" s="8">
         <v>46225.581494178245</v>
@@ -6808,7 +6811,7 @@
         <v>46225.61592174768</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
@@ -6817,7 +6820,7 @@
         <v>70</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I95" s="9"/>
       <c r="J95" s="8">
@@ -6833,10 +6836,10 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P95" s="9" t="s">
         <v>26</v>
@@ -6859,7 +6862,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B96" s="5">
         <v>46225.5814984375</v>
@@ -6869,7 +6872,7 @@
         <v>46225.615894421295</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -6878,7 +6881,7 @@
         <v>70</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I96" s="5">
         <v>46302</v>
@@ -6896,13 +6899,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -6912,7 +6915,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B97" s="8">
         <v>46225.58150320602</v>
@@ -6922,7 +6925,7 @@
         <v>46225.61589104167</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
@@ -6931,7 +6934,7 @@
         <v>70</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I97" s="8">
         <v>46302</v>
@@ -6949,13 +6952,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q97" s="9"/>
       <c r="R97" s="9"/>
@@ -6965,7 +6968,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B98" s="5">
         <v>46225.60673211806</v>
@@ -6975,7 +6978,7 @@
         <v>46225.615888125</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -6984,7 +6987,7 @@
         <v>70</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I98" s="5">
         <v>46302</v>
@@ -7002,13 +7005,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7018,7 +7021,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B99" s="8">
         <v>46225.60674163194</v>
@@ -7028,7 +7031,7 @@
         <v>46225.61588293982</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
@@ -7037,7 +7040,7 @@
         <v>70</v>
       </c>
       <c r="H99" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I99" s="8">
         <v>46302</v>
@@ -7055,13 +7058,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q99" s="9"/>
       <c r="R99" s="9"/>
@@ -7071,7 +7074,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B100" s="5">
         <v>46225.58150777778</v>
@@ -7081,16 +7084,16 @@
         <v>46225.61603868056</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I100" s="5">
         <v>46303</v>
@@ -7108,13 +7111,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q100" s="5">
         <v>46303</v>
@@ -7134,7 +7137,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B101" s="8">
         <v>46225.58151239583</v>
@@ -7144,16 +7147,16 @@
         <v>46225.61600570602</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H101" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I101" s="9"/>
       <c r="J101" s="8">
@@ -7169,13 +7172,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7185,7 +7188,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B102" s="5">
         <v>46225.58151694444</v>
@@ -7195,16 +7198,16 @@
         <v>46225.61600274306</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I102" s="6"/>
       <c r="J102" s="5">
@@ -7220,13 +7223,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7236,7 +7239,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B103" s="8">
         <v>46225.606768564816</v>
@@ -7246,16 +7249,16 @@
         <v>46225.615999965274</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H103" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I103" s="8">
         <v>46303</v>
@@ -7273,13 +7276,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q103" s="9"/>
       <c r="R103" s="9"/>
@@ -7289,7 +7292,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B104" s="5">
         <v>46225.606777395835</v>
@@ -7299,16 +7302,16 @@
         <v>46225.61599523148</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I104" s="5">
         <v>46303</v>
@@ -7326,13 +7329,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7342,7 +7345,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B105" s="8">
         <v>46225.581521562504</v>
@@ -7352,16 +7355,16 @@
         <v>46225.61624585648</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H105" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I105" s="8">
         <v>46304</v>
@@ -7379,13 +7382,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q105" s="8">
         <v>46304</v>
@@ -7405,7 +7408,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B106" s="5">
         <v>46225.58152704861</v>
@@ -7415,16 +7418,16 @@
         <v>46225.61621090278</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I106" s="6"/>
       <c r="J106" s="5">
@@ -7440,13 +7443,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7456,7 +7459,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B107" s="8">
         <v>46225.58153157408</v>
@@ -7466,16 +7469,16 @@
         <v>46225.61620709491</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H107" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I107" s="9"/>
       <c r="J107" s="8">
@@ -7491,13 +7494,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q107" s="9"/>
       <c r="R107" s="9"/>
@@ -7507,7 +7510,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B108" s="5">
         <v>46225.60680554398</v>
@@ -7517,16 +7520,16 @@
         <v>46225.616203564816</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I108" s="5">
         <v>46304</v>
@@ -7544,10 +7547,10 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P108" s="6" t="s">
         <v>26</v>
@@ -7560,7 +7563,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B109" s="8">
         <v>46225.60681763889</v>
@@ -7570,16 +7573,16 @@
         <v>46225.61619854167</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H109" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I109" s="8">
         <v>46304</v>
@@ -7597,10 +7600,10 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P109" s="9" t="s">
         <v>26</v>
@@ -7613,7 +7616,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B110" s="5">
         <v>46225.58153574074</v>
@@ -7623,7 +7626,7 @@
         <v>46225.60402078704</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>25</v>
@@ -7647,7 +7650,7 @@
         <v>26</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>26</v>
@@ -7660,7 +7663,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B111" s="8">
         <v>46225.58153866898</v>
@@ -7670,16 +7673,16 @@
         <v>46225.61649424769</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H111" s="9" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="I111" s="8">
         <v>46307</v>
@@ -7697,13 +7700,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q111" s="8">
         <v>46311</v>
@@ -7723,7 +7726,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B112" s="5">
         <v>46225.58154590278</v>
@@ -7733,7 +7736,7 @@
         <v>46225.61639241898</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -7760,13 +7763,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q112" s="5">
         <v>46311</v>
@@ -7786,7 +7789,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B113" s="8">
         <v>46225.59432256944</v>
@@ -7796,7 +7799,7 @@
         <v>46225.6052183912</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>25</v>
@@ -7820,7 +7823,7 @@
         <v>26</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P113" s="9" t="s">
         <v>26</v>
@@ -7833,7 +7836,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B114" s="5">
         <v>46225.59476561342</v>
@@ -7843,7 +7846,7 @@
         <v>46225.616553796295</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -7870,13 +7873,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q114" s="5">
         <v>46318</v>
@@ -7896,7 +7899,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B115" s="8">
         <v>46225.59487494213</v>
@@ -7906,7 +7909,7 @@
         <v>46225.61655020833</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
@@ -7933,13 +7936,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q115" s="8">
         <v>46325</v>

--- a/data/50001580- CIA. RIO MINERALES.xlsx
+++ b/data/50001580- CIA. RIO MINERALES.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1346" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1347" uniqueCount="333">
   <si>
     <t>50001580- "CIA. RIO MINERALES"</t>
   </si>
@@ -94,6 +94,9 @@
     <t/>
   </si>
   <si>
+    <t>Tarea Terminada</t>
+  </si>
+  <si>
     <t>1216788234855925</t>
   </si>
   <si>
@@ -106,73 +109,117 @@
     <t>cperez@zitron.com</t>
   </si>
   <si>
+    <t xml:space="preserve">Apertura de pedido: 13/07/2025
+Numero de oferta: 26CR0001
+Importe OC N° 2523: USD$41.392.-
+Incotem: EXW
+Condición de pago: Prepayment
+Fecha de entrega: 07-09-2026</t>
+  </si>
+  <si>
     <t>Baja</t>
   </si>
   <si>
+    <t>1216788234855937</t>
+  </si>
+  <si>
+    <t>Alcance del proyecto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Configuración: Tobera + Rejilla + FAR90/100+ Ventilador ZVN 1-9-63/2 + FAR90/100 + Tipo A + Tablero YD 63kW
+Cantidad: 2
+Tobera Aerodinámica Ø900 
+Rejilla  Ø900 
+Silenciador FAR 90/100 L:1000MM
+Ventilador: ZVN 1-9-63/2 
+Silenciador FAR 90/100 L: 1000MM
+Pieza de Adaptacion Tipo A Ø900 - L: 100MM</t>
+  </si>
+  <si>
+    <t>1216788147959199</t>
+  </si>
+  <si>
+    <t>Definicion Tecnica de componentes principales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Definición Rodete ZVN 1-9:
+        Alabe s/ plano 4999.01
+        Código 300000
+        Rodete de placas s/plano 4999.00
+        Z8 N590
+        Calaje y consumo: hgutierrez@zitron.com por favor tu apoyo.
+    Datos eléctricos motor 63KW:
+        63 kW, 460 V, 60 Hz, IP-55, f.s 1
+        Motor OMEG (Cod. 350007)
+        Se requiere duplicado de placa
+    Tratamiento superficial estándar Zitrón:
+        Preparación de superficie: SA 2 ½
+        1ª capa imprimación 60 micras Hempadur 15570 Color 12430
+        2ª capa Acabado 40 micras Hempathane HS 55610 Color 20450 RAL 9001
+    Datos Eléctricos para tableros
+        Tablero YD  63kW, 460 VAC, 60 Hz, IP66.
+        Incluye luces piloto, botones y protección de entrada
+</t>
+  </si>
+  <si>
+    <t>Ingenieria Electrica ot 4379,Ingenieria Detalle,Reserva Alabes OT4378,Reserva rodete OT4378,Reserva motor  OT4378</t>
+  </si>
+  <si>
+    <t>1216788147959211</t>
+  </si>
+  <si>
+    <t>Plazo Contractual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fecha de entrega: 07-09-2026
+Incotem: EXW
+Condición de pago: Prepayment
+</t>
+  </si>
+  <si>
+    <t>1216769310026539</t>
+  </si>
+  <si>
+    <t>Servicios</t>
+  </si>
+  <si>
+    <t>Ingenieria Electrica ot 4379,Revision Tableros ot 4379</t>
+  </si>
+  <si>
+    <t>1216769310026543</t>
+  </si>
+  <si>
+    <t>Ingenieria Electrica ot 4379</t>
+  </si>
+  <si>
+    <t>IGNACIO GARCIA MARTINEZ</t>
+  </si>
+  <si>
+    <t>ignacio@zitron.com</t>
+  </si>
+  <si>
+    <t>Servicios,Propuesta Tableros ot 4379</t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
   </si>
   <si>
-    <t>1216788234855937</t>
-  </si>
-  <si>
-    <t>Alcance del proyecto</t>
-  </si>
-  <si>
-    <t>1216788147959199</t>
-  </si>
-  <si>
-    <t>Definicion Tecnica de componentes principales</t>
-  </si>
-  <si>
-    <t>Ingenieria Electrica ot 4379,Ingenieria Detalle,Reserva Alabes OT4378,Reserva rodete OT4378,Reserva motor  OT4378</t>
-  </si>
-  <si>
-    <t>1216788147959211</t>
-  </si>
-  <si>
-    <t>Plazo Contractual</t>
-  </si>
-  <si>
-    <t>1216769310026539</t>
-  </si>
-  <si>
-    <t>Servicios</t>
-  </si>
-  <si>
-    <t>Ingenieria Electrica ot 4379,Revision Tableros ot 4379</t>
-  </si>
-  <si>
-    <t>1216769310026543</t>
-  </si>
-  <si>
-    <t>Ingenieria Electrica ot 4379</t>
-  </si>
-  <si>
-    <t>IGNACIO GARCIA MARTINEZ</t>
-  </si>
-  <si>
-    <t>ignacio@zitron.com</t>
-  </si>
-  <si>
-    <t>Servicios,Propuesta Tableros ot 4379</t>
+    <t>1216769310026544</t>
+  </si>
+  <si>
+    <t>Revision Tableros ot 4379</t>
+  </si>
+  <si>
+    <t>sergio saavedra fernandez</t>
+  </si>
+  <si>
+    <t>sergio.saavedra@zitron.com</t>
+  </si>
+  <si>
+    <t>ot  4379 -  TABLERO YD 63 KW,ot 4379 -  TABLERO YD 63 KW</t>
   </si>
   <si>
     <t>Tarea sin iniciar</t>
-  </si>
-  <si>
-    <t>1216769310026544</t>
-  </si>
-  <si>
-    <t>Revision Tableros ot 4379</t>
-  </si>
-  <si>
-    <t>sergio saavedra fernandez</t>
-  </si>
-  <si>
-    <t>sergio.saavedra@zitron.com</t>
-  </si>
-  <si>
-    <t>ot  4379 -  TABLERO YD 63 KW,ot 4379 -  TABLERO YD 63 KW</t>
   </si>
   <si>
     <t>1216769310026574</t>
@@ -1048,17 +1095,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF62d26f"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFBFBFBF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF62d26f"/>
       </patternFill>
     </fill>
     <fill>
@@ -1129,8 +1176,8 @@
     <xf numFmtId="14" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1623,9 +1670,11 @@
       <c r="B4" s="5">
         <v>46225.58085064815</v>
       </c>
-      <c r="C4" s="6"/>
+      <c r="C4" s="5">
+        <v>46226.57179957176</v>
+      </c>
       <c r="D4" s="5">
-        <v>46225.58105582176</v>
+        <v>46226.57181140046</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1660,94 +1709,102 @@
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
       <c r="S4" s="6"/>
-      <c r="T4" s="6"/>
-      <c r="U4" s="6"/>
+      <c r="T4" s="6">
+        <v>1</v>
+      </c>
+      <c r="U4" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="9">
+        <v>46225.58093664351</v>
+      </c>
+      <c r="C5" s="9">
+        <v>46226.56305846065</v>
+      </c>
+      <c r="D5" s="9">
+        <v>46226.56308402777</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="9">
+        <v>46225</v>
+      </c>
+      <c r="J5" s="9">
+        <v>46225</v>
+      </c>
+      <c r="K5" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L5" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="M5" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N5" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="O5" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="P5" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q5" s="9">
+        <v>46134</v>
+      </c>
+      <c r="R5" s="9">
+        <v>46134</v>
+      </c>
+      <c r="S5" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T5" s="10">
+        <v>1</v>
+      </c>
+      <c r="U5" s="7" t="s">
         <v>27</v>
-      </c>
-      <c r="B5" s="8">
-        <v>46225.58093664351</v>
-      </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="8">
-        <v>46225.61061649305</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="I5" s="8">
-        <v>46225</v>
-      </c>
-      <c r="J5" s="8">
-        <v>46225</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L5" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M5" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N5" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="O5" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="P5" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q5" s="8">
-        <v>46134</v>
-      </c>
-      <c r="R5" s="8">
-        <v>46134</v>
-      </c>
-      <c r="S5" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="T5" s="9">
-        <v>0</v>
-      </c>
-      <c r="U5" s="11" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B6" s="5">
         <v>46225.5809400463</v>
       </c>
-      <c r="C6" s="6"/>
+      <c r="C6" s="5">
+        <v>46226.5677469213</v>
+      </c>
       <c r="D6" s="5">
-        <v>46225.61061321759</v>
+        <v>46226.56777076389</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I6" s="5">
         <v>46225</v>
@@ -1759,7 +1816,7 @@
         <v>26</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="M6" s="6" t="s">
         <v>26</v>
@@ -1779,101 +1836,105 @@
       <c r="R6" s="5">
         <v>46134</v>
       </c>
-      <c r="S6" s="10" t="s">
+      <c r="S6" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T6" s="6">
+        <v>1</v>
+      </c>
+      <c r="U6" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="9">
+        <v>46225.580943657405</v>
+      </c>
+      <c r="C7" s="9">
+        <v>46226.571240590274</v>
+      </c>
+      <c r="D7" s="9">
+        <v>46226.571264432874</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H7" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="T6" s="6">
-        <v>0</v>
-      </c>
-      <c r="U6" s="11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" s="8">
-        <v>46225.580943657405</v>
-      </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="8">
-        <v>46225.6106097338</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="I7" s="8">
+      <c r="I7" s="9">
         <v>46225</v>
       </c>
-      <c r="J7" s="8">
+      <c r="J7" s="9">
         <v>46225</v>
       </c>
-      <c r="K7" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L7" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M7" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N7" s="9" t="s">
+      <c r="K7" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N7" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="O7" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="P7" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q7" s="8">
+      <c r="O7" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="P7" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q7" s="9">
         <v>46134</v>
       </c>
-      <c r="R7" s="8">
+      <c r="R7" s="9">
         <v>46134</v>
       </c>
-      <c r="S7" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="T7" s="9">
-        <v>0</v>
-      </c>
-      <c r="U7" s="11" t="s">
-        <v>32</v>
+      <c r="S7" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T7" s="10">
+        <v>1</v>
+      </c>
+      <c r="U7" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B8" s="5">
         <v>46225.58094813657</v>
       </c>
-      <c r="C8" s="6"/>
+      <c r="C8" s="5">
+        <v>46226.57178239583</v>
+      </c>
       <c r="D8" s="5">
-        <v>46225.61060402778</v>
+        <v>46226.571800578706</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I8" s="5">
         <v>46225</v>
@@ -1885,7 +1946,7 @@
         <v>26</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="M8" s="6" t="s">
         <v>26</v>
@@ -1905,85 +1966,85 @@
       <c r="R8" s="5">
         <v>46134</v>
       </c>
-      <c r="S8" s="10" t="s">
-        <v>31</v>
+      <c r="S8" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="T8" s="6">
+        <v>1</v>
+      </c>
+      <c r="U8" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="9">
+        <v>46225.58253893518</v>
+      </c>
+      <c r="C9" s="10"/>
+      <c r="D9" s="9">
+        <v>46225.60046916667</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L9" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M9" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="U8" s="11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B9" s="8">
-        <v>46225.58253893518</v>
-      </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="8">
-        <v>46225.60046916667</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L9" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M9" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="N9" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="O9" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="P9" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q9" s="9"/>
-      <c r="R9" s="9"/>
-      <c r="S9" s="9"/>
-      <c r="T9" s="9"/>
-      <c r="U9" s="9"/>
+      <c r="N9" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="O9" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="P9" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q9" s="10"/>
+      <c r="R9" s="10"/>
+      <c r="S9" s="10"/>
+      <c r="T9" s="10"/>
+      <c r="U9" s="10"/>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B10" s="5">
         <v>46225.58269137732</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46225.612125914355</v>
+        <v>46226.571272939815</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="I10" s="5">
         <v>46226</v>
@@ -2001,13 +2062,13 @@
         <v>26</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P10" s="6" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Q10" s="5">
         <v>46230</v>
@@ -2015,82 +2076,82 @@
       <c r="R10" s="5">
         <v>46226</v>
       </c>
-      <c r="S10" s="10" t="s">
-        <v>31</v>
+      <c r="S10" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="T10" s="6">
         <v>0</v>
       </c>
-      <c r="U10" s="12" t="s">
-        <v>48</v>
+      <c r="U10" s="11" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="B11" s="8">
+      <c r="A11" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11" s="9">
         <v>46225.58274704861</v>
       </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="8">
+      <c r="C11" s="10"/>
+      <c r="D11" s="9">
         <v>46225.61217166667</v>
       </c>
-      <c r="E11" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="I11" s="8">
+      <c r="E11" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I11" s="9">
         <v>46294</v>
       </c>
-      <c r="J11" s="8">
+      <c r="J11" s="9">
         <v>46300</v>
       </c>
-      <c r="K11" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L11" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M11" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N11" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="O11" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="P11" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q11" s="8">
+      <c r="K11" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L11" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M11" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N11" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="O11" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="P11" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q11" s="9">
         <v>46300</v>
       </c>
-      <c r="R11" s="8">
+      <c r="R11" s="9">
         <v>46294</v>
       </c>
-      <c r="S11" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="T11" s="9">
+      <c r="S11" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T11" s="10">
         <v>0</v>
       </c>
       <c r="U11" s="12" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B12" s="5">
         <v>46225.59567834491</v>
@@ -2100,16 +2161,16 @@
         <v>46225.612248819445</v>
       </c>
       <c r="E12" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G12" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="F12" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>51</v>
-      </c>
       <c r="H12" s="6" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I12" s="5">
         <v>46294</v>
@@ -2127,13 +2188,13 @@
         <v>26</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="Q12" s="6"/>
       <c r="R12" s="6"/>
@@ -2142,61 +2203,61 @@
       <c r="U12" s="6"/>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="B13" s="8">
+      <c r="A13" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" s="9">
         <v>46225.595835520835</v>
       </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="8">
+      <c r="C13" s="10"/>
+      <c r="D13" s="9">
         <v>46225.61224515046</v>
       </c>
-      <c r="E13" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="I13" s="8">
+      <c r="E13" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I13" s="9">
         <v>46294</v>
       </c>
-      <c r="J13" s="8">
+      <c r="J13" s="9">
         <v>46300</v>
       </c>
-      <c r="K13" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L13" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M13" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N13" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="O13" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="P13" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q13" s="9"/>
-      <c r="R13" s="9"/>
-      <c r="S13" s="9"/>
-      <c r="T13" s="9"/>
-      <c r="U13" s="9"/>
+      <c r="K13" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L13" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M13" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N13" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="O13" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="P13" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q13" s="10"/>
+      <c r="R13" s="10"/>
+      <c r="S13" s="10"/>
+      <c r="T13" s="10"/>
+      <c r="U13" s="10"/>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B14" s="5">
         <v>46225.58085679398</v>
@@ -2206,7 +2267,7 @@
         <v>46225.59597591435</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>25</v>
@@ -2230,7 +2291,7 @@
         <v>26</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="P14" s="6" t="s">
         <v>26</v>
@@ -2242,71 +2303,71 @@
       <c r="U14" s="6"/>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B15" s="8">
+      <c r="A15" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B15" s="9">
         <v>46225.58095215278</v>
       </c>
-      <c r="C15" s="9"/>
-      <c r="D15" s="8">
-        <v>46225.612305092596</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="H15" s="9" t="s">
+      <c r="C15" s="10"/>
+      <c r="D15" s="9">
+        <v>46226.571272754634</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="I15" s="8">
+      <c r="H15" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="I15" s="9">
         <v>46226</v>
       </c>
-      <c r="J15" s="8">
+      <c r="J15" s="9">
         <v>46227</v>
       </c>
-      <c r="K15" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L15" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M15" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N15" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="O15" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="P15" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q15" s="8">
+      <c r="K15" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L15" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M15" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N15" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="O15" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="P15" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q15" s="9">
         <v>46227</v>
       </c>
-      <c r="R15" s="8">
+      <c r="R15" s="9">
         <v>46226</v>
       </c>
-      <c r="S15" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="T15" s="9">
+      <c r="S15" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T15" s="10">
         <v>0</v>
       </c>
-      <c r="U15" s="12" t="s">
-        <v>48</v>
+      <c r="U15" s="11" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B16" s="5">
         <v>46225.580861423616</v>
@@ -2316,7 +2377,7 @@
         <v>46225.59611458333</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>25</v>
@@ -2340,7 +2401,7 @@
         <v>26</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="P16" s="6" t="s">
         <v>26</v>
@@ -2352,90 +2413,90 @@
       <c r="U16" s="6"/>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="B17" s="8">
+      <c r="A17" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B17" s="9">
         <v>46225.580958923616</v>
       </c>
-      <c r="C17" s="9"/>
-      <c r="D17" s="8">
-        <v>46225.61237894676</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H17" s="9" t="s">
+      <c r="C17" s="10"/>
+      <c r="D17" s="9">
+        <v>46226.57127291667</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="I17" s="9">
+        <v>46226</v>
+      </c>
+      <c r="J17" s="9">
+        <v>46227</v>
+      </c>
+      <c r="K17" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L17" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M17" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N17" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="I17" s="8">
+      <c r="O17" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="P17" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q17" s="9">
+        <v>46227</v>
+      </c>
+      <c r="R17" s="9">
         <v>46226</v>
       </c>
-      <c r="J17" s="8">
-        <v>46227</v>
-      </c>
-      <c r="K17" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L17" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M17" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N17" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="O17" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="P17" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q17" s="8">
-        <v>46227</v>
-      </c>
-      <c r="R17" s="8">
-        <v>46226</v>
-      </c>
-      <c r="S17" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="T17" s="9">
+      <c r="S17" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T17" s="10">
         <v>0</v>
       </c>
-      <c r="U17" s="12" t="s">
-        <v>48</v>
+      <c r="U17" s="11" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B18" s="5">
         <v>46225.58096494213</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46225.61237618055</v>
+        <v>46226.57127292824</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I18" s="5">
         <v>46226</v>
@@ -2453,13 +2514,13 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="Q18" s="5">
         <v>46227</v>
@@ -2467,82 +2528,82 @@
       <c r="R18" s="5">
         <v>46226</v>
       </c>
-      <c r="S18" s="10" t="s">
-        <v>31</v>
+      <c r="S18" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="T18" s="6">
         <v>0</v>
       </c>
-      <c r="U18" s="12" t="s">
-        <v>48</v>
+      <c r="U18" s="11" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="B19" s="9">
+        <v>46225.58097109954</v>
+      </c>
+      <c r="C19" s="10"/>
+      <c r="D19" s="9">
+        <v>46226.571272870366</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H19" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="B19" s="8">
-        <v>46225.58097109954</v>
-      </c>
-      <c r="C19" s="9"/>
-      <c r="D19" s="8">
-        <v>46225.612370937495</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H19" s="9" t="s">
+      <c r="I19" s="9">
+        <v>46226</v>
+      </c>
+      <c r="J19" s="9">
+        <v>46227</v>
+      </c>
+      <c r="K19" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L19" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M19" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N19" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="I19" s="8">
+      <c r="O19" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="P19" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q19" s="9">
+        <v>46227</v>
+      </c>
+      <c r="R19" s="9">
         <v>46226</v>
       </c>
-      <c r="J19" s="8">
-        <v>46227</v>
-      </c>
-      <c r="K19" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L19" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M19" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N19" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="O19" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="P19" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q19" s="8">
-        <v>46227</v>
-      </c>
-      <c r="R19" s="8">
-        <v>46226</v>
-      </c>
-      <c r="S19" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="T19" s="9">
+      <c r="S19" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T19" s="10">
         <v>0</v>
       </c>
-      <c r="U19" s="12" t="s">
-        <v>48</v>
+      <c r="U19" s="11" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B20" s="5">
         <v>46225.58086628473</v>
@@ -2552,7 +2613,7 @@
         <v>46225.59619578704</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>25</v>
@@ -2576,7 +2637,7 @@
         <v>26</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="P20" s="6" t="s">
         <v>26</v>
@@ -2588,71 +2649,71 @@
       <c r="U20" s="6"/>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="B21" s="8">
+      <c r="A21" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="B21" s="9">
         <v>46225.580978240745</v>
       </c>
-      <c r="C21" s="9"/>
-      <c r="D21" s="8">
+      <c r="C21" s="10"/>
+      <c r="D21" s="9">
         <v>46225.61247136574</v>
       </c>
-      <c r="E21" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G21" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="I21" s="8">
+      <c r="E21" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="I21" s="9">
         <v>46245</v>
       </c>
-      <c r="J21" s="8">
+      <c r="J21" s="9">
         <v>46246</v>
       </c>
-      <c r="K21" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L21" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M21" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N21" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="O21" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="P21" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q21" s="8">
+      <c r="K21" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L21" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M21" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N21" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="O21" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="P21" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q21" s="9">
         <v>46246</v>
       </c>
-      <c r="R21" s="8">
+      <c r="R21" s="9">
         <v>46245</v>
       </c>
-      <c r="S21" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="T21" s="9">
+      <c r="S21" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T21" s="10">
         <v>0</v>
       </c>
       <c r="U21" s="12" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="B22" s="5">
         <v>46225.5809840625</v>
@@ -2662,16 +2723,16 @@
         <v>46225.612467824074</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I22" s="5">
         <v>46245</v>
@@ -2689,13 +2750,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="Q22" s="5">
         <v>46246</v>
@@ -2703,82 +2764,82 @@
       <c r="R22" s="5">
         <v>46245</v>
       </c>
-      <c r="S22" s="10" t="s">
-        <v>31</v>
+      <c r="S22" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="T22" s="6">
         <v>0</v>
       </c>
       <c r="U22" s="12" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="B23" s="9">
+        <v>46225.58098827546</v>
+      </c>
+      <c r="C23" s="10"/>
+      <c r="D23" s="9">
+        <v>46225.612464756945</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="I23" s="9">
+        <v>46245</v>
+      </c>
+      <c r="J23" s="9">
+        <v>46246</v>
+      </c>
+      <c r="K23" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L23" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M23" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N23" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="O23" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="B23" s="8">
-        <v>46225.58098827546</v>
-      </c>
-      <c r="C23" s="9"/>
-      <c r="D23" s="8">
-        <v>46225.612464756945</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G23" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="I23" s="8">
+      <c r="P23" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q23" s="9">
+        <v>46246</v>
+      </c>
+      <c r="R23" s="9">
         <v>46245</v>
       </c>
-      <c r="J23" s="8">
-        <v>46246</v>
-      </c>
-      <c r="K23" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L23" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M23" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N23" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="O23" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="P23" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q23" s="8">
-        <v>46246</v>
-      </c>
-      <c r="R23" s="8">
-        <v>46245</v>
-      </c>
-      <c r="S23" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="T23" s="9">
+      <c r="S23" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T23" s="10">
         <v>0</v>
       </c>
       <c r="U23" s="12" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B24" s="5">
         <v>46225.58100011574</v>
@@ -2788,16 +2849,16 @@
         <v>46225.61246184028</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I24" s="5">
         <v>46245</v>
@@ -2815,13 +2876,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="Q24" s="5">
         <v>46246</v>
@@ -2829,82 +2890,82 @@
       <c r="R24" s="5">
         <v>46245</v>
       </c>
-      <c r="S24" s="10" t="s">
-        <v>31</v>
+      <c r="S24" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="T24" s="6">
         <v>0</v>
       </c>
       <c r="U24" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A25" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="B25" s="9">
+        <v>46225.59619364583</v>
+      </c>
+      <c r="C25" s="10"/>
+      <c r="D25" s="9">
+        <v>46225.61245637732</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H25" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="I25" s="9">
+        <v>46231</v>
+      </c>
+      <c r="J25" s="9">
+        <v>46232</v>
+      </c>
+      <c r="K25" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L25" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M25" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N25" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="O25" s="10" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="B25" s="8">
-        <v>46225.59619364583</v>
-      </c>
-      <c r="C25" s="9"/>
-      <c r="D25" s="8">
-        <v>46225.61245637732</v>
-      </c>
-      <c r="E25" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G25" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H25" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="I25" s="8">
+      <c r="P25" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q25" s="9">
+        <v>46232</v>
+      </c>
+      <c r="R25" s="9">
         <v>46231</v>
       </c>
-      <c r="J25" s="8">
-        <v>46232</v>
-      </c>
-      <c r="K25" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L25" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M25" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N25" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="O25" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="P25" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q25" s="8">
-        <v>46232</v>
-      </c>
-      <c r="R25" s="8">
-        <v>46231</v>
-      </c>
-      <c r="S25" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="T25" s="9">
+      <c r="S25" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T25" s="10">
         <v>0</v>
       </c>
       <c r="U25" s="12" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B26" s="5">
         <v>46225.58087085648</v>
@@ -2914,7 +2975,7 @@
         <v>46225.596821886575</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>25</v>
@@ -2938,7 +2999,7 @@
         <v>26</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="P26" s="6" t="s">
         <v>26</v>
@@ -2950,71 +3011,71 @@
       <c r="U26" s="6"/>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="B27" s="8">
+      <c r="A27" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="B27" s="9">
         <v>46225.58100560185</v>
       </c>
-      <c r="C27" s="9"/>
-      <c r="D27" s="8">
+      <c r="C27" s="10"/>
+      <c r="D27" s="9">
         <v>46225.61255763889</v>
       </c>
-      <c r="E27" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="F27" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G27" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="I27" s="8">
+      <c r="E27" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="F27" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="H27" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="I27" s="9">
         <v>46247</v>
       </c>
-      <c r="J27" s="8">
+      <c r="J27" s="9">
         <v>46259</v>
       </c>
-      <c r="K27" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L27" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M27" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N27" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="O27" s="9" t="s">
+      <c r="K27" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L27" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M27" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N27" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="P27" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q27" s="8">
+      <c r="O27" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="P27" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q27" s="9">
         <v>46259</v>
       </c>
-      <c r="R27" s="8">
+      <c r="R27" s="9">
         <v>46247</v>
       </c>
-      <c r="S27" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="T27" s="9">
+      <c r="S27" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T27" s="10">
         <v>0</v>
       </c>
       <c r="U27" s="12" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="B28" s="5">
         <v>46225.58101144676</v>
@@ -3024,16 +3085,16 @@
         <v>46225.61262662037</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="I28" s="5">
         <v>46247</v>
@@ -3051,88 +3112,88 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
-      <c r="S28" s="10" t="s">
-        <v>31</v>
+      <c r="S28" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="12" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A29" s="7" t="s">
+      <c r="A29" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="B29" s="9">
+        <v>46225.581017233795</v>
+      </c>
+      <c r="C29" s="10"/>
+      <c r="D29" s="9">
+        <v>46225.61262351852</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="F29" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G29" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="H29" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="B29" s="8">
-        <v>46225.581017233795</v>
-      </c>
-      <c r="C29" s="9"/>
-      <c r="D29" s="8">
-        <v>46225.61262351852</v>
-      </c>
-      <c r="E29" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="F29" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G29" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="I29" s="8">
+      <c r="I29" s="9">
         <v>46251</v>
       </c>
-      <c r="J29" s="8">
+      <c r="J29" s="9">
         <v>46259</v>
       </c>
-      <c r="K29" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L29" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M29" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N29" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="O29" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="P29" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q29" s="9"/>
-      <c r="R29" s="9"/>
-      <c r="S29" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="T29" s="9">
+      <c r="K29" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L29" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M29" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N29" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="O29" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="P29" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q29" s="10"/>
+      <c r="R29" s="10"/>
+      <c r="S29" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T29" s="10">
         <v>0</v>
       </c>
       <c r="U29" s="12" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B30" s="5">
         <v>46225.58102277778</v>
@@ -3142,16 +3203,16 @@
         <v>46225.61255446759</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="I30" s="5">
         <v>46247</v>
@@ -3169,10 +3230,10 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="P30" s="6" t="s">
         <v>26</v>
@@ -3183,72 +3244,72 @@
       <c r="R30" s="5">
         <v>46247</v>
       </c>
-      <c r="S30" s="10" t="s">
-        <v>31</v>
+      <c r="S30" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
       <c r="U30" s="12" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="B31" s="8">
+      <c r="A31" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="B31" s="9">
         <v>46225.58102737268</v>
       </c>
-      <c r="C31" s="9"/>
-      <c r="D31" s="8">
+      <c r="C31" s="10"/>
+      <c r="D31" s="9">
         <v>46225.61269579861</v>
       </c>
-      <c r="E31" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="F31" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G31" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="H31" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="I31" s="8">
+      <c r="E31" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G31" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="H31" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="I31" s="9">
         <v>46247</v>
       </c>
-      <c r="J31" s="8">
+      <c r="J31" s="9">
         <v>46248</v>
       </c>
-      <c r="K31" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L31" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M31" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N31" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="O31" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="P31" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q31" s="9"/>
-      <c r="R31" s="9"/>
-      <c r="S31" s="9"/>
-      <c r="T31" s="9"/>
-      <c r="U31" s="9"/>
+      <c r="K31" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L31" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M31" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N31" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="O31" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="P31" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q31" s="10"/>
+      <c r="R31" s="10"/>
+      <c r="S31" s="10"/>
+      <c r="T31" s="10"/>
+      <c r="U31" s="10"/>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="B32" s="5">
         <v>46225.581032222224</v>
@@ -3258,16 +3319,16 @@
         <v>46225.612692442126</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="I32" s="5">
         <v>46251</v>
@@ -3285,13 +3346,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3300,71 +3361,71 @@
       <c r="U32" s="6"/>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A33" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="B33" s="8">
+      <c r="A33" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="B33" s="9">
         <v>46225.581037199074</v>
       </c>
-      <c r="C33" s="9"/>
-      <c r="D33" s="8">
+      <c r="C33" s="10"/>
+      <c r="D33" s="9">
         <v>46225.61279568287</v>
       </c>
-      <c r="E33" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="F33" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G33" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="H33" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="I33" s="8">
+      <c r="E33" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="H33" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="I33" s="9">
         <v>46247</v>
       </c>
-      <c r="J33" s="8">
+      <c r="J33" s="9">
         <v>46259</v>
       </c>
-      <c r="K33" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L33" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M33" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N33" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="O33" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="P33" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q33" s="8">
+      <c r="K33" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L33" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M33" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N33" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="O33" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="P33" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q33" s="9">
         <v>46259</v>
       </c>
-      <c r="R33" s="8">
+      <c r="R33" s="9">
         <v>46247</v>
       </c>
-      <c r="S33" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="T33" s="9">
+      <c r="S33" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T33" s="10">
         <v>0</v>
       </c>
       <c r="U33" s="12" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B34" s="5">
         <v>46225.58104158565</v>
@@ -3374,16 +3435,16 @@
         <v>46225.61298453704</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="I34" s="5">
         <v>46247</v>
@@ -3401,13 +3462,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3416,61 +3477,61 @@
       <c r="U34" s="6"/>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A35" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="B35" s="8">
+      <c r="A35" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="B35" s="9">
         <v>46225.5810464699</v>
       </c>
-      <c r="C35" s="9"/>
-      <c r="D35" s="8">
+      <c r="C35" s="10"/>
+      <c r="D35" s="9">
         <v>46225.61298125</v>
       </c>
-      <c r="E35" s="9" t="s">
+      <c r="E35" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="F35" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G35" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="H35" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="I35" s="9">
+        <v>46251</v>
+      </c>
+      <c r="J35" s="9">
+        <v>46259</v>
+      </c>
+      <c r="K35" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L35" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M35" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N35" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="F35" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G35" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="I35" s="8">
-        <v>46251</v>
-      </c>
-      <c r="J35" s="8">
-        <v>46259</v>
-      </c>
-      <c r="K35" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L35" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M35" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N35" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="O35" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="P35" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q35" s="9"/>
-      <c r="R35" s="9"/>
-      <c r="S35" s="9"/>
-      <c r="T35" s="9"/>
-      <c r="U35" s="9"/>
+      <c r="O35" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="P35" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q35" s="10"/>
+      <c r="R35" s="10"/>
+      <c r="S35" s="10"/>
+      <c r="T35" s="10"/>
+      <c r="U35" s="10"/>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B36" s="5">
         <v>46225.58105121528</v>
@@ -3480,16 +3541,16 @@
         <v>46225.61316422454</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="I36" s="5">
         <v>46247</v>
@@ -3507,10 +3568,10 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3521,72 +3582,72 @@
       <c r="R36" s="5">
         <v>46247</v>
       </c>
-      <c r="S36" s="10" t="s">
-        <v>31</v>
+      <c r="S36" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="T36" s="6">
         <v>0</v>
       </c>
       <c r="U36" s="12" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A37" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="B37" s="8">
+      <c r="A37" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="B37" s="9">
         <v>46225.58109630787</v>
       </c>
-      <c r="C37" s="9"/>
-      <c r="D37" s="8">
+      <c r="C37" s="10"/>
+      <c r="D37" s="9">
         <v>46225.613052245375</v>
       </c>
-      <c r="E37" s="9" t="s">
+      <c r="E37" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="F37" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G37" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="H37" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="I37" s="9">
+        <v>46247</v>
+      </c>
+      <c r="J37" s="9">
+        <v>46255</v>
+      </c>
+      <c r="K37" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L37" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M37" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N37" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="F37" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G37" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="H37" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="I37" s="8">
-        <v>46247</v>
-      </c>
-      <c r="J37" s="8">
-        <v>46255</v>
-      </c>
-      <c r="K37" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L37" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M37" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N37" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="O37" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="P37" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="Q37" s="9"/>
-      <c r="R37" s="9"/>
-      <c r="S37" s="9"/>
-      <c r="T37" s="9"/>
-      <c r="U37" s="9"/>
+      <c r="O37" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="P37" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q37" s="10"/>
+      <c r="R37" s="10"/>
+      <c r="S37" s="10"/>
+      <c r="T37" s="10"/>
+      <c r="U37" s="10"/>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="B38" s="5">
         <v>46225.58110178241</v>
@@ -3596,16 +3657,16 @@
         <v>46225.613047719904</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="I38" s="5">
         <v>46258</v>
@@ -3623,13 +3684,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3638,61 +3699,61 @@
       <c r="U38" s="6"/>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A39" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="B39" s="8">
+      <c r="A39" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="B39" s="9">
         <v>46225.58110600694</v>
       </c>
-      <c r="C39" s="9"/>
-      <c r="D39" s="8">
+      <c r="C39" s="10"/>
+      <c r="D39" s="9">
         <v>46225.613129363424</v>
       </c>
-      <c r="E39" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="F39" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G39" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="H39" s="9" t="s">
+      <c r="E39" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G39" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="H39" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="I39" s="9">
+        <v>46289</v>
+      </c>
+      <c r="J39" s="9">
+        <v>46289</v>
+      </c>
+      <c r="K39" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L39" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M39" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N39" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="O39" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="I39" s="8">
-        <v>46289</v>
-      </c>
-      <c r="J39" s="8">
-        <v>46289</v>
-      </c>
-      <c r="K39" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L39" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M39" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N39" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="O39" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="P39" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q39" s="9"/>
-      <c r="R39" s="9"/>
-      <c r="S39" s="9"/>
-      <c r="T39" s="9"/>
-      <c r="U39" s="9"/>
+      <c r="P39" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q39" s="10"/>
+      <c r="R39" s="10"/>
+      <c r="S39" s="10"/>
+      <c r="T39" s="10"/>
+      <c r="U39" s="10"/>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="B40" s="5">
         <v>46225.59682005787</v>
@@ -3702,16 +3763,16 @@
         <v>46225.6133383912</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="I40" s="5">
         <v>46233</v>
@@ -3729,10 +3790,10 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>26</v>
@@ -3743,72 +3804,72 @@
       <c r="R40" s="5">
         <v>46233</v>
       </c>
-      <c r="S40" s="10" t="s">
-        <v>31</v>
+      <c r="S40" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="T40" s="6">
         <v>0</v>
       </c>
       <c r="U40" s="12" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A41" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="B41" s="8">
+      <c r="A41" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="B41" s="9">
         <v>46225.59686481481</v>
       </c>
-      <c r="C41" s="9"/>
-      <c r="D41" s="8">
+      <c r="C41" s="10"/>
+      <c r="D41" s="9">
         <v>46225.613313634254</v>
       </c>
-      <c r="E41" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="F41" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G41" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="I41" s="8">
+      <c r="E41" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="F41" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G41" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="H41" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="I41" s="9">
         <v>46233</v>
       </c>
-      <c r="J41" s="8">
+      <c r="J41" s="9">
         <v>46241</v>
       </c>
-      <c r="K41" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L41" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M41" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N41" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="O41" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="P41" s="9" t="s">
+      <c r="K41" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L41" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M41" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N41" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="Q41" s="9"/>
-      <c r="R41" s="9"/>
-      <c r="S41" s="9"/>
-      <c r="T41" s="9"/>
-      <c r="U41" s="9"/>
+      <c r="O41" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="P41" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q41" s="10"/>
+      <c r="R41" s="10"/>
+      <c r="S41" s="10"/>
+      <c r="T41" s="10"/>
+      <c r="U41" s="10"/>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B42" s="5">
         <v>46225.59692966435</v>
@@ -3818,16 +3879,16 @@
         <v>46225.613310636574</v>
       </c>
       <c r="E42" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="H42" s="6" t="s">
         <v>150</v>
-      </c>
-      <c r="F42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G42" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>145</v>
       </c>
       <c r="I42" s="5">
         <v>46244</v>
@@ -3845,13 +3906,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -3860,55 +3921,55 @@
       <c r="U42" s="6"/>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A43" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="B43" s="8">
+      <c r="A43" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="B43" s="9">
         <v>46225.58111748843</v>
       </c>
-      <c r="C43" s="9"/>
-      <c r="D43" s="8">
+      <c r="C43" s="10"/>
+      <c r="D43" s="9">
         <v>46225.589328946764</v>
       </c>
-      <c r="E43" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="F43" s="9" t="s">
+      <c r="E43" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="F43" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="G43" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H43" s="9"/>
-      <c r="I43" s="9"/>
-      <c r="J43" s="9"/>
-      <c r="K43" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L43" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M43" s="9" t="s">
+      <c r="G43" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="H43" s="10"/>
+      <c r="I43" s="10"/>
+      <c r="J43" s="10"/>
+      <c r="K43" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L43" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M43" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="N43" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="O43" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="P43" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q43" s="9"/>
-      <c r="R43" s="9"/>
-      <c r="S43" s="9"/>
-      <c r="T43" s="9"/>
-      <c r="U43" s="9"/>
+      <c r="N43" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="O43" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="P43" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q43" s="10"/>
+      <c r="R43" s="10"/>
+      <c r="S43" s="10"/>
+      <c r="T43" s="10"/>
+      <c r="U43" s="10"/>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B44" s="5">
         <v>46225.58112127315</v>
@@ -3918,16 +3979,16 @@
         <v>46225.61343114583</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="I44" s="5">
         <v>46230</v>
@@ -3945,13 +4006,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="Q44" s="5">
         <v>46234</v>
@@ -3959,82 +4020,82 @@
       <c r="R44" s="5">
         <v>46230</v>
       </c>
-      <c r="S44" s="10" t="s">
-        <v>31</v>
+      <c r="S44" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="T44" s="6">
         <v>0</v>
       </c>
       <c r="U44" s="12" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A45" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="B45" s="8">
+      <c r="A45" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="B45" s="9">
         <v>46225.58112643519</v>
       </c>
-      <c r="C45" s="9"/>
-      <c r="D45" s="8">
+      <c r="C45" s="10"/>
+      <c r="D45" s="9">
         <v>46225.613428275465</v>
       </c>
-      <c r="E45" s="9" t="s">
+      <c r="E45" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="F45" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G45" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="H45" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="I45" s="9">
+        <v>46237</v>
+      </c>
+      <c r="J45" s="9">
+        <v>46241</v>
+      </c>
+      <c r="K45" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L45" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M45" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N45" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="O45" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="F45" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G45" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="H45" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="I45" s="8">
+      <c r="P45" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="Q45" s="9">
+        <v>46241</v>
+      </c>
+      <c r="R45" s="9">
         <v>46237</v>
       </c>
-      <c r="J45" s="8">
-        <v>46241</v>
-      </c>
-      <c r="K45" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L45" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M45" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N45" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="O45" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="P45" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="Q45" s="8">
-        <v>46241</v>
-      </c>
-      <c r="R45" s="8">
-        <v>46237</v>
-      </c>
-      <c r="S45" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="T45" s="9">
+      <c r="S45" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T45" s="10">
         <v>0</v>
       </c>
       <c r="U45" s="12" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="B46" s="5">
         <v>46225.58113097222</v>
@@ -4044,16 +4105,16 @@
         <v>46225.61342412037</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="I46" s="5">
         <v>46244</v>
@@ -4071,13 +4132,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="Q46" s="5">
         <v>46244</v>
@@ -4085,82 +4146,82 @@
       <c r="R46" s="5">
         <v>46244</v>
       </c>
-      <c r="S46" s="10" t="s">
-        <v>31</v>
+      <c r="S46" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="T46" s="6">
         <v>0</v>
       </c>
       <c r="U46" s="12" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A47" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="B47" s="8">
+      <c r="A47" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="B47" s="9">
         <v>46225.58114445602</v>
       </c>
-      <c r="C47" s="9"/>
-      <c r="D47" s="8">
+      <c r="C47" s="10"/>
+      <c r="D47" s="9">
         <v>46225.61347256944</v>
       </c>
-      <c r="E47" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="F47" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G47" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="H47" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="I47" s="8">
+      <c r="E47" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="F47" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="H47" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="I47" s="9">
         <v>46290</v>
       </c>
-      <c r="J47" s="8">
+      <c r="J47" s="9">
         <v>46290</v>
       </c>
-      <c r="K47" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L47" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M47" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N47" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="O47" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="P47" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="Q47" s="8">
+      <c r="K47" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L47" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M47" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N47" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="O47" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="P47" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q47" s="9">
         <v>46290</v>
       </c>
-      <c r="R47" s="8">
+      <c r="R47" s="9">
         <v>46290</v>
       </c>
-      <c r="S47" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="T47" s="9">
+      <c r="S47" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T47" s="10">
         <v>0</v>
       </c>
       <c r="U47" s="12" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="B48" s="5">
         <v>46225.58114871528</v>
@@ -4170,16 +4231,16 @@
         <v>46225.61551950232</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="I48" s="5">
         <v>46290</v>
@@ -4197,13 +4258,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4212,61 +4273,61 @@
       <c r="U48" s="6"/>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A49" s="7" t="s">
+      <c r="A49" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="B49" s="9">
+        <v>46225.58115283565</v>
+      </c>
+      <c r="C49" s="10"/>
+      <c r="D49" s="9">
+        <v>46225.615519513885</v>
+      </c>
+      <c r="E49" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="F49" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G49" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="H49" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="B49" s="8">
-        <v>46225.58115283565</v>
-      </c>
-      <c r="C49" s="9"/>
-      <c r="D49" s="8">
-        <v>46225.615519513885</v>
-      </c>
-      <c r="E49" s="9" t="s">
+      <c r="I49" s="9">
+        <v>46290</v>
+      </c>
+      <c r="J49" s="9">
+        <v>46290</v>
+      </c>
+      <c r="K49" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L49" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M49" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N49" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="F49" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G49" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="H49" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="I49" s="8">
-        <v>46290</v>
-      </c>
-      <c r="J49" s="8">
-        <v>46290</v>
-      </c>
-      <c r="K49" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L49" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M49" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N49" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="O49" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="P49" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="Q49" s="9"/>
-      <c r="R49" s="9"/>
-      <c r="S49" s="9"/>
-      <c r="T49" s="9"/>
-      <c r="U49" s="9"/>
+      <c r="O49" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="P49" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q49" s="10"/>
+      <c r="R49" s="10"/>
+      <c r="S49" s="10"/>
+      <c r="T49" s="10"/>
+      <c r="U49" s="10"/>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="B50" s="5">
         <v>46225.581171631944</v>
@@ -4276,7 +4337,7 @@
         <v>46225.59181146991</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>25</v>
@@ -4300,7 +4361,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4312,71 +4373,71 @@
       <c r="U50" s="6"/>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A51" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="B51" s="8">
+      <c r="A51" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="B51" s="9">
         <v>46225.58117489584</v>
       </c>
-      <c r="C51" s="9"/>
-      <c r="D51" s="8">
+      <c r="C51" s="10"/>
+      <c r="D51" s="9">
         <v>46225.61367097222</v>
       </c>
-      <c r="E51" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="F51" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G51" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="H51" s="9" t="s">
+      <c r="E51" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="F51" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G51" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="H51" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="I51" s="9">
+        <v>46260</v>
+      </c>
+      <c r="J51" s="9">
+        <v>46260</v>
+      </c>
+      <c r="K51" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L51" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M51" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N51" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="I51" s="8">
+      <c r="O51" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="P51" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="Q51" s="9">
         <v>46260</v>
       </c>
-      <c r="J51" s="8">
+      <c r="R51" s="9">
         <v>46260</v>
       </c>
-      <c r="K51" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L51" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M51" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N51" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="O51" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="P51" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="Q51" s="8">
-        <v>46260</v>
-      </c>
-      <c r="R51" s="8">
-        <v>46260</v>
-      </c>
-      <c r="S51" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="T51" s="9">
+      <c r="S51" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T51" s="10">
         <v>0</v>
       </c>
       <c r="U51" s="12" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="B52" s="5">
         <v>46225.58118028935</v>
@@ -4386,16 +4447,16 @@
         <v>46225.613667349535</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="I52" s="5">
         <v>46260</v>
@@ -4413,13 +4474,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="Q52" s="5">
         <v>46260</v>
@@ -4427,82 +4488,82 @@
       <c r="R52" s="5">
         <v>46260</v>
       </c>
-      <c r="S52" s="10" t="s">
-        <v>31</v>
+      <c r="S52" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="T52" s="6">
         <v>0</v>
       </c>
       <c r="U52" s="12" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A53" s="7" t="s">
+      <c r="A53" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="B53" s="9">
+        <v>46225.58118576389</v>
+      </c>
+      <c r="C53" s="10"/>
+      <c r="D53" s="9">
+        <v>46225.61366387732</v>
+      </c>
+      <c r="E53" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="F53" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G53" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="H53" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="B53" s="8">
-        <v>46225.58118576389</v>
-      </c>
-      <c r="C53" s="9"/>
-      <c r="D53" s="8">
-        <v>46225.61366387732</v>
-      </c>
-      <c r="E53" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="F53" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G53" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="H53" s="9" t="s">
+      <c r="I53" s="9">
+        <v>46260</v>
+      </c>
+      <c r="J53" s="9">
+        <v>46260</v>
+      </c>
+      <c r="K53" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L53" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M53" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N53" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="I53" s="8">
+      <c r="O53" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="P53" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="Q53" s="9">
         <v>46260</v>
       </c>
-      <c r="J53" s="8">
+      <c r="R53" s="9">
         <v>46260</v>
       </c>
-      <c r="K53" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L53" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M53" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N53" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="O53" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="P53" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="Q53" s="8">
-        <v>46260</v>
-      </c>
-      <c r="R53" s="8">
-        <v>46260</v>
-      </c>
-      <c r="S53" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="T53" s="9">
+      <c r="S53" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T53" s="10">
         <v>0</v>
       </c>
       <c r="U53" s="12" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B54" s="5">
         <v>46225.58119107639</v>
@@ -4512,16 +4573,16 @@
         <v>46225.61417395833</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="I54" s="5">
         <v>46261</v>
@@ -4539,13 +4600,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="Q54" s="5">
         <v>46261</v>
@@ -4553,82 +4614,82 @@
       <c r="R54" s="5">
         <v>46261</v>
       </c>
-      <c r="S54" s="10" t="s">
-        <v>31</v>
+      <c r="S54" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="T54" s="6">
         <v>0</v>
       </c>
       <c r="U54" s="12" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A55" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="B55" s="8">
+      <c r="A55" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="B55" s="9">
         <v>46225.58119642361</v>
       </c>
-      <c r="C55" s="9"/>
-      <c r="D55" s="8">
+      <c r="C55" s="10"/>
+      <c r="D55" s="9">
         <v>46225.61417104167</v>
       </c>
-      <c r="E55" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="F55" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G55" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="H55" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="I55" s="8">
+      <c r="E55" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="F55" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G55" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="H55" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="I55" s="9">
         <v>46261</v>
       </c>
-      <c r="J55" s="8">
+      <c r="J55" s="9">
         <v>46261</v>
       </c>
-      <c r="K55" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L55" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M55" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N55" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="O55" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="P55" s="9" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q55" s="8">
+      <c r="K55" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L55" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M55" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N55" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="O55" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="P55" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q55" s="9">
         <v>46261</v>
       </c>
-      <c r="R55" s="8">
+      <c r="R55" s="9">
         <v>46261</v>
       </c>
-      <c r="S55" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="T55" s="9">
+      <c r="S55" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T55" s="10">
         <v>0</v>
       </c>
       <c r="U55" s="12" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="B56" s="5">
         <v>46225.581201678244</v>
@@ -4638,16 +4699,16 @@
         <v>46225.61416773148</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="I56" s="5">
         <v>46261</v>
@@ -4665,13 +4726,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="Q56" s="5">
         <v>46261</v>
@@ -4679,66 +4740,66 @@
       <c r="R56" s="5">
         <v>46261</v>
       </c>
-      <c r="S56" s="10" t="s">
-        <v>31</v>
+      <c r="S56" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="T56" s="6">
         <v>0</v>
       </c>
       <c r="U56" s="12" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A57" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="B57" s="8">
+      <c r="A57" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="B57" s="9">
         <v>46225.58120702546</v>
       </c>
-      <c r="C57" s="9"/>
-      <c r="D57" s="8">
+      <c r="C57" s="10"/>
+      <c r="D57" s="9">
         <v>46225.59190644676</v>
       </c>
-      <c r="E57" s="9" t="s">
-        <v>198</v>
-      </c>
-      <c r="F57" s="9" t="s">
+      <c r="E57" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="F57" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="G57" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H57" s="9"/>
-      <c r="I57" s="9"/>
-      <c r="J57" s="9"/>
-      <c r="K57" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L57" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M57" s="9" t="s">
+      <c r="G57" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="H57" s="10"/>
+      <c r="I57" s="10"/>
+      <c r="J57" s="10"/>
+      <c r="K57" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L57" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M57" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="N57" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="O57" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="P57" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q57" s="9"/>
-      <c r="R57" s="9"/>
-      <c r="S57" s="9"/>
-      <c r="T57" s="9"/>
-      <c r="U57" s="9"/>
+      <c r="N57" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="O57" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="P57" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q57" s="10"/>
+      <c r="R57" s="10"/>
+      <c r="S57" s="10"/>
+      <c r="T57" s="10"/>
+      <c r="U57" s="10"/>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B58" s="5">
         <v>46225.58121010417</v>
@@ -4748,16 +4809,16 @@
         <v>46225.6142333912</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="I58" s="5">
         <v>46262</v>
@@ -4775,13 +4836,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="Q58" s="5">
         <v>46266</v>
@@ -4789,82 +4850,82 @@
       <c r="R58" s="5">
         <v>46262</v>
       </c>
-      <c r="S58" s="10" t="s">
-        <v>31</v>
+      <c r="S58" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="T58" s="6">
         <v>0</v>
       </c>
       <c r="U58" s="12" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A59" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="B59" s="8">
+      <c r="A59" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="B59" s="9">
         <v>46225.581215474536</v>
       </c>
-      <c r="C59" s="9"/>
-      <c r="D59" s="8">
+      <c r="C59" s="10"/>
+      <c r="D59" s="9">
         <v>46225.61435628472</v>
       </c>
-      <c r="E59" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="F59" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G59" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="H59" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="I59" s="8">
+      <c r="E59" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="F59" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G59" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="H59" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="I59" s="9">
         <v>46267</v>
       </c>
-      <c r="J59" s="8">
+      <c r="J59" s="9">
         <v>46273</v>
       </c>
-      <c r="K59" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L59" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M59" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N59" s="9" t="s">
-        <v>198</v>
-      </c>
-      <c r="O59" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="P59" s="9" t="s">
-        <v>198</v>
-      </c>
-      <c r="Q59" s="8">
+      <c r="K59" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L59" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M59" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N59" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="O59" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="P59" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q59" s="9">
         <v>46273</v>
       </c>
-      <c r="R59" s="8">
+      <c r="R59" s="9">
         <v>46267</v>
       </c>
-      <c r="S59" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="T59" s="9">
+      <c r="S59" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T59" s="10">
         <v>0</v>
       </c>
       <c r="U59" s="12" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B60" s="5">
         <v>46225.581219618056</v>
@@ -4874,16 +4935,16 @@
         <v>46225.614318611115</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="I60" s="5">
         <v>46267</v>
@@ -4901,13 +4962,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -4916,61 +4977,61 @@
       <c r="U60" s="6"/>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A61" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="B61" s="8">
+      <c r="A61" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="B61" s="9">
         <v>46225.58123596065</v>
       </c>
-      <c r="C61" s="9"/>
-      <c r="D61" s="8">
+      <c r="C61" s="10"/>
+      <c r="D61" s="9">
         <v>46225.61431550926</v>
       </c>
-      <c r="E61" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="F61" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G61" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="I61" s="8">
+      <c r="E61" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="F61" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G61" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="H61" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="I61" s="9">
         <v>46267</v>
       </c>
-      <c r="J61" s="8">
+      <c r="J61" s="9">
         <v>46273</v>
       </c>
-      <c r="K61" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L61" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M61" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N61" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="O61" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="P61" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="Q61" s="9"/>
-      <c r="R61" s="9"/>
-      <c r="S61" s="9"/>
-      <c r="T61" s="9"/>
-      <c r="U61" s="9"/>
+      <c r="K61" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L61" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M61" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N61" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="O61" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="P61" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q61" s="10"/>
+      <c r="R61" s="10"/>
+      <c r="S61" s="10"/>
+      <c r="T61" s="10"/>
+      <c r="U61" s="10"/>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B62" s="5">
         <v>46225.58129219907</v>
@@ -4980,16 +5041,16 @@
         <v>46225.61447392361</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="I62" s="5">
         <v>46274</v>
@@ -5007,13 +5068,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="Q62" s="5">
         <v>46274</v>
@@ -5021,70 +5082,70 @@
       <c r="R62" s="5">
         <v>46274</v>
       </c>
-      <c r="S62" s="10" t="s">
-        <v>31</v>
+      <c r="S62" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="T62" s="6">
         <v>0</v>
       </c>
       <c r="U62" s="12" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A63" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="B63" s="8">
+      <c r="A63" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="B63" s="9">
         <v>46225.58129802083</v>
       </c>
-      <c r="C63" s="9"/>
-      <c r="D63" s="8">
+      <c r="C63" s="10"/>
+      <c r="D63" s="9">
         <v>46225.61443357639</v>
       </c>
-      <c r="E63" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="F63" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G63" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="H63" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="I63" s="9"/>
-      <c r="J63" s="8">
+      <c r="E63" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="F63" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G63" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="H63" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="I63" s="10"/>
+      <c r="J63" s="9">
         <v>46274</v>
       </c>
-      <c r="K63" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L63" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M63" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N63" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="O63" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="P63" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="Q63" s="9"/>
-      <c r="R63" s="9"/>
-      <c r="S63" s="9"/>
-      <c r="T63" s="9"/>
-      <c r="U63" s="9"/>
+      <c r="K63" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L63" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M63" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N63" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="O63" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="P63" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="Q63" s="10"/>
+      <c r="R63" s="10"/>
+      <c r="S63" s="10"/>
+      <c r="T63" s="10"/>
+      <c r="U63" s="10"/>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B64" s="5">
         <v>46225.581304374995</v>
@@ -5094,16 +5155,16 @@
         <v>46225.61443052083</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="I64" s="6"/>
       <c r="J64" s="5">
@@ -5119,13 +5180,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5134,55 +5195,55 @@
       <c r="U64" s="6"/>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A65" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="B65" s="8">
+      <c r="A65" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="B65" s="9">
         <v>46225.58131015046</v>
       </c>
-      <c r="C65" s="9"/>
-      <c r="D65" s="8">
+      <c r="C65" s="10"/>
+      <c r="D65" s="9">
         <v>46225.59759329861</v>
       </c>
-      <c r="E65" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="F65" s="9" t="s">
+      <c r="E65" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="F65" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="G65" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H65" s="9"/>
-      <c r="I65" s="9"/>
-      <c r="J65" s="9"/>
-      <c r="K65" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L65" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M65" s="9" t="s">
+      <c r="G65" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="H65" s="10"/>
+      <c r="I65" s="10"/>
+      <c r="J65" s="10"/>
+      <c r="K65" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L65" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M65" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="N65" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="O65" s="9" t="s">
-        <v>220</v>
-      </c>
-      <c r="P65" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q65" s="9"/>
-      <c r="R65" s="9"/>
-      <c r="S65" s="9"/>
-      <c r="T65" s="9"/>
-      <c r="U65" s="9"/>
+      <c r="N65" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="O65" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="P65" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q65" s="10"/>
+      <c r="R65" s="10"/>
+      <c r="S65" s="10"/>
+      <c r="T65" s="10"/>
+      <c r="U65" s="10"/>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="B66" s="5">
         <v>46225.58131376158</v>
@@ -5192,16 +5253,16 @@
         <v>46225.61459215278</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="I66" s="5">
         <v>46230</v>
@@ -5219,13 +5280,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="Q66" s="5">
         <v>46231</v>
@@ -5233,82 +5294,82 @@
       <c r="R66" s="5">
         <v>46230</v>
       </c>
-      <c r="S66" s="10" t="s">
-        <v>31</v>
+      <c r="S66" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="T66" s="6">
         <v>0</v>
       </c>
       <c r="U66" s="12" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A67" s="7" t="s">
+      <c r="A67" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="B67" s="9">
+        <v>46225.58131929398</v>
+      </c>
+      <c r="C67" s="10"/>
+      <c r="D67" s="9">
+        <v>46225.61459149305</v>
+      </c>
+      <c r="E67" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="F67" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G67" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="H67" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="I67" s="9">
+        <v>46230</v>
+      </c>
+      <c r="J67" s="9">
+        <v>46231</v>
+      </c>
+      <c r="K67" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L67" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M67" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N67" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="B67" s="8">
-        <v>46225.58131929398</v>
-      </c>
-      <c r="C67" s="9"/>
-      <c r="D67" s="8">
-        <v>46225.61459149305</v>
-      </c>
-      <c r="E67" s="9" t="s">
-        <v>225</v>
-      </c>
-      <c r="F67" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G67" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="I67" s="8">
+      <c r="O67" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="P67" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q67" s="9">
+        <v>46231</v>
+      </c>
+      <c r="R67" s="9">
         <v>46230</v>
       </c>
-      <c r="J67" s="8">
-        <v>46231</v>
-      </c>
-      <c r="K67" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L67" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M67" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N67" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="O67" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="P67" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="Q67" s="8">
-        <v>46231</v>
-      </c>
-      <c r="R67" s="8">
-        <v>46230</v>
-      </c>
-      <c r="S67" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="T67" s="9">
+      <c r="S67" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T67" s="10">
         <v>0</v>
       </c>
       <c r="U67" s="12" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="B68" s="5">
         <v>46225.58132505787</v>
@@ -5318,16 +5379,16 @@
         <v>46225.61459082176</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="I68" s="5">
         <v>46230</v>
@@ -5345,13 +5406,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="Q68" s="5">
         <v>46231</v>
@@ -5359,82 +5420,82 @@
       <c r="R68" s="5">
         <v>46230</v>
       </c>
-      <c r="S68" s="10" t="s">
-        <v>31</v>
+      <c r="S68" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="T68" s="6">
         <v>0</v>
       </c>
       <c r="U68" s="12" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A69" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="B69" s="8">
+      <c r="A69" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="B69" s="9">
         <v>46225.597591134254</v>
       </c>
-      <c r="C69" s="9"/>
-      <c r="D69" s="8">
+      <c r="C69" s="10"/>
+      <c r="D69" s="9">
         <v>46225.61467041667</v>
       </c>
-      <c r="E69" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="F69" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G69" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="H69" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="I69" s="8">
+      <c r="E69" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="F69" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G69" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="H69" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="I69" s="9">
         <v>46293</v>
       </c>
-      <c r="J69" s="8">
+      <c r="J69" s="9">
         <v>46293</v>
       </c>
-      <c r="K69" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L69" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M69" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N69" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="O69" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="P69" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q69" s="8">
+      <c r="K69" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L69" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M69" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N69" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="O69" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="P69" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q69" s="9">
         <v>46293</v>
       </c>
-      <c r="R69" s="8">
+      <c r="R69" s="9">
         <v>46293</v>
       </c>
-      <c r="S69" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="T69" s="9">
+      <c r="S69" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T69" s="10">
         <v>0</v>
       </c>
       <c r="U69" s="12" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B70" s="5">
         <v>46225.58133054398</v>
@@ -5444,7 +5505,7 @@
         <v>46225.59299179398</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>25</v>
@@ -5468,7 +5529,7 @@
         <v>26</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -5480,71 +5541,71 @@
       <c r="U70" s="6"/>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A71" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="B71" s="8">
+      <c r="A71" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="B71" s="9">
         <v>46225.58133395833</v>
       </c>
-      <c r="C71" s="9"/>
-      <c r="D71" s="8">
+      <c r="C71" s="10"/>
+      <c r="D71" s="9">
         <v>46225.614863599534</v>
       </c>
-      <c r="E71" s="9" t="s">
-        <v>234</v>
-      </c>
-      <c r="F71" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G71" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H71" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="I71" s="8">
+      <c r="E71" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="F71" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G71" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H71" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="I71" s="9">
         <v>46275</v>
       </c>
-      <c r="J71" s="8">
+      <c r="J71" s="9">
         <v>46281</v>
       </c>
-      <c r="K71" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L71" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M71" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N71" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="O71" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="P71" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="Q71" s="8">
+      <c r="K71" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L71" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M71" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N71" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="O71" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="P71" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q71" s="9">
         <v>46281</v>
       </c>
-      <c r="R71" s="8">
+      <c r="R71" s="9">
         <v>46275</v>
       </c>
-      <c r="S71" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="T71" s="9">
+      <c r="S71" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T71" s="10">
         <v>0</v>
       </c>
       <c r="U71" s="12" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="B72" s="5">
         <v>46225.58133853009</v>
@@ -5554,16 +5615,16 @@
         <v>46225.61483068287</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I72" s="5">
         <v>46275</v>
@@ -5581,13 +5642,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5596,61 +5657,61 @@
       <c r="U72" s="6"/>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A73" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="B73" s="8">
+      <c r="A73" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="B73" s="9">
         <v>46225.58134314815</v>
       </c>
-      <c r="C73" s="9"/>
-      <c r="D73" s="8">
+      <c r="C73" s="10"/>
+      <c r="D73" s="9">
         <v>46225.61482673611</v>
       </c>
-      <c r="E73" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="F73" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G73" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H73" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="I73" s="8">
+      <c r="E73" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="F73" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G73" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H73" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="I73" s="9">
         <v>46275</v>
       </c>
-      <c r="J73" s="8">
+      <c r="J73" s="9">
         <v>46281</v>
       </c>
-      <c r="K73" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L73" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M73" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N73" s="9" t="s">
-        <v>234</v>
-      </c>
-      <c r="O73" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="P73" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="Q73" s="9"/>
-      <c r="R73" s="9"/>
-      <c r="S73" s="9"/>
-      <c r="T73" s="9"/>
-      <c r="U73" s="9"/>
+      <c r="K73" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L73" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M73" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N73" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="O73" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="P73" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="Q73" s="10"/>
+      <c r="R73" s="10"/>
+      <c r="S73" s="10"/>
+      <c r="T73" s="10"/>
+      <c r="U73" s="10"/>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="B74" s="5">
         <v>46225.58134744213</v>
@@ -5660,16 +5721,16 @@
         <v>46225.61499751157</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I74" s="5">
         <v>46286</v>
@@ -5687,13 +5748,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="Q74" s="5">
         <v>46286</v>
@@ -5701,72 +5762,72 @@
       <c r="R74" s="5">
         <v>46286</v>
       </c>
-      <c r="S74" s="10" t="s">
-        <v>31</v>
+      <c r="S74" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="T74" s="6">
         <v>0</v>
       </c>
       <c r="U74" s="12" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A75" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="B75" s="8">
+      <c r="A75" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="B75" s="9">
         <v>46225.581351932866</v>
       </c>
-      <c r="C75" s="9"/>
-      <c r="D75" s="8">
+      <c r="C75" s="10"/>
+      <c r="D75" s="9">
         <v>46225.61504185185</v>
       </c>
-      <c r="E75" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="F75" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G75" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H75" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="I75" s="8">
+      <c r="E75" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="F75" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G75" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H75" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="I75" s="9">
         <v>46286</v>
       </c>
-      <c r="J75" s="8">
+      <c r="J75" s="9">
         <v>46286</v>
       </c>
-      <c r="K75" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L75" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M75" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N75" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="O75" s="9" t="s">
-        <v>242</v>
-      </c>
-      <c r="P75" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="Q75" s="9"/>
-      <c r="R75" s="9"/>
-      <c r="S75" s="9"/>
-      <c r="T75" s="9"/>
-      <c r="U75" s="9"/>
+      <c r="K75" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L75" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M75" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N75" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="O75" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="P75" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q75" s="10"/>
+      <c r="R75" s="10"/>
+      <c r="S75" s="10"/>
+      <c r="T75" s="10"/>
+      <c r="U75" s="10"/>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="B76" s="5">
         <v>46225.58135922454</v>
@@ -5776,16 +5837,16 @@
         <v>46225.615038819444</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I76" s="5">
         <v>46286</v>
@@ -5803,13 +5864,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -5818,71 +5879,71 @@
       <c r="U76" s="6"/>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A77" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="B77" s="8">
+      <c r="A77" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="B77" s="9">
         <v>46225.5813728588</v>
       </c>
-      <c r="C77" s="9"/>
-      <c r="D77" s="8">
+      <c r="C77" s="10"/>
+      <c r="D77" s="9">
         <v>46225.61522760417</v>
       </c>
-      <c r="E77" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="F77" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G77" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H77" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="I77" s="8">
+      <c r="E77" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="F77" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G77" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H77" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="I77" s="9">
         <v>46287</v>
       </c>
-      <c r="J77" s="8">
+      <c r="J77" s="9">
         <v>46287</v>
       </c>
-      <c r="K77" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L77" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M77" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N77" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="O77" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="P77" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="Q77" s="8">
+      <c r="K77" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L77" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M77" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N77" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="O77" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="P77" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q77" s="9">
         <v>46287</v>
       </c>
-      <c r="R77" s="8">
+      <c r="R77" s="9">
         <v>46287</v>
       </c>
-      <c r="S77" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="T77" s="9">
+      <c r="S77" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T77" s="10">
         <v>0</v>
       </c>
       <c r="U77" s="12" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="B78" s="5">
         <v>46225.58137722222</v>
@@ -5892,16 +5953,16 @@
         <v>46225.61518142361</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I78" s="6"/>
       <c r="J78" s="5">
@@ -5917,13 +5978,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -5932,59 +5993,59 @@
       <c r="U78" s="6"/>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A79" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="B79" s="8">
+      <c r="A79" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="B79" s="9">
         <v>46225.58138231482</v>
       </c>
-      <c r="C79" s="9"/>
-      <c r="D79" s="8">
+      <c r="C79" s="10"/>
+      <c r="D79" s="9">
         <v>46225.615182291665</v>
       </c>
-      <c r="E79" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="F79" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G79" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H79" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="I79" s="9"/>
-      <c r="J79" s="8">
+      <c r="E79" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="F79" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G79" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H79" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="I79" s="10"/>
+      <c r="J79" s="9">
         <v>46287</v>
       </c>
-      <c r="K79" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L79" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M79" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N79" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="O79" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="P79" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="Q79" s="9"/>
-      <c r="R79" s="9"/>
-      <c r="S79" s="9"/>
-      <c r="T79" s="9"/>
-      <c r="U79" s="9"/>
+      <c r="K79" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L79" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M79" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N79" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="O79" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="P79" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q79" s="10"/>
+      <c r="R79" s="10"/>
+      <c r="S79" s="10"/>
+      <c r="T79" s="10"/>
+      <c r="U79" s="10"/>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="B80" s="5">
         <v>46225.58138733797</v>
@@ -5994,16 +6055,16 @@
         <v>46225.61538164352</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I80" s="5">
         <v>46288</v>
@@ -6021,13 +6082,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="Q80" s="5">
         <v>46288</v>
@@ -6035,72 +6096,72 @@
       <c r="R80" s="5">
         <v>46288</v>
       </c>
-      <c r="S80" s="10" t="s">
-        <v>31</v>
+      <c r="S80" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="T80" s="6">
         <v>0</v>
       </c>
       <c r="U80" s="12" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A81" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="B81" s="8">
+      <c r="A81" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="B81" s="9">
         <v>46225.58139180556</v>
       </c>
-      <c r="C81" s="9"/>
-      <c r="D81" s="8">
+      <c r="C81" s="10"/>
+      <c r="D81" s="9">
         <v>46225.61534716435</v>
       </c>
-      <c r="E81" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="F81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G81" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H81" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="I81" s="8">
+      <c r="E81" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="F81" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G81" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H81" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="I81" s="9">
         <v>46288</v>
       </c>
-      <c r="J81" s="8">
+      <c r="J81" s="9">
         <v>46288</v>
       </c>
-      <c r="K81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N81" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="O81" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="P81" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="Q81" s="9"/>
-      <c r="R81" s="9"/>
-      <c r="S81" s="9"/>
-      <c r="T81" s="9"/>
-      <c r="U81" s="9"/>
+      <c r="K81" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L81" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M81" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N81" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="O81" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="P81" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="Q81" s="10"/>
+      <c r="R81" s="10"/>
+      <c r="S81" s="10"/>
+      <c r="T81" s="10"/>
+      <c r="U81" s="10"/>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="B82" s="5">
         <v>46225.58139752314</v>
@@ -6110,16 +6171,16 @@
         <v>46225.615343854166</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I82" s="5">
         <v>46288</v>
@@ -6137,13 +6198,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6152,71 +6213,71 @@
       <c r="U82" s="6"/>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A83" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="B83" s="8">
+      <c r="A83" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="B83" s="9">
         <v>46225.58140275463</v>
       </c>
-      <c r="C83" s="9"/>
-      <c r="D83" s="8">
+      <c r="C83" s="10"/>
+      <c r="D83" s="9">
         <v>46225.61555996528</v>
       </c>
-      <c r="E83" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="F83" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G83" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H83" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="I83" s="8">
+      <c r="E83" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="F83" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G83" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H83" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="I83" s="9">
         <v>46289</v>
       </c>
-      <c r="J83" s="8">
+      <c r="J83" s="9">
         <v>46289</v>
       </c>
-      <c r="K83" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L83" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M83" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N83" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="O83" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="P83" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="Q83" s="8">
+      <c r="K83" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L83" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M83" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N83" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="O83" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="P83" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q83" s="9">
         <v>46289</v>
       </c>
-      <c r="R83" s="8">
+      <c r="R83" s="9">
         <v>46289</v>
       </c>
-      <c r="S83" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="T83" s="9">
+      <c r="S83" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T83" s="10">
         <v>0</v>
       </c>
       <c r="U83" s="12" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="B84" s="5">
         <v>46225.581407488426</v>
@@ -6226,16 +6287,16 @@
         <v>46225.61551967592</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I84" s="6"/>
       <c r="J84" s="5">
@@ -6251,13 +6312,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6266,59 +6327,59 @@
       <c r="U84" s="6"/>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A85" s="7" t="s">
-        <v>263</v>
-      </c>
-      <c r="B85" s="8">
+      <c r="A85" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="B85" s="9">
         <v>46225.581414988425</v>
       </c>
-      <c r="C85" s="9"/>
-      <c r="D85" s="8">
+      <c r="C85" s="10"/>
+      <c r="D85" s="9">
         <v>46225.61552056713</v>
       </c>
-      <c r="E85" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="F85" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G85" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H85" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="I85" s="9"/>
-      <c r="J85" s="8">
+      <c r="E85" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="F85" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G85" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H85" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="I85" s="10"/>
+      <c r="J85" s="9">
         <v>46289</v>
       </c>
-      <c r="K85" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L85" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M85" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N85" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="O85" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="P85" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="Q85" s="9"/>
-      <c r="R85" s="9"/>
-      <c r="S85" s="9"/>
-      <c r="T85" s="9"/>
-      <c r="U85" s="9"/>
+      <c r="K85" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L85" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M85" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N85" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="O85" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="P85" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q85" s="10"/>
+      <c r="R85" s="10"/>
+      <c r="S85" s="10"/>
+      <c r="T85" s="10"/>
+      <c r="U85" s="10"/>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="B86" s="5">
         <v>46225.58145953703</v>
@@ -6328,7 +6389,7 @@
         <v>46225.61568145834</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6353,13 +6414,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="Q86" s="5">
         <v>46293</v>
@@ -6367,72 +6428,72 @@
       <c r="R86" s="5">
         <v>46293</v>
       </c>
-      <c r="S86" s="10" t="s">
-        <v>31</v>
+      <c r="S86" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="T86" s="6">
         <v>0</v>
       </c>
       <c r="U86" s="12" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A87" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="B87" s="8">
+      <c r="A87" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="B87" s="9">
         <v>46225.58146568287</v>
       </c>
-      <c r="C87" s="9"/>
-      <c r="D87" s="8">
+      <c r="C87" s="10"/>
+      <c r="D87" s="9">
         <v>46225.61568175926</v>
       </c>
-      <c r="E87" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="F87" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G87" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H87" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="I87" s="8">
+      <c r="E87" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="F87" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G87" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H87" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="I87" s="9">
         <v>46293</v>
       </c>
-      <c r="J87" s="8">
+      <c r="J87" s="9">
         <v>46293</v>
       </c>
-      <c r="K87" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L87" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M87" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N87" s="9" t="s">
-        <v>265</v>
-      </c>
-      <c r="O87" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="P87" s="9" t="s">
-        <v>267</v>
-      </c>
-      <c r="Q87" s="9"/>
-      <c r="R87" s="9"/>
-      <c r="S87" s="9"/>
-      <c r="T87" s="9"/>
-      <c r="U87" s="9"/>
+      <c r="K87" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L87" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M87" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N87" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="O87" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="P87" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q87" s="10"/>
+      <c r="R87" s="10"/>
+      <c r="S87" s="10"/>
+      <c r="T87" s="10"/>
+      <c r="U87" s="10"/>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="B88" s="5">
         <v>46225.58147099537</v>
@@ -6442,16 +6503,16 @@
         <v>46225.615682592594</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I88" s="5">
         <v>46293</v>
@@ -6469,13 +6530,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6484,55 +6545,55 @@
       <c r="U88" s="6"/>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A89" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="B89" s="8">
+      <c r="A89" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="B89" s="9">
         <v>46225.58147606481</v>
       </c>
-      <c r="C89" s="9"/>
-      <c r="D89" s="8">
+      <c r="C89" s="10"/>
+      <c r="D89" s="9">
         <v>46225.60367008102</v>
       </c>
-      <c r="E89" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="F89" s="9" t="s">
+      <c r="E89" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="F89" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="G89" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H89" s="9"/>
-      <c r="I89" s="9"/>
-      <c r="J89" s="9"/>
-      <c r="K89" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L89" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M89" s="9" t="s">
+      <c r="G89" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="H89" s="10"/>
+      <c r="I89" s="10"/>
+      <c r="J89" s="10"/>
+      <c r="K89" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L89" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M89" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="N89" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="O89" s="9" t="s">
-        <v>271</v>
-      </c>
-      <c r="P89" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q89" s="9"/>
-      <c r="R89" s="9"/>
-      <c r="S89" s="9"/>
-      <c r="T89" s="9"/>
-      <c r="U89" s="9"/>
+      <c r="N89" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="O89" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="P89" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q89" s="10"/>
+      <c r="R89" s="10"/>
+      <c r="S89" s="10"/>
+      <c r="T89" s="10"/>
+      <c r="U89" s="10"/>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B90" s="5">
         <v>46225.58147990741</v>
@@ -6542,16 +6603,16 @@
         <v>46225.615814467594</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="I90" s="5">
         <v>46301</v>
@@ -6569,13 +6630,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="Q90" s="5">
         <v>46301</v>
@@ -6583,70 +6644,70 @@
       <c r="R90" s="5">
         <v>46301</v>
       </c>
-      <c r="S90" s="10" t="s">
-        <v>31</v>
+      <c r="S90" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="T90" s="6">
         <v>0</v>
       </c>
       <c r="U90" s="12" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A91" s="7" t="s">
+      <c r="A91" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B91" s="9">
+        <v>46225.58148496528</v>
+      </c>
+      <c r="C91" s="10"/>
+      <c r="D91" s="9">
+        <v>46225.61578579861</v>
+      </c>
+      <c r="E91" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="F91" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G91" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="H91" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="I91" s="10"/>
+      <c r="J91" s="9">
+        <v>46301</v>
+      </c>
+      <c r="K91" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L91" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M91" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N91" s="10" t="s">
         <v>278</v>
       </c>
-      <c r="B91" s="8">
-        <v>46225.58148496528</v>
-      </c>
-      <c r="C91" s="9"/>
-      <c r="D91" s="8">
-        <v>46225.61578579861</v>
-      </c>
-      <c r="E91" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="F91" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G91" s="9" t="s">
-        <v>274</v>
-      </c>
-      <c r="H91" s="9" t="s">
-        <v>275</v>
-      </c>
-      <c r="I91" s="9"/>
-      <c r="J91" s="8">
-        <v>46301</v>
-      </c>
-      <c r="K91" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L91" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M91" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N91" s="9" t="s">
-        <v>273</v>
-      </c>
-      <c r="O91" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="P91" s="9" t="s">
-        <v>279</v>
-      </c>
-      <c r="Q91" s="9"/>
-      <c r="R91" s="9"/>
-      <c r="S91" s="9"/>
-      <c r="T91" s="9"/>
-      <c r="U91" s="9"/>
+      <c r="O91" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="P91" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="Q91" s="10"/>
+      <c r="R91" s="10"/>
+      <c r="S91" s="10"/>
+      <c r="T91" s="10"/>
+      <c r="U91" s="10"/>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="B92" s="5">
         <v>46225.58148953704</v>
@@ -6656,16 +6717,16 @@
         <v>46225.61578274306</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="I92" s="5">
         <v>46301</v>
@@ -6683,13 +6744,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6698,59 +6759,59 @@
       <c r="U92" s="6"/>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A93" s="7" t="s">
-        <v>281</v>
-      </c>
-      <c r="B93" s="8">
+      <c r="A93" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="B93" s="9">
         <v>46225.6055390625</v>
       </c>
-      <c r="C93" s="9"/>
-      <c r="D93" s="8">
+      <c r="C93" s="10"/>
+      <c r="D93" s="9">
         <v>46225.61577960648</v>
       </c>
-      <c r="E93" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="F93" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G93" s="9" t="s">
-        <v>274</v>
-      </c>
-      <c r="H93" s="9" t="s">
-        <v>275</v>
-      </c>
-      <c r="I93" s="9"/>
-      <c r="J93" s="8">
+      <c r="E93" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="F93" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G93" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="H93" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="I93" s="10"/>
+      <c r="J93" s="9">
         <v>46301</v>
       </c>
-      <c r="K93" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L93" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M93" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N93" s="9" t="s">
-        <v>273</v>
-      </c>
-      <c r="O93" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="P93" s="9" t="s">
-        <v>283</v>
-      </c>
-      <c r="Q93" s="9"/>
-      <c r="R93" s="9"/>
-      <c r="S93" s="9"/>
-      <c r="T93" s="9"/>
-      <c r="U93" s="9"/>
+      <c r="K93" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L93" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M93" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N93" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="O93" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="P93" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="Q93" s="10"/>
+      <c r="R93" s="10"/>
+      <c r="S93" s="10"/>
+      <c r="T93" s="10"/>
+      <c r="U93" s="10"/>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="B94" s="5">
         <v>46225.605553333335</v>
@@ -6760,16 +6821,16 @@
         <v>46225.61577443287</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="I94" s="6"/>
       <c r="J94" s="5">
@@ -6785,13 +6846,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -6800,69 +6861,69 @@
       <c r="U94" s="6"/>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A95" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="B95" s="8">
+      <c r="A95" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="B95" s="9">
         <v>46225.581494178245</v>
       </c>
-      <c r="C95" s="9"/>
-      <c r="D95" s="8">
+      <c r="C95" s="10"/>
+      <c r="D95" s="9">
         <v>46225.61592174768</v>
       </c>
-      <c r="E95" s="9" t="s">
-        <v>286</v>
-      </c>
-      <c r="F95" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G95" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H95" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="I95" s="9"/>
-      <c r="J95" s="8">
+      <c r="E95" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="F95" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G95" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H95" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="I95" s="10"/>
+      <c r="J95" s="9">
         <v>46302</v>
       </c>
-      <c r="K95" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L95" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M95" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N95" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="O95" s="9" t="s">
-        <v>287</v>
-      </c>
-      <c r="P95" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q95" s="8">
+      <c r="K95" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L95" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M95" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N95" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="O95" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="P95" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q95" s="9">
         <v>46302</v>
       </c>
-      <c r="R95" s="8">
+      <c r="R95" s="9">
         <v>46302</v>
       </c>
-      <c r="S95" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="T95" s="9">
+      <c r="S95" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T95" s="10">
         <v>0</v>
       </c>
       <c r="U95" s="12" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="B96" s="5">
         <v>46225.5814984375</v>
@@ -6872,16 +6933,16 @@
         <v>46225.615894421295</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I96" s="5">
         <v>46302</v>
@@ -6899,13 +6960,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -6914,61 +6975,61 @@
       <c r="U96" s="6"/>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A97" s="7" t="s">
-        <v>290</v>
-      </c>
-      <c r="B97" s="8">
+      <c r="A97" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="B97" s="9">
         <v>46225.58150320602</v>
       </c>
-      <c r="C97" s="9"/>
-      <c r="D97" s="8">
+      <c r="C97" s="10"/>
+      <c r="D97" s="9">
         <v>46225.61589104167</v>
       </c>
-      <c r="E97" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="F97" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G97" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H97" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="I97" s="8">
+      <c r="E97" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="F97" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G97" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H97" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="I97" s="9">
         <v>46302</v>
       </c>
-      <c r="J97" s="8">
+      <c r="J97" s="9">
         <v>46302</v>
       </c>
-      <c r="K97" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L97" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M97" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N97" s="9" t="s">
-        <v>286</v>
-      </c>
-      <c r="O97" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="P97" s="9" t="s">
-        <v>289</v>
-      </c>
-      <c r="Q97" s="9"/>
-      <c r="R97" s="9"/>
-      <c r="S97" s="9"/>
-      <c r="T97" s="9"/>
-      <c r="U97" s="9"/>
+      <c r="K97" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L97" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M97" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N97" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="O97" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="P97" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q97" s="10"/>
+      <c r="R97" s="10"/>
+      <c r="S97" s="10"/>
+      <c r="T97" s="10"/>
+      <c r="U97" s="10"/>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="B98" s="5">
         <v>46225.60673211806</v>
@@ -6978,16 +7039,16 @@
         <v>46225.615888125</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I98" s="5">
         <v>46302</v>
@@ -7005,13 +7066,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7020,61 +7081,61 @@
       <c r="U98" s="6"/>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A99" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="B99" s="8">
+      <c r="A99" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="B99" s="9">
         <v>46225.60674163194</v>
       </c>
-      <c r="C99" s="9"/>
-      <c r="D99" s="8">
+      <c r="C99" s="10"/>
+      <c r="D99" s="9">
         <v>46225.61588293982</v>
       </c>
-      <c r="E99" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="F99" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G99" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H99" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="I99" s="8">
+      <c r="E99" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="F99" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G99" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H99" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="I99" s="9">
         <v>46302</v>
       </c>
-      <c r="J99" s="8">
+      <c r="J99" s="9">
         <v>46302</v>
       </c>
-      <c r="K99" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L99" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M99" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N99" s="9" t="s">
-        <v>286</v>
-      </c>
-      <c r="O99" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="P99" s="9" t="s">
-        <v>292</v>
-      </c>
-      <c r="Q99" s="9"/>
-      <c r="R99" s="9"/>
-      <c r="S99" s="9"/>
-      <c r="T99" s="9"/>
-      <c r="U99" s="9"/>
+      <c r="K99" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L99" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M99" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N99" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="O99" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="P99" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q99" s="10"/>
+      <c r="R99" s="10"/>
+      <c r="S99" s="10"/>
+      <c r="T99" s="10"/>
+      <c r="U99" s="10"/>
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B100" s="5">
         <v>46225.58150777778</v>
@@ -7084,16 +7145,16 @@
         <v>46225.61603868056</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="I100" s="5">
         <v>46303</v>
@@ -7111,13 +7172,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="Q100" s="5">
         <v>46303</v>
@@ -7125,70 +7186,70 @@
       <c r="R100" s="5">
         <v>46303</v>
       </c>
-      <c r="S100" s="10" t="s">
-        <v>31</v>
+      <c r="S100" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="T100" s="6">
         <v>0</v>
       </c>
       <c r="U100" s="12" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A101" s="7" t="s">
-        <v>296</v>
-      </c>
-      <c r="B101" s="8">
+      <c r="A101" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="B101" s="9">
         <v>46225.58151239583</v>
       </c>
-      <c r="C101" s="9"/>
-      <c r="D101" s="8">
+      <c r="C101" s="10"/>
+      <c r="D101" s="9">
         <v>46225.61600570602</v>
       </c>
-      <c r="E101" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="F101" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G101" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="H101" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="I101" s="9"/>
-      <c r="J101" s="8">
+      <c r="E101" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="F101" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G101" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="H101" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="I101" s="10"/>
+      <c r="J101" s="9">
         <v>46303</v>
       </c>
-      <c r="K101" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L101" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M101" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N101" s="9" t="s">
-        <v>295</v>
-      </c>
-      <c r="O101" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="P101" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="Q101" s="9"/>
-      <c r="R101" s="9"/>
-      <c r="S101" s="9"/>
-      <c r="T101" s="9"/>
-      <c r="U101" s="9"/>
+      <c r="K101" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L101" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M101" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N101" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="O101" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="P101" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="Q101" s="10"/>
+      <c r="R101" s="10"/>
+      <c r="S101" s="10"/>
+      <c r="T101" s="10"/>
+      <c r="U101" s="10"/>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B102" s="5">
         <v>46225.58151694444</v>
@@ -7198,16 +7259,16 @@
         <v>46225.61600274306</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="I102" s="6"/>
       <c r="J102" s="5">
@@ -7223,13 +7284,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7238,61 +7299,61 @@
       <c r="U102" s="6"/>
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A103" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="B103" s="8">
+      <c r="A103" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="B103" s="9">
         <v>46225.606768564816</v>
       </c>
-      <c r="C103" s="9"/>
-      <c r="D103" s="8">
+      <c r="C103" s="10"/>
+      <c r="D103" s="9">
         <v>46225.615999965274</v>
       </c>
-      <c r="E103" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="F103" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G103" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="H103" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="I103" s="8">
+      <c r="E103" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="F103" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G103" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="H103" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="I103" s="9">
         <v>46303</v>
       </c>
-      <c r="J103" s="8">
+      <c r="J103" s="9">
         <v>46303</v>
       </c>
-      <c r="K103" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L103" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M103" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N103" s="9" t="s">
-        <v>295</v>
-      </c>
-      <c r="O103" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="P103" s="9" t="s">
+      <c r="K103" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L103" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M103" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N103" s="10" t="s">
         <v>300</v>
       </c>
-      <c r="Q103" s="9"/>
-      <c r="R103" s="9"/>
-      <c r="S103" s="9"/>
-      <c r="T103" s="9"/>
-      <c r="U103" s="9"/>
+      <c r="O103" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="P103" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="Q103" s="10"/>
+      <c r="R103" s="10"/>
+      <c r="S103" s="10"/>
+      <c r="T103" s="10"/>
+      <c r="U103" s="10"/>
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B104" s="5">
         <v>46225.606777395835</v>
@@ -7302,16 +7363,16 @@
         <v>46225.61599523148</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="I104" s="5">
         <v>46303</v>
@@ -7329,13 +7390,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7344,71 +7405,71 @@
       <c r="U104" s="6"/>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A105" s="7" t="s">
-        <v>302</v>
-      </c>
-      <c r="B105" s="8">
+      <c r="A105" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="B105" s="9">
         <v>46225.581521562504</v>
       </c>
-      <c r="C105" s="9"/>
-      <c r="D105" s="8">
+      <c r="C105" s="10"/>
+      <c r="D105" s="9">
         <v>46225.61624585648</v>
       </c>
-      <c r="E105" s="9" t="s">
-        <v>303</v>
-      </c>
-      <c r="F105" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G105" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="H105" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="I105" s="8">
+      <c r="E105" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="F105" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G105" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="H105" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="I105" s="9">
         <v>46304</v>
       </c>
-      <c r="J105" s="8">
+      <c r="J105" s="9">
         <v>46304</v>
       </c>
-      <c r="K105" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L105" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M105" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N105" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="O105" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="P105" s="9" t="s">
-        <v>304</v>
-      </c>
-      <c r="Q105" s="8">
+      <c r="K105" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L105" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M105" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N105" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="O105" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="P105" s="10" t="s">
+        <v>309</v>
+      </c>
+      <c r="Q105" s="9">
         <v>46304</v>
       </c>
-      <c r="R105" s="8">
+      <c r="R105" s="9">
         <v>46304</v>
       </c>
-      <c r="S105" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="T105" s="9">
+      <c r="S105" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T105" s="10">
         <v>0</v>
       </c>
       <c r="U105" s="12" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="B106" s="5">
         <v>46225.58152704861</v>
@@ -7418,16 +7479,16 @@
         <v>46225.61621090278</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="I106" s="6"/>
       <c r="J106" s="5">
@@ -7443,13 +7504,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7458,59 +7519,59 @@
       <c r="U106" s="6"/>
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A107" s="7" t="s">
-        <v>307</v>
-      </c>
-      <c r="B107" s="8">
+      <c r="A107" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="B107" s="9">
         <v>46225.58153157408</v>
       </c>
-      <c r="C107" s="9"/>
-      <c r="D107" s="8">
+      <c r="C107" s="10"/>
+      <c r="D107" s="9">
         <v>46225.61620709491</v>
       </c>
-      <c r="E107" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="F107" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G107" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="H107" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="I107" s="9"/>
-      <c r="J107" s="8">
+      <c r="E107" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="F107" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G107" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="H107" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="I107" s="10"/>
+      <c r="J107" s="9">
         <v>46304</v>
       </c>
-      <c r="K107" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L107" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M107" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N107" s="9" t="s">
-        <v>303</v>
-      </c>
-      <c r="O107" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="P107" s="9" t="s">
-        <v>306</v>
-      </c>
-      <c r="Q107" s="9"/>
-      <c r="R107" s="9"/>
-      <c r="S107" s="9"/>
-      <c r="T107" s="9"/>
-      <c r="U107" s="9"/>
+      <c r="K107" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L107" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M107" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N107" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="O107" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="P107" s="10" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q107" s="10"/>
+      <c r="R107" s="10"/>
+      <c r="S107" s="10"/>
+      <c r="T107" s="10"/>
+      <c r="U107" s="10"/>
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="B108" s="5">
         <v>46225.60680554398</v>
@@ -7520,16 +7581,16 @@
         <v>46225.616203564816</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="I108" s="5">
         <v>46304</v>
@@ -7547,10 +7608,10 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="P108" s="6" t="s">
         <v>26</v>
@@ -7562,61 +7623,61 @@
       <c r="U108" s="6"/>
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A109" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="B109" s="8">
+      <c r="A109" s="8" t="s">
+        <v>314</v>
+      </c>
+      <c r="B109" s="9">
         <v>46225.60681763889</v>
       </c>
-      <c r="C109" s="9"/>
-      <c r="D109" s="8">
+      <c r="C109" s="10"/>
+      <c r="D109" s="9">
         <v>46225.61619854167</v>
       </c>
-      <c r="E109" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="F109" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G109" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="H109" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="I109" s="8">
+      <c r="E109" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="F109" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G109" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="H109" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="I109" s="9">
         <v>46304</v>
       </c>
-      <c r="J109" s="8">
+      <c r="J109" s="9">
         <v>46304</v>
       </c>
-      <c r="K109" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L109" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M109" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N109" s="9" t="s">
-        <v>303</v>
-      </c>
-      <c r="O109" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="P109" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q109" s="9"/>
-      <c r="R109" s="9"/>
-      <c r="S109" s="9"/>
-      <c r="T109" s="9"/>
-      <c r="U109" s="9"/>
+      <c r="K109" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L109" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M109" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N109" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="O109" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="P109" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q109" s="10"/>
+      <c r="R109" s="10"/>
+      <c r="S109" s="10"/>
+      <c r="T109" s="10"/>
+      <c r="U109" s="10"/>
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="B110" s="5">
         <v>46225.58153574074</v>
@@ -7626,7 +7687,7 @@
         <v>46225.60402078704</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>25</v>
@@ -7650,7 +7711,7 @@
         <v>26</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>26</v>
@@ -7662,71 +7723,71 @@
       <c r="U110" s="6"/>
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A111" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="B111" s="8">
+      <c r="A111" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="B111" s="9">
         <v>46225.58153866898</v>
       </c>
-      <c r="C111" s="9"/>
-      <c r="D111" s="8">
+      <c r="C111" s="10"/>
+      <c r="D111" s="9">
         <v>46225.61649424769</v>
       </c>
-      <c r="E111" s="9" t="s">
-        <v>314</v>
-      </c>
-      <c r="F111" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G111" s="9" t="s">
-        <v>315</v>
-      </c>
-      <c r="H111" s="9" t="s">
+      <c r="E111" s="10" t="s">
+        <v>319</v>
+      </c>
+      <c r="F111" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G111" s="10" t="s">
+        <v>320</v>
+      </c>
+      <c r="H111" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="I111" s="9">
+        <v>46307</v>
+      </c>
+      <c r="J111" s="9">
+        <v>46311</v>
+      </c>
+      <c r="K111" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L111" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M111" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N111" s="10" t="s">
         <v>316</v>
       </c>
-      <c r="I111" s="8">
+      <c r="O111" s="10" t="s">
+        <v>322</v>
+      </c>
+      <c r="P111" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="Q111" s="9">
+        <v>46311</v>
+      </c>
+      <c r="R111" s="9">
         <v>46307</v>
       </c>
-      <c r="J111" s="8">
-        <v>46311</v>
-      </c>
-      <c r="K111" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L111" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M111" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N111" s="9" t="s">
-        <v>311</v>
-      </c>
-      <c r="O111" s="9" t="s">
-        <v>317</v>
-      </c>
-      <c r="P111" s="9" t="s">
-        <v>311</v>
-      </c>
-      <c r="Q111" s="8">
-        <v>46311</v>
-      </c>
-      <c r="R111" s="8">
-        <v>46307</v>
-      </c>
-      <c r="S111" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="T111" s="9">
+      <c r="S111" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T111" s="10">
         <v>0</v>
       </c>
       <c r="U111" s="12" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="B112" s="5">
         <v>46225.58154590278</v>
@@ -7736,16 +7797,16 @@
         <v>46225.61639241898</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I112" s="5">
         <v>46307</v>
@@ -7763,13 +7824,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="Q112" s="5">
         <v>46311</v>
@@ -7777,66 +7838,66 @@
       <c r="R112" s="5">
         <v>46307</v>
       </c>
-      <c r="S112" s="10" t="s">
-        <v>31</v>
+      <c r="S112" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="T112" s="6">
         <v>0</v>
       </c>
       <c r="U112" s="12" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A113" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="B113" s="8">
+      <c r="A113" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="B113" s="9">
         <v>46225.59432256944</v>
       </c>
-      <c r="C113" s="9"/>
-      <c r="D113" s="8">
+      <c r="C113" s="10"/>
+      <c r="D113" s="9">
         <v>46225.6052183912</v>
       </c>
-      <c r="E113" s="9" t="s">
-        <v>321</v>
-      </c>
-      <c r="F113" s="9" t="s">
+      <c r="E113" s="10" t="s">
+        <v>326</v>
+      </c>
+      <c r="F113" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="G113" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H113" s="9"/>
-      <c r="I113" s="9"/>
-      <c r="J113" s="9"/>
-      <c r="K113" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L113" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M113" s="9" t="s">
+      <c r="G113" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="H113" s="10"/>
+      <c r="I113" s="10"/>
+      <c r="J113" s="10"/>
+      <c r="K113" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L113" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M113" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="N113" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="O113" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="P113" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q113" s="9"/>
-      <c r="R113" s="9"/>
-      <c r="S113" s="9"/>
-      <c r="T113" s="9"/>
-      <c r="U113" s="9"/>
+      <c r="N113" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="O113" s="10" t="s">
+        <v>327</v>
+      </c>
+      <c r="P113" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q113" s="10"/>
+      <c r="R113" s="10"/>
+      <c r="S113" s="10"/>
+      <c r="T113" s="10"/>
+      <c r="U113" s="10"/>
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="B114" s="5">
         <v>46225.59476561342</v>
@@ -7846,16 +7907,16 @@
         <v>46225.616553796295</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="I114" s="5">
         <v>46314</v>
@@ -7873,13 +7934,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="Q114" s="5">
         <v>46318</v>
@@ -7887,77 +7948,77 @@
       <c r="R114" s="5">
         <v>46314</v>
       </c>
-      <c r="S114" s="10" t="s">
-        <v>31</v>
+      <c r="S114" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="T114" s="6">
         <v>0</v>
       </c>
       <c r="U114" s="12" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A115" s="7" t="s">
+      <c r="A115" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="B115" s="9">
+        <v>46225.59487494213</v>
+      </c>
+      <c r="C115" s="10"/>
+      <c r="D115" s="9">
+        <v>46225.61655020833</v>
+      </c>
+      <c r="E115" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="F115" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G115" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="H115" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="I115" s="9">
+        <v>46321</v>
+      </c>
+      <c r="J115" s="9">
+        <v>46325</v>
+      </c>
+      <c r="K115" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L115" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M115" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N115" s="10" t="s">
         <v>326</v>
       </c>
-      <c r="B115" s="8">
-        <v>46225.59487494213</v>
-      </c>
-      <c r="C115" s="9"/>
-      <c r="D115" s="8">
-        <v>46225.61655020833</v>
-      </c>
-      <c r="E115" s="9" t="s">
-        <v>327</v>
-      </c>
-      <c r="F115" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G115" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="H115" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="I115" s="8">
+      <c r="O115" s="10" t="s">
+        <v>329</v>
+      </c>
+      <c r="P115" s="10" t="s">
+        <v>326</v>
+      </c>
+      <c r="Q115" s="9">
+        <v>46325</v>
+      </c>
+      <c r="R115" s="9">
         <v>46321</v>
       </c>
-      <c r="J115" s="8">
-        <v>46325</v>
-      </c>
-      <c r="K115" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L115" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M115" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N115" s="9" t="s">
-        <v>321</v>
-      </c>
-      <c r="O115" s="9" t="s">
-        <v>324</v>
-      </c>
-      <c r="P115" s="9" t="s">
-        <v>321</v>
-      </c>
-      <c r="Q115" s="8">
-        <v>46325</v>
-      </c>
-      <c r="R115" s="8">
-        <v>46321</v>
-      </c>
-      <c r="S115" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="T115" s="9">
+      <c r="S115" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T115" s="10">
         <v>0</v>
       </c>
       <c r="U115" s="12" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001580- CIA. RIO MINERALES.xlsx
+++ b/data/50001580- CIA. RIO MINERALES.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1347" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1348" uniqueCount="334">
   <si>
     <t>50001580- "CIA. RIO MINERALES"</t>
   </si>
@@ -250,6 +250,14 @@
   </si>
   <si>
     <t>1216788147959225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Ficha técnica ventilador
+    Hoja de datos motor
+    Plano Montaje
+    Plano Cimentación
+    Manual de Operación y Servicio
+</t>
   </si>
   <si>
     <t>Ingenieria Jefe de proyecto:,Plano Preliminar OT4378</t>
@@ -1857,7 +1865,7 @@
         <v>46226.571240590274</v>
       </c>
       <c r="D7" s="9">
-        <v>46226.571264432874</v>
+        <v>46226.572476099536</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>38</v>
@@ -2262,9 +2270,11 @@
       <c r="B14" s="5">
         <v>46225.58085679398</v>
       </c>
-      <c r="C14" s="6"/>
+      <c r="C14" s="5">
+        <v>46226.57610013889</v>
+      </c>
       <c r="D14" s="5">
-        <v>46225.59597591435</v>
+        <v>46226.576112442126</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>66</v>
@@ -2299,8 +2309,12 @@
       <c r="Q14" s="6"/>
       <c r="R14" s="6"/>
       <c r="S14" s="6"/>
-      <c r="T14" s="6"/>
-      <c r="U14" s="6"/>
+      <c r="T14" s="6">
+        <v>1</v>
+      </c>
+      <c r="U14" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
@@ -2309,9 +2323,11 @@
       <c r="B15" s="9">
         <v>46225.58095215278</v>
       </c>
-      <c r="C15" s="10"/>
+      <c r="C15" s="9">
+        <v>46226.576076365745</v>
+      </c>
       <c r="D15" s="9">
-        <v>46226.571272754634</v>
+        <v>46226.57609552083</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>67</v>
@@ -2335,7 +2351,7 @@
         <v>26</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="M15" s="10" t="s">
         <v>26</v>
@@ -2347,7 +2363,7 @@
         <v>38</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Q15" s="9">
         <v>46227</v>
@@ -2359,15 +2375,15 @@
         <v>33</v>
       </c>
       <c r="T15" s="10">
-        <v>0</v>
-      </c>
-      <c r="U15" s="11" t="s">
-        <v>52</v>
+        <v>1</v>
+      </c>
+      <c r="U15" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B16" s="5">
         <v>46225.580861423616</v>
@@ -2377,7 +2393,7 @@
         <v>46225.59611458333</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>25</v>
@@ -2401,7 +2417,7 @@
         <v>26</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="P16" s="6" t="s">
         <v>26</v>
@@ -2414,7 +2430,7 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B17" s="9">
         <v>46225.580958923616</v>
@@ -2424,16 +2440,16 @@
         <v>46226.57127291667</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I17" s="9">
         <v>46226</v>
@@ -2451,13 +2467,13 @@
         <v>26</v>
       </c>
       <c r="N17" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="O17" s="10" t="s">
         <v>38</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q17" s="9">
         <v>46227</v>
@@ -2477,7 +2493,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B18" s="5">
         <v>46225.58096494213</v>
@@ -2487,16 +2503,16 @@
         <v>46226.57127292824</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I18" s="5">
         <v>46226</v>
@@ -2514,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="O18" s="6" t="s">
         <v>38</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Q18" s="5">
         <v>46227</v>
@@ -2540,7 +2556,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B19" s="9">
         <v>46225.58097109954</v>
@@ -2550,16 +2566,16 @@
         <v>46226.571272870366</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I19" s="9">
         <v>46226</v>
@@ -2577,13 +2593,13 @@
         <v>26</v>
       </c>
       <c r="N19" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="O19" s="10" t="s">
         <v>38</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q19" s="9">
         <v>46227</v>
@@ -2603,7 +2619,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B20" s="5">
         <v>46225.58086628473</v>
@@ -2613,7 +2629,7 @@
         <v>46225.59619578704</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>25</v>
@@ -2637,7 +2653,7 @@
         <v>26</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P20" s="6" t="s">
         <v>26</v>
@@ -2650,7 +2666,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B21" s="9">
         <v>46225.580978240745</v>
@@ -2660,16 +2676,16 @@
         <v>46225.61247136574</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I21" s="9">
         <v>46245</v>
@@ -2687,13 +2703,13 @@
         <v>26</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q21" s="9">
         <v>46246</v>
@@ -2713,7 +2729,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B22" s="5">
         <v>46225.5809840625</v>
@@ -2723,16 +2739,16 @@
         <v>46225.612467824074</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I22" s="5">
         <v>46245</v>
@@ -2750,13 +2766,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q22" s="5">
         <v>46246</v>
@@ -2776,7 +2792,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B23" s="9">
         <v>46225.58098827546</v>
@@ -2786,16 +2802,16 @@
         <v>46225.612464756945</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I23" s="9">
         <v>46245</v>
@@ -2813,13 +2829,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q23" s="9">
         <v>46246</v>
@@ -2839,7 +2855,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B24" s="5">
         <v>46225.58100011574</v>
@@ -2849,16 +2865,16 @@
         <v>46225.61246184028</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I24" s="5">
         <v>46245</v>
@@ -2876,13 +2892,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q24" s="5">
         <v>46246</v>
@@ -2902,7 +2918,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B25" s="9">
         <v>46225.59619364583</v>
@@ -2912,16 +2928,16 @@
         <v>46225.61245637732</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I25" s="9">
         <v>46231</v>
@@ -2939,13 +2955,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O25" s="10" t="s">
         <v>48</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q25" s="9">
         <v>46232</v>
@@ -2965,7 +2981,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B26" s="5">
         <v>46225.58087085648</v>
@@ -2975,7 +2991,7 @@
         <v>46225.596821886575</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>25</v>
@@ -2999,7 +3015,7 @@
         <v>26</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P26" s="6" t="s">
         <v>26</v>
@@ -3012,7 +3028,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B27" s="9">
         <v>46225.58100560185</v>
@@ -3022,16 +3038,16 @@
         <v>46225.61255763889</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I27" s="9">
         <v>46247</v>
@@ -3049,13 +3065,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q27" s="9">
         <v>46259</v>
@@ -3075,7 +3091,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B28" s="5">
         <v>46225.58101144676</v>
@@ -3085,16 +3101,16 @@
         <v>46225.61262662037</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I28" s="5">
         <v>46247</v>
@@ -3112,13 +3128,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3134,7 +3150,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B29" s="9">
         <v>46225.581017233795</v>
@@ -3144,16 +3160,16 @@
         <v>46225.61262351852</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I29" s="9">
         <v>46251</v>
@@ -3171,13 +3187,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
@@ -3193,7 +3209,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B30" s="5">
         <v>46225.58102277778</v>
@@ -3203,16 +3219,16 @@
         <v>46225.61255446759</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I30" s="5">
         <v>46247</v>
@@ -3230,10 +3246,10 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P30" s="6" t="s">
         <v>26</v>
@@ -3256,7 +3272,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B31" s="9">
         <v>46225.58102737268</v>
@@ -3266,16 +3282,16 @@
         <v>46225.61269579861</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I31" s="9">
         <v>46247</v>
@@ -3293,13 +3309,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3309,7 +3325,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B32" s="5">
         <v>46225.581032222224</v>
@@ -3319,16 +3335,16 @@
         <v>46225.612692442126</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I32" s="5">
         <v>46251</v>
@@ -3346,13 +3362,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3362,7 +3378,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B33" s="9">
         <v>46225.581037199074</v>
@@ -3372,16 +3388,16 @@
         <v>46225.61279568287</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I33" s="9">
         <v>46247</v>
@@ -3399,10 +3415,10 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P33" s="10" t="s">
         <v>26</v>
@@ -3425,7 +3441,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B34" s="5">
         <v>46225.58104158565</v>
@@ -3435,16 +3451,16 @@
         <v>46225.61298453704</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I34" s="5">
         <v>46247</v>
@@ -3462,13 +3478,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3478,7 +3494,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B35" s="9">
         <v>46225.5810464699</v>
@@ -3488,16 +3504,16 @@
         <v>46225.61298125</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I35" s="9">
         <v>46251</v>
@@ -3515,13 +3531,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -3531,7 +3547,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B36" s="5">
         <v>46225.58105121528</v>
@@ -3541,16 +3557,16 @@
         <v>46225.61316422454</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I36" s="5">
         <v>46247</v>
@@ -3568,10 +3584,10 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3594,7 +3610,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B37" s="9">
         <v>46225.58109630787</v>
@@ -3604,16 +3620,16 @@
         <v>46225.613052245375</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I37" s="9">
         <v>46247</v>
@@ -3631,13 +3647,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3647,7 +3663,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B38" s="5">
         <v>46225.58110178241</v>
@@ -3657,16 +3673,16 @@
         <v>46225.613047719904</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I38" s="5">
         <v>46258</v>
@@ -3684,13 +3700,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3700,7 +3716,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B39" s="9">
         <v>46225.58110600694</v>
@@ -3710,16 +3726,16 @@
         <v>46225.613129363424</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I39" s="9">
         <v>46289</v>
@@ -3737,13 +3753,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
@@ -3753,7 +3769,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B40" s="5">
         <v>46225.59682005787</v>
@@ -3763,16 +3779,16 @@
         <v>46225.6133383912</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I40" s="5">
         <v>46233</v>
@@ -3790,10 +3806,10 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>26</v>
@@ -3816,7 +3832,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B41" s="9">
         <v>46225.59686481481</v>
@@ -3826,16 +3842,16 @@
         <v>46225.613313634254</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I41" s="9">
         <v>46233</v>
@@ -3853,13 +3869,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -3869,7 +3885,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B42" s="5">
         <v>46225.59692966435</v>
@@ -3879,16 +3895,16 @@
         <v>46225.613310636574</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I42" s="5">
         <v>46244</v>
@@ -3906,13 +3922,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -3922,7 +3938,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B43" s="9">
         <v>46225.58111748843</v>
@@ -3932,7 +3948,7 @@
         <v>46225.589328946764</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>25</v>
@@ -3956,7 +3972,7 @@
         <v>26</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -3969,26 +3985,26 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B44" s="5">
         <v>46225.58112127315</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46225.61343114583</v>
+        <v>46226.57609570602</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I44" s="5">
         <v>46230</v>
@@ -4006,13 +4022,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>67</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q44" s="5">
         <v>46234</v>
@@ -4026,13 +4042,13 @@
       <c r="T44" s="6">
         <v>0</v>
       </c>
-      <c r="U44" s="12" t="s">
-        <v>58</v>
+      <c r="U44" s="11" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B45" s="9">
         <v>46225.58112643519</v>
@@ -4042,16 +4058,16 @@
         <v>46225.613428275465</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I45" s="9">
         <v>46237</v>
@@ -4069,13 +4085,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q45" s="9">
         <v>46241</v>
@@ -4095,7 +4111,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B46" s="5">
         <v>46225.58113097222</v>
@@ -4105,16 +4121,16 @@
         <v>46225.61342412037</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I46" s="5">
         <v>46244</v>
@@ -4132,13 +4148,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q46" s="5">
         <v>46244</v>
@@ -4158,7 +4174,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B47" s="9">
         <v>46225.58114445602</v>
@@ -4168,16 +4184,16 @@
         <v>46225.61347256944</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I47" s="9">
         <v>46290</v>
@@ -4195,13 +4211,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q47" s="9">
         <v>46290</v>
@@ -4221,7 +4237,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B48" s="5">
         <v>46225.58114871528</v>
@@ -4231,16 +4247,16 @@
         <v>46225.61551950232</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I48" s="5">
         <v>46290</v>
@@ -4258,13 +4274,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4274,7 +4290,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B49" s="9">
         <v>46225.58115283565</v>
@@ -4284,16 +4300,16 @@
         <v>46225.615519513885</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I49" s="9">
         <v>46290</v>
@@ -4311,13 +4327,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q49" s="10"/>
       <c r="R49" s="10"/>
@@ -4327,7 +4343,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B50" s="5">
         <v>46225.581171631944</v>
@@ -4337,7 +4353,7 @@
         <v>46225.59181146991</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>25</v>
@@ -4361,7 +4377,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4374,7 +4390,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B51" s="9">
         <v>46225.58117489584</v>
@@ -4384,16 +4400,16 @@
         <v>46225.61367097222</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I51" s="9">
         <v>46260</v>
@@ -4411,13 +4427,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q51" s="9">
         <v>46260</v>
@@ -4437,7 +4453,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B52" s="5">
         <v>46225.58118028935</v>
@@ -4447,16 +4463,16 @@
         <v>46225.613667349535</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I52" s="5">
         <v>46260</v>
@@ -4474,13 +4490,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q52" s="5">
         <v>46260</v>
@@ -4500,7 +4516,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B53" s="9">
         <v>46225.58118576389</v>
@@ -4510,16 +4526,16 @@
         <v>46225.61366387732</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I53" s="9">
         <v>46260</v>
@@ -4537,13 +4553,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q53" s="9">
         <v>46260</v>
@@ -4563,7 +4579,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B54" s="5">
         <v>46225.58119107639</v>
@@ -4573,16 +4589,16 @@
         <v>46225.61417395833</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I54" s="5">
         <v>46261</v>
@@ -4600,13 +4616,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q54" s="5">
         <v>46261</v>
@@ -4626,7 +4642,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B55" s="9">
         <v>46225.58119642361</v>
@@ -4636,16 +4652,16 @@
         <v>46225.61417104167</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I55" s="9">
         <v>46261</v>
@@ -4663,13 +4679,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q55" s="9">
         <v>46261</v>
@@ -4689,7 +4705,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B56" s="5">
         <v>46225.581201678244</v>
@@ -4699,16 +4715,16 @@
         <v>46225.61416773148</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I56" s="5">
         <v>46261</v>
@@ -4726,13 +4742,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q56" s="5">
         <v>46261</v>
@@ -4752,7 +4768,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B57" s="9">
         <v>46225.58120702546</v>
@@ -4762,7 +4778,7 @@
         <v>46225.59190644676</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>25</v>
@@ -4786,7 +4802,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P57" s="10" t="s">
         <v>26</v>
@@ -4799,7 +4815,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B58" s="5">
         <v>46225.58121010417</v>
@@ -4809,16 +4825,16 @@
         <v>46225.6142333912</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I58" s="5">
         <v>46262</v>
@@ -4836,13 +4852,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q58" s="5">
         <v>46266</v>
@@ -4862,7 +4878,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B59" s="9">
         <v>46225.581215474536</v>
@@ -4872,16 +4888,16 @@
         <v>46225.61435628472</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I59" s="9">
         <v>46267</v>
@@ -4899,13 +4915,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q59" s="9">
         <v>46273</v>
@@ -4925,7 +4941,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B60" s="5">
         <v>46225.581219618056</v>
@@ -4935,16 +4951,16 @@
         <v>46225.614318611115</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I60" s="5">
         <v>46267</v>
@@ -4962,13 +4978,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -4978,7 +4994,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B61" s="9">
         <v>46225.58123596065</v>
@@ -4988,16 +5004,16 @@
         <v>46225.61431550926</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I61" s="9">
         <v>46267</v>
@@ -5015,13 +5031,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q61" s="10"/>
       <c r="R61" s="10"/>
@@ -5031,7 +5047,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B62" s="5">
         <v>46225.58129219907</v>
@@ -5041,16 +5057,16 @@
         <v>46225.61447392361</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I62" s="5">
         <v>46274</v>
@@ -5068,13 +5084,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q62" s="5">
         <v>46274</v>
@@ -5094,7 +5110,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B63" s="9">
         <v>46225.58129802083</v>
@@ -5104,16 +5120,16 @@
         <v>46225.61443357639</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I63" s="10"/>
       <c r="J63" s="9">
@@ -5129,13 +5145,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5145,7 +5161,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B64" s="5">
         <v>46225.581304374995</v>
@@ -5155,16 +5171,16 @@
         <v>46225.61443052083</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I64" s="6"/>
       <c r="J64" s="5">
@@ -5180,13 +5196,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5196,7 +5212,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B65" s="9">
         <v>46225.58131015046</v>
@@ -5206,7 +5222,7 @@
         <v>46225.59759329861</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>25</v>
@@ -5230,7 +5246,7 @@
         <v>26</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P65" s="10" t="s">
         <v>26</v>
@@ -5243,7 +5259,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B66" s="5">
         <v>46225.58131376158</v>
@@ -5253,16 +5269,16 @@
         <v>46225.61459215278</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I66" s="5">
         <v>46230</v>
@@ -5280,13 +5296,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q66" s="5">
         <v>46231</v>
@@ -5306,7 +5322,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B67" s="9">
         <v>46225.58131929398</v>
@@ -5316,16 +5332,16 @@
         <v>46225.61459149305</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I67" s="9">
         <v>46230</v>
@@ -5343,13 +5359,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q67" s="9">
         <v>46231</v>
@@ -5369,7 +5385,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B68" s="5">
         <v>46225.58132505787</v>
@@ -5379,16 +5395,16 @@
         <v>46225.61459082176</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I68" s="5">
         <v>46230</v>
@@ -5406,13 +5422,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q68" s="5">
         <v>46231</v>
@@ -5432,7 +5448,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B69" s="9">
         <v>46225.597591134254</v>
@@ -5448,10 +5464,10 @@
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I69" s="9">
         <v>46293</v>
@@ -5469,10 +5485,10 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P69" s="10" t="s">
         <v>57</v>
@@ -5495,7 +5511,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B70" s="5">
         <v>46225.58133054398</v>
@@ -5505,7 +5521,7 @@
         <v>46225.59299179398</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>25</v>
@@ -5529,7 +5545,7 @@
         <v>26</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -5542,7 +5558,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B71" s="9">
         <v>46225.58133395833</v>
@@ -5552,16 +5568,16 @@
         <v>46225.614863599534</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I71" s="9">
         <v>46275</v>
@@ -5579,13 +5595,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q71" s="9">
         <v>46281</v>
@@ -5605,7 +5621,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B72" s="5">
         <v>46225.58133853009</v>
@@ -5615,16 +5631,16 @@
         <v>46225.61483068287</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I72" s="5">
         <v>46275</v>
@@ -5642,13 +5658,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5658,7 +5674,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B73" s="9">
         <v>46225.58134314815</v>
@@ -5668,16 +5684,16 @@
         <v>46225.61482673611</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I73" s="9">
         <v>46275</v>
@@ -5695,13 +5711,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -5711,7 +5727,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B74" s="5">
         <v>46225.58134744213</v>
@@ -5721,16 +5737,16 @@
         <v>46225.61499751157</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I74" s="5">
         <v>46286</v>
@@ -5748,13 +5764,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q74" s="5">
         <v>46286</v>
@@ -5774,7 +5790,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B75" s="9">
         <v>46225.581351932866</v>
@@ -5784,16 +5800,16 @@
         <v>46225.61504185185</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I75" s="9">
         <v>46286</v>
@@ -5811,13 +5827,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -5827,7 +5843,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B76" s="5">
         <v>46225.58135922454</v>
@@ -5837,16 +5853,16 @@
         <v>46225.615038819444</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I76" s="5">
         <v>46286</v>
@@ -5864,13 +5880,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -5880,7 +5896,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B77" s="9">
         <v>46225.5813728588</v>
@@ -5890,16 +5906,16 @@
         <v>46225.61522760417</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I77" s="9">
         <v>46287</v>
@@ -5917,13 +5933,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q77" s="9">
         <v>46287</v>
@@ -5943,7 +5959,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B78" s="5">
         <v>46225.58137722222</v>
@@ -5953,16 +5969,16 @@
         <v>46225.61518142361</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I78" s="6"/>
       <c r="J78" s="5">
@@ -5978,13 +5994,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -5994,7 +6010,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B79" s="9">
         <v>46225.58138231482</v>
@@ -6004,16 +6020,16 @@
         <v>46225.615182291665</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I79" s="10"/>
       <c r="J79" s="9">
@@ -6029,13 +6045,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6045,7 +6061,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B80" s="5">
         <v>46225.58138733797</v>
@@ -6055,16 +6071,16 @@
         <v>46225.61538164352</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I80" s="5">
         <v>46288</v>
@@ -6082,13 +6098,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q80" s="5">
         <v>46288</v>
@@ -6108,7 +6124,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B81" s="9">
         <v>46225.58139180556</v>
@@ -6118,16 +6134,16 @@
         <v>46225.61534716435</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I81" s="9">
         <v>46288</v>
@@ -6145,13 +6161,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6161,7 +6177,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B82" s="5">
         <v>46225.58139752314</v>
@@ -6171,16 +6187,16 @@
         <v>46225.615343854166</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I82" s="5">
         <v>46288</v>
@@ -6198,13 +6214,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6214,7 +6230,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B83" s="9">
         <v>46225.58140275463</v>
@@ -6224,16 +6240,16 @@
         <v>46225.61555996528</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I83" s="9">
         <v>46289</v>
@@ -6251,13 +6267,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q83" s="9">
         <v>46289</v>
@@ -6277,7 +6293,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B84" s="5">
         <v>46225.581407488426</v>
@@ -6287,16 +6303,16 @@
         <v>46225.61551967592</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I84" s="6"/>
       <c r="J84" s="5">
@@ -6312,13 +6328,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6328,7 +6344,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B85" s="9">
         <v>46225.581414988425</v>
@@ -6338,16 +6354,16 @@
         <v>46225.61552056713</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I85" s="10"/>
       <c r="J85" s="9">
@@ -6363,13 +6379,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6379,7 +6395,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B86" s="5">
         <v>46225.58145953703</v>
@@ -6389,7 +6405,7 @@
         <v>46225.61568145834</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6414,13 +6430,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q86" s="5">
         <v>46293</v>
@@ -6440,7 +6456,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B87" s="9">
         <v>46225.58146568287</v>
@@ -6450,16 +6466,16 @@
         <v>46225.61568175926</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I87" s="9">
         <v>46293</v>
@@ -6477,13 +6493,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6493,7 +6509,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B88" s="5">
         <v>46225.58147099537</v>
@@ -6503,16 +6519,16 @@
         <v>46225.615682592594</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I88" s="5">
         <v>46293</v>
@@ -6530,13 +6546,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6546,7 +6562,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B89" s="9">
         <v>46225.58147606481</v>
@@ -6556,7 +6572,7 @@
         <v>46225.60367008102</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>25</v>
@@ -6580,7 +6596,7 @@
         <v>26</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P89" s="10" t="s">
         <v>26</v>
@@ -6593,7 +6609,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B90" s="5">
         <v>46225.58147990741</v>
@@ -6603,16 +6619,16 @@
         <v>46225.615814467594</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I90" s="5">
         <v>46301</v>
@@ -6630,13 +6646,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q90" s="5">
         <v>46301</v>
@@ -6656,7 +6672,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B91" s="9">
         <v>46225.58148496528</v>
@@ -6666,16 +6682,16 @@
         <v>46225.61578579861</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I91" s="10"/>
       <c r="J91" s="9">
@@ -6691,13 +6707,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -6707,7 +6723,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B92" s="5">
         <v>46225.58148953704</v>
@@ -6717,16 +6733,16 @@
         <v>46225.61578274306</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I92" s="5">
         <v>46301</v>
@@ -6744,13 +6760,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6760,7 +6776,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B93" s="9">
         <v>46225.6055390625</v>
@@ -6770,16 +6786,16 @@
         <v>46225.61577960648</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I93" s="10"/>
       <c r="J93" s="9">
@@ -6795,13 +6811,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O93" s="10" t="s">
         <v>60</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -6811,7 +6827,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B94" s="5">
         <v>46225.605553333335</v>
@@ -6821,16 +6837,16 @@
         <v>46225.61577443287</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I94" s="6"/>
       <c r="J94" s="5">
@@ -6846,13 +6862,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O94" s="6" t="s">
         <v>64</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -6862,7 +6878,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B95" s="9">
         <v>46225.581494178245</v>
@@ -6872,16 +6888,16 @@
         <v>46225.61592174768</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I95" s="10"/>
       <c r="J95" s="9">
@@ -6897,10 +6913,10 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P95" s="10" t="s">
         <v>26</v>
@@ -6923,7 +6939,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B96" s="5">
         <v>46225.5814984375</v>
@@ -6933,16 +6949,16 @@
         <v>46225.615894421295</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I96" s="5">
         <v>46302</v>
@@ -6960,13 +6976,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -6976,7 +6992,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B97" s="9">
         <v>46225.58150320602</v>
@@ -6986,16 +7002,16 @@
         <v>46225.61589104167</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I97" s="9">
         <v>46302</v>
@@ -7013,13 +7029,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7029,7 +7045,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B98" s="5">
         <v>46225.60673211806</v>
@@ -7039,16 +7055,16 @@
         <v>46225.615888125</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I98" s="5">
         <v>46302</v>
@@ -7066,13 +7082,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7082,7 +7098,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B99" s="9">
         <v>46225.60674163194</v>
@@ -7092,16 +7108,16 @@
         <v>46225.61588293982</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I99" s="9">
         <v>46302</v>
@@ -7119,13 +7135,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7135,7 +7151,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B100" s="5">
         <v>46225.58150777778</v>
@@ -7145,16 +7161,16 @@
         <v>46225.61603868056</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I100" s="5">
         <v>46303</v>
@@ -7172,13 +7188,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q100" s="5">
         <v>46303</v>
@@ -7198,7 +7214,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B101" s="9">
         <v>46225.58151239583</v>
@@ -7208,16 +7224,16 @@
         <v>46225.61600570602</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I101" s="10"/>
       <c r="J101" s="9">
@@ -7233,13 +7249,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7249,7 +7265,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B102" s="5">
         <v>46225.58151694444</v>
@@ -7259,16 +7275,16 @@
         <v>46225.61600274306</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I102" s="6"/>
       <c r="J102" s="5">
@@ -7284,13 +7300,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7300,7 +7316,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B103" s="9">
         <v>46225.606768564816</v>
@@ -7310,16 +7326,16 @@
         <v>46225.615999965274</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I103" s="9">
         <v>46303</v>
@@ -7337,13 +7353,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7353,7 +7369,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B104" s="5">
         <v>46225.606777395835</v>
@@ -7363,16 +7379,16 @@
         <v>46225.61599523148</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I104" s="5">
         <v>46303</v>
@@ -7390,13 +7406,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7406,7 +7422,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B105" s="9">
         <v>46225.581521562504</v>
@@ -7416,16 +7432,16 @@
         <v>46225.61624585648</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I105" s="9">
         <v>46304</v>
@@ -7443,13 +7459,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q105" s="9">
         <v>46304</v>
@@ -7469,7 +7485,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B106" s="5">
         <v>46225.58152704861</v>
@@ -7479,16 +7495,16 @@
         <v>46225.61621090278</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I106" s="6"/>
       <c r="J106" s="5">
@@ -7504,13 +7520,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7520,7 +7536,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B107" s="9">
         <v>46225.58153157408</v>
@@ -7530,16 +7546,16 @@
         <v>46225.61620709491</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I107" s="10"/>
       <c r="J107" s="9">
@@ -7555,13 +7571,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q107" s="10"/>
       <c r="R107" s="10"/>
@@ -7571,7 +7587,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B108" s="5">
         <v>46225.60680554398</v>
@@ -7581,16 +7597,16 @@
         <v>46225.616203564816</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I108" s="5">
         <v>46304</v>
@@ -7608,10 +7624,10 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P108" s="6" t="s">
         <v>26</v>
@@ -7624,7 +7640,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B109" s="9">
         <v>46225.60681763889</v>
@@ -7634,16 +7650,16 @@
         <v>46225.61619854167</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I109" s="9">
         <v>46304</v>
@@ -7661,10 +7677,10 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P109" s="10" t="s">
         <v>26</v>
@@ -7677,7 +7693,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B110" s="5">
         <v>46225.58153574074</v>
@@ -7687,7 +7703,7 @@
         <v>46225.60402078704</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>25</v>
@@ -7711,7 +7727,7 @@
         <v>26</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>26</v>
@@ -7724,7 +7740,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B111" s="9">
         <v>46225.58153866898</v>
@@ -7734,16 +7750,16 @@
         <v>46225.61649424769</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H111" s="10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="I111" s="9">
         <v>46307</v>
@@ -7761,13 +7777,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q111" s="9">
         <v>46311</v>
@@ -7787,7 +7803,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B112" s="5">
         <v>46225.58154590278</v>
@@ -7797,7 +7813,7 @@
         <v>46225.61639241898</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -7824,13 +7840,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q112" s="5">
         <v>46311</v>
@@ -7850,7 +7866,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B113" s="9">
         <v>46225.59432256944</v>
@@ -7860,7 +7876,7 @@
         <v>46225.6052183912</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>25</v>
@@ -7884,7 +7900,7 @@
         <v>26</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="P113" s="10" t="s">
         <v>26</v>
@@ -7897,7 +7913,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B114" s="5">
         <v>46225.59476561342</v>
@@ -7907,7 +7923,7 @@
         <v>46225.616553796295</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -7934,13 +7950,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q114" s="5">
         <v>46318</v>
@@ -7960,7 +7976,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B115" s="9">
         <v>46225.59487494213</v>
@@ -7970,7 +7986,7 @@
         <v>46225.61655020833</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
@@ -7997,13 +8013,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q115" s="9">
         <v>46325</v>

--- a/data/50001580- CIA. RIO MINERALES.xlsx
+++ b/data/50001580- CIA. RIO MINERALES.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1348" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1348" uniqueCount="336">
   <si>
     <t>50001580- "CIA. RIO MINERALES"</t>
   </si>
@@ -263,6 +263,9 @@
     <t>Ingenieria Jefe de proyecto:,Plano Preliminar OT4378</t>
   </si>
   <si>
+    <t>Alta</t>
+  </si>
+  <si>
     <t>1216769310026532</t>
   </si>
   <si>
@@ -546,6 +549,9 @@
   </si>
   <si>
     <t>Ingenieria y diseñoo:,Plano Definitivos OT4378</t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1216788235072362</t>
@@ -2040,7 +2046,7 @@
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46226.571272939815</v>
+        <v>46230.17415309028</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -2327,7 +2333,7 @@
         <v>46226.576076365745</v>
       </c>
       <c r="D15" s="9">
-        <v>46226.57609552083</v>
+        <v>46228.19449930555</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>67</v>
@@ -2371,8 +2377,8 @@
       <c r="R15" s="9">
         <v>46226</v>
       </c>
-      <c r="S15" s="7" t="s">
-        <v>33</v>
+      <c r="S15" s="12" t="s">
+        <v>71</v>
       </c>
       <c r="T15" s="10">
         <v>1</v>
@@ -2383,7 +2389,7 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B16" s="5">
         <v>46225.580861423616</v>
@@ -2393,7 +2399,7 @@
         <v>46225.59611458333</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>25</v>
@@ -2417,7 +2423,7 @@
         <v>26</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="P16" s="6" t="s">
         <v>26</v>
@@ -2430,26 +2436,26 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B17" s="9">
         <v>46225.580958923616</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="9">
-        <v>46226.57127291667</v>
+        <v>46228.19449648148</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I17" s="9">
         <v>46226</v>
@@ -2467,13 +2473,13 @@
         <v>26</v>
       </c>
       <c r="N17" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O17" s="10" t="s">
         <v>38</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q17" s="9">
         <v>46227</v>
@@ -2481,8 +2487,8 @@
       <c r="R17" s="9">
         <v>46226</v>
       </c>
-      <c r="S17" s="7" t="s">
-        <v>33</v>
+      <c r="S17" s="12" t="s">
+        <v>71</v>
       </c>
       <c r="T17" s="10">
         <v>0</v>
@@ -2493,26 +2499,26 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B18" s="5">
         <v>46225.58096494213</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46226.57127292824</v>
+        <v>46228.19450158565</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I18" s="5">
         <v>46226</v>
@@ -2530,13 +2536,13 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O18" s="6" t="s">
         <v>38</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q18" s="5">
         <v>46227</v>
@@ -2544,8 +2550,8 @@
       <c r="R18" s="5">
         <v>46226</v>
       </c>
-      <c r="S18" s="7" t="s">
-        <v>33</v>
+      <c r="S18" s="12" t="s">
+        <v>71</v>
       </c>
       <c r="T18" s="6">
         <v>0</v>
@@ -2556,26 +2562,26 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B19" s="9">
         <v>46225.58097109954</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46226.571272870366</v>
+        <v>46228.19449678241</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I19" s="9">
         <v>46226</v>
@@ -2593,13 +2599,13 @@
         <v>26</v>
       </c>
       <c r="N19" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O19" s="10" t="s">
         <v>38</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q19" s="9">
         <v>46227</v>
@@ -2607,8 +2613,8 @@
       <c r="R19" s="9">
         <v>46226</v>
       </c>
-      <c r="S19" s="7" t="s">
-        <v>33</v>
+      <c r="S19" s="12" t="s">
+        <v>71</v>
       </c>
       <c r="T19" s="10">
         <v>0</v>
@@ -2619,7 +2625,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B20" s="5">
         <v>46225.58086628473</v>
@@ -2629,7 +2635,7 @@
         <v>46225.59619578704</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>25</v>
@@ -2653,7 +2659,7 @@
         <v>26</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P20" s="6" t="s">
         <v>26</v>
@@ -2666,7 +2672,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B21" s="9">
         <v>46225.580978240745</v>
@@ -2676,16 +2682,16 @@
         <v>46225.61247136574</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I21" s="9">
         <v>46245</v>
@@ -2703,13 +2709,13 @@
         <v>26</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q21" s="9">
         <v>46246</v>
@@ -2729,7 +2735,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B22" s="5">
         <v>46225.5809840625</v>
@@ -2739,16 +2745,16 @@
         <v>46225.612467824074</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I22" s="5">
         <v>46245</v>
@@ -2766,13 +2772,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q22" s="5">
         <v>46246</v>
@@ -2792,7 +2798,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B23" s="9">
         <v>46225.58098827546</v>
@@ -2802,16 +2808,16 @@
         <v>46225.612464756945</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I23" s="9">
         <v>46245</v>
@@ -2829,13 +2835,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q23" s="9">
         <v>46246</v>
@@ -2855,7 +2861,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B24" s="5">
         <v>46225.58100011574</v>
@@ -2865,16 +2871,16 @@
         <v>46225.61246184028</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I24" s="5">
         <v>46245</v>
@@ -2892,13 +2898,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q24" s="5">
         <v>46246</v>
@@ -2918,7 +2924,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B25" s="9">
         <v>46225.59619364583</v>
@@ -2928,16 +2934,16 @@
         <v>46225.61245637732</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I25" s="9">
         <v>46231</v>
@@ -2955,13 +2961,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O25" s="10" t="s">
         <v>48</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q25" s="9">
         <v>46232</v>
@@ -2981,7 +2987,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B26" s="5">
         <v>46225.58087085648</v>
@@ -2991,7 +2997,7 @@
         <v>46225.596821886575</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>25</v>
@@ -3015,7 +3021,7 @@
         <v>26</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P26" s="6" t="s">
         <v>26</v>
@@ -3028,7 +3034,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B27" s="9">
         <v>46225.58100560185</v>
@@ -3038,16 +3044,16 @@
         <v>46225.61255763889</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I27" s="9">
         <v>46247</v>
@@ -3065,13 +3071,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q27" s="9">
         <v>46259</v>
@@ -3091,7 +3097,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B28" s="5">
         <v>46225.58101144676</v>
@@ -3101,16 +3107,16 @@
         <v>46225.61262662037</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I28" s="5">
         <v>46247</v>
@@ -3128,13 +3134,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3150,7 +3156,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B29" s="9">
         <v>46225.581017233795</v>
@@ -3160,16 +3166,16 @@
         <v>46225.61262351852</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I29" s="9">
         <v>46251</v>
@@ -3187,13 +3193,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
@@ -3209,7 +3215,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B30" s="5">
         <v>46225.58102277778</v>
@@ -3219,16 +3225,16 @@
         <v>46225.61255446759</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I30" s="5">
         <v>46247</v>
@@ -3246,10 +3252,10 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P30" s="6" t="s">
         <v>26</v>
@@ -3272,7 +3278,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B31" s="9">
         <v>46225.58102737268</v>
@@ -3282,16 +3288,16 @@
         <v>46225.61269579861</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I31" s="9">
         <v>46247</v>
@@ -3309,13 +3315,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3325,7 +3331,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B32" s="5">
         <v>46225.581032222224</v>
@@ -3335,16 +3341,16 @@
         <v>46225.612692442126</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I32" s="5">
         <v>46251</v>
@@ -3362,13 +3368,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3378,7 +3384,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B33" s="9">
         <v>46225.581037199074</v>
@@ -3388,16 +3394,16 @@
         <v>46225.61279568287</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I33" s="9">
         <v>46247</v>
@@ -3415,10 +3421,10 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P33" s="10" t="s">
         <v>26</v>
@@ -3441,7 +3447,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B34" s="5">
         <v>46225.58104158565</v>
@@ -3451,16 +3457,16 @@
         <v>46225.61298453704</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I34" s="5">
         <v>46247</v>
@@ -3478,13 +3484,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3494,7 +3500,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B35" s="9">
         <v>46225.5810464699</v>
@@ -3504,16 +3510,16 @@
         <v>46225.61298125</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I35" s="9">
         <v>46251</v>
@@ -3531,13 +3537,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -3547,7 +3553,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B36" s="5">
         <v>46225.58105121528</v>
@@ -3557,16 +3563,16 @@
         <v>46225.61316422454</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I36" s="5">
         <v>46247</v>
@@ -3584,10 +3590,10 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3610,7 +3616,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B37" s="9">
         <v>46225.58109630787</v>
@@ -3620,16 +3626,16 @@
         <v>46225.613052245375</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I37" s="9">
         <v>46247</v>
@@ -3647,13 +3653,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3663,7 +3669,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B38" s="5">
         <v>46225.58110178241</v>
@@ -3673,16 +3679,16 @@
         <v>46225.613047719904</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I38" s="5">
         <v>46258</v>
@@ -3700,13 +3706,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3716,7 +3722,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B39" s="9">
         <v>46225.58110600694</v>
@@ -3726,16 +3732,16 @@
         <v>46225.613129363424</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I39" s="9">
         <v>46289</v>
@@ -3753,13 +3759,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
@@ -3769,7 +3775,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B40" s="5">
         <v>46225.59682005787</v>
@@ -3779,16 +3785,16 @@
         <v>46225.6133383912</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I40" s="5">
         <v>46233</v>
@@ -3806,10 +3812,10 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>26</v>
@@ -3832,7 +3838,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B41" s="9">
         <v>46225.59686481481</v>
@@ -3842,16 +3848,16 @@
         <v>46225.613313634254</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I41" s="9">
         <v>46233</v>
@@ -3869,13 +3875,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -3885,7 +3891,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B42" s="5">
         <v>46225.59692966435</v>
@@ -3895,16 +3901,16 @@
         <v>46225.613310636574</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I42" s="5">
         <v>46244</v>
@@ -3922,13 +3928,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -3938,7 +3944,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B43" s="9">
         <v>46225.58111748843</v>
@@ -3948,7 +3954,7 @@
         <v>46225.589328946764</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>25</v>
@@ -3972,7 +3978,7 @@
         <v>26</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -3985,26 +3991,26 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B44" s="5">
         <v>46225.58112127315</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46226.57609570602</v>
+        <v>46227.178273171296</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I44" s="5">
         <v>46230</v>
@@ -4022,13 +4028,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>67</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q44" s="5">
         <v>46234</v>
@@ -4036,8 +4042,8 @@
       <c r="R44" s="5">
         <v>46230</v>
       </c>
-      <c r="S44" s="7" t="s">
-        <v>33</v>
+      <c r="S44" s="11" t="s">
+        <v>167</v>
       </c>
       <c r="T44" s="6">
         <v>0</v>
@@ -4048,7 +4054,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B45" s="9">
         <v>46225.58112643519</v>
@@ -4058,16 +4064,16 @@
         <v>46225.613428275465</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I45" s="9">
         <v>46237</v>
@@ -4085,13 +4091,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q45" s="9">
         <v>46241</v>
@@ -4111,7 +4117,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B46" s="5">
         <v>46225.58113097222</v>
@@ -4121,16 +4127,16 @@
         <v>46225.61342412037</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I46" s="5">
         <v>46244</v>
@@ -4148,13 +4154,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q46" s="5">
         <v>46244</v>
@@ -4174,7 +4180,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B47" s="9">
         <v>46225.58114445602</v>
@@ -4184,16 +4190,16 @@
         <v>46225.61347256944</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="I47" s="9">
         <v>46290</v>
@@ -4211,13 +4217,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q47" s="9">
         <v>46290</v>
@@ -4237,7 +4243,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B48" s="5">
         <v>46225.58114871528</v>
@@ -4247,16 +4253,16 @@
         <v>46225.61551950232</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="I48" s="5">
         <v>46290</v>
@@ -4274,13 +4280,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4290,7 +4296,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B49" s="9">
         <v>46225.58115283565</v>
@@ -4300,16 +4306,16 @@
         <v>46225.615519513885</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="I49" s="9">
         <v>46290</v>
@@ -4327,13 +4333,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q49" s="10"/>
       <c r="R49" s="10"/>
@@ -4343,7 +4349,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B50" s="5">
         <v>46225.581171631944</v>
@@ -4353,7 +4359,7 @@
         <v>46225.59181146991</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>25</v>
@@ -4377,7 +4383,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4390,7 +4396,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B51" s="9">
         <v>46225.58117489584</v>
@@ -4400,16 +4406,16 @@
         <v>46225.61367097222</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="I51" s="9">
         <v>46260</v>
@@ -4427,13 +4433,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q51" s="9">
         <v>46260</v>
@@ -4453,7 +4459,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B52" s="5">
         <v>46225.58118028935</v>
@@ -4463,16 +4469,16 @@
         <v>46225.613667349535</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="I52" s="5">
         <v>46260</v>
@@ -4490,13 +4496,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q52" s="5">
         <v>46260</v>
@@ -4516,7 +4522,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B53" s="9">
         <v>46225.58118576389</v>
@@ -4526,16 +4532,16 @@
         <v>46225.61366387732</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="I53" s="9">
         <v>46260</v>
@@ -4553,13 +4559,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q53" s="9">
         <v>46260</v>
@@ -4579,7 +4585,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B54" s="5">
         <v>46225.58119107639</v>
@@ -4589,16 +4595,16 @@
         <v>46225.61417395833</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I54" s="5">
         <v>46261</v>
@@ -4616,13 +4622,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q54" s="5">
         <v>46261</v>
@@ -4642,7 +4648,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B55" s="9">
         <v>46225.58119642361</v>
@@ -4652,16 +4658,16 @@
         <v>46225.61417104167</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I55" s="9">
         <v>46261</v>
@@ -4679,13 +4685,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q55" s="9">
         <v>46261</v>
@@ -4705,7 +4711,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B56" s="5">
         <v>46225.581201678244</v>
@@ -4715,16 +4721,16 @@
         <v>46225.61416773148</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I56" s="5">
         <v>46261</v>
@@ -4742,13 +4748,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q56" s="5">
         <v>46261</v>
@@ -4768,7 +4774,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B57" s="9">
         <v>46225.58120702546</v>
@@ -4778,7 +4784,7 @@
         <v>46225.59190644676</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>25</v>
@@ -4802,7 +4808,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="P57" s="10" t="s">
         <v>26</v>
@@ -4815,7 +4821,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B58" s="5">
         <v>46225.58121010417</v>
@@ -4825,16 +4831,16 @@
         <v>46225.6142333912</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I58" s="5">
         <v>46262</v>
@@ -4852,13 +4858,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q58" s="5">
         <v>46266</v>
@@ -4878,7 +4884,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B59" s="9">
         <v>46225.581215474536</v>
@@ -4888,16 +4894,16 @@
         <v>46225.61435628472</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I59" s="9">
         <v>46267</v>
@@ -4915,13 +4921,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q59" s="9">
         <v>46273</v>
@@ -4941,7 +4947,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B60" s="5">
         <v>46225.581219618056</v>
@@ -4951,16 +4957,16 @@
         <v>46225.614318611115</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I60" s="5">
         <v>46267</v>
@@ -4978,13 +4984,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -4994,7 +5000,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B61" s="9">
         <v>46225.58123596065</v>
@@ -5004,16 +5010,16 @@
         <v>46225.61431550926</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I61" s="9">
         <v>46267</v>
@@ -5031,13 +5037,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q61" s="10"/>
       <c r="R61" s="10"/>
@@ -5047,7 +5053,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B62" s="5">
         <v>46225.58129219907</v>
@@ -5057,16 +5063,16 @@
         <v>46225.61447392361</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I62" s="5">
         <v>46274</v>
@@ -5084,13 +5090,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q62" s="5">
         <v>46274</v>
@@ -5110,7 +5116,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B63" s="9">
         <v>46225.58129802083</v>
@@ -5120,16 +5126,16 @@
         <v>46225.61443357639</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I63" s="10"/>
       <c r="J63" s="9">
@@ -5145,13 +5151,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5161,7 +5167,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B64" s="5">
         <v>46225.581304374995</v>
@@ -5171,16 +5177,16 @@
         <v>46225.61443052083</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I64" s="6"/>
       <c r="J64" s="5">
@@ -5196,13 +5202,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5212,7 +5218,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B65" s="9">
         <v>46225.58131015046</v>
@@ -5222,7 +5228,7 @@
         <v>46225.59759329861</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>25</v>
@@ -5246,7 +5252,7 @@
         <v>26</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="P65" s="10" t="s">
         <v>26</v>
@@ -5259,7 +5265,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B66" s="5">
         <v>46225.58131376158</v>
@@ -5269,16 +5275,16 @@
         <v>46225.61459215278</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="I66" s="5">
         <v>46230</v>
@@ -5296,13 +5302,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q66" s="5">
         <v>46231</v>
@@ -5322,7 +5328,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B67" s="9">
         <v>46225.58131929398</v>
@@ -5332,16 +5338,16 @@
         <v>46225.61459149305</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="I67" s="9">
         <v>46230</v>
@@ -5359,13 +5365,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q67" s="9">
         <v>46231</v>
@@ -5385,7 +5391,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B68" s="5">
         <v>46225.58132505787</v>
@@ -5395,16 +5401,16 @@
         <v>46225.61459082176</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="I68" s="5">
         <v>46230</v>
@@ -5422,13 +5428,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q68" s="5">
         <v>46231</v>
@@ -5448,7 +5454,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B69" s="9">
         <v>46225.597591134254</v>
@@ -5464,10 +5470,10 @@
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="I69" s="9">
         <v>46293</v>
@@ -5485,10 +5491,10 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P69" s="10" t="s">
         <v>57</v>
@@ -5511,7 +5517,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B70" s="5">
         <v>46225.58133054398</v>
@@ -5521,7 +5527,7 @@
         <v>46225.59299179398</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>25</v>
@@ -5545,7 +5551,7 @@
         <v>26</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -5558,7 +5564,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B71" s="9">
         <v>46225.58133395833</v>
@@ -5568,16 +5574,16 @@
         <v>46225.614863599534</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I71" s="9">
         <v>46275</v>
@@ -5595,13 +5601,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q71" s="9">
         <v>46281</v>
@@ -5621,7 +5627,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B72" s="5">
         <v>46225.58133853009</v>
@@ -5631,16 +5637,16 @@
         <v>46225.61483068287</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I72" s="5">
         <v>46275</v>
@@ -5658,13 +5664,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5674,7 +5680,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B73" s="9">
         <v>46225.58134314815</v>
@@ -5684,16 +5690,16 @@
         <v>46225.61482673611</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I73" s="9">
         <v>46275</v>
@@ -5711,13 +5717,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -5727,7 +5733,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B74" s="5">
         <v>46225.58134744213</v>
@@ -5737,16 +5743,16 @@
         <v>46225.61499751157</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I74" s="5">
         <v>46286</v>
@@ -5764,13 +5770,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q74" s="5">
         <v>46286</v>
@@ -5790,7 +5796,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B75" s="9">
         <v>46225.581351932866</v>
@@ -5800,16 +5806,16 @@
         <v>46225.61504185185</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I75" s="9">
         <v>46286</v>
@@ -5827,13 +5833,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -5843,7 +5849,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B76" s="5">
         <v>46225.58135922454</v>
@@ -5853,16 +5859,16 @@
         <v>46225.615038819444</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I76" s="5">
         <v>46286</v>
@@ -5880,13 +5886,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -5896,7 +5902,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B77" s="9">
         <v>46225.5813728588</v>
@@ -5906,16 +5912,16 @@
         <v>46225.61522760417</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I77" s="9">
         <v>46287</v>
@@ -5933,13 +5939,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q77" s="9">
         <v>46287</v>
@@ -5959,7 +5965,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B78" s="5">
         <v>46225.58137722222</v>
@@ -5969,16 +5975,16 @@
         <v>46225.61518142361</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I78" s="6"/>
       <c r="J78" s="5">
@@ -5994,13 +6000,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6010,7 +6016,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B79" s="9">
         <v>46225.58138231482</v>
@@ -6020,16 +6026,16 @@
         <v>46225.615182291665</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I79" s="10"/>
       <c r="J79" s="9">
@@ -6045,13 +6051,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6061,7 +6067,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B80" s="5">
         <v>46225.58138733797</v>
@@ -6071,16 +6077,16 @@
         <v>46225.61538164352</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I80" s="5">
         <v>46288</v>
@@ -6098,13 +6104,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q80" s="5">
         <v>46288</v>
@@ -6124,7 +6130,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B81" s="9">
         <v>46225.58139180556</v>
@@ -6134,16 +6140,16 @@
         <v>46225.61534716435</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I81" s="9">
         <v>46288</v>
@@ -6161,13 +6167,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6177,7 +6183,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B82" s="5">
         <v>46225.58139752314</v>
@@ -6187,16 +6193,16 @@
         <v>46225.615343854166</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I82" s="5">
         <v>46288</v>
@@ -6214,13 +6220,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6230,7 +6236,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B83" s="9">
         <v>46225.58140275463</v>
@@ -6240,16 +6246,16 @@
         <v>46225.61555996528</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I83" s="9">
         <v>46289</v>
@@ -6267,13 +6273,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q83" s="9">
         <v>46289</v>
@@ -6293,7 +6299,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B84" s="5">
         <v>46225.581407488426</v>
@@ -6303,16 +6309,16 @@
         <v>46225.61551967592</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I84" s="6"/>
       <c r="J84" s="5">
@@ -6328,13 +6334,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6344,7 +6350,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B85" s="9">
         <v>46225.581414988425</v>
@@ -6354,16 +6360,16 @@
         <v>46225.61552056713</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I85" s="10"/>
       <c r="J85" s="9">
@@ -6379,13 +6385,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6395,7 +6401,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B86" s="5">
         <v>46225.58145953703</v>
@@ -6405,7 +6411,7 @@
         <v>46225.61568145834</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6430,13 +6436,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q86" s="5">
         <v>46293</v>
@@ -6456,7 +6462,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B87" s="9">
         <v>46225.58146568287</v>
@@ -6466,16 +6472,16 @@
         <v>46225.61568175926</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I87" s="9">
         <v>46293</v>
@@ -6493,13 +6499,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6509,7 +6515,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B88" s="5">
         <v>46225.58147099537</v>
@@ -6519,16 +6525,16 @@
         <v>46225.615682592594</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I88" s="5">
         <v>46293</v>
@@ -6546,13 +6552,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6562,7 +6568,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B89" s="9">
         <v>46225.58147606481</v>
@@ -6572,7 +6578,7 @@
         <v>46225.60367008102</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>25</v>
@@ -6596,7 +6602,7 @@
         <v>26</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="P89" s="10" t="s">
         <v>26</v>
@@ -6609,7 +6615,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B90" s="5">
         <v>46225.58147990741</v>
@@ -6619,16 +6625,16 @@
         <v>46225.615814467594</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="I90" s="5">
         <v>46301</v>
@@ -6646,13 +6652,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q90" s="5">
         <v>46301</v>
@@ -6672,7 +6678,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B91" s="9">
         <v>46225.58148496528</v>
@@ -6682,16 +6688,16 @@
         <v>46225.61578579861</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="I91" s="10"/>
       <c r="J91" s="9">
@@ -6707,13 +6713,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -6723,7 +6729,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B92" s="5">
         <v>46225.58148953704</v>
@@ -6733,16 +6739,16 @@
         <v>46225.61578274306</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="I92" s="5">
         <v>46301</v>
@@ -6760,13 +6766,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6776,7 +6782,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B93" s="9">
         <v>46225.6055390625</v>
@@ -6786,16 +6792,16 @@
         <v>46225.61577960648</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="I93" s="10"/>
       <c r="J93" s="9">
@@ -6811,13 +6817,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="O93" s="10" t="s">
         <v>60</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -6827,7 +6833,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B94" s="5">
         <v>46225.605553333335</v>
@@ -6837,16 +6843,16 @@
         <v>46225.61577443287</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="I94" s="6"/>
       <c r="J94" s="5">
@@ -6862,13 +6868,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="O94" s="6" t="s">
         <v>64</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -6878,7 +6884,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B95" s="9">
         <v>46225.581494178245</v>
@@ -6888,16 +6894,16 @@
         <v>46225.61592174768</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I95" s="10"/>
       <c r="J95" s="9">
@@ -6913,10 +6919,10 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="P95" s="10" t="s">
         <v>26</v>
@@ -6939,7 +6945,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B96" s="5">
         <v>46225.5814984375</v>
@@ -6949,16 +6955,16 @@
         <v>46225.615894421295</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I96" s="5">
         <v>46302</v>
@@ -6976,13 +6982,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -6992,7 +6998,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B97" s="9">
         <v>46225.58150320602</v>
@@ -7002,16 +7008,16 @@
         <v>46225.61589104167</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I97" s="9">
         <v>46302</v>
@@ -7029,13 +7035,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7045,7 +7051,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B98" s="5">
         <v>46225.60673211806</v>
@@ -7055,16 +7061,16 @@
         <v>46225.615888125</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I98" s="5">
         <v>46302</v>
@@ -7082,13 +7088,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7098,7 +7104,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B99" s="9">
         <v>46225.60674163194</v>
@@ -7108,16 +7114,16 @@
         <v>46225.61588293982</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I99" s="9">
         <v>46302</v>
@@ -7135,13 +7141,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7151,7 +7157,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B100" s="5">
         <v>46225.58150777778</v>
@@ -7161,16 +7167,16 @@
         <v>46225.61603868056</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I100" s="5">
         <v>46303</v>
@@ -7188,13 +7194,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q100" s="5">
         <v>46303</v>
@@ -7214,7 +7220,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B101" s="9">
         <v>46225.58151239583</v>
@@ -7224,16 +7230,16 @@
         <v>46225.61600570602</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I101" s="10"/>
       <c r="J101" s="9">
@@ -7249,13 +7255,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7265,7 +7271,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B102" s="5">
         <v>46225.58151694444</v>
@@ -7275,16 +7281,16 @@
         <v>46225.61600274306</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I102" s="6"/>
       <c r="J102" s="5">
@@ -7300,13 +7306,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7316,7 +7322,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B103" s="9">
         <v>46225.606768564816</v>
@@ -7326,16 +7332,16 @@
         <v>46225.615999965274</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I103" s="9">
         <v>46303</v>
@@ -7353,13 +7359,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7369,7 +7375,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B104" s="5">
         <v>46225.606777395835</v>
@@ -7379,16 +7385,16 @@
         <v>46225.61599523148</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I104" s="5">
         <v>46303</v>
@@ -7406,13 +7412,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7422,7 +7428,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B105" s="9">
         <v>46225.581521562504</v>
@@ -7432,16 +7438,16 @@
         <v>46225.61624585648</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I105" s="9">
         <v>46304</v>
@@ -7459,13 +7465,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q105" s="9">
         <v>46304</v>
@@ -7485,7 +7491,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B106" s="5">
         <v>46225.58152704861</v>
@@ -7495,16 +7501,16 @@
         <v>46225.61621090278</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I106" s="6"/>
       <c r="J106" s="5">
@@ -7520,13 +7526,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7536,7 +7542,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B107" s="9">
         <v>46225.58153157408</v>
@@ -7546,16 +7552,16 @@
         <v>46225.61620709491</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I107" s="10"/>
       <c r="J107" s="9">
@@ -7571,13 +7577,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q107" s="10"/>
       <c r="R107" s="10"/>
@@ -7587,7 +7593,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B108" s="5">
         <v>46225.60680554398</v>
@@ -7597,16 +7603,16 @@
         <v>46225.616203564816</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I108" s="5">
         <v>46304</v>
@@ -7624,10 +7630,10 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="P108" s="6" t="s">
         <v>26</v>
@@ -7640,7 +7646,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B109" s="9">
         <v>46225.60681763889</v>
@@ -7650,16 +7656,16 @@
         <v>46225.61619854167</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I109" s="9">
         <v>46304</v>
@@ -7677,10 +7683,10 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="P109" s="10" t="s">
         <v>26</v>
@@ -7693,7 +7699,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B110" s="5">
         <v>46225.58153574074</v>
@@ -7703,7 +7709,7 @@
         <v>46225.60402078704</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>25</v>
@@ -7727,7 +7733,7 @@
         <v>26</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>26</v>
@@ -7740,7 +7746,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B111" s="9">
         <v>46225.58153866898</v>
@@ -7750,16 +7756,16 @@
         <v>46225.61649424769</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="H111" s="10" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="I111" s="9">
         <v>46307</v>
@@ -7777,13 +7783,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q111" s="9">
         <v>46311</v>
@@ -7803,7 +7809,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B112" s="5">
         <v>46225.58154590278</v>
@@ -7813,7 +7819,7 @@
         <v>46225.61639241898</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -7840,13 +7846,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q112" s="5">
         <v>46311</v>
@@ -7866,7 +7872,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B113" s="9">
         <v>46225.59432256944</v>
@@ -7876,7 +7882,7 @@
         <v>46225.6052183912</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>25</v>
@@ -7900,7 +7906,7 @@
         <v>26</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="P113" s="10" t="s">
         <v>26</v>
@@ -7913,7 +7919,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B114" s="5">
         <v>46225.59476561342</v>
@@ -7923,7 +7929,7 @@
         <v>46225.616553796295</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -7950,13 +7956,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q114" s="5">
         <v>46318</v>
@@ -7976,7 +7982,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B115" s="9">
         <v>46225.59487494213</v>
@@ -7986,7 +7992,7 @@
         <v>46225.61655020833</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
@@ -8013,13 +8019,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q115" s="9">
         <v>46325</v>

--- a/data/50001580- CIA. RIO MINERALES.xlsx
+++ b/data/50001580- CIA. RIO MINERALES.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1348" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1349" uniqueCount="336">
   <si>
     <t>50001580- "CIA. RIO MINERALES"</t>
   </si>
@@ -6408,7 +6408,7 @@
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46225.61568145834</v>
+        <v>46230.71234510417</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>273</v>
@@ -6417,9 +6417,11 @@
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H86" s="6"/>
+        <v>77</v>
+      </c>
+      <c r="H86" s="6" t="s">
+        <v>78</v>
+      </c>
       <c r="I86" s="5">
         <v>46293</v>
       </c>

--- a/data/50001580- CIA. RIO MINERALES.xlsx
+++ b/data/50001580- CIA. RIO MINERALES.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1349" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1349" uniqueCount="338">
   <si>
     <t>50001580- "CIA. RIO MINERALES"</t>
   </si>
@@ -201,6 +201,9 @@
     <t>Servicios,Propuesta Tableros ot 4379</t>
   </si>
   <si>
+    <t>Alta</t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
   </si>
   <si>
@@ -263,9 +266,6 @@
     <t>Ingenieria Jefe de proyecto:,Plano Preliminar OT4378</t>
   </si>
   <si>
-    <t>Alta</t>
-  </si>
-  <si>
     <t>1216769310026532</t>
   </si>
   <si>
@@ -558,6 +558,12 @@
   </si>
   <si>
     <t>Plano Definitivos OT4378</t>
+  </si>
+  <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
   </si>
   <si>
     <t>Ingenieria y diseñoo:,Check Planos OT4378</t>
@@ -1124,12 +1130,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFeec300"/>
+        <fgColor rgb="FFe8384f"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFe8384f"/>
+        <fgColor rgb="FFeec300"/>
       </patternFill>
     </fill>
   </fills>
@@ -2046,7 +2052,7 @@
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46230.17415309028</v>
+        <v>46231.20725755787</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -2090,19 +2096,19 @@
       <c r="R10" s="5">
         <v>46226</v>
       </c>
-      <c r="S10" s="7" t="s">
-        <v>33</v>
+      <c r="S10" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="T10" s="6">
         <v>0</v>
       </c>
-      <c r="U10" s="11" t="s">
-        <v>52</v>
+      <c r="U10" s="12" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B11" s="9">
         <v>46225.58274704861</v>
@@ -2112,16 +2118,16 @@
         <v>46225.61217166667</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I11" s="9">
         <v>46294</v>
@@ -2142,7 +2148,7 @@
         <v>45</v>
       </c>
       <c r="O11" s="10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P11" s="10" t="s">
         <v>45</v>
@@ -2159,13 +2165,13 @@
       <c r="T11" s="10">
         <v>0</v>
       </c>
-      <c r="U11" s="12" t="s">
-        <v>58</v>
+      <c r="U11" s="11" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B12" s="5">
         <v>46225.59567834491</v>
@@ -2175,16 +2181,16 @@
         <v>46225.612248819445</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I12" s="5">
         <v>46294</v>
@@ -2202,13 +2208,13 @@
         <v>26</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Q12" s="6"/>
       <c r="R12" s="6"/>
@@ -2218,7 +2224,7 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B13" s="9">
         <v>46225.595835520835</v>
@@ -2228,16 +2234,16 @@
         <v>46225.61224515046</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I13" s="9">
         <v>46294</v>
@@ -2255,13 +2261,13 @@
         <v>26</v>
       </c>
       <c r="N13" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="O13" s="10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="P13" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Q13" s="10"/>
       <c r="R13" s="10"/>
@@ -2271,7 +2277,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B14" s="5">
         <v>46225.58085679398</v>
@@ -2283,7 +2289,7 @@
         <v>46226.576112442126</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>25</v>
@@ -2307,7 +2313,7 @@
         <v>26</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P14" s="6" t="s">
         <v>26</v>
@@ -2324,7 +2330,7 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B15" s="9">
         <v>46225.58095215278</v>
@@ -2336,7 +2342,7 @@
         <v>46228.19449930555</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>26</v>
@@ -2357,19 +2363,19 @@
         <v>26</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M15" s="10" t="s">
         <v>26</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O15" s="10" t="s">
         <v>38</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Q15" s="9">
         <v>46227</v>
@@ -2377,8 +2383,8 @@
       <c r="R15" s="9">
         <v>46226</v>
       </c>
-      <c r="S15" s="12" t="s">
-        <v>71</v>
+      <c r="S15" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="T15" s="10">
         <v>1</v>
@@ -2487,14 +2493,14 @@
       <c r="R17" s="9">
         <v>46226</v>
       </c>
-      <c r="S17" s="12" t="s">
-        <v>71</v>
+      <c r="S17" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="T17" s="10">
         <v>0</v>
       </c>
-      <c r="U17" s="11" t="s">
-        <v>52</v>
+      <c r="U17" s="12" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
@@ -2550,14 +2556,14 @@
       <c r="R18" s="5">
         <v>46226</v>
       </c>
-      <c r="S18" s="12" t="s">
-        <v>71</v>
+      <c r="S18" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="T18" s="6">
         <v>0</v>
       </c>
-      <c r="U18" s="11" t="s">
-        <v>52</v>
+      <c r="U18" s="12" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
@@ -2613,14 +2619,14 @@
       <c r="R19" s="9">
         <v>46226</v>
       </c>
-      <c r="S19" s="12" t="s">
-        <v>71</v>
+      <c r="S19" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="T19" s="10">
         <v>0</v>
       </c>
-      <c r="U19" s="11" t="s">
-        <v>52</v>
+      <c r="U19" s="12" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
@@ -2729,8 +2735,8 @@
       <c r="T21" s="10">
         <v>0</v>
       </c>
-      <c r="U21" s="12" t="s">
-        <v>58</v>
+      <c r="U21" s="11" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
@@ -2792,8 +2798,8 @@
       <c r="T22" s="6">
         <v>0</v>
       </c>
-      <c r="U22" s="12" t="s">
-        <v>58</v>
+      <c r="U22" s="11" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
@@ -2855,8 +2861,8 @@
       <c r="T23" s="10">
         <v>0</v>
       </c>
-      <c r="U23" s="12" t="s">
-        <v>58</v>
+      <c r="U23" s="11" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
@@ -2918,8 +2924,8 @@
       <c r="T24" s="6">
         <v>0</v>
       </c>
-      <c r="U24" s="12" t="s">
-        <v>58</v>
+      <c r="U24" s="11" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
@@ -2981,8 +2987,8 @@
       <c r="T25" s="10">
         <v>0</v>
       </c>
-      <c r="U25" s="12" t="s">
-        <v>58</v>
+      <c r="U25" s="11" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
@@ -3091,8 +3097,8 @@
       <c r="T27" s="10">
         <v>0</v>
       </c>
-      <c r="U27" s="12" t="s">
-        <v>58</v>
+      <c r="U27" s="11" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
@@ -3150,8 +3156,8 @@
       <c r="T28" s="6">
         <v>0</v>
       </c>
-      <c r="U28" s="12" t="s">
-        <v>58</v>
+      <c r="U28" s="11" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
@@ -3209,8 +3215,8 @@
       <c r="T29" s="10">
         <v>0</v>
       </c>
-      <c r="U29" s="12" t="s">
-        <v>58</v>
+      <c r="U29" s="11" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
@@ -3272,8 +3278,8 @@
       <c r="T30" s="6">
         <v>0</v>
       </c>
-      <c r="U30" s="12" t="s">
-        <v>58</v>
+      <c r="U30" s="11" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
@@ -3441,8 +3447,8 @@
       <c r="T33" s="10">
         <v>0</v>
       </c>
-      <c r="U33" s="12" t="s">
-        <v>58</v>
+      <c r="U33" s="11" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
@@ -3610,8 +3616,8 @@
       <c r="T36" s="6">
         <v>0</v>
       </c>
-      <c r="U36" s="12" t="s">
-        <v>58</v>
+      <c r="U36" s="11" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
@@ -3832,8 +3838,8 @@
       <c r="T40" s="6">
         <v>0</v>
       </c>
-      <c r="U40" s="12" t="s">
-        <v>58</v>
+      <c r="U40" s="11" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
@@ -3951,7 +3957,7 @@
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46225.589328946764</v>
+        <v>46231.54140574074</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>160</v>
@@ -3996,9 +4002,11 @@
       <c r="B44" s="5">
         <v>46225.58112127315</v>
       </c>
-      <c r="C44" s="6"/>
+      <c r="C44" s="5">
+        <v>46231.54139886574</v>
+      </c>
       <c r="D44" s="5">
-        <v>46227.178273171296</v>
+        <v>46231.54141615741</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>163</v>
@@ -4031,7 +4039,7 @@
         <v>160</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>166</v>
@@ -4042,14 +4050,14 @@
       <c r="R44" s="5">
         <v>46230</v>
       </c>
-      <c r="S44" s="11" t="s">
+      <c r="S44" s="12" t="s">
         <v>167</v>
       </c>
       <c r="T44" s="6">
-        <v>0</v>
-      </c>
-      <c r="U44" s="11" t="s">
-        <v>52</v>
+        <v>1</v>
+      </c>
+      <c r="U44" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
@@ -4061,7 +4069,7 @@
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46225.613428275465</v>
+        <v>46231.54154219908</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>169</v>
@@ -4070,10 +4078,10 @@
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="I45" s="9">
         <v>46237</v>
@@ -4097,7 +4105,7 @@
         <v>163</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q45" s="9">
         <v>46241</v>
@@ -4112,12 +4120,12 @@
         <v>0</v>
       </c>
       <c r="U45" s="12" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B46" s="5">
         <v>46225.58113097222</v>
@@ -4160,7 +4168,7 @@
         <v>169</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q46" s="5">
         <v>46244</v>
@@ -4174,13 +4182,13 @@
       <c r="T46" s="6">
         <v>0</v>
       </c>
-      <c r="U46" s="12" t="s">
-        <v>58</v>
+      <c r="U46" s="11" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B47" s="9">
         <v>46225.58114445602</v>
@@ -4190,16 +4198,16 @@
         <v>46225.61347256944</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="I47" s="9">
         <v>46290</v>
@@ -4220,7 +4228,7 @@
         <v>160</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="P47" s="10" t="s">
         <v>160</v>
@@ -4237,13 +4245,13 @@
       <c r="T47" s="10">
         <v>0</v>
       </c>
-      <c r="U47" s="12" t="s">
-        <v>58</v>
+      <c r="U47" s="11" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B48" s="5">
         <v>46225.58114871528</v>
@@ -4253,16 +4261,16 @@
         <v>46225.61551950232</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="I48" s="5">
         <v>46290</v>
@@ -4280,13 +4288,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4296,7 +4304,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B49" s="9">
         <v>46225.58115283565</v>
@@ -4306,16 +4314,16 @@
         <v>46225.615519513885</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="I49" s="9">
         <v>46290</v>
@@ -4333,13 +4341,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q49" s="10"/>
       <c r="R49" s="10"/>
@@ -4349,7 +4357,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B50" s="5">
         <v>46225.581171631944</v>
@@ -4359,7 +4367,7 @@
         <v>46225.59181146991</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>25</v>
@@ -4383,7 +4391,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4396,7 +4404,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B51" s="9">
         <v>46225.58117489584</v>
@@ -4406,16 +4414,16 @@
         <v>46225.61367097222</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I51" s="9">
         <v>46260</v>
@@ -4433,13 +4441,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="O51" s="10" t="s">
         <v>115</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q51" s="9">
         <v>46260</v>
@@ -4453,13 +4461,13 @@
       <c r="T51" s="10">
         <v>0</v>
       </c>
-      <c r="U51" s="12" t="s">
-        <v>58</v>
+      <c r="U51" s="11" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B52" s="5">
         <v>46225.58118028935</v>
@@ -4469,16 +4477,16 @@
         <v>46225.613667349535</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I52" s="5">
         <v>46260</v>
@@ -4496,13 +4504,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>123</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q52" s="5">
         <v>46260</v>
@@ -4516,13 +4524,13 @@
       <c r="T52" s="6">
         <v>0</v>
       </c>
-      <c r="U52" s="12" t="s">
-        <v>58</v>
+      <c r="U52" s="11" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B53" s="9">
         <v>46225.58118576389</v>
@@ -4532,16 +4540,16 @@
         <v>46225.61366387732</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I53" s="9">
         <v>46260</v>
@@ -4559,13 +4567,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="O53" s="10" t="s">
         <v>131</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q53" s="9">
         <v>46260</v>
@@ -4579,13 +4587,13 @@
       <c r="T53" s="10">
         <v>0</v>
       </c>
-      <c r="U53" s="12" t="s">
-        <v>58</v>
+      <c r="U53" s="11" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B54" s="5">
         <v>46225.58119107639</v>
@@ -4595,7 +4603,7 @@
         <v>46225.61417395833</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
@@ -4622,13 +4630,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q54" s="5">
         <v>46261</v>
@@ -4642,13 +4650,13 @@
       <c r="T54" s="6">
         <v>0</v>
       </c>
-      <c r="U54" s="12" t="s">
-        <v>58</v>
+      <c r="U54" s="11" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B55" s="9">
         <v>46225.58119642361</v>
@@ -4658,7 +4666,7 @@
         <v>46225.61417104167</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
@@ -4685,13 +4693,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q55" s="9">
         <v>46261</v>
@@ -4705,13 +4713,13 @@
       <c r="T55" s="10">
         <v>0</v>
       </c>
-      <c r="U55" s="12" t="s">
-        <v>58</v>
+      <c r="U55" s="11" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B56" s="5">
         <v>46225.581201678244</v>
@@ -4721,7 +4729,7 @@
         <v>46225.61416773148</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
@@ -4748,13 +4756,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q56" s="5">
         <v>46261</v>
@@ -4768,13 +4776,13 @@
       <c r="T56" s="6">
         <v>0</v>
       </c>
-      <c r="U56" s="12" t="s">
-        <v>58</v>
+      <c r="U56" s="11" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B57" s="9">
         <v>46225.58120702546</v>
@@ -4784,7 +4792,7 @@
         <v>46225.59190644676</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>25</v>
@@ -4808,7 +4816,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="P57" s="10" t="s">
         <v>26</v>
@@ -4821,7 +4829,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B58" s="5">
         <v>46225.58121010417</v>
@@ -4837,10 +4845,10 @@
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I58" s="5">
         <v>46262</v>
@@ -4858,13 +4866,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>96</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q58" s="5">
         <v>46266</v>
@@ -4878,13 +4886,13 @@
       <c r="T58" s="6">
         <v>0</v>
       </c>
-      <c r="U58" s="12" t="s">
-        <v>58</v>
+      <c r="U58" s="11" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B59" s="9">
         <v>46225.581215474536</v>
@@ -4900,10 +4908,10 @@
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I59" s="9">
         <v>46267</v>
@@ -4921,13 +4929,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q59" s="9">
         <v>46273</v>
@@ -4941,13 +4949,13 @@
       <c r="T59" s="10">
         <v>0</v>
       </c>
-      <c r="U59" s="12" t="s">
-        <v>58</v>
+      <c r="U59" s="11" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B60" s="5">
         <v>46225.581219618056</v>
@@ -4957,16 +4965,16 @@
         <v>46225.614318611115</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I60" s="5">
         <v>46267</v>
@@ -4987,10 +4995,10 @@
         <v>143</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5000,7 +5008,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B61" s="9">
         <v>46225.58123596065</v>
@@ -5010,16 +5018,16 @@
         <v>46225.61431550926</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I61" s="9">
         <v>46267</v>
@@ -5040,10 +5048,10 @@
         <v>143</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q61" s="10"/>
       <c r="R61" s="10"/>
@@ -5053,7 +5061,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B62" s="5">
         <v>46225.58129219907</v>
@@ -5063,7 +5071,7 @@
         <v>46225.61447392361</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
@@ -5090,13 +5098,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q62" s="5">
         <v>46274</v>
@@ -5110,13 +5118,13 @@
       <c r="T62" s="6">
         <v>0</v>
       </c>
-      <c r="U62" s="12" t="s">
-        <v>58</v>
+      <c r="U62" s="11" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B63" s="9">
         <v>46225.58129802083</v>
@@ -5126,7 +5134,7 @@
         <v>46225.61443357639</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
@@ -5151,13 +5159,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5167,7 +5175,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B64" s="5">
         <v>46225.581304374995</v>
@@ -5177,7 +5185,7 @@
         <v>46225.61443052083</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5202,13 +5210,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5218,7 +5226,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B65" s="9">
         <v>46225.58131015046</v>
@@ -5228,7 +5236,7 @@
         <v>46225.59759329861</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>25</v>
@@ -5252,7 +5260,7 @@
         <v>26</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="P65" s="10" t="s">
         <v>26</v>
@@ -5265,26 +5273,26 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B66" s="5">
         <v>46225.58131376158</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46225.61459215278</v>
+        <v>46231.17194483796</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I66" s="5">
         <v>46230</v>
@@ -5302,13 +5310,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="O66" s="6" t="s">
         <v>76</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q66" s="5">
         <v>46231</v>
@@ -5322,32 +5330,32 @@
       <c r="T66" s="6">
         <v>0</v>
       </c>
-      <c r="U66" s="12" t="s">
-        <v>58</v>
+      <c r="U66" s="11" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B67" s="9">
         <v>46225.58131929398</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46225.61459149305</v>
+        <v>46231.17194690972</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I67" s="9">
         <v>46230</v>
@@ -5365,13 +5373,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="O67" s="10" t="s">
         <v>81</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q67" s="9">
         <v>46231</v>
@@ -5385,32 +5393,32 @@
       <c r="T67" s="10">
         <v>0</v>
       </c>
-      <c r="U67" s="12" t="s">
-        <v>58</v>
+      <c r="U67" s="11" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B68" s="5">
         <v>46225.58132505787</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46225.61459082176</v>
+        <v>46231.171948055555</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I68" s="5">
         <v>46230</v>
@@ -5428,13 +5436,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>84</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q68" s="5">
         <v>46231</v>
@@ -5448,13 +5456,13 @@
       <c r="T68" s="6">
         <v>0</v>
       </c>
-      <c r="U68" s="12" t="s">
-        <v>58</v>
+      <c r="U68" s="11" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B69" s="9">
         <v>46225.597591134254</v>
@@ -5464,16 +5472,16 @@
         <v>46225.61467041667</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I69" s="9">
         <v>46293</v>
@@ -5491,13 +5499,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="O69" s="10" t="s">
         <v>157</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q69" s="9">
         <v>46293</v>
@@ -5511,13 +5519,13 @@
       <c r="T69" s="10">
         <v>0</v>
       </c>
-      <c r="U69" s="12" t="s">
-        <v>58</v>
+      <c r="U69" s="11" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B70" s="5">
         <v>46225.58133054398</v>
@@ -5527,7 +5535,7 @@
         <v>46225.59299179398</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>25</v>
@@ -5551,7 +5559,7 @@
         <v>26</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -5564,7 +5572,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B71" s="9">
         <v>46225.58133395833</v>
@@ -5574,7 +5582,7 @@
         <v>46225.614863599534</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
@@ -5601,13 +5609,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q71" s="9">
         <v>46281</v>
@@ -5621,13 +5629,13 @@
       <c r="T71" s="10">
         <v>0</v>
       </c>
-      <c r="U71" s="12" t="s">
-        <v>58</v>
+      <c r="U71" s="11" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B72" s="5">
         <v>46225.58133853009</v>
@@ -5637,7 +5645,7 @@
         <v>46225.61483068287</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5664,13 +5672,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5680,7 +5688,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B73" s="9">
         <v>46225.58134314815</v>
@@ -5690,7 +5698,7 @@
         <v>46225.61482673611</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5717,13 +5725,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -5733,7 +5741,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B74" s="5">
         <v>46225.58134744213</v>
@@ -5743,7 +5751,7 @@
         <v>46225.61499751157</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5770,13 +5778,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q74" s="5">
         <v>46286</v>
@@ -5790,13 +5798,13 @@
       <c r="T74" s="6">
         <v>0</v>
       </c>
-      <c r="U74" s="12" t="s">
-        <v>58</v>
+      <c r="U74" s="11" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B75" s="9">
         <v>46225.581351932866</v>
@@ -5806,7 +5814,7 @@
         <v>46225.61504185185</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -5833,13 +5841,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -5849,7 +5857,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B76" s="5">
         <v>46225.58135922454</v>
@@ -5859,7 +5867,7 @@
         <v>46225.615038819444</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5886,13 +5894,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -5902,7 +5910,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B77" s="9">
         <v>46225.5813728588</v>
@@ -5912,7 +5920,7 @@
         <v>46225.61522760417</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -5939,13 +5947,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q77" s="9">
         <v>46287</v>
@@ -5959,13 +5967,13 @@
       <c r="T77" s="10">
         <v>0</v>
       </c>
-      <c r="U77" s="12" t="s">
-        <v>58</v>
+      <c r="U77" s="11" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B78" s="5">
         <v>46225.58137722222</v>
@@ -5975,7 +5983,7 @@
         <v>46225.61518142361</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6000,13 +6008,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6016,7 +6024,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B79" s="9">
         <v>46225.58138231482</v>
@@ -6026,7 +6034,7 @@
         <v>46225.615182291665</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6051,13 +6059,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6067,7 +6075,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B80" s="5">
         <v>46225.58138733797</v>
@@ -6077,7 +6085,7 @@
         <v>46225.61538164352</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6104,13 +6112,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q80" s="5">
         <v>46288</v>
@@ -6124,13 +6132,13 @@
       <c r="T80" s="6">
         <v>0</v>
       </c>
-      <c r="U80" s="12" t="s">
-        <v>58</v>
+      <c r="U80" s="11" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B81" s="9">
         <v>46225.58139180556</v>
@@ -6140,7 +6148,7 @@
         <v>46225.61534716435</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6167,13 +6175,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6183,7 +6191,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B82" s="5">
         <v>46225.58139752314</v>
@@ -6193,7 +6201,7 @@
         <v>46225.615343854166</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6220,13 +6228,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6236,7 +6244,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B83" s="9">
         <v>46225.58140275463</v>
@@ -6246,7 +6254,7 @@
         <v>46225.61555996528</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6273,13 +6281,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q83" s="9">
         <v>46289</v>
@@ -6293,13 +6301,13 @@
       <c r="T83" s="10">
         <v>0</v>
       </c>
-      <c r="U83" s="12" t="s">
-        <v>58</v>
+      <c r="U83" s="11" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B84" s="5">
         <v>46225.581407488426</v>
@@ -6309,7 +6317,7 @@
         <v>46225.61551967592</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6334,13 +6342,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6350,7 +6358,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B85" s="9">
         <v>46225.581414988425</v>
@@ -6360,7 +6368,7 @@
         <v>46225.61552056713</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6385,13 +6393,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6401,7 +6409,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B86" s="5">
         <v>46225.58145953703</v>
@@ -6411,7 +6419,7 @@
         <v>46230.71234510417</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6438,13 +6446,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q86" s="5">
         <v>46293</v>
@@ -6458,13 +6466,13 @@
       <c r="T86" s="6">
         <v>0</v>
       </c>
-      <c r="U86" s="12" t="s">
-        <v>58</v>
+      <c r="U86" s="11" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B87" s="9">
         <v>46225.58146568287</v>
@@ -6474,7 +6482,7 @@
         <v>46225.61568175926</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6501,13 +6509,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6517,7 +6525,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B88" s="5">
         <v>46225.58147099537</v>
@@ -6527,7 +6535,7 @@
         <v>46225.615682592594</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6554,13 +6562,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6570,7 +6578,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B89" s="9">
         <v>46225.58147606481</v>
@@ -6580,7 +6588,7 @@
         <v>46225.60367008102</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>25</v>
@@ -6604,7 +6612,7 @@
         <v>26</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="P89" s="10" t="s">
         <v>26</v>
@@ -6617,7 +6625,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B90" s="5">
         <v>46225.58147990741</v>
@@ -6627,16 +6635,16 @@
         <v>46225.615814467594</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="I90" s="5">
         <v>46301</v>
@@ -6654,13 +6662,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q90" s="5">
         <v>46301</v>
@@ -6674,13 +6682,13 @@
       <c r="T90" s="6">
         <v>0</v>
       </c>
-      <c r="U90" s="12" t="s">
-        <v>58</v>
+      <c r="U90" s="11" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B91" s="9">
         <v>46225.58148496528</v>
@@ -6690,16 +6698,16 @@
         <v>46225.61578579861</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="I91" s="10"/>
       <c r="J91" s="9">
@@ -6715,13 +6723,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -6731,7 +6739,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B92" s="5">
         <v>46225.58148953704</v>
@@ -6741,16 +6749,16 @@
         <v>46225.61578274306</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="I92" s="5">
         <v>46301</v>
@@ -6768,13 +6776,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6784,7 +6792,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B93" s="9">
         <v>46225.6055390625</v>
@@ -6794,16 +6802,16 @@
         <v>46225.61577960648</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="I93" s="10"/>
       <c r="J93" s="9">
@@ -6819,13 +6827,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -6835,7 +6843,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B94" s="5">
         <v>46225.605553333335</v>
@@ -6845,16 +6853,16 @@
         <v>46225.61577443287</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="I94" s="6"/>
       <c r="J94" s="5">
@@ -6870,13 +6878,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -6886,7 +6894,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B95" s="9">
         <v>46225.581494178245</v>
@@ -6896,7 +6904,7 @@
         <v>46225.61592174768</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -6921,10 +6929,10 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="P95" s="10" t="s">
         <v>26</v>
@@ -6941,13 +6949,13 @@
       <c r="T95" s="10">
         <v>0</v>
       </c>
-      <c r="U95" s="12" t="s">
-        <v>58</v>
+      <c r="U95" s="11" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B96" s="5">
         <v>46225.5814984375</v>
@@ -6957,7 +6965,7 @@
         <v>46225.615894421295</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -6984,13 +6992,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7000,7 +7008,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B97" s="9">
         <v>46225.58150320602</v>
@@ -7010,7 +7018,7 @@
         <v>46225.61589104167</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7037,13 +7045,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7053,7 +7061,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B98" s="5">
         <v>46225.60673211806</v>
@@ -7063,7 +7071,7 @@
         <v>46225.615888125</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7090,13 +7098,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7106,7 +7114,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B99" s="9">
         <v>46225.60674163194</v>
@@ -7116,7 +7124,7 @@
         <v>46225.61588293982</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7143,13 +7151,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7159,7 +7167,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B100" s="5">
         <v>46225.58150777778</v>
@@ -7169,16 +7177,16 @@
         <v>46225.61603868056</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I100" s="5">
         <v>46303</v>
@@ -7196,13 +7204,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q100" s="5">
         <v>46303</v>
@@ -7216,13 +7224,13 @@
       <c r="T100" s="6">
         <v>0</v>
       </c>
-      <c r="U100" s="12" t="s">
-        <v>58</v>
+      <c r="U100" s="11" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B101" s="9">
         <v>46225.58151239583</v>
@@ -7232,16 +7240,16 @@
         <v>46225.61600570602</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I101" s="10"/>
       <c r="J101" s="9">
@@ -7257,13 +7265,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7273,7 +7281,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B102" s="5">
         <v>46225.58151694444</v>
@@ -7283,16 +7291,16 @@
         <v>46225.61600274306</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I102" s="6"/>
       <c r="J102" s="5">
@@ -7308,13 +7316,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7324,7 +7332,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B103" s="9">
         <v>46225.606768564816</v>
@@ -7334,16 +7342,16 @@
         <v>46225.615999965274</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I103" s="9">
         <v>46303</v>
@@ -7361,13 +7369,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7377,7 +7385,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B104" s="5">
         <v>46225.606777395835</v>
@@ -7387,16 +7395,16 @@
         <v>46225.61599523148</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I104" s="5">
         <v>46303</v>
@@ -7414,13 +7422,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7430,7 +7438,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B105" s="9">
         <v>46225.581521562504</v>
@@ -7440,16 +7448,16 @@
         <v>46225.61624585648</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I105" s="9">
         <v>46304</v>
@@ -7467,13 +7475,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q105" s="9">
         <v>46304</v>
@@ -7487,13 +7495,13 @@
       <c r="T105" s="10">
         <v>0</v>
       </c>
-      <c r="U105" s="12" t="s">
-        <v>58</v>
+      <c r="U105" s="11" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B106" s="5">
         <v>46225.58152704861</v>
@@ -7503,16 +7511,16 @@
         <v>46225.61621090278</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I106" s="6"/>
       <c r="J106" s="5">
@@ -7528,13 +7536,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7544,7 +7552,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B107" s="9">
         <v>46225.58153157408</v>
@@ -7554,16 +7562,16 @@
         <v>46225.61620709491</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I107" s="10"/>
       <c r="J107" s="9">
@@ -7579,13 +7587,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q107" s="10"/>
       <c r="R107" s="10"/>
@@ -7595,7 +7603,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B108" s="5">
         <v>46225.60680554398</v>
@@ -7605,16 +7613,16 @@
         <v>46225.616203564816</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I108" s="5">
         <v>46304</v>
@@ -7632,10 +7640,10 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="P108" s="6" t="s">
         <v>26</v>
@@ -7648,7 +7656,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B109" s="9">
         <v>46225.60681763889</v>
@@ -7658,16 +7666,16 @@
         <v>46225.61619854167</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I109" s="9">
         <v>46304</v>
@@ -7685,10 +7693,10 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="P109" s="10" t="s">
         <v>26</v>
@@ -7701,7 +7709,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B110" s="5">
         <v>46225.58153574074</v>
@@ -7711,7 +7719,7 @@
         <v>46225.60402078704</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>25</v>
@@ -7735,7 +7743,7 @@
         <v>26</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>26</v>
@@ -7748,7 +7756,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B111" s="9">
         <v>46225.58153866898</v>
@@ -7758,16 +7766,16 @@
         <v>46225.61649424769</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="H111" s="10" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="I111" s="9">
         <v>46307</v>
@@ -7785,13 +7793,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q111" s="9">
         <v>46311</v>
@@ -7805,13 +7813,13 @@
       <c r="T111" s="10">
         <v>0</v>
       </c>
-      <c r="U111" s="12" t="s">
-        <v>58</v>
+      <c r="U111" s="11" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B112" s="5">
         <v>46225.58154590278</v>
@@ -7821,7 +7829,7 @@
         <v>46225.61639241898</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -7848,13 +7856,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q112" s="5">
         <v>46311</v>
@@ -7868,13 +7876,13 @@
       <c r="T112" s="6">
         <v>0</v>
       </c>
-      <c r="U112" s="12" t="s">
-        <v>58</v>
+      <c r="U112" s="11" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B113" s="9">
         <v>46225.59432256944</v>
@@ -7884,7 +7892,7 @@
         <v>46225.6052183912</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>25</v>
@@ -7908,7 +7916,7 @@
         <v>26</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="P113" s="10" t="s">
         <v>26</v>
@@ -7921,7 +7929,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B114" s="5">
         <v>46225.59476561342</v>
@@ -7931,7 +7939,7 @@
         <v>46225.616553796295</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -7958,13 +7966,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q114" s="5">
         <v>46318</v>
@@ -7978,13 +7986,13 @@
       <c r="T114" s="6">
         <v>0</v>
       </c>
-      <c r="U114" s="12" t="s">
-        <v>58</v>
+      <c r="U114" s="11" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B115" s="9">
         <v>46225.59487494213</v>
@@ -7994,7 +8002,7 @@
         <v>46225.61655020833</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
@@ -8021,13 +8029,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q115" s="9">
         <v>46325</v>
@@ -8041,8 +8049,8 @@
       <c r="T115" s="10">
         <v>0</v>
       </c>
-      <c r="U115" s="12" t="s">
-        <v>58</v>
+      <c r="U115" s="11" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001580- CIA. RIO MINERALES.xlsx
+++ b/data/50001580- CIA. RIO MINERALES.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1349" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1359" uniqueCount="349">
   <si>
     <t>50001580- "CIA. RIO MINERALES"</t>
   </si>
@@ -776,7 +776,19 @@
     <t>Montaje:</t>
   </si>
   <si>
-    <t>RE-PINTADOOT4378,Montaje Alabe OT4378,Montaje Rodete OT4378,Pruebas FAT OT4378,Revestimiento OT4378,Montaje motor OT4378</t>
+    <t>Montaje Alabe OT4378,Montaje Rodete OT4378,Revestimiento OT4378,Montaje motor OT4378</t>
+  </si>
+  <si>
+    <t>1216991376879757</t>
+  </si>
+  <si>
+    <t>Conexión eléctrica OT4378</t>
+  </si>
+  <si>
+    <t>Montaje motor OT4378</t>
+  </si>
+  <si>
+    <t>Pruebas FAT OT4378</t>
   </si>
   <si>
     <t>1216788353013131</t>
@@ -785,6 +797,9 @@
     <t>Revestimiento OT4378</t>
   </si>
   <si>
+    <t>Montaje:,Montaje Alabe OT4378</t>
+  </si>
+  <si>
     <t>1216788148296193</t>
   </si>
   <si>
@@ -803,6 +818,12 @@
     <t>Montaje Alabe OT4378</t>
   </si>
   <si>
+    <t>OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,Revestimiento OT4378</t>
+  </si>
+  <si>
+    <t>Montaje:,Montaje Rodete OT4378</t>
+  </si>
+  <si>
     <t>1216788055319725</t>
   </si>
   <si>
@@ -821,6 +842,12 @@
     <t>Montaje Rodete OT4378</t>
   </si>
   <si>
+    <t>OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,Montaje Alabe OT4378</t>
+  </si>
+  <si>
+    <t>Montaje:,Montaje motor OT4378</t>
+  </si>
+  <si>
     <t>1216788353064043</t>
   </si>
   <si>
@@ -836,7 +863,10 @@
     <t>1216788353066344</t>
   </si>
   <si>
-    <t>Montaje motor OT4378</t>
+    <t>OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,Montaje Rodete OT4378</t>
+  </si>
+  <si>
+    <t>Montaje:,Conexión eléctrica OT4378</t>
   </si>
   <si>
     <t>1216788353066361</t>
@@ -857,7 +887,10 @@
     <t>1216788055348894</t>
   </si>
   <si>
-    <t>Pruebas FAT OT4378</t>
+    <t>OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,Conexión eléctrica OT4378</t>
+  </si>
+  <si>
+    <t>RE-PINTADOOT4378</t>
   </si>
   <si>
     <t>1216788055348911</t>
@@ -875,7 +908,7 @@
     <t>1216788055309881</t>
   </si>
   <si>
-    <t>RE-PINTADOOT4378</t>
+    <t>OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,Pruebas FAT OT4378</t>
   </si>
   <si>
     <t>1216788148384002</t>
@@ -1585,7 +1618,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U115"/>
+  <dimension ref="A1:U116"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10.4" customWidth="1"/>
@@ -2937,7 +2970,7 @@
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46225.61245637732</v>
+        <v>46232.25114619213</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>102</v>
@@ -5280,7 +5313,7 @@
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46231.17194483796</v>
+        <v>46232.18544357639</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>232</v>
@@ -5324,8 +5357,8 @@
       <c r="R66" s="5">
         <v>46230</v>
       </c>
-      <c r="S66" s="7" t="s">
-        <v>33</v>
+      <c r="S66" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="T66" s="6">
         <v>0</v>
@@ -5343,7 +5376,7 @@
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46231.17194690972</v>
+        <v>46232.18544451389</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>235</v>
@@ -5387,8 +5420,8 @@
       <c r="R67" s="9">
         <v>46230</v>
       </c>
-      <c r="S67" s="7" t="s">
-        <v>33</v>
+      <c r="S67" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="T67" s="10">
         <v>0</v>
@@ -5406,7 +5439,7 @@
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46231.171948055555</v>
+        <v>46232.18544357639</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>238</v>
@@ -5450,8 +5483,8 @@
       <c r="R68" s="5">
         <v>46230</v>
       </c>
-      <c r="S68" s="7" t="s">
-        <v>33</v>
+      <c r="S68" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="T68" s="6">
         <v>0</v>
@@ -5532,7 +5565,7 @@
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46225.59299179398</v>
+        <v>46232.60338619213</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>241</v>
@@ -5575,11 +5608,11 @@
         <v>243</v>
       </c>
       <c r="B71" s="9">
-        <v>46225.58133395833</v>
+        <v>46232.60331346065</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46225.614863599534</v>
+        <v>46232.624382951384</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>244</v>
@@ -5588,16 +5621,14 @@
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="H71" s="10" t="s">
-        <v>78</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H71" s="10"/>
       <c r="I71" s="9">
-        <v>46275</v>
+        <v>46289</v>
       </c>
       <c r="J71" s="9">
-        <v>46281</v>
+        <v>46289</v>
       </c>
       <c r="K71" s="10" t="s">
         <v>26</v>
@@ -5612,40 +5643,30 @@
         <v>241</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>179</v>
+        <v>245</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="Q71" s="9">
-        <v>46281</v>
-      </c>
-      <c r="R71" s="9">
-        <v>46275</v>
-      </c>
-      <c r="S71" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T71" s="10">
-        <v>0</v>
-      </c>
-      <c r="U71" s="11" t="s">
-        <v>59</v>
-      </c>
+        <v>246</v>
+      </c>
+      <c r="Q71" s="10"/>
+      <c r="R71" s="10"/>
+      <c r="S71" s="10"/>
+      <c r="T71" s="10"/>
+      <c r="U71" s="10"/>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B72" s="5">
-        <v>46225.58133853009</v>
+        <v>46225.58133395833</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46225.61483068287</v>
+        <v>46232.62438273148</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>181</v>
+        <v>248</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5672,30 +5693,40 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="Q72" s="6"/>
-      <c r="R72" s="6"/>
-      <c r="S72" s="6"/>
-      <c r="T72" s="6"/>
-      <c r="U72" s="6"/>
+        <v>249</v>
+      </c>
+      <c r="Q72" s="5">
+        <v>46281</v>
+      </c>
+      <c r="R72" s="5">
+        <v>46275</v>
+      </c>
+      <c r="S72" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T72" s="6">
+        <v>0</v>
+      </c>
+      <c r="U72" s="11" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B73" s="9">
-        <v>46225.58134314815</v>
+        <v>46225.58133853009</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46225.61482673611</v>
+        <v>46225.61483068287</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>181</v>
@@ -5725,13 +5756,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="O73" s="10" t="s">
         <v>181</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -5741,17 +5772,17 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B74" s="5">
-        <v>46225.58134744213</v>
+        <v>46225.58134314815</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46225.61499751157</v>
+        <v>46225.61482673611</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>250</v>
+        <v>181</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5763,10 +5794,10 @@
         <v>78</v>
       </c>
       <c r="I74" s="5">
-        <v>46286</v>
+        <v>46275</v>
       </c>
       <c r="J74" s="5">
-        <v>46286</v>
+        <v>46281</v>
       </c>
       <c r="K74" s="6" t="s">
         <v>26</v>
@@ -5778,43 +5809,33 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="Q74" s="5">
-        <v>46286</v>
-      </c>
-      <c r="R74" s="5">
-        <v>46286</v>
-      </c>
-      <c r="S74" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T74" s="6">
-        <v>0</v>
-      </c>
-      <c r="U74" s="11" t="s">
-        <v>59</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="Q74" s="6"/>
+      <c r="R74" s="6"/>
+      <c r="S74" s="6"/>
+      <c r="T74" s="6"/>
+      <c r="U74" s="6"/>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B75" s="9">
-        <v>46225.581351932866</v>
+        <v>46225.58134744213</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46225.61504185185</v>
+        <v>46232.62438234954</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>181</v>
+        <v>255</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -5841,30 +5862,40 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q75" s="10"/>
-      <c r="R75" s="10"/>
-      <c r="S75" s="10"/>
-      <c r="T75" s="10"/>
-      <c r="U75" s="10"/>
+        <v>257</v>
+      </c>
+      <c r="Q75" s="9">
+        <v>46286</v>
+      </c>
+      <c r="R75" s="9">
+        <v>46286</v>
+      </c>
+      <c r="S75" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T75" s="10">
+        <v>0</v>
+      </c>
+      <c r="U75" s="11" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B76" s="5">
-        <v>46225.58135922454</v>
+        <v>46225.581351932866</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46225.615038819444</v>
+        <v>46225.61504185185</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>181</v>
@@ -5894,13 +5925,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -5910,17 +5941,17 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="B77" s="9">
-        <v>46225.5813728588</v>
+        <v>46225.58135922454</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46225.61522760417</v>
+        <v>46225.615038819444</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>256</v>
+        <v>181</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -5932,10 +5963,10 @@
         <v>78</v>
       </c>
       <c r="I77" s="9">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="J77" s="9">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="K77" s="10" t="s">
         <v>26</v>
@@ -5947,43 +5978,33 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>179</v>
+        <v>259</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="Q77" s="9">
-        <v>46287</v>
-      </c>
-      <c r="R77" s="9">
-        <v>46287</v>
-      </c>
-      <c r="S77" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T77" s="10">
-        <v>0</v>
-      </c>
-      <c r="U77" s="11" t="s">
-        <v>59</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="Q77" s="10"/>
+      <c r="R77" s="10"/>
+      <c r="S77" s="10"/>
+      <c r="T77" s="10"/>
+      <c r="U77" s="10"/>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="B78" s="5">
-        <v>46225.58137722222</v>
+        <v>46225.5813728588</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46225.61518142361</v>
+        <v>46232.624382071765</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>181</v>
+        <v>263</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -5994,7 +6015,9 @@
       <c r="H78" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="I78" s="6"/>
+      <c r="I78" s="5">
+        <v>46287</v>
+      </c>
       <c r="J78" s="5">
         <v>46287</v>
       </c>
@@ -6008,30 +6031,40 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>256</v>
+        <v>241</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="Q78" s="6"/>
-      <c r="R78" s="6"/>
-      <c r="S78" s="6"/>
-      <c r="T78" s="6"/>
-      <c r="U78" s="6"/>
+        <v>265</v>
+      </c>
+      <c r="Q78" s="5">
+        <v>46287</v>
+      </c>
+      <c r="R78" s="5">
+        <v>46287</v>
+      </c>
+      <c r="S78" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T78" s="6">
+        <v>0</v>
+      </c>
+      <c r="U78" s="11" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B79" s="9">
-        <v>46225.58138231482</v>
+        <v>46225.58137722222</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46225.615182291665</v>
+        <v>46225.61518142361</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>181</v>
@@ -6059,13 +6092,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6075,17 +6108,17 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="B80" s="5">
-        <v>46225.58138733797</v>
+        <v>46225.58138231482</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46225.61538164352</v>
+        <v>46225.615182291665</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>262</v>
+        <v>181</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6096,11 +6129,9 @@
       <c r="H80" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="I80" s="5">
-        <v>46288</v>
-      </c>
+      <c r="I80" s="6"/>
       <c r="J80" s="5">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="K80" s="6" t="s">
         <v>26</v>
@@ -6112,43 +6143,33 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>241</v>
+        <v>263</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>179</v>
+        <v>267</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="Q80" s="5">
-        <v>46288</v>
-      </c>
-      <c r="R80" s="5">
-        <v>46288</v>
-      </c>
-      <c r="S80" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T80" s="6">
-        <v>0</v>
-      </c>
-      <c r="U80" s="11" t="s">
-        <v>59</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="Q80" s="6"/>
+      <c r="R80" s="6"/>
+      <c r="S80" s="6"/>
+      <c r="T80" s="6"/>
+      <c r="U80" s="6"/>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="B81" s="9">
-        <v>46225.58139180556</v>
+        <v>46225.58138733797</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46225.61534716435</v>
+        <v>46232.624381828704</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>181</v>
+        <v>245</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6175,30 +6196,40 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>262</v>
+        <v>241</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>265</v>
-      </c>
-      <c r="Q81" s="10"/>
-      <c r="R81" s="10"/>
-      <c r="S81" s="10"/>
-      <c r="T81" s="10"/>
-      <c r="U81" s="10"/>
+        <v>272</v>
+      </c>
+      <c r="Q81" s="9">
+        <v>46288</v>
+      </c>
+      <c r="R81" s="9">
+        <v>46288</v>
+      </c>
+      <c r="S81" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T81" s="10">
+        <v>0</v>
+      </c>
+      <c r="U81" s="11" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="B82" s="5">
-        <v>46225.58139752314</v>
+        <v>46225.58139180556</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46225.615343854166</v>
+        <v>46225.61534716435</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>181</v>
@@ -6228,13 +6259,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>262</v>
+        <v>245</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6244,17 +6275,17 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="B83" s="9">
-        <v>46225.58140275463</v>
+        <v>46225.58139752314</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46225.61555996528</v>
+        <v>46225.615343854166</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>269</v>
+        <v>181</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6266,10 +6297,10 @@
         <v>78</v>
       </c>
       <c r="I83" s="9">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="J83" s="9">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="K83" s="10" t="s">
         <v>26</v>
@@ -6281,43 +6312,33 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>179</v>
+        <v>274</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="Q83" s="9">
-        <v>46289</v>
-      </c>
-      <c r="R83" s="9">
-        <v>46289</v>
-      </c>
-      <c r="S83" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T83" s="10">
-        <v>0</v>
-      </c>
-      <c r="U83" s="11" t="s">
-        <v>59</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="Q83" s="10"/>
+      <c r="R83" s="10"/>
+      <c r="S83" s="10"/>
+      <c r="T83" s="10"/>
+      <c r="U83" s="10"/>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="B84" s="5">
-        <v>46225.581407488426</v>
+        <v>46225.58140275463</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46225.61551967592</v>
+        <v>46232.62438278935</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>181</v>
+        <v>246</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6328,44 +6349,56 @@
       <c r="H84" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="I84" s="6"/>
+      <c r="I84" s="5">
+        <v>46290</v>
+      </c>
       <c r="J84" s="5">
+        <v>46290</v>
+      </c>
+      <c r="K84" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L84" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M84" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N84" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="O84" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="P84" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="Q84" s="5">
         <v>46289</v>
       </c>
-      <c r="K84" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L84" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M84" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N84" s="6" t="s">
-        <v>269</v>
-      </c>
-      <c r="O84" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="P84" s="6" t="s">
-        <v>272</v>
-      </c>
-      <c r="Q84" s="6"/>
-      <c r="R84" s="6"/>
-      <c r="S84" s="6"/>
-      <c r="T84" s="6"/>
-      <c r="U84" s="6"/>
+      <c r="R84" s="5">
+        <v>46289</v>
+      </c>
+      <c r="S84" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T84" s="6">
+        <v>0</v>
+      </c>
+      <c r="U84" s="11" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="B85" s="9">
-        <v>46225.581414988425</v>
+        <v>46225.581407488426</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46225.61552056713</v>
+        <v>46225.61551967592</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>181</v>
@@ -6393,13 +6426,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>269</v>
+        <v>246</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6409,17 +6442,17 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="B86" s="5">
-        <v>46225.58145953703</v>
+        <v>46225.581414988425</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46230.71234510417</v>
+        <v>46225.61552056713</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>275</v>
+        <v>181</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6430,11 +6463,9 @@
       <c r="H86" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="I86" s="5">
-        <v>46293</v>
-      </c>
+      <c r="I86" s="6"/>
       <c r="J86" s="5">
-        <v>46293</v>
+        <v>46289</v>
       </c>
       <c r="K86" s="6" t="s">
         <v>26</v>
@@ -6446,43 +6477,33 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>179</v>
+        <v>282</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="Q86" s="5">
-        <v>46293</v>
-      </c>
-      <c r="R86" s="5">
-        <v>46293</v>
-      </c>
-      <c r="S86" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T86" s="6">
-        <v>0</v>
-      </c>
-      <c r="U86" s="11" t="s">
-        <v>59</v>
-      </c>
+        <v>283</v>
+      </c>
+      <c r="Q86" s="6"/>
+      <c r="R86" s="6"/>
+      <c r="S86" s="6"/>
+      <c r="T86" s="6"/>
+      <c r="U86" s="6"/>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="B87" s="9">
-        <v>46225.58146568287</v>
+        <v>46225.58145953703</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46225.61568175926</v>
+        <v>46232.62438171296</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>181</v>
+        <v>280</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6509,30 +6530,40 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>275</v>
+        <v>241</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>181</v>
+        <v>286</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>277</v>
-      </c>
-      <c r="Q87" s="10"/>
-      <c r="R87" s="10"/>
-      <c r="S87" s="10"/>
-      <c r="T87" s="10"/>
-      <c r="U87" s="10"/>
+        <v>26</v>
+      </c>
+      <c r="Q87" s="9">
+        <v>46293</v>
+      </c>
+      <c r="R87" s="9">
+        <v>46293</v>
+      </c>
+      <c r="S87" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T87" s="10">
+        <v>0</v>
+      </c>
+      <c r="U87" s="11" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="B88" s="5">
-        <v>46225.58147099537</v>
+        <v>46225.58146568287</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46225.615682592594</v>
+        <v>46225.61568175926</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>181</v>
@@ -6562,13 +6593,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="O88" s="6" t="s">
         <v>181</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6578,44 +6609,50 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="B89" s="9">
-        <v>46225.58147606481</v>
+        <v>46225.58147099537</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46225.60367008102</v>
+        <v>46225.615682592594</v>
       </c>
       <c r="E89" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="F89" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G89" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H89" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="I89" s="9">
+        <v>46293</v>
+      </c>
+      <c r="J89" s="9">
+        <v>46293</v>
+      </c>
+      <c r="K89" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L89" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M89" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N89" s="10" t="s">
         <v>280</v>
       </c>
-      <c r="F89" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="G89" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H89" s="10"/>
-      <c r="I89" s="10"/>
-      <c r="J89" s="10"/>
-      <c r="K89" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L89" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M89" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="N89" s="10" t="s">
-        <v>26</v>
-      </c>
       <c r="O89" s="10" t="s">
-        <v>281</v>
+        <v>181</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>26</v>
+        <v>288</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6625,33 +6662,27 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="B90" s="5">
-        <v>46225.58147990741</v>
+        <v>46225.58147606481</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46225.615814467594</v>
+        <v>46225.60367008102</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="F90" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="I90" s="5">
-        <v>46301</v>
-      </c>
-      <c r="J90" s="5">
-        <v>46301</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H90" s="6"/>
+      <c r="I90" s="6"/>
+      <c r="J90" s="6"/>
       <c r="K90" s="6" t="s">
         <v>26</v>
       </c>
@@ -6659,57 +6690,49 @@
         <v>26</v>
       </c>
       <c r="M90" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>280</v>
+        <v>26</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="Q90" s="5">
-        <v>46301</v>
-      </c>
-      <c r="R90" s="5">
-        <v>46301</v>
-      </c>
-      <c r="S90" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T90" s="6">
-        <v>0</v>
-      </c>
-      <c r="U90" s="11" t="s">
-        <v>59</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q90" s="6"/>
+      <c r="R90" s="6"/>
+      <c r="S90" s="6"/>
+      <c r="T90" s="6"/>
+      <c r="U90" s="6"/>
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="B91" s="9">
-        <v>46225.58148496528</v>
+        <v>46225.58147990741</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46225.61578579861</v>
+        <v>46225.615814467594</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>181</v>
+        <v>294</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>285</v>
-      </c>
-      <c r="I91" s="10"/>
+        <v>296</v>
+      </c>
+      <c r="I91" s="9">
+        <v>46301</v>
+      </c>
       <c r="J91" s="9">
         <v>46301</v>
       </c>
@@ -6723,30 +6746,40 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>181</v>
+        <v>297</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>289</v>
-      </c>
-      <c r="Q91" s="10"/>
-      <c r="R91" s="10"/>
-      <c r="S91" s="10"/>
-      <c r="T91" s="10"/>
-      <c r="U91" s="10"/>
+        <v>298</v>
+      </c>
+      <c r="Q91" s="9">
+        <v>46301</v>
+      </c>
+      <c r="R91" s="9">
+        <v>46301</v>
+      </c>
+      <c r="S91" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T91" s="10">
+        <v>0</v>
+      </c>
+      <c r="U91" s="11" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="B92" s="5">
-        <v>46225.58148953704</v>
+        <v>46225.58148496528</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46225.61578274306</v>
+        <v>46225.61578579861</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>181</v>
@@ -6755,14 +6788,12 @@
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="I92" s="5">
-        <v>46301</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="I92" s="6"/>
       <c r="J92" s="5">
         <v>46301</v>
       </c>
@@ -6776,13 +6807,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="O92" s="6" t="s">
         <v>181</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6792,28 +6823,30 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="B93" s="9">
-        <v>46225.6055390625</v>
+        <v>46225.58148953704</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46225.61577960648</v>
+        <v>46225.61578274306</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>292</v>
+        <v>181</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>285</v>
-      </c>
-      <c r="I93" s="10"/>
+        <v>296</v>
+      </c>
+      <c r="I93" s="9">
+        <v>46301</v>
+      </c>
       <c r="J93" s="9">
         <v>46301</v>
       </c>
@@ -6827,13 +6860,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>61</v>
+        <v>181</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -6843,26 +6876,26 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="B94" s="5">
-        <v>46225.605553333335</v>
+        <v>46225.6055390625</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46225.61577443287</v>
+        <v>46225.61577960648</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="I94" s="6"/>
       <c r="J94" s="5">
@@ -6878,13 +6911,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -6894,30 +6927,30 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B95" s="9">
-        <v>46225.581494178245</v>
+        <v>46225.605553333335</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46225.61592174768</v>
+        <v>46225.61577443287</v>
       </c>
       <c r="E95" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="F95" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G95" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="H95" s="10" t="s">
         <v>296</v>
-      </c>
-      <c r="F95" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G95" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="H95" s="10" t="s">
-        <v>78</v>
       </c>
       <c r="I95" s="10"/>
       <c r="J95" s="9">
-        <v>46302</v>
+        <v>46301</v>
       </c>
       <c r="K95" s="10" t="s">
         <v>26</v>
@@ -6929,43 +6962,33 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>280</v>
+        <v>294</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>297</v>
+        <v>65</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q95" s="9">
-        <v>46302</v>
-      </c>
-      <c r="R95" s="9">
-        <v>46302</v>
-      </c>
-      <c r="S95" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T95" s="10">
-        <v>0</v>
-      </c>
-      <c r="U95" s="11" t="s">
-        <v>59</v>
-      </c>
+        <v>304</v>
+      </c>
+      <c r="Q95" s="10"/>
+      <c r="R95" s="10"/>
+      <c r="S95" s="10"/>
+      <c r="T95" s="10"/>
+      <c r="U95" s="10"/>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="B96" s="5">
-        <v>46225.5814984375</v>
+        <v>46225.581494178245</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46225.615894421295</v>
+        <v>46225.61592174768</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>181</v>
+        <v>307</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -6976,9 +6999,7 @@
       <c r="H96" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="I96" s="5">
-        <v>46302</v>
-      </c>
+      <c r="I96" s="6"/>
       <c r="J96" s="5">
         <v>46302</v>
       </c>
@@ -6992,30 +7013,40 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>181</v>
+        <v>308</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>299</v>
-      </c>
-      <c r="Q96" s="6"/>
-      <c r="R96" s="6"/>
-      <c r="S96" s="6"/>
-      <c r="T96" s="6"/>
-      <c r="U96" s="6"/>
+        <v>26</v>
+      </c>
+      <c r="Q96" s="5">
+        <v>46302</v>
+      </c>
+      <c r="R96" s="5">
+        <v>46302</v>
+      </c>
+      <c r="S96" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T96" s="6">
+        <v>0</v>
+      </c>
+      <c r="U96" s="11" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="B97" s="9">
-        <v>46225.58150320602</v>
+        <v>46225.5814984375</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46225.61589104167</v>
+        <v>46225.615894421295</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>181</v>
@@ -7045,13 +7076,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="O97" s="10" t="s">
         <v>181</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7061,17 +7092,17 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="B98" s="5">
-        <v>46225.60673211806</v>
+        <v>46225.58150320602</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46225.615888125</v>
+        <v>46225.61589104167</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>292</v>
+        <v>181</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7098,13 +7129,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>292</v>
+        <v>181</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7114,17 +7145,17 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="B99" s="9">
-        <v>46225.60674163194</v>
+        <v>46225.60673211806</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46225.61588293982</v>
+        <v>46225.615888125</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7151,13 +7182,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7167,32 +7198,32 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="B100" s="5">
-        <v>46225.58150777778</v>
+        <v>46225.60674163194</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46225.61603868056</v>
+        <v>46225.61588293982</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>211</v>
+        <v>77</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>212</v>
+        <v>78</v>
       </c>
       <c r="I100" s="5">
-        <v>46303</v>
+        <v>46302</v>
       </c>
       <c r="J100" s="5">
-        <v>46303</v>
+        <v>46302</v>
       </c>
       <c r="K100" s="6" t="s">
         <v>26</v>
@@ -7204,43 +7235,33 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>280</v>
+        <v>307</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>286</v>
+        <v>303</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="Q100" s="5">
-        <v>46303</v>
-      </c>
-      <c r="R100" s="5">
-        <v>46303</v>
-      </c>
-      <c r="S100" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T100" s="6">
-        <v>0</v>
-      </c>
-      <c r="U100" s="11" t="s">
-        <v>59</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="Q100" s="6"/>
+      <c r="R100" s="6"/>
+      <c r="S100" s="6"/>
+      <c r="T100" s="6"/>
+      <c r="U100" s="6"/>
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="B101" s="9">
-        <v>46225.58151239583</v>
+        <v>46225.58150777778</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46225.61600570602</v>
+        <v>46225.61603868056</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>181</v>
+        <v>316</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7251,7 +7272,9 @@
       <c r="H101" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="I101" s="10"/>
+      <c r="I101" s="9">
+        <v>46303</v>
+      </c>
       <c r="J101" s="9">
         <v>46303</v>
       </c>
@@ -7265,30 +7288,40 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>305</v>
+        <v>291</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>181</v>
+        <v>297</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>307</v>
-      </c>
-      <c r="Q101" s="10"/>
-      <c r="R101" s="10"/>
-      <c r="S101" s="10"/>
-      <c r="T101" s="10"/>
-      <c r="U101" s="10"/>
+        <v>291</v>
+      </c>
+      <c r="Q101" s="9">
+        <v>46303</v>
+      </c>
+      <c r="R101" s="9">
+        <v>46303</v>
+      </c>
+      <c r="S101" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T101" s="10">
+        <v>0</v>
+      </c>
+      <c r="U101" s="11" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="B102" s="5">
-        <v>46225.58151694444</v>
+        <v>46225.58151239583</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46225.61600274306</v>
+        <v>46225.61600570602</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>181</v>
@@ -7316,13 +7349,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="O102" s="6" t="s">
         <v>181</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7332,17 +7365,17 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="B103" s="9">
-        <v>46225.606768564816</v>
+        <v>46225.58151694444</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46225.615999965274</v>
+        <v>46225.61600274306</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>292</v>
+        <v>181</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7353,9 +7386,7 @@
       <c r="H103" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="I103" s="9">
-        <v>46303</v>
-      </c>
+      <c r="I103" s="10"/>
       <c r="J103" s="9">
         <v>46303</v>
       </c>
@@ -7369,13 +7400,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>292</v>
+        <v>181</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7385,17 +7416,17 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="B104" s="5">
-        <v>46225.606777395835</v>
+        <v>46225.606768564816</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46225.61599523148</v>
+        <v>46225.615999965274</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7422,13 +7453,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7438,17 +7469,17 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="B105" s="9">
-        <v>46225.581521562504</v>
+        <v>46225.606777395835</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46225.61624585648</v>
+        <v>46225.61599523148</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7460,10 +7491,10 @@
         <v>212</v>
       </c>
       <c r="I105" s="9">
-        <v>46304</v>
+        <v>46303</v>
       </c>
       <c r="J105" s="9">
-        <v>46304</v>
+        <v>46303</v>
       </c>
       <c r="K105" s="10" t="s">
         <v>26</v>
@@ -7475,43 +7506,33 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>280</v>
+        <v>316</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>286</v>
+        <v>303</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>314</v>
-      </c>
-      <c r="Q105" s="9">
-        <v>46304</v>
-      </c>
-      <c r="R105" s="9">
-        <v>46304</v>
-      </c>
-      <c r="S105" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T105" s="10">
-        <v>0</v>
-      </c>
-      <c r="U105" s="11" t="s">
-        <v>59</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="Q105" s="10"/>
+      <c r="R105" s="10"/>
+      <c r="S105" s="10"/>
+      <c r="T105" s="10"/>
+      <c r="U105" s="10"/>
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="B106" s="5">
-        <v>46225.58152704861</v>
+        <v>46225.581521562504</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46225.61621090278</v>
+        <v>46225.61624585648</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>181</v>
+        <v>324</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7522,7 +7543,9 @@
       <c r="H106" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="I106" s="6"/>
+      <c r="I106" s="5">
+        <v>46304</v>
+      </c>
       <c r="J106" s="5">
         <v>46304</v>
       </c>
@@ -7536,30 +7559,40 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>313</v>
+        <v>291</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>181</v>
+        <v>297</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>316</v>
-      </c>
-      <c r="Q106" s="6"/>
-      <c r="R106" s="6"/>
-      <c r="S106" s="6"/>
-      <c r="T106" s="6"/>
-      <c r="U106" s="6"/>
+        <v>325</v>
+      </c>
+      <c r="Q106" s="5">
+        <v>46304</v>
+      </c>
+      <c r="R106" s="5">
+        <v>46304</v>
+      </c>
+      <c r="S106" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T106" s="6">
+        <v>0</v>
+      </c>
+      <c r="U106" s="11" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="B107" s="9">
-        <v>46225.58153157408</v>
+        <v>46225.58152704861</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46225.61620709491</v>
+        <v>46225.61621090278</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>181</v>
@@ -7587,13 +7620,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="O107" s="10" t="s">
         <v>181</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="Q107" s="10"/>
       <c r="R107" s="10"/>
@@ -7603,17 +7636,17 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="B108" s="5">
-        <v>46225.60680554398</v>
+        <v>46225.58153157408</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46225.616203564816</v>
+        <v>46225.61620709491</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>292</v>
+        <v>181</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7624,9 +7657,7 @@
       <c r="H108" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="I108" s="5">
-        <v>46304</v>
-      </c>
+      <c r="I108" s="6"/>
       <c r="J108" s="5">
         <v>46304</v>
       </c>
@@ -7640,13 +7671,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>292</v>
+        <v>181</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>26</v>
+        <v>327</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -7656,17 +7687,17 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="B109" s="9">
-        <v>46225.60681763889</v>
+        <v>46225.60680554398</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46225.61619854167</v>
+        <v>46225.616203564816</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
@@ -7693,10 +7724,10 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="P109" s="10" t="s">
         <v>26</v>
@@ -7709,27 +7740,33 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="B110" s="5">
-        <v>46225.58153574074</v>
+        <v>46225.60681763889</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46225.60402078704</v>
+        <v>46225.61619854167</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="F110" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H110" s="6"/>
-      <c r="I110" s="6"/>
-      <c r="J110" s="6"/>
+        <v>211</v>
+      </c>
+      <c r="H110" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="I110" s="5">
+        <v>46304</v>
+      </c>
+      <c r="J110" s="5">
+        <v>46304</v>
+      </c>
       <c r="K110" s="6" t="s">
         <v>26</v>
       </c>
@@ -7737,13 +7774,13 @@
         <v>26</v>
       </c>
       <c r="M110" s="6" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>26</v>
+        <v>324</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>322</v>
+        <v>303</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>26</v>
@@ -7756,33 +7793,27 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="B111" s="9">
-        <v>46225.58153866898</v>
+        <v>46225.58153574074</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46225.61649424769</v>
+        <v>46225.60402078704</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="F111" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>325</v>
-      </c>
-      <c r="H111" s="10" t="s">
-        <v>326</v>
-      </c>
-      <c r="I111" s="9">
-        <v>46307</v>
-      </c>
-      <c r="J111" s="9">
-        <v>46311</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H111" s="10"/>
+      <c r="I111" s="10"/>
+      <c r="J111" s="10"/>
       <c r="K111" s="10" t="s">
         <v>26</v>
       </c>
@@ -7790,55 +7821,45 @@
         <v>26</v>
       </c>
       <c r="M111" s="10" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>321</v>
+        <v>26</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>321</v>
-      </c>
-      <c r="Q111" s="9">
-        <v>46311</v>
-      </c>
-      <c r="R111" s="9">
-        <v>46307</v>
-      </c>
-      <c r="S111" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T111" s="10">
-        <v>0</v>
-      </c>
-      <c r="U111" s="11" t="s">
-        <v>59</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q111" s="10"/>
+      <c r="R111" s="10"/>
+      <c r="S111" s="10"/>
+      <c r="T111" s="10"/>
+      <c r="U111" s="10"/>
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="B112" s="5">
-        <v>46225.58154590278</v>
+        <v>46225.58153866898</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46225.61639241898</v>
+        <v>46225.61649424769</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>30</v>
+        <v>336</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>31</v>
+        <v>337</v>
       </c>
       <c r="I112" s="5">
         <v>46307</v>
@@ -7856,13 +7877,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="Q112" s="5">
         <v>46311</v>
@@ -7882,27 +7903,33 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="B113" s="9">
-        <v>46225.59432256944</v>
+        <v>46225.58154590278</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46225.6052183912</v>
+        <v>46225.61639241898</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="F113" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G113" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H113" s="10"/>
-      <c r="I113" s="10"/>
-      <c r="J113" s="10"/>
+        <v>30</v>
+      </c>
+      <c r="H113" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="I113" s="9">
+        <v>46307</v>
+      </c>
+      <c r="J113" s="9">
+        <v>46311</v>
+      </c>
       <c r="K113" s="10" t="s">
         <v>26</v>
       </c>
@@ -7910,52 +7937,56 @@
         <v>26</v>
       </c>
       <c r="M113" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N113" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="O113" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="P113" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="Q113" s="9">
+        <v>46311</v>
+      </c>
+      <c r="R113" s="9">
+        <v>46307</v>
+      </c>
+      <c r="S113" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T113" s="10">
         <v>0</v>
       </c>
-      <c r="N113" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O113" s="10" t="s">
-        <v>332</v>
-      </c>
-      <c r="P113" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q113" s="10"/>
-      <c r="R113" s="10"/>
-      <c r="S113" s="10"/>
-      <c r="T113" s="10"/>
-      <c r="U113" s="10"/>
+      <c r="U113" s="11" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="B114" s="5">
-        <v>46225.59476561342</v>
+        <v>46225.59432256944</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46225.616553796295</v>
+        <v>46225.6052183912</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="F114" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="H114" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="I114" s="5">
-        <v>46314</v>
-      </c>
-      <c r="J114" s="5">
-        <v>46318</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H114" s="6"/>
+      <c r="I114" s="6"/>
+      <c r="J114" s="6"/>
       <c r="K114" s="6" t="s">
         <v>26</v>
       </c>
@@ -7963,46 +7994,36 @@
         <v>26</v>
       </c>
       <c r="M114" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>331</v>
+        <v>26</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>313</v>
+        <v>343</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>335</v>
-      </c>
-      <c r="Q114" s="5">
-        <v>46318</v>
-      </c>
-      <c r="R114" s="5">
-        <v>46314</v>
-      </c>
-      <c r="S114" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T114" s="6">
-        <v>0</v>
-      </c>
-      <c r="U114" s="11" t="s">
-        <v>59</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q114" s="6"/>
+      <c r="R114" s="6"/>
+      <c r="S114" s="6"/>
+      <c r="T114" s="6"/>
+      <c r="U114" s="6"/>
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="B115" s="9">
-        <v>46225.59487494213</v>
+        <v>46225.59476561342</v>
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46225.61655020833</v>
+        <v>46225.616553796295</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
@@ -8014,10 +8035,10 @@
         <v>50</v>
       </c>
       <c r="I115" s="9">
-        <v>46321</v>
+        <v>46314</v>
       </c>
       <c r="J115" s="9">
-        <v>46325</v>
+        <v>46318</v>
       </c>
       <c r="K115" s="10" t="s">
         <v>26</v>
@@ -8029,19 +8050,19 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="Q115" s="9">
-        <v>46325</v>
+        <v>46318</v>
       </c>
       <c r="R115" s="9">
-        <v>46321</v>
+        <v>46314</v>
       </c>
       <c r="S115" s="7" t="s">
         <v>33</v>
@@ -8050,6 +8071,69 @@
         <v>0</v>
       </c>
       <c r="U115" s="11" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="116" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A116" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="B116" s="5">
+        <v>46225.59487494213</v>
+      </c>
+      <c r="C116" s="6"/>
+      <c r="D116" s="5">
+        <v>46225.61655020833</v>
+      </c>
+      <c r="E116" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="F116" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G116" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H116" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I116" s="5">
+        <v>46321</v>
+      </c>
+      <c r="J116" s="5">
+        <v>46325</v>
+      </c>
+      <c r="K116" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L116" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M116" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N116" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="O116" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="P116" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="Q116" s="5">
+        <v>46325</v>
+      </c>
+      <c r="R116" s="5">
+        <v>46321</v>
+      </c>
+      <c r="S116" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T116" s="6">
+        <v>0</v>
+      </c>
+      <c r="U116" s="11" t="s">
         <v>59</v>
       </c>
     </row>

--- a/data/50001580- CIA. RIO MINERALES.xlsx
+++ b/data/50001580- CIA. RIO MINERALES.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1359" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1360" uniqueCount="349">
   <si>
     <t>50001580- "CIA. RIO MINERALES"</t>
   </si>
@@ -779,109 +779,109 @@
     <t>Montaje Alabe OT4378,Montaje Rodete OT4378,Revestimiento OT4378,Montaje motor OT4378</t>
   </si>
   <si>
+    <t>1216788353013131</t>
+  </si>
+  <si>
+    <t>Revestimiento OT4378</t>
+  </si>
+  <si>
+    <t>Montaje:,Montaje Alabe OT4378</t>
+  </si>
+  <si>
+    <t>1216788148296193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,Revestimiento OT4378,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A </t>
+  </si>
+  <si>
+    <t>1216788148296210</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revestimiento OT4378,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A </t>
+  </si>
+  <si>
+    <t>1216788055319708</t>
+  </si>
+  <si>
+    <t>Montaje Alabe OT4378</t>
+  </si>
+  <si>
+    <t>OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,Revestimiento OT4378</t>
+  </si>
+  <si>
+    <t>Montaje:,Montaje Rodete OT4378</t>
+  </si>
+  <si>
+    <t>1216788055319725</t>
+  </si>
+  <si>
+    <t>OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,Recepcion Alabe OT4378,Check Planos OT4378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montaje Alabe OT4378,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A </t>
+  </si>
+  <si>
+    <t>1216788055329220</t>
+  </si>
+  <si>
+    <t>1216788055333603</t>
+  </si>
+  <si>
+    <t>Montaje Rodete OT4378</t>
+  </si>
+  <si>
+    <t>OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,Montaje Alabe OT4378</t>
+  </si>
+  <si>
+    <t>Montaje:,Montaje motor OT4378</t>
+  </si>
+  <si>
+    <t>1216788353064043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion Rodete OT4378,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A </t>
+  </si>
+  <si>
+    <t>OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,Montaje Rodete OT4378</t>
+  </si>
+  <si>
+    <t>1216788353064065</t>
+  </si>
+  <si>
+    <t>1216788353066344</t>
+  </si>
+  <si>
+    <t>Montaje motor OT4378</t>
+  </si>
+  <si>
+    <t>OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,Montaje Rodete OT4378</t>
+  </si>
+  <si>
+    <t>Montaje:,Conexión eléctrica OT4378</t>
+  </si>
+  <si>
+    <t>1216788353066361</t>
+  </si>
+  <si>
+    <t>Recepcion motor OT4378,Check Planos OT4378</t>
+  </si>
+  <si>
+    <t>OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,Montaje motor OT4378</t>
+  </si>
+  <si>
+    <t>1216788240795540</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montaje motor OT4378,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A </t>
+  </si>
+  <si>
     <t>1216991376879757</t>
   </si>
   <si>
     <t>Conexión eléctrica OT4378</t>
   </si>
   <si>
-    <t>Montaje motor OT4378</t>
-  </si>
-  <si>
     <t>Pruebas FAT OT4378</t>
-  </si>
-  <si>
-    <t>1216788353013131</t>
-  </si>
-  <si>
-    <t>Revestimiento OT4378</t>
-  </si>
-  <si>
-    <t>Montaje:,Montaje Alabe OT4378</t>
-  </si>
-  <si>
-    <t>1216788148296193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,Revestimiento OT4378,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A </t>
-  </si>
-  <si>
-    <t>1216788148296210</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revestimiento OT4378,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A </t>
-  </si>
-  <si>
-    <t>1216788055319708</t>
-  </si>
-  <si>
-    <t>Montaje Alabe OT4378</t>
-  </si>
-  <si>
-    <t>OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,Revestimiento OT4378</t>
-  </si>
-  <si>
-    <t>Montaje:,Montaje Rodete OT4378</t>
-  </si>
-  <si>
-    <t>1216788055319725</t>
-  </si>
-  <si>
-    <t>OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,Recepcion Alabe OT4378,Check Planos OT4378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Montaje Alabe OT4378,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A </t>
-  </si>
-  <si>
-    <t>1216788055329220</t>
-  </si>
-  <si>
-    <t>1216788055333603</t>
-  </si>
-  <si>
-    <t>Montaje Rodete OT4378</t>
-  </si>
-  <si>
-    <t>OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,Montaje Alabe OT4378</t>
-  </si>
-  <si>
-    <t>Montaje:,Montaje motor OT4378</t>
-  </si>
-  <si>
-    <t>1216788353064043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion Rodete OT4378,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A </t>
-  </si>
-  <si>
-    <t>OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,Montaje Rodete OT4378</t>
-  </si>
-  <si>
-    <t>1216788353064065</t>
-  </si>
-  <si>
-    <t>1216788353066344</t>
-  </si>
-  <si>
-    <t>OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,Montaje Rodete OT4378</t>
-  </si>
-  <si>
-    <t>Montaje:,Conexión eléctrica OT4378</t>
-  </si>
-  <si>
-    <t>1216788353066361</t>
-  </si>
-  <si>
-    <t>Recepcion motor OT4378,Check Planos OT4378</t>
-  </si>
-  <si>
-    <t>OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,Montaje motor OT4378</t>
-  </si>
-  <si>
-    <t>1216788240795540</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Montaje motor OT4378,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A </t>
   </si>
   <si>
     <t>1216788055348894</t>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46232.60338619213</v>
+        <v>46232.67654627315</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>241</v>
@@ -5608,11 +5608,11 @@
         <v>243</v>
       </c>
       <c r="B71" s="9">
-        <v>46232.60331346065</v>
+        <v>46225.58133395833</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46232.624382951384</v>
+        <v>46232.62438273148</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>244</v>
@@ -5621,14 +5621,16 @@
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H71" s="10"/>
+        <v>77</v>
+      </c>
+      <c r="H71" s="10" t="s">
+        <v>78</v>
+      </c>
       <c r="I71" s="9">
-        <v>46289</v>
+        <v>46275</v>
       </c>
       <c r="J71" s="9">
-        <v>46289</v>
+        <v>46281</v>
       </c>
       <c r="K71" s="10" t="s">
         <v>26</v>
@@ -5643,30 +5645,40 @@
         <v>241</v>
       </c>
       <c r="O71" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="P71" s="10" t="s">
         <v>245</v>
       </c>
-      <c r="P71" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="Q71" s="10"/>
-      <c r="R71" s="10"/>
-      <c r="S71" s="10"/>
-      <c r="T71" s="10"/>
-      <c r="U71" s="10"/>
+      <c r="Q71" s="9">
+        <v>46281</v>
+      </c>
+      <c r="R71" s="9">
+        <v>46275</v>
+      </c>
+      <c r="S71" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T71" s="10">
+        <v>0</v>
+      </c>
+      <c r="U71" s="11" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B72" s="5">
-        <v>46225.58133395833</v>
+        <v>46225.58133853009</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46232.62438273148</v>
+        <v>46225.61483068287</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>248</v>
+        <v>181</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5693,40 +5705,30 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="Q72" s="5">
-        <v>46281</v>
-      </c>
-      <c r="R72" s="5">
-        <v>46275</v>
-      </c>
-      <c r="S72" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T72" s="6">
-        <v>0</v>
-      </c>
-      <c r="U72" s="11" t="s">
-        <v>59</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="Q72" s="6"/>
+      <c r="R72" s="6"/>
+      <c r="S72" s="6"/>
+      <c r="T72" s="6"/>
+      <c r="U72" s="6"/>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B73" s="9">
-        <v>46225.58133853009</v>
+        <v>46225.58134314815</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46225.61483068287</v>
+        <v>46225.61482673611</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>181</v>
@@ -5756,13 +5758,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="O73" s="10" t="s">
         <v>181</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -5772,17 +5774,17 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B74" s="5">
-        <v>46225.58134314815</v>
+        <v>46225.58134744213</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46225.61482673611</v>
+        <v>46232.62438234954</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>181</v>
+        <v>251</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5794,10 +5796,10 @@
         <v>78</v>
       </c>
       <c r="I74" s="5">
-        <v>46275</v>
+        <v>46286</v>
       </c>
       <c r="J74" s="5">
-        <v>46281</v>
+        <v>46286</v>
       </c>
       <c r="K74" s="6" t="s">
         <v>26</v>
@@ -5809,33 +5811,43 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>181</v>
+        <v>252</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="Q74" s="6"/>
-      <c r="R74" s="6"/>
-      <c r="S74" s="6"/>
-      <c r="T74" s="6"/>
-      <c r="U74" s="6"/>
+      <c r="Q74" s="5">
+        <v>46286</v>
+      </c>
+      <c r="R74" s="5">
+        <v>46286</v>
+      </c>
+      <c r="S74" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T74" s="6">
+        <v>0</v>
+      </c>
+      <c r="U74" s="11" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
         <v>254</v>
       </c>
       <c r="B75" s="9">
-        <v>46225.58134744213</v>
+        <v>46225.581351932866</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46232.62438234954</v>
+        <v>46225.61504185185</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>255</v>
+        <v>181</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -5862,40 +5874,30 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="O75" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="P75" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="P75" s="10" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q75" s="9">
-        <v>46286</v>
-      </c>
-      <c r="R75" s="9">
-        <v>46286</v>
-      </c>
-      <c r="S75" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T75" s="10">
-        <v>0</v>
-      </c>
-      <c r="U75" s="11" t="s">
-        <v>59</v>
-      </c>
+      <c r="Q75" s="10"/>
+      <c r="R75" s="10"/>
+      <c r="S75" s="10"/>
+      <c r="T75" s="10"/>
+      <c r="U75" s="10"/>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B76" s="5">
-        <v>46225.581351932866</v>
+        <v>46225.58135922454</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46225.61504185185</v>
+        <v>46225.615038819444</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>181</v>
@@ -5925,13 +5927,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="O76" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="O76" s="6" t="s">
-        <v>259</v>
-      </c>
       <c r="P76" s="6" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -5941,17 +5943,17 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B77" s="9">
-        <v>46225.58135922454</v>
+        <v>46225.5813728588</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46225.615038819444</v>
+        <v>46232.624382071765</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>181</v>
+        <v>259</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -5963,10 +5965,10 @@
         <v>78</v>
       </c>
       <c r="I77" s="9">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="J77" s="9">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="K77" s="10" t="s">
         <v>26</v>
@@ -5978,33 +5980,43 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>260</v>
-      </c>
-      <c r="Q77" s="10"/>
-      <c r="R77" s="10"/>
-      <c r="S77" s="10"/>
-      <c r="T77" s="10"/>
-      <c r="U77" s="10"/>
+        <v>261</v>
+      </c>
+      <c r="Q77" s="9">
+        <v>46287</v>
+      </c>
+      <c r="R77" s="9">
+        <v>46287</v>
+      </c>
+      <c r="S77" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T77" s="10">
+        <v>0</v>
+      </c>
+      <c r="U77" s="11" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
         <v>262</v>
       </c>
       <c r="B78" s="5">
-        <v>46225.5813728588</v>
+        <v>46225.58137722222</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46232.624382071765</v>
+        <v>46225.61518142361</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>263</v>
+        <v>181</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6015,9 +6027,7 @@
       <c r="H78" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="I78" s="5">
-        <v>46287</v>
-      </c>
+      <c r="I78" s="6"/>
       <c r="J78" s="5">
         <v>46287</v>
       </c>
@@ -6031,40 +6041,30 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="O78" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="P78" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="P78" s="6" t="s">
-        <v>265</v>
-      </c>
-      <c r="Q78" s="5">
-        <v>46287</v>
-      </c>
-      <c r="R78" s="5">
-        <v>46287</v>
-      </c>
-      <c r="S78" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T78" s="6">
-        <v>0</v>
-      </c>
-      <c r="U78" s="11" t="s">
-        <v>59</v>
-      </c>
+      <c r="Q78" s="6"/>
+      <c r="R78" s="6"/>
+      <c r="S78" s="6"/>
+      <c r="T78" s="6"/>
+      <c r="U78" s="6"/>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B79" s="9">
-        <v>46225.58137722222</v>
+        <v>46225.58138231482</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46225.61518142361</v>
+        <v>46225.615182291665</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>181</v>
@@ -6092,13 +6092,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="O79" s="10" t="s">
         <v>263</v>
       </c>
-      <c r="O79" s="10" t="s">
-        <v>267</v>
-      </c>
       <c r="P79" s="10" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6108,17 +6108,17 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B80" s="5">
-        <v>46225.58138231482</v>
+        <v>46225.58138733797</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46225.615182291665</v>
+        <v>46232.624381828704</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>181</v>
+        <v>267</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6129,9 +6129,11 @@
       <c r="H80" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="I80" s="6"/>
+      <c r="I80" s="5">
+        <v>46288</v>
+      </c>
       <c r="J80" s="5">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="K80" s="6" t="s">
         <v>26</v>
@@ -6143,33 +6145,43 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>263</v>
+        <v>241</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>268</v>
-      </c>
-      <c r="Q80" s="6"/>
-      <c r="R80" s="6"/>
-      <c r="S80" s="6"/>
-      <c r="T80" s="6"/>
-      <c r="U80" s="6"/>
+        <v>269</v>
+      </c>
+      <c r="Q80" s="5">
+        <v>46288</v>
+      </c>
+      <c r="R80" s="5">
+        <v>46288</v>
+      </c>
+      <c r="S80" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T80" s="6">
+        <v>0</v>
+      </c>
+      <c r="U80" s="11" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
         <v>270</v>
       </c>
       <c r="B81" s="9">
-        <v>46225.58138733797</v>
+        <v>46225.58139180556</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46232.624381828704</v>
+        <v>46225.61534716435</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>245</v>
+        <v>181</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6196,7 +6208,7 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>241</v>
+        <v>267</v>
       </c>
       <c r="O81" s="10" t="s">
         <v>271</v>
@@ -6204,32 +6216,22 @@
       <c r="P81" s="10" t="s">
         <v>272</v>
       </c>
-      <c r="Q81" s="9">
-        <v>46288</v>
-      </c>
-      <c r="R81" s="9">
-        <v>46288</v>
-      </c>
-      <c r="S81" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T81" s="10">
-        <v>0</v>
-      </c>
-      <c r="U81" s="11" t="s">
-        <v>59</v>
-      </c>
+      <c r="Q81" s="10"/>
+      <c r="R81" s="10"/>
+      <c r="S81" s="10"/>
+      <c r="T81" s="10"/>
+      <c r="U81" s="10"/>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
         <v>273</v>
       </c>
       <c r="B82" s="5">
-        <v>46225.58139180556</v>
+        <v>46225.58139752314</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46225.61534716435</v>
+        <v>46225.615343854166</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>181</v>
@@ -6259,13 +6261,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>245</v>
+        <v>267</v>
       </c>
       <c r="O82" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="P82" s="6" t="s">
         <v>274</v>
-      </c>
-      <c r="P82" s="6" t="s">
-        <v>275</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6275,17 +6277,17 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B83" s="9">
-        <v>46225.58139752314</v>
+        <v>46232.60331346065</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46225.615343854166</v>
+        <v>46232.67660064815</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>181</v>
+        <v>276</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6297,10 +6299,10 @@
         <v>78</v>
       </c>
       <c r="I83" s="9">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="J83" s="9">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="K83" s="10" t="s">
         <v>26</v>
@@ -6312,10 +6314,10 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="P83" s="10" t="s">
         <v>277</v>
@@ -6338,7 +6340,7 @@
         <v>46232.62438278935</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>246</v>
+        <v>277</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6426,7 +6428,7 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>246</v>
+        <v>277</v>
       </c>
       <c r="O85" s="10" t="s">
         <v>282</v>
@@ -6477,7 +6479,7 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>246</v>
+        <v>277</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>282</v>

--- a/data/50001580- CIA. RIO MINERALES.xlsx
+++ b/data/50001580- CIA. RIO MINERALES.xlsx
@@ -2970,7 +2970,7 @@
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46232.25114619213</v>
+        <v>46233.168979988426</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>102</v>
@@ -3014,8 +3014,8 @@
       <c r="R25" s="9">
         <v>46231</v>
       </c>
-      <c r="S25" s="7" t="s">
-        <v>33</v>
+      <c r="S25" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="T25" s="10">
         <v>0</v>

--- a/data/50001580- CIA. RIO MINERALES.xlsx
+++ b/data/50001580- CIA. RIO MINERALES.xlsx
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46231.54154219908</v>
+        <v>46234.186226550926</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>169</v>
@@ -4146,8 +4146,8 @@
       <c r="R45" s="9">
         <v>46237</v>
       </c>
-      <c r="S45" s="7" t="s">
-        <v>33</v>
+      <c r="S45" s="12" t="s">
+        <v>167</v>
       </c>
       <c r="T45" s="10">
         <v>0</v>

--- a/data/50001580- CIA. RIO MINERALES.xlsx
+++ b/data/50001580- CIA. RIO MINERALES.xlsx
@@ -551,22 +551,22 @@
     <t>Ingenieria y diseñoo:,Plano Definitivos OT4378</t>
   </si>
   <si>
+    <t>1216788235072362</t>
+  </si>
+  <si>
+    <t>Plano Definitivos OT4378</t>
+  </si>
+  <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,Check Planos OT4378</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1216788235072362</t>
-  </si>
-  <si>
-    <t>Plano Definitivos OT4378</t>
-  </si>
-  <si>
-    <t>Gonzalo Javier Dávila Bade</t>
-  </si>
-  <si>
-    <t>gonzalo.davila@zitron.com</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,Check Planos OT4378</t>
   </si>
   <si>
     <t>1216788352823818</t>
@@ -4039,7 +4039,7 @@
         <v>46231.54139886574</v>
       </c>
       <c r="D44" s="5">
-        <v>46231.54141615741</v>
+        <v>46235.20153063658</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>163</v>
@@ -4083,8 +4083,8 @@
       <c r="R44" s="5">
         <v>46230</v>
       </c>
-      <c r="S44" s="12" t="s">
-        <v>167</v>
+      <c r="S44" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="T44" s="6">
         <v>1</v>
@@ -4095,7 +4095,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B45" s="9">
         <v>46225.58112643519</v>
@@ -4105,16 +4105,16 @@
         <v>46234.186226550926</v>
       </c>
       <c r="E45" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="F45" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G45" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="F45" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G45" s="10" t="s">
+      <c r="H45" s="10" t="s">
         <v>170</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>171</v>
       </c>
       <c r="I45" s="9">
         <v>46237</v>
@@ -4138,7 +4138,7 @@
         <v>163</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q45" s="9">
         <v>46241</v>
@@ -4147,7 +4147,7 @@
         <v>46237</v>
       </c>
       <c r="S45" s="12" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="T45" s="10">
         <v>0</v>
@@ -4198,7 +4198,7 @@
         <v>160</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>174</v>

--- a/data/50001580- CIA. RIO MINERALES.xlsx
+++ b/data/50001580- CIA. RIO MINERALES.xlsx
@@ -2482,7 +2482,7 @@
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="9">
-        <v>46228.19449648148</v>
+        <v>46237.5500087963</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>76</v>
@@ -2532,8 +2532,8 @@
       <c r="T17" s="10">
         <v>0</v>
       </c>
-      <c r="U17" s="12" t="s">
-        <v>53</v>
+      <c r="U17" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46228.19450158565</v>
+        <v>46237.550030706014</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>81</v>
@@ -2595,8 +2595,8 @@
       <c r="T18" s="6">
         <v>0</v>
       </c>
-      <c r="U18" s="12" t="s">
-        <v>53</v>
+      <c r="U18" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46228.19449678241</v>
+        <v>46237.55005269676</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>84</v>
@@ -2658,8 +2658,8 @@
       <c r="T19" s="10">
         <v>0</v>
       </c>
-      <c r="U19" s="12" t="s">
-        <v>53</v>
+      <c r="U19" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46225.613052245375</v>
+        <v>46237.553714594906</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>139</v>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46225.61342412037</v>
+        <v>46237.17292835648</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>90</v>
@@ -4209,8 +4209,8 @@
       <c r="R46" s="5">
         <v>46244</v>
       </c>
-      <c r="S46" s="7" t="s">
-        <v>33</v>
+      <c r="S46" s="12" t="s">
+        <v>172</v>
       </c>
       <c r="T46" s="6">
         <v>0</v>

--- a/data/50001580- CIA. RIO MINERALES.xlsx
+++ b/data/50001580- CIA. RIO MINERALES.xlsx
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46225.61247136574</v>
+        <v>46238.48697899305</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>88</v>
@@ -2768,8 +2768,8 @@
       <c r="T21" s="10">
         <v>0</v>
       </c>
-      <c r="U21" s="11" t="s">
-        <v>59</v>
+      <c r="U21" s="12" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46225.612467824074</v>
+        <v>46238.48697804398</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>93</v>
@@ -2831,8 +2831,8 @@
       <c r="T22" s="6">
         <v>0</v>
       </c>
-      <c r="U22" s="11" t="s">
-        <v>59</v>
+      <c r="U22" s="12" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46225.612464756945</v>
+        <v>46238.486978981484</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>96</v>
@@ -2894,8 +2894,8 @@
       <c r="T23" s="10">
         <v>0</v>
       </c>
-      <c r="U23" s="11" t="s">
-        <v>59</v>
+      <c r="U23" s="12" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46225.61246184028</v>
+        <v>46238.486978483794</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>99</v>
@@ -2957,8 +2957,8 @@
       <c r="T24" s="6">
         <v>0</v>
       </c>
-      <c r="U24" s="11" t="s">
-        <v>59</v>
+      <c r="U24" s="12" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
@@ -3990,7 +3990,7 @@
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46231.54140574074</v>
+        <v>46238.48696734954</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>160</v>
@@ -4100,9 +4100,11 @@
       <c r="B45" s="9">
         <v>46225.58112643519</v>
       </c>
-      <c r="C45" s="10"/>
+      <c r="C45" s="9">
+        <v>46238.48690554398</v>
+      </c>
       <c r="D45" s="9">
-        <v>46234.186226550926</v>
+        <v>46238.48692438657</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>168</v>
@@ -4150,10 +4152,10 @@
         <v>172</v>
       </c>
       <c r="T45" s="10">
-        <v>0</v>
-      </c>
-      <c r="U45" s="12" t="s">
-        <v>53</v>
+        <v>1</v>
+      </c>
+      <c r="U45" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
@@ -4163,9 +4165,11 @@
       <c r="B46" s="5">
         <v>46225.58113097222</v>
       </c>
-      <c r="C46" s="6"/>
+      <c r="C46" s="5">
+        <v>46238.48695046296</v>
+      </c>
       <c r="D46" s="5">
-        <v>46237.17292835648</v>
+        <v>46238.48696579861</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>90</v>
@@ -4213,10 +4217,10 @@
         <v>172</v>
       </c>
       <c r="T46" s="6">
-        <v>0</v>
-      </c>
-      <c r="U46" s="11" t="s">
-        <v>59</v>
+        <v>1</v>
+      </c>
+      <c r="U46" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
@@ -4995,7 +4999,7 @@
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46225.614318611115</v>
+        <v>46238.48696543981</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>181</v>
@@ -5048,7 +5052,7 @@
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46225.61431550926</v>
+        <v>46238.48696587963</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>181</v>
@@ -5164,7 +5168,7 @@
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46225.61443357639</v>
+        <v>46238.486964502314</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>181</v>
@@ -5215,7 +5219,7 @@
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46225.61443052083</v>
+        <v>46238.48696504629</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>181</v>
@@ -5844,7 +5848,7 @@
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46225.61504185185</v>
+        <v>46238.48696328704</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>181</v>
@@ -5897,7 +5901,7 @@
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46225.615038819444</v>
+        <v>46238.486963877316</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>181</v>
@@ -6178,7 +6182,7 @@
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46225.61534716435</v>
+        <v>46238.48696648148</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>181</v>
@@ -6231,7 +6235,7 @@
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46225.615343854166</v>
+        <v>46238.48696707176</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>181</v>

--- a/data/50001580- CIA. RIO MINERALES.xlsx
+++ b/data/50001580- CIA. RIO MINERALES.xlsx
@@ -326,6 +326,9 @@
     <t>Propuesta compras:,Generación OC corte laser  OT4378</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>1216788054986657</t>
   </si>
   <si>
@@ -564,9 +567,6 @@
   </si>
   <si>
     <t>Ingenieria y diseñoo:,Check Planos OT4378</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1216788352823818</t>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46238.48697899305</v>
+        <v>46239.17859991898</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>88</v>
@@ -2762,8 +2762,8 @@
       <c r="R21" s="9">
         <v>46245</v>
       </c>
-      <c r="S21" s="7" t="s">
-        <v>33</v>
+      <c r="S21" s="12" t="s">
+        <v>92</v>
       </c>
       <c r="T21" s="10">
         <v>0</v>
@@ -2774,17 +2774,17 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B22" s="5">
         <v>46225.5809840625</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46238.48697804398</v>
+        <v>46239.1785987037</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
@@ -2817,7 +2817,7 @@
         <v>90</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q22" s="5">
         <v>46246</v>
@@ -2825,8 +2825,8 @@
       <c r="R22" s="5">
         <v>46245</v>
       </c>
-      <c r="S22" s="7" t="s">
-        <v>33</v>
+      <c r="S22" s="12" t="s">
+        <v>92</v>
       </c>
       <c r="T22" s="6">
         <v>0</v>
@@ -2837,17 +2837,17 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B23" s="9">
         <v>46225.58098827546</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46238.486978981484</v>
+        <v>46239.17859943287</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
@@ -2880,7 +2880,7 @@
         <v>90</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q23" s="9">
         <v>46246</v>
@@ -2888,8 +2888,8 @@
       <c r="R23" s="9">
         <v>46245</v>
       </c>
-      <c r="S23" s="7" t="s">
-        <v>33</v>
+      <c r="S23" s="12" t="s">
+        <v>92</v>
       </c>
       <c r="T23" s="10">
         <v>0</v>
@@ -2900,17 +2900,17 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B24" s="5">
         <v>46225.58100011574</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46238.486978483794</v>
+        <v>46239.17859915509</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
@@ -2943,7 +2943,7 @@
         <v>90</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q24" s="5">
         <v>46246</v>
@@ -2951,8 +2951,8 @@
       <c r="R24" s="5">
         <v>46245</v>
       </c>
-      <c r="S24" s="7" t="s">
-        <v>33</v>
+      <c r="S24" s="12" t="s">
+        <v>92</v>
       </c>
       <c r="T24" s="6">
         <v>0</v>
@@ -2963,7 +2963,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B25" s="9">
         <v>46225.59619364583</v>
@@ -2973,7 +2973,7 @@
         <v>46233.168979988426</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
@@ -3006,7 +3006,7 @@
         <v>48</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q25" s="9">
         <v>46232</v>
@@ -3026,7 +3026,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B26" s="5">
         <v>46225.58087085648</v>
@@ -3036,7 +3036,7 @@
         <v>46225.596821886575</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>25</v>
@@ -3060,7 +3060,7 @@
         <v>26</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P26" s="6" t="s">
         <v>26</v>
@@ -3073,7 +3073,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B27" s="9">
         <v>46225.58100560185</v>
@@ -3083,16 +3083,16 @@
         <v>46225.61255763889</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I27" s="9">
         <v>46247</v>
@@ -3110,13 +3110,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q27" s="9">
         <v>46259</v>
@@ -3136,7 +3136,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B28" s="5">
         <v>46225.58101144676</v>
@@ -3146,16 +3146,16 @@
         <v>46225.61262662037</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I28" s="5">
         <v>46247</v>
@@ -3173,13 +3173,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>88</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3195,7 +3195,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B29" s="9">
         <v>46225.581017233795</v>
@@ -3205,16 +3205,16 @@
         <v>46225.61262351852</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I29" s="9">
         <v>46251</v>
@@ -3232,13 +3232,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
@@ -3254,7 +3254,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B30" s="5">
         <v>46225.58102277778</v>
@@ -3264,16 +3264,16 @@
         <v>46225.61255446759</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I30" s="5">
         <v>46247</v>
@@ -3291,10 +3291,10 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P30" s="6" t="s">
         <v>26</v>
@@ -3317,7 +3317,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B31" s="9">
         <v>46225.58102737268</v>
@@ -3327,16 +3327,16 @@
         <v>46225.61269579861</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I31" s="9">
         <v>46247</v>
@@ -3354,13 +3354,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3370,7 +3370,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B32" s="5">
         <v>46225.581032222224</v>
@@ -3380,16 +3380,16 @@
         <v>46225.612692442126</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I32" s="5">
         <v>46251</v>
@@ -3407,13 +3407,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3423,7 +3423,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B33" s="9">
         <v>46225.581037199074</v>
@@ -3433,16 +3433,16 @@
         <v>46225.61279568287</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I33" s="9">
         <v>46247</v>
@@ -3460,10 +3460,10 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="P33" s="10" t="s">
         <v>26</v>
@@ -3486,7 +3486,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B34" s="5">
         <v>46225.58104158565</v>
@@ -3496,16 +3496,16 @@
         <v>46225.61298453704</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I34" s="5">
         <v>46247</v>
@@ -3523,13 +3523,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3539,7 +3539,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B35" s="9">
         <v>46225.5810464699</v>
@@ -3549,16 +3549,16 @@
         <v>46225.61298125</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I35" s="9">
         <v>46251</v>
@@ -3576,13 +3576,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -3592,7 +3592,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B36" s="5">
         <v>46225.58105121528</v>
@@ -3602,16 +3602,16 @@
         <v>46225.61316422454</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I36" s="5">
         <v>46247</v>
@@ -3629,10 +3629,10 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3655,7 +3655,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B37" s="9">
         <v>46225.58109630787</v>
@@ -3665,16 +3665,16 @@
         <v>46237.553714594906</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I37" s="9">
         <v>46247</v>
@@ -3692,13 +3692,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3708,7 +3708,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B38" s="5">
         <v>46225.58110178241</v>
@@ -3718,16 +3718,16 @@
         <v>46225.613047719904</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I38" s="5">
         <v>46258</v>
@@ -3745,13 +3745,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3761,7 +3761,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B39" s="9">
         <v>46225.58110600694</v>
@@ -3771,16 +3771,16 @@
         <v>46225.613129363424</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I39" s="9">
         <v>46289</v>
@@ -3798,13 +3798,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
@@ -3814,7 +3814,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B40" s="5">
         <v>46225.59682005787</v>
@@ -3824,16 +3824,16 @@
         <v>46225.6133383912</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I40" s="5">
         <v>46233</v>
@@ -3851,10 +3851,10 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>26</v>
@@ -3877,7 +3877,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B41" s="9">
         <v>46225.59686481481</v>
@@ -3887,16 +3887,16 @@
         <v>46225.613313634254</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I41" s="9">
         <v>46233</v>
@@ -3914,13 +3914,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -3930,7 +3930,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B42" s="5">
         <v>46225.59692966435</v>
@@ -3940,16 +3940,16 @@
         <v>46225.613310636574</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I42" s="5">
         <v>46244</v>
@@ -3967,13 +3967,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -3983,7 +3983,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B43" s="9">
         <v>46225.58111748843</v>
@@ -3993,7 +3993,7 @@
         <v>46238.48696734954</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>25</v>
@@ -4017,7 +4017,7 @@
         <v>26</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4030,7 +4030,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B44" s="5">
         <v>46225.58112127315</v>
@@ -4042,16 +4042,16 @@
         <v>46235.20153063658</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I44" s="5">
         <v>46230</v>
@@ -4069,13 +4069,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>68</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q44" s="5">
         <v>46234</v>
@@ -4095,7 +4095,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B45" s="9">
         <v>46225.58112643519</v>
@@ -4107,16 +4107,16 @@
         <v>46238.48692438657</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I45" s="9">
         <v>46237</v>
@@ -4134,13 +4134,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q45" s="9">
         <v>46241</v>
@@ -4149,7 +4149,7 @@
         <v>46237</v>
       </c>
       <c r="S45" s="12" t="s">
-        <v>172</v>
+        <v>92</v>
       </c>
       <c r="T45" s="10">
         <v>1</v>
@@ -4178,10 +4178,10 @@
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I46" s="5">
         <v>46244</v>
@@ -4199,10 +4199,10 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>174</v>
@@ -4214,7 +4214,7 @@
         <v>46244</v>
       </c>
       <c r="S46" s="12" t="s">
-        <v>172</v>
+        <v>92</v>
       </c>
       <c r="T46" s="6">
         <v>1</v>
@@ -4262,13 +4262,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O47" s="10" t="s">
         <v>179</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q47" s="9">
         <v>46290</v>
@@ -4481,7 +4481,7 @@
         <v>186</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P51" s="10" t="s">
         <v>192</v>
@@ -4544,7 +4544,7 @@
         <v>186</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>195</v>
@@ -4607,7 +4607,7 @@
         <v>186</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P53" s="10" t="s">
         <v>198</v>
@@ -4646,10 +4646,10 @@
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I54" s="5">
         <v>46261</v>
@@ -4709,10 +4709,10 @@
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I55" s="9">
         <v>46261</v>
@@ -4772,10 +4772,10 @@
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I56" s="5">
         <v>46261</v>
@@ -4876,7 +4876,7 @@
         <v>46225.6142333912</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
@@ -4906,7 +4906,7 @@
         <v>208</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>213</v>
@@ -4939,7 +4939,7 @@
         <v>46225.61435628472</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
@@ -5029,7 +5029,7 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>216</v>
@@ -5082,7 +5082,7 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O61" s="10" t="s">
         <v>219</v>
@@ -5114,10 +5114,10 @@
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I62" s="5">
         <v>46274</v>
@@ -5177,10 +5177,10 @@
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I63" s="10"/>
       <c r="J63" s="9">
@@ -5228,10 +5228,10 @@
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I64" s="6"/>
       <c r="J64" s="5">
@@ -5539,7 +5539,7 @@
         <v>229</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P69" s="10" t="s">
         <v>58</v>

--- a/data/50001580- CIA. RIO MINERALES.xlsx
+++ b/data/50001580- CIA. RIO MINERALES.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1360" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1324" uniqueCount="341">
   <si>
     <t>50001580- "CIA. RIO MINERALES"</t>
   </si>
@@ -1025,7 +1025,7 @@
     <t>Despacho OT4378</t>
   </si>
   <si>
-    <t>Instalación Tableros,Costos,Logistica:,Gestion</t>
+    <t>Costos,Logistica:,Gestion</t>
   </si>
   <si>
     <t>1216788240917408</t>
@@ -1071,30 +1071,6 @@
   </si>
   <si>
     <t>Costos</t>
-  </si>
-  <si>
-    <t>1216769310026562</t>
-  </si>
-  <si>
-    <t>Puesta en Marcha</t>
-  </si>
-  <si>
-    <t>Instalación Tableros,Puesta en marcha  tableros</t>
-  </si>
-  <si>
-    <t>1216769310026568</t>
-  </si>
-  <si>
-    <t>Instalación Tableros</t>
-  </si>
-  <si>
-    <t>Puesta en marcha  tableros,Puesta en Marcha</t>
-  </si>
-  <si>
-    <t>1216769310026569</t>
-  </si>
-  <si>
-    <t>Puesta en marcha  tableros</t>
   </si>
 </sst>
 </file>
@@ -1618,7 +1594,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U116"/>
+  <dimension ref="A1:U113"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10.4" customWidth="1"/>
@@ -7535,7 +7511,7 @@
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46225.61624585648</v>
+        <v>46240.71657643518</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>324</v>
@@ -7967,179 +7943,6 @@
         <v>0</v>
       </c>
       <c r="U113" s="11" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="114" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A114" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="B114" s="5">
-        <v>46225.59432256944</v>
-      </c>
-      <c r="C114" s="6"/>
-      <c r="D114" s="5">
-        <v>46225.6052183912</v>
-      </c>
-      <c r="E114" s="6" t="s">
-        <v>342</v>
-      </c>
-      <c r="F114" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G114" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H114" s="6"/>
-      <c r="I114" s="6"/>
-      <c r="J114" s="6"/>
-      <c r="K114" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L114" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M114" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="N114" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O114" s="6" t="s">
-        <v>343</v>
-      </c>
-      <c r="P114" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q114" s="6"/>
-      <c r="R114" s="6"/>
-      <c r="S114" s="6"/>
-      <c r="T114" s="6"/>
-      <c r="U114" s="6"/>
-    </row>
-    <row r="115" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A115" s="8" t="s">
-        <v>344</v>
-      </c>
-      <c r="B115" s="9">
-        <v>46225.59476561342</v>
-      </c>
-      <c r="C115" s="10"/>
-      <c r="D115" s="9">
-        <v>46225.616553796295</v>
-      </c>
-      <c r="E115" s="10" t="s">
-        <v>345</v>
-      </c>
-      <c r="F115" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G115" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="H115" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="I115" s="9">
-        <v>46314</v>
-      </c>
-      <c r="J115" s="9">
-        <v>46318</v>
-      </c>
-      <c r="K115" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L115" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M115" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N115" s="10" t="s">
-        <v>342</v>
-      </c>
-      <c r="O115" s="10" t="s">
-        <v>324</v>
-      </c>
-      <c r="P115" s="10" t="s">
-        <v>346</v>
-      </c>
-      <c r="Q115" s="9">
-        <v>46318</v>
-      </c>
-      <c r="R115" s="9">
-        <v>46314</v>
-      </c>
-      <c r="S115" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T115" s="10">
-        <v>0</v>
-      </c>
-      <c r="U115" s="11" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="116" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A116" s="4" t="s">
-        <v>347</v>
-      </c>
-      <c r="B116" s="5">
-        <v>46225.59487494213</v>
-      </c>
-      <c r="C116" s="6"/>
-      <c r="D116" s="5">
-        <v>46225.61655020833</v>
-      </c>
-      <c r="E116" s="6" t="s">
-        <v>348</v>
-      </c>
-      <c r="F116" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G116" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="H116" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="I116" s="5">
-        <v>46321</v>
-      </c>
-      <c r="J116" s="5">
-        <v>46325</v>
-      </c>
-      <c r="K116" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L116" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M116" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N116" s="6" t="s">
-        <v>342</v>
-      </c>
-      <c r="O116" s="6" t="s">
-        <v>345</v>
-      </c>
-      <c r="P116" s="6" t="s">
-        <v>342</v>
-      </c>
-      <c r="Q116" s="5">
-        <v>46325</v>
-      </c>
-      <c r="R116" s="5">
-        <v>46321</v>
-      </c>
-      <c r="S116" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T116" s="6">
-        <v>0</v>
-      </c>
-      <c r="U116" s="11" t="s">
         <v>59</v>
       </c>
     </row>

--- a/data/50001580- CIA. RIO MINERALES.xlsx
+++ b/data/50001580- CIA. RIO MINERALES.xlsx
@@ -3860,7 +3860,7 @@
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46225.613313634254</v>
+        <v>46241.17189372685</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>104</v>

--- a/data/50001580- CIA. RIO MINERALES.xlsx
+++ b/data/50001580- CIA. RIO MINERALES.xlsx
@@ -4080,7 +4080,7 @@
         <v>46238.48690554398</v>
       </c>
       <c r="D45" s="9">
-        <v>46238.48692438657</v>
+        <v>46242.202891875</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>169</v>
@@ -4124,8 +4124,8 @@
       <c r="R45" s="9">
         <v>46237</v>
       </c>
-      <c r="S45" s="12" t="s">
-        <v>92</v>
+      <c r="S45" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="T45" s="10">
         <v>1</v>

--- a/data/50001580- CIA. RIO MINERALES.xlsx
+++ b/data/50001580- CIA. RIO MINERALES.xlsx
@@ -4145,7 +4145,7 @@
         <v>46238.48695046296</v>
       </c>
       <c r="D46" s="5">
-        <v>46238.48696579861</v>
+        <v>46245.1918381713</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>90</v>
@@ -4189,8 +4189,8 @@
       <c r="R46" s="5">
         <v>46244</v>
       </c>
-      <c r="S46" s="12" t="s">
-        <v>92</v>
+      <c r="S46" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="T46" s="6">
         <v>1</v>

--- a/data/50001580- CIA. RIO MINERALES.xlsx
+++ b/data/50001580- CIA. RIO MINERALES.xlsx
@@ -2694,7 +2694,7 @@
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46239.17859991898</v>
+        <v>46246.25088460648</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>88</v>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46239.1785987037</v>
+        <v>46246.25088115741</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>94</v>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46239.17859943287</v>
+        <v>46246.25088320602</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>97</v>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46239.17859915509</v>
+        <v>46246.25088594908</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>100</v>

--- a/data/50001580- CIA. RIO MINERALES.xlsx
+++ b/data/50001580- CIA. RIO MINERALES.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1324" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1324" uniqueCount="340">
   <si>
     <t>50001580- "CIA. RIO MINERALES"</t>
   </si>
@@ -324,9 +324,6 @@
   </si>
   <si>
     <t>Propuesta compras:,Generación OC corte laser  OT4378</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1216788054986657</t>
@@ -2694,7 +2691,7 @@
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46246.25088460648</v>
+        <v>46247.17789210648</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>88</v>
@@ -2738,8 +2735,8 @@
       <c r="R21" s="9">
         <v>46245</v>
       </c>
-      <c r="S21" s="12" t="s">
-        <v>92</v>
+      <c r="S21" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="T21" s="10">
         <v>0</v>
@@ -2750,17 +2747,17 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B22" s="5">
         <v>46225.5809840625</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46246.25088115741</v>
+        <v>46247.17788666667</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
@@ -2793,7 +2790,7 @@
         <v>90</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q22" s="5">
         <v>46246</v>
@@ -2801,8 +2798,8 @@
       <c r="R22" s="5">
         <v>46245</v>
       </c>
-      <c r="S22" s="12" t="s">
-        <v>92</v>
+      <c r="S22" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="T22" s="6">
         <v>0</v>
@@ -2813,17 +2810,17 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B23" s="9">
         <v>46225.58098827546</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46246.25088320602</v>
+        <v>46247.17788644676</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
@@ -2856,7 +2853,7 @@
         <v>90</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Q23" s="9">
         <v>46246</v>
@@ -2864,8 +2861,8 @@
       <c r="R23" s="9">
         <v>46245</v>
       </c>
-      <c r="S23" s="12" t="s">
-        <v>92</v>
+      <c r="S23" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="T23" s="10">
         <v>0</v>
@@ -2876,17 +2873,17 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B24" s="5">
         <v>46225.58100011574</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46246.25088594908</v>
+        <v>46247.17788643518</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
@@ -2919,7 +2916,7 @@
         <v>90</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Q24" s="5">
         <v>46246</v>
@@ -2927,8 +2924,8 @@
       <c r="R24" s="5">
         <v>46245</v>
       </c>
-      <c r="S24" s="12" t="s">
-        <v>92</v>
+      <c r="S24" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="T24" s="6">
         <v>0</v>
@@ -2939,7 +2936,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B25" s="9">
         <v>46225.59619364583</v>
@@ -2949,7 +2946,7 @@
         <v>46233.168979988426</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
@@ -2982,7 +2979,7 @@
         <v>48</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="Q25" s="9">
         <v>46232</v>
@@ -3002,7 +2999,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B26" s="5">
         <v>46225.58087085648</v>
@@ -3012,7 +3009,7 @@
         <v>46225.596821886575</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>25</v>
@@ -3036,7 +3033,7 @@
         <v>26</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="P26" s="6" t="s">
         <v>26</v>
@@ -3049,7 +3046,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B27" s="9">
         <v>46225.58100560185</v>
@@ -3059,16 +3056,16 @@
         <v>46225.61255763889</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="H27" s="10" t="s">
         <v>109</v>
-      </c>
-      <c r="H27" s="10" t="s">
-        <v>110</v>
       </c>
       <c r="I27" s="9">
         <v>46247</v>
@@ -3086,13 +3083,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q27" s="9">
         <v>46259</v>
@@ -3112,7 +3109,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B28" s="5">
         <v>46225.58101144676</v>
@@ -3122,16 +3119,16 @@
         <v>46225.61262662037</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>109</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>110</v>
       </c>
       <c r="I28" s="5">
         <v>46247</v>
@@ -3149,13 +3146,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>88</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3171,7 +3168,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B29" s="9">
         <v>46225.581017233795</v>
@@ -3181,16 +3178,16 @@
         <v>46225.61262351852</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="H29" s="10" t="s">
         <v>109</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>110</v>
       </c>
       <c r="I29" s="9">
         <v>46251</v>
@@ -3208,13 +3205,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
@@ -3230,7 +3227,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B30" s="5">
         <v>46225.58102277778</v>
@@ -3240,16 +3237,16 @@
         <v>46225.61255446759</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>109</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>110</v>
       </c>
       <c r="I30" s="5">
         <v>46247</v>
@@ -3267,10 +3264,10 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="P30" s="6" t="s">
         <v>26</v>
@@ -3293,7 +3290,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B31" s="9">
         <v>46225.58102737268</v>
@@ -3303,16 +3300,16 @@
         <v>46225.61269579861</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="H31" s="10" t="s">
         <v>109</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>110</v>
       </c>
       <c r="I31" s="9">
         <v>46247</v>
@@ -3330,13 +3327,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3346,7 +3343,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B32" s="5">
         <v>46225.581032222224</v>
@@ -3356,16 +3353,16 @@
         <v>46225.612692442126</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>109</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>110</v>
       </c>
       <c r="I32" s="5">
         <v>46251</v>
@@ -3383,13 +3380,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3399,7 +3396,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B33" s="9">
         <v>46225.581037199074</v>
@@ -3409,16 +3406,16 @@
         <v>46225.61279568287</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="H33" s="10" t="s">
         <v>109</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>110</v>
       </c>
       <c r="I33" s="9">
         <v>46247</v>
@@ -3436,10 +3433,10 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="P33" s="10" t="s">
         <v>26</v>
@@ -3462,7 +3459,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B34" s="5">
         <v>46225.58104158565</v>
@@ -3472,16 +3469,16 @@
         <v>46225.61298453704</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>109</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>110</v>
       </c>
       <c r="I34" s="5">
         <v>46247</v>
@@ -3499,13 +3496,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3515,7 +3512,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B35" s="9">
         <v>46225.5810464699</v>
@@ -3525,16 +3522,16 @@
         <v>46225.61298125</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="H35" s="10" t="s">
         <v>109</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>110</v>
       </c>
       <c r="I35" s="9">
         <v>46251</v>
@@ -3552,13 +3549,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -3568,7 +3565,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B36" s="5">
         <v>46225.58105121528</v>
@@ -3578,16 +3575,16 @@
         <v>46225.61316422454</v>
       </c>
       <c r="E36" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G36" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="F36" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G36" s="6" t="s">
+      <c r="H36" s="6" t="s">
         <v>136</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>137</v>
       </c>
       <c r="I36" s="5">
         <v>46247</v>
@@ -3605,10 +3602,10 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3631,7 +3628,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B37" s="9">
         <v>46225.58109630787</v>
@@ -3641,16 +3638,16 @@
         <v>46237.553714594906</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="H37" s="10" t="s">
         <v>136</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>137</v>
       </c>
       <c r="I37" s="9">
         <v>46247</v>
@@ -3668,13 +3665,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O37" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="P37" s="10" t="s">
         <v>141</v>
-      </c>
-      <c r="P37" s="10" t="s">
-        <v>142</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3684,7 +3681,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B38" s="5">
         <v>46225.58110178241</v>
@@ -3694,16 +3691,16 @@
         <v>46225.613047719904</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>136</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>137</v>
       </c>
       <c r="I38" s="5">
         <v>46258</v>
@@ -3721,13 +3718,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3737,7 +3734,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B39" s="9">
         <v>46225.58110600694</v>
@@ -3747,16 +3744,16 @@
         <v>46225.613129363424</v>
       </c>
       <c r="E39" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G39" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="F39" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G39" s="10" t="s">
+      <c r="H39" s="10" t="s">
         <v>148</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>149</v>
       </c>
       <c r="I39" s="9">
         <v>46289</v>
@@ -3774,13 +3771,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
@@ -3790,7 +3787,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B40" s="5">
         <v>46225.59682005787</v>
@@ -3800,16 +3797,16 @@
         <v>46225.6133383912</v>
       </c>
       <c r="E40" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G40" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="F40" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G40" s="6" t="s">
+      <c r="H40" s="6" t="s">
         <v>152</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>153</v>
       </c>
       <c r="I40" s="5">
         <v>46233</v>
@@ -3827,10 +3824,10 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>26</v>
@@ -3853,7 +3850,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B41" s="9">
         <v>46225.59686481481</v>
@@ -3863,16 +3860,16 @@
         <v>46241.17189372685</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="H41" s="10" t="s">
         <v>152</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>153</v>
       </c>
       <c r="I41" s="9">
         <v>46233</v>
@@ -3890,13 +3887,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -3906,7 +3903,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B42" s="5">
         <v>46225.59692966435</v>
@@ -3916,16 +3913,16 @@
         <v>46225.613310636574</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="H42" s="6" t="s">
         <v>152</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>153</v>
       </c>
       <c r="I42" s="5">
         <v>46244</v>
@@ -3943,13 +3940,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -3959,7 +3956,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B43" s="9">
         <v>46225.58111748843</v>
@@ -3969,7 +3966,7 @@
         <v>46238.48696734954</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>25</v>
@@ -3993,7 +3990,7 @@
         <v>26</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4006,7 +4003,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B44" s="5">
         <v>46225.58112127315</v>
@@ -4018,16 +4015,16 @@
         <v>46235.20153063658</v>
       </c>
       <c r="E44" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G44" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="F44" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G44" s="6" t="s">
+      <c r="H44" s="6" t="s">
         <v>165</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>166</v>
       </c>
       <c r="I44" s="5">
         <v>46230</v>
@@ -4045,13 +4042,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>68</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q44" s="5">
         <v>46234</v>
@@ -4071,7 +4068,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B45" s="9">
         <v>46225.58112643519</v>
@@ -4083,16 +4080,16 @@
         <v>46242.202891875</v>
       </c>
       <c r="E45" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="F45" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G45" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="F45" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G45" s="10" t="s">
+      <c r="H45" s="10" t="s">
         <v>170</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>171</v>
       </c>
       <c r="I45" s="9">
         <v>46237</v>
@@ -4110,13 +4107,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q45" s="9">
         <v>46241</v>
@@ -4136,7 +4133,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B46" s="5">
         <v>46225.58113097222</v>
@@ -4154,10 +4151,10 @@
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="H46" s="6" t="s">
         <v>165</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>166</v>
       </c>
       <c r="I46" s="5">
         <v>46244</v>
@@ -4175,13 +4172,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q46" s="5">
         <v>46244</v>
@@ -4201,7 +4198,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B47" s="9">
         <v>46225.58114445602</v>
@@ -4211,16 +4208,16 @@
         <v>46225.61347256944</v>
       </c>
       <c r="E47" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="F47" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="F47" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G47" s="10" t="s">
+      <c r="H47" s="10" t="s">
         <v>177</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>178</v>
       </c>
       <c r="I47" s="9">
         <v>46290</v>
@@ -4238,13 +4235,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q47" s="9">
         <v>46290</v>
@@ -4264,7 +4261,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B48" s="5">
         <v>46225.58114871528</v>
@@ -4274,16 +4271,16 @@
         <v>46225.61551950232</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>177</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>178</v>
       </c>
       <c r="I48" s="5">
         <v>46290</v>
@@ -4301,13 +4298,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="O48" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="P48" s="6" t="s">
         <v>181</v>
-      </c>
-      <c r="P48" s="6" t="s">
-        <v>182</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4317,7 +4314,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B49" s="9">
         <v>46225.58115283565</v>
@@ -4327,16 +4324,16 @@
         <v>46225.615519513885</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="H49" s="10" t="s">
         <v>177</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>178</v>
       </c>
       <c r="I49" s="9">
         <v>46290</v>
@@ -4354,13 +4351,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q49" s="10"/>
       <c r="R49" s="10"/>
@@ -4370,7 +4367,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B50" s="5">
         <v>46225.581171631944</v>
@@ -4380,7 +4377,7 @@
         <v>46225.59181146991</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>25</v>
@@ -4404,7 +4401,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4417,7 +4414,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B51" s="9">
         <v>46225.58117489584</v>
@@ -4427,16 +4424,16 @@
         <v>46225.61367097222</v>
       </c>
       <c r="E51" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="F51" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G51" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="F51" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G51" s="10" t="s">
+      <c r="H51" s="10" t="s">
         <v>190</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>191</v>
       </c>
       <c r="I51" s="9">
         <v>46260</v>
@@ -4454,13 +4451,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Q51" s="9">
         <v>46260</v>
@@ -4480,7 +4477,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B52" s="5">
         <v>46225.58118028935</v>
@@ -4490,16 +4487,16 @@
         <v>46225.613667349535</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>190</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>191</v>
       </c>
       <c r="I52" s="5">
         <v>46260</v>
@@ -4517,13 +4514,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q52" s="5">
         <v>46260</v>
@@ -4543,7 +4540,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B53" s="9">
         <v>46225.58118576389</v>
@@ -4553,16 +4550,16 @@
         <v>46225.61366387732</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="H53" s="10" t="s">
         <v>190</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>191</v>
       </c>
       <c r="I53" s="9">
         <v>46260</v>
@@ -4580,13 +4577,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q53" s="9">
         <v>46260</v>
@@ -4606,7 +4603,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B54" s="5">
         <v>46225.58119107639</v>
@@ -4616,16 +4613,16 @@
         <v>46225.61417395833</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>148</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>149</v>
       </c>
       <c r="I54" s="5">
         <v>46261</v>
@@ -4643,13 +4640,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q54" s="5">
         <v>46261</v>
@@ -4669,7 +4666,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B55" s="9">
         <v>46225.58119642361</v>
@@ -4679,16 +4676,16 @@
         <v>46225.61417104167</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="H55" s="10" t="s">
         <v>148</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>149</v>
       </c>
       <c r="I55" s="9">
         <v>46261</v>
@@ -4706,13 +4703,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q55" s="9">
         <v>46261</v>
@@ -4732,7 +4729,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B56" s="5">
         <v>46225.581201678244</v>
@@ -4742,16 +4739,16 @@
         <v>46225.61416773148</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>148</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>149</v>
       </c>
       <c r="I56" s="5">
         <v>46261</v>
@@ -4769,13 +4766,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q56" s="5">
         <v>46261</v>
@@ -4795,7 +4792,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B57" s="9">
         <v>46225.58120702546</v>
@@ -4805,7 +4802,7 @@
         <v>46225.59190644676</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>25</v>
@@ -4829,7 +4826,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P57" s="10" t="s">
         <v>26</v>
@@ -4842,7 +4839,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B58" s="5">
         <v>46225.58121010417</v>
@@ -4852,16 +4849,16 @@
         <v>46225.6142333912</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>211</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>212</v>
       </c>
       <c r="I58" s="5">
         <v>46262</v>
@@ -4879,13 +4876,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q58" s="5">
         <v>46266</v>
@@ -4905,7 +4902,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B59" s="9">
         <v>46225.581215474536</v>
@@ -4915,16 +4912,16 @@
         <v>46225.61435628472</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="H59" s="10" t="s">
         <v>211</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>212</v>
       </c>
       <c r="I59" s="9">
         <v>46267</v>
@@ -4942,13 +4939,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Q59" s="9">
         <v>46273</v>
@@ -4968,7 +4965,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B60" s="5">
         <v>46225.581219618056</v>
@@ -4978,16 +4975,16 @@
         <v>46238.48696543981</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>211</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>212</v>
       </c>
       <c r="I60" s="5">
         <v>46267</v>
@@ -5005,13 +5002,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O60" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="P60" s="6" t="s">
         <v>216</v>
-      </c>
-      <c r="P60" s="6" t="s">
-        <v>217</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5021,7 +5018,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B61" s="9">
         <v>46225.58123596065</v>
@@ -5031,16 +5028,16 @@
         <v>46238.48696587963</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="H61" s="10" t="s">
         <v>211</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>212</v>
       </c>
       <c r="I61" s="9">
         <v>46267</v>
@@ -5058,13 +5055,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O61" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="P61" s="10" t="s">
         <v>219</v>
-      </c>
-      <c r="P61" s="10" t="s">
-        <v>220</v>
       </c>
       <c r="Q61" s="10"/>
       <c r="R61" s="10"/>
@@ -5074,7 +5071,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B62" s="5">
         <v>46225.58129219907</v>
@@ -5084,16 +5081,16 @@
         <v>46225.61447392361</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>148</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>149</v>
       </c>
       <c r="I62" s="5">
         <v>46274</v>
@@ -5111,13 +5108,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Q62" s="5">
         <v>46274</v>
@@ -5137,7 +5134,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B63" s="9">
         <v>46225.58129802083</v>
@@ -5147,16 +5144,16 @@
         <v>46238.486964502314</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="H63" s="10" t="s">
         <v>148</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>149</v>
       </c>
       <c r="I63" s="10"/>
       <c r="J63" s="9">
@@ -5172,13 +5169,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O63" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="P63" s="10" t="s">
         <v>224</v>
-      </c>
-      <c r="P63" s="10" t="s">
-        <v>225</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5188,7 +5185,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B64" s="5">
         <v>46225.581304374995</v>
@@ -5198,16 +5195,16 @@
         <v>46238.48696504629</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>148</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>149</v>
       </c>
       <c r="I64" s="6"/>
       <c r="J64" s="5">
@@ -5223,13 +5220,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5239,7 +5236,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B65" s="9">
         <v>46225.58131015046</v>
@@ -5249,7 +5246,7 @@
         <v>46225.59759329861</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>25</v>
@@ -5273,7 +5270,7 @@
         <v>26</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="P65" s="10" t="s">
         <v>26</v>
@@ -5286,7 +5283,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B66" s="5">
         <v>46225.58131376158</v>
@@ -5296,16 +5293,16 @@
         <v>46232.18544357639</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>190</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>191</v>
       </c>
       <c r="I66" s="5">
         <v>46230</v>
@@ -5323,13 +5320,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="O66" s="6" t="s">
         <v>76</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q66" s="5">
         <v>46231</v>
@@ -5349,7 +5346,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B67" s="9">
         <v>46225.58131929398</v>
@@ -5359,16 +5356,16 @@
         <v>46232.18544451389</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="H67" s="10" t="s">
         <v>190</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>191</v>
       </c>
       <c r="I67" s="9">
         <v>46230</v>
@@ -5386,13 +5383,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="O67" s="10" t="s">
         <v>81</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Q67" s="9">
         <v>46231</v>
@@ -5412,7 +5409,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B68" s="5">
         <v>46225.58132505787</v>
@@ -5422,16 +5419,16 @@
         <v>46232.18544357639</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>190</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>191</v>
       </c>
       <c r="I68" s="5">
         <v>46230</v>
@@ -5449,13 +5446,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>84</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q68" s="5">
         <v>46231</v>
@@ -5475,7 +5472,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B69" s="9">
         <v>46225.597591134254</v>
@@ -5491,10 +5488,10 @@
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="H69" s="10" t="s">
         <v>190</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>191</v>
       </c>
       <c r="I69" s="9">
         <v>46293</v>
@@ -5512,10 +5509,10 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="P69" s="10" t="s">
         <v>58</v>
@@ -5538,7 +5535,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B70" s="5">
         <v>46225.58133054398</v>
@@ -5548,7 +5545,7 @@
         <v>46232.67654627315</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>25</v>
@@ -5572,7 +5569,7 @@
         <v>26</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -5585,7 +5582,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B71" s="9">
         <v>46225.58133395833</v>
@@ -5595,7 +5592,7 @@
         <v>46232.62438273148</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
@@ -5622,13 +5619,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="Q71" s="9">
         <v>46281</v>
@@ -5648,7 +5645,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B72" s="5">
         <v>46225.58133853009</v>
@@ -5658,7 +5655,7 @@
         <v>46225.61483068287</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5685,13 +5682,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5701,7 +5698,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B73" s="9">
         <v>46225.58134314815</v>
@@ -5711,7 +5708,7 @@
         <v>46225.61482673611</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5738,13 +5735,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -5754,7 +5751,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B74" s="5">
         <v>46225.58134744213</v>
@@ -5764,7 +5761,7 @@
         <v>46232.62438234954</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5791,13 +5788,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="O74" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="P74" s="6" t="s">
         <v>252</v>
-      </c>
-      <c r="P74" s="6" t="s">
-        <v>253</v>
       </c>
       <c r="Q74" s="5">
         <v>46286</v>
@@ -5817,7 +5814,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B75" s="9">
         <v>46225.581351932866</v>
@@ -5827,7 +5824,7 @@
         <v>46238.48696328704</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -5854,13 +5851,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O75" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="P75" s="10" t="s">
         <v>255</v>
-      </c>
-      <c r="P75" s="10" t="s">
-        <v>256</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -5870,7 +5867,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B76" s="5">
         <v>46225.58135922454</v>
@@ -5880,7 +5877,7 @@
         <v>46238.486963877316</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5907,13 +5904,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O76" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="P76" s="6" t="s">
         <v>255</v>
-      </c>
-      <c r="P76" s="6" t="s">
-        <v>256</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -5923,7 +5920,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B77" s="9">
         <v>46225.5813728588</v>
@@ -5933,7 +5930,7 @@
         <v>46232.624382071765</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -5960,13 +5957,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="O77" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="P77" s="10" t="s">
         <v>260</v>
-      </c>
-      <c r="P77" s="10" t="s">
-        <v>261</v>
       </c>
       <c r="Q77" s="9">
         <v>46287</v>
@@ -5986,7 +5983,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B78" s="5">
         <v>46225.58137722222</v>
@@ -5996,7 +5993,7 @@
         <v>46225.61518142361</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6021,13 +6018,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="O78" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="P78" s="6" t="s">
         <v>263</v>
-      </c>
-      <c r="P78" s="6" t="s">
-        <v>264</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6037,7 +6034,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B79" s="9">
         <v>46225.58138231482</v>
@@ -6047,7 +6044,7 @@
         <v>46225.615182291665</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6072,13 +6069,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="O79" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="P79" s="10" t="s">
         <v>263</v>
-      </c>
-      <c r="P79" s="10" t="s">
-        <v>264</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6088,7 +6085,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B80" s="5">
         <v>46225.58138733797</v>
@@ -6098,7 +6095,7 @@
         <v>46232.624381828704</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6125,13 +6122,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="O80" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="P80" s="6" t="s">
         <v>268</v>
-      </c>
-      <c r="P80" s="6" t="s">
-        <v>269</v>
       </c>
       <c r="Q80" s="5">
         <v>46288</v>
@@ -6151,7 +6148,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B81" s="9">
         <v>46225.58139180556</v>
@@ -6161,7 +6158,7 @@
         <v>46238.48696648148</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6188,13 +6185,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="O81" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="P81" s="10" t="s">
         <v>271</v>
-      </c>
-      <c r="P81" s="10" t="s">
-        <v>272</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6204,7 +6201,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B82" s="5">
         <v>46225.58139752314</v>
@@ -6214,7 +6211,7 @@
         <v>46238.48696707176</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6241,13 +6238,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6257,7 +6254,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B83" s="9">
         <v>46232.60331346065</v>
@@ -6267,7 +6264,7 @@
         <v>46232.67660064815</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6294,13 +6291,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6310,7 +6307,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B84" s="5">
         <v>46225.58140275463</v>
@@ -6320,7 +6317,7 @@
         <v>46232.62438278935</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6347,13 +6344,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="O84" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="P84" s="6" t="s">
         <v>279</v>
-      </c>
-      <c r="P84" s="6" t="s">
-        <v>280</v>
       </c>
       <c r="Q84" s="5">
         <v>46289</v>
@@ -6373,7 +6370,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B85" s="9">
         <v>46225.581407488426</v>
@@ -6383,7 +6380,7 @@
         <v>46225.61551967592</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6408,13 +6405,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="O85" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="P85" s="10" t="s">
         <v>282</v>
-      </c>
-      <c r="P85" s="10" t="s">
-        <v>283</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6424,7 +6421,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B86" s="5">
         <v>46225.581414988425</v>
@@ -6434,7 +6431,7 @@
         <v>46225.61552056713</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6459,13 +6456,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="O86" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="P86" s="6" t="s">
         <v>282</v>
-      </c>
-      <c r="P86" s="6" t="s">
-        <v>283</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6475,7 +6472,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B87" s="9">
         <v>46225.58145953703</v>
@@ -6485,7 +6482,7 @@
         <v>46232.62438171296</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6512,10 +6509,10 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="P87" s="10" t="s">
         <v>26</v>
@@ -6538,7 +6535,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B88" s="5">
         <v>46225.58146568287</v>
@@ -6548,7 +6545,7 @@
         <v>46225.61568175926</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6575,13 +6572,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6591,7 +6588,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B89" s="9">
         <v>46225.58147099537</v>
@@ -6601,7 +6598,7 @@
         <v>46225.615682592594</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6628,13 +6625,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6644,7 +6641,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B90" s="5">
         <v>46225.58147606481</v>
@@ -6654,7 +6651,7 @@
         <v>46225.60367008102</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>25</v>
@@ -6678,7 +6675,7 @@
         <v>26</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>26</v>
@@ -6691,7 +6688,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B91" s="9">
         <v>46225.58147990741</v>
@@ -6701,16 +6698,16 @@
         <v>46225.615814467594</v>
       </c>
       <c r="E91" s="10" t="s">
+        <v>293</v>
+      </c>
+      <c r="F91" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G91" s="10" t="s">
         <v>294</v>
       </c>
-      <c r="F91" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G91" s="10" t="s">
+      <c r="H91" s="10" t="s">
         <v>295</v>
-      </c>
-      <c r="H91" s="10" t="s">
-        <v>296</v>
       </c>
       <c r="I91" s="9">
         <v>46301</v>
@@ -6728,13 +6725,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O91" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="P91" s="10" t="s">
         <v>297</v>
-      </c>
-      <c r="P91" s="10" t="s">
-        <v>298</v>
       </c>
       <c r="Q91" s="9">
         <v>46301</v>
@@ -6754,7 +6751,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B92" s="5">
         <v>46225.58148496528</v>
@@ -6764,16 +6761,16 @@
         <v>46225.61578579861</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="H92" s="6" t="s">
         <v>295</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>296</v>
       </c>
       <c r="I92" s="6"/>
       <c r="J92" s="5">
@@ -6789,13 +6786,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6805,7 +6802,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B93" s="9">
         <v>46225.58148953704</v>
@@ -6815,16 +6812,16 @@
         <v>46225.61578274306</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="H93" s="10" t="s">
         <v>295</v>
-      </c>
-      <c r="H93" s="10" t="s">
-        <v>296</v>
       </c>
       <c r="I93" s="9">
         <v>46301</v>
@@ -6842,13 +6839,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -6858,7 +6855,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B94" s="5">
         <v>46225.6055390625</v>
@@ -6868,16 +6865,16 @@
         <v>46225.61577960648</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="H94" s="6" t="s">
         <v>295</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>296</v>
       </c>
       <c r="I94" s="6"/>
       <c r="J94" s="5">
@@ -6893,13 +6890,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="O94" s="6" t="s">
         <v>61</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -6909,7 +6906,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B95" s="9">
         <v>46225.605553333335</v>
@@ -6919,16 +6916,16 @@
         <v>46225.61577443287</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="H95" s="10" t="s">
         <v>295</v>
-      </c>
-      <c r="H95" s="10" t="s">
-        <v>296</v>
       </c>
       <c r="I95" s="10"/>
       <c r="J95" s="9">
@@ -6944,13 +6941,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="O95" s="10" t="s">
         <v>65</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -6960,7 +6957,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B96" s="5">
         <v>46225.581494178245</v>
@@ -6970,7 +6967,7 @@
         <v>46225.61592174768</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -6995,10 +6992,10 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>26</v>
@@ -7021,7 +7018,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B97" s="9">
         <v>46225.5814984375</v>
@@ -7031,7 +7028,7 @@
         <v>46225.615894421295</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7058,13 +7055,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7074,7 +7071,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B98" s="5">
         <v>46225.58150320602</v>
@@ -7084,7 +7081,7 @@
         <v>46225.61589104167</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7111,13 +7108,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7127,7 +7124,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B99" s="9">
         <v>46225.60673211806</v>
@@ -7137,7 +7134,7 @@
         <v>46225.615888125</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7164,13 +7161,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7180,7 +7177,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B100" s="5">
         <v>46225.60674163194</v>
@@ -7190,7 +7187,7 @@
         <v>46225.61588293982</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7217,13 +7214,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7233,7 +7230,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B101" s="9">
         <v>46225.58150777778</v>
@@ -7243,16 +7240,16 @@
         <v>46225.61603868056</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="H101" s="10" t="s">
         <v>211</v>
-      </c>
-      <c r="H101" s="10" t="s">
-        <v>212</v>
       </c>
       <c r="I101" s="9">
         <v>46303</v>
@@ -7270,13 +7267,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="Q101" s="9">
         <v>46303</v>
@@ -7296,7 +7293,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B102" s="5">
         <v>46225.58151239583</v>
@@ -7306,16 +7303,16 @@
         <v>46225.61600570602</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="H102" s="6" t="s">
         <v>211</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>212</v>
       </c>
       <c r="I102" s="6"/>
       <c r="J102" s="5">
@@ -7331,13 +7328,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7347,7 +7344,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B103" s="9">
         <v>46225.58151694444</v>
@@ -7357,16 +7354,16 @@
         <v>46225.61600274306</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="H103" s="10" t="s">
         <v>211</v>
-      </c>
-      <c r="H103" s="10" t="s">
-        <v>212</v>
       </c>
       <c r="I103" s="10"/>
       <c r="J103" s="9">
@@ -7382,13 +7379,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7398,7 +7395,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B104" s="5">
         <v>46225.606768564816</v>
@@ -7408,16 +7405,16 @@
         <v>46225.615999965274</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="H104" s="6" t="s">
         <v>211</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>212</v>
       </c>
       <c r="I104" s="5">
         <v>46303</v>
@@ -7435,13 +7432,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7451,7 +7448,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B105" s="9">
         <v>46225.606777395835</v>
@@ -7461,16 +7458,16 @@
         <v>46225.61599523148</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="H105" s="10" t="s">
         <v>211</v>
-      </c>
-      <c r="H105" s="10" t="s">
-        <v>212</v>
       </c>
       <c r="I105" s="9">
         <v>46303</v>
@@ -7488,13 +7485,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7504,7 +7501,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B106" s="5">
         <v>46225.581521562504</v>
@@ -7514,16 +7511,16 @@
         <v>46240.71657643518</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="H106" s="6" t="s">
         <v>211</v>
-      </c>
-      <c r="H106" s="6" t="s">
-        <v>212</v>
       </c>
       <c r="I106" s="5">
         <v>46304</v>
@@ -7541,13 +7538,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="Q106" s="5">
         <v>46304</v>
@@ -7567,7 +7564,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B107" s="9">
         <v>46225.58152704861</v>
@@ -7577,16 +7574,16 @@
         <v>46225.61621090278</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="H107" s="10" t="s">
         <v>211</v>
-      </c>
-      <c r="H107" s="10" t="s">
-        <v>212</v>
       </c>
       <c r="I107" s="10"/>
       <c r="J107" s="9">
@@ -7602,13 +7599,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Q107" s="10"/>
       <c r="R107" s="10"/>
@@ -7618,7 +7615,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B108" s="5">
         <v>46225.58153157408</v>
@@ -7628,16 +7625,16 @@
         <v>46225.61620709491</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="H108" s="6" t="s">
         <v>211</v>
-      </c>
-      <c r="H108" s="6" t="s">
-        <v>212</v>
       </c>
       <c r="I108" s="6"/>
       <c r="J108" s="5">
@@ -7653,13 +7650,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -7669,7 +7666,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B109" s="9">
         <v>46225.60680554398</v>
@@ -7679,16 +7676,16 @@
         <v>46225.616203564816</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="H109" s="10" t="s">
         <v>211</v>
-      </c>
-      <c r="H109" s="10" t="s">
-        <v>212</v>
       </c>
       <c r="I109" s="9">
         <v>46304</v>
@@ -7706,10 +7703,10 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P109" s="10" t="s">
         <v>26</v>
@@ -7722,7 +7719,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B110" s="5">
         <v>46225.60681763889</v>
@@ -7732,16 +7729,16 @@
         <v>46225.61619854167</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="H110" s="6" t="s">
         <v>211</v>
-      </c>
-      <c r="H110" s="6" t="s">
-        <v>212</v>
       </c>
       <c r="I110" s="5">
         <v>46304</v>
@@ -7759,10 +7756,10 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>26</v>
@@ -7775,7 +7772,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B111" s="9">
         <v>46225.58153574074</v>
@@ -7785,7 +7782,7 @@
         <v>46225.60402078704</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>25</v>
@@ -7809,7 +7806,7 @@
         <v>26</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="P111" s="10" t="s">
         <v>26</v>
@@ -7822,7 +7819,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B112" s="5">
         <v>46225.58153866898</v>
@@ -7832,16 +7829,16 @@
         <v>46225.61649424769</v>
       </c>
       <c r="E112" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="F112" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G112" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="F112" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G112" s="6" t="s">
+      <c r="H112" s="6" t="s">
         <v>336</v>
-      </c>
-      <c r="H112" s="6" t="s">
-        <v>337</v>
       </c>
       <c r="I112" s="5">
         <v>46307</v>
@@ -7859,13 +7856,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="Q112" s="5">
         <v>46311</v>
@@ -7885,7 +7882,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B113" s="9">
         <v>46225.58154590278</v>
@@ -7895,7 +7892,7 @@
         <v>46225.61639241898</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
@@ -7922,13 +7919,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="P113" s="10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="Q113" s="9">
         <v>46311</v>

--- a/data/50001580- CIA. RIO MINERALES.xlsx
+++ b/data/50001580- CIA. RIO MINERALES.xlsx
@@ -3116,7 +3116,7 @@
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46225.61262662037</v>
+        <v>46248.17134739584</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>112</v>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46225.61269579861</v>
+        <v>46248.17134908565</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>94</v>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46225.61298453704</v>
+        <v>46248.17135226852</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>100</v>

--- a/data/50001580- CIA. RIO MINERALES.xlsx
+++ b/data/50001580- CIA. RIO MINERALES.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1324" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1324" uniqueCount="341">
   <si>
     <t>50001580- "CIA. RIO MINERALES"</t>
   </si>
@@ -381,6 +381,9 @@
   </si>
   <si>
     <t>Generación OC corte laser  OT4378,Fabricacion corte laser OT4378</t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1216788240366658</t>
@@ -3053,7 +3056,7 @@
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46225.61255763889</v>
+        <v>46252.20325089121</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>106</v>
@@ -3097,8 +3100,8 @@
       <c r="R27" s="9">
         <v>46247</v>
       </c>
-      <c r="S27" s="7" t="s">
-        <v>33</v>
+      <c r="S27" s="12" t="s">
+        <v>111</v>
       </c>
       <c r="T27" s="10">
         <v>0</v>
@@ -3109,7 +3112,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B28" s="5">
         <v>46225.58101144676</v>
@@ -3119,7 +3122,7 @@
         <v>46248.17134739584</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
@@ -3152,7 +3155,7 @@
         <v>88</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3168,7 +3171,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B29" s="9">
         <v>46225.581017233795</v>
@@ -3178,7 +3181,7 @@
         <v>46225.61262351852</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
@@ -3208,10 +3211,10 @@
         <v>106</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
@@ -3227,17 +3230,17 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B30" s="5">
         <v>46225.58102277778</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46225.61255446759</v>
+        <v>46252.203251087965</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
@@ -3267,7 +3270,7 @@
         <v>105</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P30" s="6" t="s">
         <v>26</v>
@@ -3278,8 +3281,8 @@
       <c r="R30" s="5">
         <v>46247</v>
       </c>
-      <c r="S30" s="7" t="s">
-        <v>33</v>
+      <c r="S30" s="12" t="s">
+        <v>111</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
@@ -3290,7 +3293,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B31" s="9">
         <v>46225.58102737268</v>
@@ -3327,13 +3330,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O31" s="10" t="s">
         <v>93</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3343,7 +3346,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B32" s="5">
         <v>46225.581032222224</v>
@@ -3353,7 +3356,7 @@
         <v>46225.612692442126</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
@@ -3380,13 +3383,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>94</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3396,17 +3399,17 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B33" s="9">
         <v>46225.581037199074</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46225.61279568287</v>
+        <v>46252.20325114584</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
@@ -3436,7 +3439,7 @@
         <v>105</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="P33" s="10" t="s">
         <v>26</v>
@@ -3447,8 +3450,8 @@
       <c r="R33" s="9">
         <v>46247</v>
       </c>
-      <c r="S33" s="7" t="s">
-        <v>33</v>
+      <c r="S33" s="12" t="s">
+        <v>111</v>
       </c>
       <c r="T33" s="10">
         <v>0</v>
@@ -3459,7 +3462,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B34" s="5">
         <v>46225.58104158565</v>
@@ -3496,13 +3499,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>99</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3512,7 +3515,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B35" s="9">
         <v>46225.5810464699</v>
@@ -3522,7 +3525,7 @@
         <v>46225.61298125</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
@@ -3549,13 +3552,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O35" s="10" t="s">
         <v>100</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -3565,7 +3568,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B36" s="5">
         <v>46225.58105121528</v>
@@ -3575,16 +3578,16 @@
         <v>46225.61316422454</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I36" s="5">
         <v>46247</v>
@@ -3605,7 +3608,7 @@
         <v>105</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3628,7 +3631,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B37" s="9">
         <v>46225.58109630787</v>
@@ -3638,16 +3641,16 @@
         <v>46237.553714594906</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I37" s="9">
         <v>46247</v>
@@ -3665,13 +3668,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3681,7 +3684,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B38" s="5">
         <v>46225.58110178241</v>
@@ -3691,16 +3694,16 @@
         <v>46225.613047719904</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I38" s="5">
         <v>46258</v>
@@ -3718,13 +3721,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3734,7 +3737,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B39" s="9">
         <v>46225.58110600694</v>
@@ -3744,16 +3747,16 @@
         <v>46225.613129363424</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I39" s="9">
         <v>46289</v>
@@ -3771,13 +3774,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
@@ -3787,7 +3790,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B40" s="5">
         <v>46225.59682005787</v>
@@ -3797,16 +3800,16 @@
         <v>46225.6133383912</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I40" s="5">
         <v>46233</v>
@@ -3827,7 +3830,7 @@
         <v>105</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>26</v>
@@ -3850,7 +3853,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B41" s="9">
         <v>46225.59686481481</v>
@@ -3866,10 +3869,10 @@
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I41" s="9">
         <v>46233</v>
@@ -3887,13 +3890,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O41" s="10" t="s">
         <v>102</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -3903,7 +3906,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B42" s="5">
         <v>46225.59692966435</v>
@@ -3913,16 +3916,16 @@
         <v>46225.613310636574</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I42" s="5">
         <v>46244</v>
@@ -3940,13 +3943,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>103</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -3956,7 +3959,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B43" s="9">
         <v>46225.58111748843</v>
@@ -3966,7 +3969,7 @@
         <v>46238.48696734954</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>25</v>
@@ -3990,7 +3993,7 @@
         <v>26</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4003,7 +4006,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B44" s="5">
         <v>46225.58112127315</v>
@@ -4015,16 +4018,16 @@
         <v>46235.20153063658</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I44" s="5">
         <v>46230</v>
@@ -4042,13 +4045,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>68</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q44" s="5">
         <v>46234</v>
@@ -4068,7 +4071,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B45" s="9">
         <v>46225.58112643519</v>
@@ -4080,16 +4083,16 @@
         <v>46242.202891875</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I45" s="9">
         <v>46237</v>
@@ -4107,13 +4110,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q45" s="9">
         <v>46241</v>
@@ -4133,7 +4136,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B46" s="5">
         <v>46225.58113097222</v>
@@ -4151,10 +4154,10 @@
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I46" s="5">
         <v>46244</v>
@@ -4172,13 +4175,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q46" s="5">
         <v>46244</v>
@@ -4198,7 +4201,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B47" s="9">
         <v>46225.58114445602</v>
@@ -4208,16 +4211,16 @@
         <v>46225.61347256944</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I47" s="9">
         <v>46290</v>
@@ -4235,13 +4238,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q47" s="9">
         <v>46290</v>
@@ -4261,7 +4264,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B48" s="5">
         <v>46225.58114871528</v>
@@ -4271,16 +4274,16 @@
         <v>46225.61551950232</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I48" s="5">
         <v>46290</v>
@@ -4298,13 +4301,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4314,7 +4317,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B49" s="9">
         <v>46225.58115283565</v>
@@ -4324,16 +4327,16 @@
         <v>46225.615519513885</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I49" s="9">
         <v>46290</v>
@@ -4351,13 +4354,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q49" s="10"/>
       <c r="R49" s="10"/>
@@ -4367,7 +4370,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B50" s="5">
         <v>46225.581171631944</v>
@@ -4377,7 +4380,7 @@
         <v>46225.59181146991</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>25</v>
@@ -4401,7 +4404,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4414,7 +4417,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B51" s="9">
         <v>46225.58117489584</v>
@@ -4424,16 +4427,16 @@
         <v>46225.61367097222</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I51" s="9">
         <v>46260</v>
@@ -4451,13 +4454,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q51" s="9">
         <v>46260</v>
@@ -4477,7 +4480,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B52" s="5">
         <v>46225.58118028935</v>
@@ -4487,16 +4490,16 @@
         <v>46225.613667349535</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I52" s="5">
         <v>46260</v>
@@ -4514,13 +4517,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q52" s="5">
         <v>46260</v>
@@ -4540,7 +4543,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B53" s="9">
         <v>46225.58118576389</v>
@@ -4550,16 +4553,16 @@
         <v>46225.61366387732</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I53" s="9">
         <v>46260</v>
@@ -4577,13 +4580,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q53" s="9">
         <v>46260</v>
@@ -4603,7 +4606,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B54" s="5">
         <v>46225.58119107639</v>
@@ -4613,16 +4616,16 @@
         <v>46225.61417395833</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I54" s="5">
         <v>46261</v>
@@ -4640,13 +4643,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q54" s="5">
         <v>46261</v>
@@ -4666,7 +4669,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B55" s="9">
         <v>46225.58119642361</v>
@@ -4676,16 +4679,16 @@
         <v>46225.61417104167</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I55" s="9">
         <v>46261</v>
@@ -4703,13 +4706,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q55" s="9">
         <v>46261</v>
@@ -4729,7 +4732,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B56" s="5">
         <v>46225.581201678244</v>
@@ -4739,16 +4742,16 @@
         <v>46225.61416773148</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I56" s="5">
         <v>46261</v>
@@ -4766,13 +4769,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q56" s="5">
         <v>46261</v>
@@ -4792,7 +4795,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B57" s="9">
         <v>46225.58120702546</v>
@@ -4802,7 +4805,7 @@
         <v>46225.59190644676</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>25</v>
@@ -4826,7 +4829,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P57" s="10" t="s">
         <v>26</v>
@@ -4839,7 +4842,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B58" s="5">
         <v>46225.58121010417</v>
@@ -4855,10 +4858,10 @@
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I58" s="5">
         <v>46262</v>
@@ -4876,13 +4879,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>96</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q58" s="5">
         <v>46266</v>
@@ -4902,7 +4905,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B59" s="9">
         <v>46225.581215474536</v>
@@ -4912,16 +4915,16 @@
         <v>46225.61435628472</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I59" s="9">
         <v>46267</v>
@@ -4939,13 +4942,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q59" s="9">
         <v>46273</v>
@@ -4965,7 +4968,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B60" s="5">
         <v>46225.581219618056</v>
@@ -4975,16 +4978,16 @@
         <v>46238.48696543981</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I60" s="5">
         <v>46267</v>
@@ -5002,13 +5005,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5018,7 +5021,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B61" s="9">
         <v>46225.58123596065</v>
@@ -5028,16 +5031,16 @@
         <v>46238.48696587963</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I61" s="9">
         <v>46267</v>
@@ -5055,13 +5058,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q61" s="10"/>
       <c r="R61" s="10"/>
@@ -5071,7 +5074,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B62" s="5">
         <v>46225.58129219907</v>
@@ -5081,16 +5084,16 @@
         <v>46225.61447392361</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I62" s="5">
         <v>46274</v>
@@ -5108,13 +5111,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q62" s="5">
         <v>46274</v>
@@ -5134,7 +5137,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B63" s="9">
         <v>46225.58129802083</v>
@@ -5144,16 +5147,16 @@
         <v>46238.486964502314</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I63" s="10"/>
       <c r="J63" s="9">
@@ -5169,13 +5172,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5185,7 +5188,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B64" s="5">
         <v>46225.581304374995</v>
@@ -5195,16 +5198,16 @@
         <v>46238.48696504629</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I64" s="6"/>
       <c r="J64" s="5">
@@ -5220,13 +5223,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5236,7 +5239,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B65" s="9">
         <v>46225.58131015046</v>
@@ -5246,7 +5249,7 @@
         <v>46225.59759329861</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>25</v>
@@ -5270,7 +5273,7 @@
         <v>26</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P65" s="10" t="s">
         <v>26</v>
@@ -5283,7 +5286,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B66" s="5">
         <v>46225.58131376158</v>
@@ -5293,16 +5296,16 @@
         <v>46232.18544357639</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I66" s="5">
         <v>46230</v>
@@ -5320,13 +5323,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O66" s="6" t="s">
         <v>76</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q66" s="5">
         <v>46231</v>
@@ -5346,7 +5349,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B67" s="9">
         <v>46225.58131929398</v>
@@ -5356,16 +5359,16 @@
         <v>46232.18544451389</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I67" s="9">
         <v>46230</v>
@@ -5383,13 +5386,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O67" s="10" t="s">
         <v>81</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q67" s="9">
         <v>46231</v>
@@ -5409,7 +5412,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B68" s="5">
         <v>46225.58132505787</v>
@@ -5419,16 +5422,16 @@
         <v>46232.18544357639</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I68" s="5">
         <v>46230</v>
@@ -5446,13 +5449,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>84</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q68" s="5">
         <v>46231</v>
@@ -5472,7 +5475,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B69" s="9">
         <v>46225.597591134254</v>
@@ -5488,10 +5491,10 @@
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I69" s="9">
         <v>46293</v>
@@ -5509,10 +5512,10 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P69" s="10" t="s">
         <v>58</v>
@@ -5535,7 +5538,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B70" s="5">
         <v>46225.58133054398</v>
@@ -5545,7 +5548,7 @@
         <v>46232.67654627315</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>25</v>
@@ -5569,7 +5572,7 @@
         <v>26</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -5582,7 +5585,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B71" s="9">
         <v>46225.58133395833</v>
@@ -5592,7 +5595,7 @@
         <v>46232.62438273148</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
@@ -5619,13 +5622,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q71" s="9">
         <v>46281</v>
@@ -5645,7 +5648,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B72" s="5">
         <v>46225.58133853009</v>
@@ -5655,7 +5658,7 @@
         <v>46225.61483068287</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5682,13 +5685,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5698,7 +5701,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B73" s="9">
         <v>46225.58134314815</v>
@@ -5708,7 +5711,7 @@
         <v>46225.61482673611</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5735,13 +5738,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -5751,7 +5754,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B74" s="5">
         <v>46225.58134744213</v>
@@ -5761,7 +5764,7 @@
         <v>46232.62438234954</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5788,13 +5791,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q74" s="5">
         <v>46286</v>
@@ -5814,7 +5817,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B75" s="9">
         <v>46225.581351932866</v>
@@ -5824,7 +5827,7 @@
         <v>46238.48696328704</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -5851,13 +5854,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -5867,7 +5870,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B76" s="5">
         <v>46225.58135922454</v>
@@ -5877,7 +5880,7 @@
         <v>46238.486963877316</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5904,13 +5907,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -5920,7 +5923,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B77" s="9">
         <v>46225.5813728588</v>
@@ -5930,7 +5933,7 @@
         <v>46232.624382071765</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -5957,13 +5960,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q77" s="9">
         <v>46287</v>
@@ -5983,7 +5986,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B78" s="5">
         <v>46225.58137722222</v>
@@ -5993,7 +5996,7 @@
         <v>46225.61518142361</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6018,13 +6021,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6034,7 +6037,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B79" s="9">
         <v>46225.58138231482</v>
@@ -6044,7 +6047,7 @@
         <v>46225.615182291665</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6069,13 +6072,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6085,7 +6088,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B80" s="5">
         <v>46225.58138733797</v>
@@ -6095,7 +6098,7 @@
         <v>46232.624381828704</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6122,13 +6125,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q80" s="5">
         <v>46288</v>
@@ -6148,7 +6151,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B81" s="9">
         <v>46225.58139180556</v>
@@ -6158,7 +6161,7 @@
         <v>46238.48696648148</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6185,13 +6188,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q81" s="10"/>
       <c r="R81" s="10"/>
@@ -6201,7 +6204,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B82" s="5">
         <v>46225.58139752314</v>
@@ -6211,7 +6214,7 @@
         <v>46238.48696707176</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6238,13 +6241,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6254,7 +6257,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B83" s="9">
         <v>46232.60331346065</v>
@@ -6264,7 +6267,7 @@
         <v>46232.67660064815</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6291,13 +6294,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6307,7 +6310,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B84" s="5">
         <v>46225.58140275463</v>
@@ -6317,7 +6320,7 @@
         <v>46232.62438278935</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6344,13 +6347,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q84" s="5">
         <v>46289</v>
@@ -6370,7 +6373,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B85" s="9">
         <v>46225.581407488426</v>
@@ -6380,7 +6383,7 @@
         <v>46225.61551967592</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6405,13 +6408,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6421,7 +6424,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B86" s="5">
         <v>46225.581414988425</v>
@@ -6431,7 +6434,7 @@
         <v>46225.61552056713</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6456,13 +6459,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6472,7 +6475,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B87" s="9">
         <v>46225.58145953703</v>
@@ -6482,7 +6485,7 @@
         <v>46232.62438171296</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6509,10 +6512,10 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="P87" s="10" t="s">
         <v>26</v>
@@ -6535,7 +6538,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B88" s="5">
         <v>46225.58146568287</v>
@@ -6545,7 +6548,7 @@
         <v>46225.61568175926</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6572,13 +6575,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6588,7 +6591,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B89" s="9">
         <v>46225.58147099537</v>
@@ -6598,7 +6601,7 @@
         <v>46225.615682592594</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6625,13 +6628,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6641,7 +6644,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B90" s="5">
         <v>46225.58147606481</v>
@@ -6651,7 +6654,7 @@
         <v>46225.60367008102</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>25</v>
@@ -6675,7 +6678,7 @@
         <v>26</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>26</v>
@@ -6688,7 +6691,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B91" s="9">
         <v>46225.58147990741</v>
@@ -6698,16 +6701,16 @@
         <v>46225.615814467594</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I91" s="9">
         <v>46301</v>
@@ -6725,13 +6728,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q91" s="9">
         <v>46301</v>
@@ -6751,7 +6754,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B92" s="5">
         <v>46225.58148496528</v>
@@ -6761,16 +6764,16 @@
         <v>46225.61578579861</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I92" s="6"/>
       <c r="J92" s="5">
@@ -6786,13 +6789,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6802,7 +6805,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B93" s="9">
         <v>46225.58148953704</v>
@@ -6812,16 +6815,16 @@
         <v>46225.61578274306</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I93" s="9">
         <v>46301</v>
@@ -6839,13 +6842,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -6855,7 +6858,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B94" s="5">
         <v>46225.6055390625</v>
@@ -6865,16 +6868,16 @@
         <v>46225.61577960648</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I94" s="6"/>
       <c r="J94" s="5">
@@ -6890,13 +6893,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O94" s="6" t="s">
         <v>61</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -6906,7 +6909,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B95" s="9">
         <v>46225.605553333335</v>
@@ -6916,16 +6919,16 @@
         <v>46225.61577443287</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I95" s="10"/>
       <c r="J95" s="9">
@@ -6941,13 +6944,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O95" s="10" t="s">
         <v>65</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -6957,7 +6960,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B96" s="5">
         <v>46225.581494178245</v>
@@ -6967,7 +6970,7 @@
         <v>46225.61592174768</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -6992,10 +6995,10 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>26</v>
@@ -7018,7 +7021,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B97" s="9">
         <v>46225.5814984375</v>
@@ -7028,7 +7031,7 @@
         <v>46225.615894421295</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7055,13 +7058,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7071,7 +7074,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B98" s="5">
         <v>46225.58150320602</v>
@@ -7081,7 +7084,7 @@
         <v>46225.61589104167</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7108,13 +7111,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7124,7 +7127,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B99" s="9">
         <v>46225.60673211806</v>
@@ -7134,7 +7137,7 @@
         <v>46225.615888125</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7161,13 +7164,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7177,7 +7180,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B100" s="5">
         <v>46225.60674163194</v>
@@ -7187,7 +7190,7 @@
         <v>46225.61588293982</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7214,13 +7217,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7230,7 +7233,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B101" s="9">
         <v>46225.58150777778</v>
@@ -7240,16 +7243,16 @@
         <v>46225.61603868056</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I101" s="9">
         <v>46303</v>
@@ -7267,13 +7270,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q101" s="9">
         <v>46303</v>
@@ -7293,7 +7296,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B102" s="5">
         <v>46225.58151239583</v>
@@ -7303,16 +7306,16 @@
         <v>46225.61600570602</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I102" s="6"/>
       <c r="J102" s="5">
@@ -7328,13 +7331,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7344,7 +7347,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B103" s="9">
         <v>46225.58151694444</v>
@@ -7354,16 +7357,16 @@
         <v>46225.61600274306</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I103" s="10"/>
       <c r="J103" s="9">
@@ -7379,13 +7382,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7395,7 +7398,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B104" s="5">
         <v>46225.606768564816</v>
@@ -7405,16 +7408,16 @@
         <v>46225.615999965274</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I104" s="5">
         <v>46303</v>
@@ -7432,13 +7435,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7448,7 +7451,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B105" s="9">
         <v>46225.606777395835</v>
@@ -7458,16 +7461,16 @@
         <v>46225.61599523148</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I105" s="9">
         <v>46303</v>
@@ -7485,13 +7488,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7501,7 +7504,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B106" s="5">
         <v>46225.581521562504</v>
@@ -7511,16 +7514,16 @@
         <v>46240.71657643518</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I106" s="5">
         <v>46304</v>
@@ -7538,13 +7541,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q106" s="5">
         <v>46304</v>
@@ -7564,7 +7567,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B107" s="9">
         <v>46225.58152704861</v>
@@ -7574,16 +7577,16 @@
         <v>46225.61621090278</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I107" s="10"/>
       <c r="J107" s="9">
@@ -7599,13 +7602,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q107" s="10"/>
       <c r="R107" s="10"/>
@@ -7615,7 +7618,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B108" s="5">
         <v>46225.58153157408</v>
@@ -7625,16 +7628,16 @@
         <v>46225.61620709491</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I108" s="6"/>
       <c r="J108" s="5">
@@ -7650,13 +7653,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -7666,7 +7669,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B109" s="9">
         <v>46225.60680554398</v>
@@ -7676,16 +7679,16 @@
         <v>46225.616203564816</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I109" s="9">
         <v>46304</v>
@@ -7703,10 +7706,10 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P109" s="10" t="s">
         <v>26</v>
@@ -7719,7 +7722,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B110" s="5">
         <v>46225.60681763889</v>
@@ -7729,16 +7732,16 @@
         <v>46225.61619854167</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I110" s="5">
         <v>46304</v>
@@ -7756,10 +7759,10 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>26</v>
@@ -7772,7 +7775,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B111" s="9">
         <v>46225.58153574074</v>
@@ -7782,7 +7785,7 @@
         <v>46225.60402078704</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>25</v>
@@ -7806,7 +7809,7 @@
         <v>26</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P111" s="10" t="s">
         <v>26</v>
@@ -7819,7 +7822,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B112" s="5">
         <v>46225.58153866898</v>
@@ -7829,16 +7832,16 @@
         <v>46225.61649424769</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="I112" s="5">
         <v>46307</v>
@@ -7856,13 +7859,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q112" s="5">
         <v>46311</v>
@@ -7882,7 +7885,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B113" s="9">
         <v>46225.58154590278</v>
@@ -7892,7 +7895,7 @@
         <v>46225.61639241898</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
@@ -7919,13 +7922,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P113" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q113" s="9">
         <v>46311</v>

--- a/data/50001580- CIA. RIO MINERALES.xlsx
+++ b/data/50001580- CIA. RIO MINERALES.xlsx
@@ -4424,7 +4424,7 @@
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46225.61367097222</v>
+        <v>46253.20084153935</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>189</v>
@@ -4468,8 +4468,8 @@
       <c r="R51" s="9">
         <v>46260</v>
       </c>
-      <c r="S51" s="7" t="s">
-        <v>33</v>
+      <c r="S51" s="12" t="s">
+        <v>111</v>
       </c>
       <c r="T51" s="10">
         <v>0</v>
@@ -4487,7 +4487,7 @@
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46225.613667349535</v>
+        <v>46253.20084106481</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>194</v>
@@ -4531,8 +4531,8 @@
       <c r="R52" s="5">
         <v>46260</v>
       </c>
-      <c r="S52" s="7" t="s">
-        <v>33</v>
+      <c r="S52" s="12" t="s">
+        <v>111</v>
       </c>
       <c r="T52" s="6">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46225.61366387732</v>
+        <v>46253.200841157406</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>197</v>
@@ -4594,8 +4594,8 @@
       <c r="R53" s="9">
         <v>46260</v>
       </c>
-      <c r="S53" s="7" t="s">
-        <v>33</v>
+      <c r="S53" s="12" t="s">
+        <v>111</v>
       </c>
       <c r="T53" s="10">
         <v>0</v>

--- a/data/50001580- CIA. RIO MINERALES.xlsx
+++ b/data/50001580- CIA. RIO MINERALES.xlsx
@@ -4613,7 +4613,7 @@
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46225.61417395833</v>
+        <v>46254.17217888889</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>200</v>
@@ -4657,8 +4657,8 @@
       <c r="R54" s="5">
         <v>46261</v>
       </c>
-      <c r="S54" s="7" t="s">
-        <v>33</v>
+      <c r="S54" s="12" t="s">
+        <v>111</v>
       </c>
       <c r="T54" s="6">
         <v>0</v>
@@ -4676,7 +4676,7 @@
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46225.61417104167</v>
+        <v>46254.17217885416</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>203</v>
@@ -4720,8 +4720,8 @@
       <c r="R55" s="9">
         <v>46261</v>
       </c>
-      <c r="S55" s="7" t="s">
-        <v>33</v>
+      <c r="S55" s="12" t="s">
+        <v>111</v>
       </c>
       <c r="T55" s="10">
         <v>0</v>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46225.61416773148</v>
+        <v>46254.17217863426</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>206</v>
@@ -4783,8 +4783,8 @@
       <c r="R56" s="5">
         <v>46261</v>
       </c>
-      <c r="S56" s="7" t="s">
-        <v>33</v>
+      <c r="S56" s="12" t="s">
+        <v>111</v>
       </c>
       <c r="T56" s="6">
         <v>0</v>

--- a/data/50001580- CIA. RIO MINERALES.xlsx
+++ b/data/50001580- CIA. RIO MINERALES.xlsx
@@ -473,7 +473,7 @@
     <t>Generacion Oc  OT4378</t>
   </si>
   <si>
-    <t xml:space="preserve">propuesta fabricación externa </t>
+    <t xml:space="preserve">propuesta fabricación externa ,propuesta fabricación externa </t>
   </si>
   <si>
     <t>Fabricación externa OT4378,Armado OT4378</t>
@@ -3638,7 +3638,7 @@
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46237.553714594906</v>
+        <v>46254.647307708336</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>140</v>

--- a/data/50001580- CIA. RIO MINERALES.xlsx
+++ b/data/50001580- CIA. RIO MINERALES.xlsx
@@ -3638,7 +3638,7 @@
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46254.647307708336</v>
+        <v>46255.170326203704</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>140</v>

--- a/data/50001580- CIA. RIO MINERALES.xlsx
+++ b/data/50001580- CIA. RIO MINERALES.xlsx
@@ -3638,7 +3638,7 @@
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46255.170326203704</v>
+        <v>46255.62865305555</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>140</v>

--- a/data/50001580- CIA. RIO MINERALES.xlsx
+++ b/data/50001580- CIA. RIO MINERALES.xlsx
@@ -3056,7 +3056,7 @@
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46252.20325089121</v>
+        <v>46259.169307696764</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>106</v>
@@ -3178,7 +3178,7 @@
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46225.61262351852</v>
+        <v>46259.169309363424</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>116</v>
@@ -3237,7 +3237,7 @@
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46252.203251087965</v>
+        <v>46259.16931034722</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>119</v>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46225.612692442126</v>
+        <v>46259.169311527774</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>124</v>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46252.20325114584</v>
+        <v>46259.16931252315</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>127</v>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46225.61298125</v>
+        <v>46259.16931366899</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>132</v>
@@ -4849,7 +4849,7 @@
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46225.6142333912</v>
+        <v>46259.18545266204</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>97</v>
@@ -4893,8 +4893,8 @@
       <c r="R58" s="5">
         <v>46262</v>
       </c>
-      <c r="S58" s="7" t="s">
-        <v>33</v>
+      <c r="S58" s="12" t="s">
+        <v>111</v>
       </c>
       <c r="T58" s="6">
         <v>0</v>

--- a/data/50001580- CIA. RIO MINERALES.xlsx
+++ b/data/50001580- CIA. RIO MINERALES.xlsx
@@ -383,250 +383,250 @@
     <t>Generación OC corte laser  OT4378,Fabricacion corte laser OT4378</t>
   </si>
   <si>
+    <t>1216788240366658</t>
+  </si>
+  <si>
+    <t>Generación OC corte laser  OT4378</t>
+  </si>
+  <si>
+    <t>Corte Laser  OT4378,Fabricacion corte laser OT4378</t>
+  </si>
+  <si>
+    <t>1216788240366678</t>
+  </si>
+  <si>
+    <t>Fabricacion corte laser OT4378</t>
+  </si>
+  <si>
+    <t>Corte Laser  OT4378,Recepcion corte laser OT4378</t>
+  </si>
+  <si>
+    <t>1216788240366987</t>
+  </si>
+  <si>
+    <t>Corte plasma  OT4378</t>
+  </si>
+  <si>
+    <t>Generacion OC Corte plasma  OT4378,Fabricación corte plasma  OT4378</t>
+  </si>
+  <si>
+    <t>1216788240366999</t>
+  </si>
+  <si>
+    <t>Corte plasma  OT4378,Fabricación corte plasma  OT4378</t>
+  </si>
+  <si>
+    <t>1216788240377532</t>
+  </si>
+  <si>
+    <t>Fabricación corte plasma  OT4378</t>
+  </si>
+  <si>
+    <t>Corte plasma  OT4378,Recepcion corte plasma OT4378</t>
+  </si>
+  <si>
+    <t>1216788240377549</t>
+  </si>
+  <si>
+    <t>Mecanizado OT4378</t>
+  </si>
+  <si>
+    <t>Generación OC mecanizado OT4378,Fabricación Mecanizado OT4378</t>
+  </si>
+  <si>
+    <t>1216788352775129</t>
+  </si>
+  <si>
+    <t>Mecanizado OT4378,Fabricación Mecanizado OT4378</t>
+  </si>
+  <si>
+    <t>1216788352775146</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado OT4378</t>
+  </si>
+  <si>
+    <t>Recepcion mecanizado OT4378,Mecanizado OT4378</t>
+  </si>
+  <si>
+    <t>1216788234970061</t>
+  </si>
+  <si>
+    <t>Fabricación externa OT4378</t>
+  </si>
+  <si>
+    <t>Rosemary Singh</t>
+  </si>
+  <si>
+    <t>rosemary.singh@zitron.com</t>
+  </si>
+  <si>
+    <t>Generacion Oc  OT4378,Armado OT4378,Control de calidad  OT4378</t>
+  </si>
+  <si>
+    <t>1216788147871096</t>
+  </si>
+  <si>
+    <t>Generacion Oc  OT4378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">propuesta fabricación externa ,propuesta fabricación externa </t>
+  </si>
+  <si>
+    <t>Fabricación externa OT4378,Armado OT4378</t>
+  </si>
+  <si>
+    <t>1216788055125022</t>
+  </si>
+  <si>
+    <t>Armado OT4378</t>
+  </si>
+  <si>
+    <t>Fabricación externa OT4378,Control de calidad  OT4378</t>
+  </si>
+  <si>
+    <t>1216788235053231</t>
+  </si>
+  <si>
+    <t>Control de calidad  OT4378</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>1216769310026586</t>
+  </si>
+  <si>
+    <t>Tableros</t>
+  </si>
+  <si>
+    <t>Eliana</t>
+  </si>
+  <si>
+    <t>ecarico@zitron.com</t>
+  </si>
+  <si>
+    <t>Generacion oc tableros ot 4379,Fabricacion tableros  ot 4379</t>
+  </si>
+  <si>
+    <t>1216769310026587</t>
+  </si>
+  <si>
+    <t>Fabricacion tableros  ot 4379,Tableros</t>
+  </si>
+  <si>
+    <t>1216769310026588</t>
+  </si>
+  <si>
+    <t>Fabricacion tableros  ot 4379</t>
+  </si>
+  <si>
+    <t>Tableros,Recepcion Tableros  ot 4379</t>
+  </si>
+  <si>
+    <t>1216788235053248</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>Check pruebas FAT OT4378,Plano Preliminar OT4378,Plano Definitivos OT4378,Check Planos OT4378</t>
+  </si>
+  <si>
+    <t>1216788235053260</t>
+  </si>
+  <si>
+    <t>Plano Preliminar OT4378</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,Plano Definitivos OT4378</t>
+  </si>
+  <si>
+    <t>1216788235072362</t>
+  </si>
+  <si>
+    <t>Plano Definitivos OT4378</t>
+  </si>
+  <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,Check Planos OT4378</t>
+  </si>
+  <si>
+    <t>1216788352823818</t>
+  </si>
+  <si>
+    <t>Propuesta Mecanizado OT4378,Propuesta Corte plasma  OT4378,propuesta Corte laser OT4378,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,Ingenieria y diseñoo:,Propuesta Fabricación externa OT4378</t>
+  </si>
+  <si>
+    <t>1216788055167269</t>
+  </si>
+  <si>
+    <t>Check pruebas FAT OT4378</t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A </t>
+  </si>
+  <si>
+    <t>1216788352861129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A </t>
+  </si>
+  <si>
+    <t>OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,Check pruebas FAT OT4378</t>
+  </si>
+  <si>
+    <t>1216788352861141</t>
+  </si>
+  <si>
+    <t>OT 4347 Preparación Materiales,Check pruebas FAT OT4378,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales</t>
+  </si>
+  <si>
+    <t>1216788240544723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega </t>
+  </si>
+  <si>
+    <t>Recepcion mecanizado OT4378,Control de calidad Corte plasma OT4378,Control de calidad Mecanizado OT4378,Control de calidad corte Laser OT4378,Recepcion corte laser OT4378,Recepcion corte plasma OT4378</t>
+  </si>
+  <si>
+    <t>1216788240544735</t>
+  </si>
+  <si>
+    <t>Recepcion corte laser OT4378</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad corte Laser OT4378,Bodega </t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1216788240366658</t>
-  </si>
-  <si>
-    <t>Generación OC corte laser  OT4378</t>
-  </si>
-  <si>
-    <t>Corte Laser  OT4378,Fabricacion corte laser OT4378</t>
-  </si>
-  <si>
-    <t>1216788240366678</t>
-  </si>
-  <si>
-    <t>Fabricacion corte laser OT4378</t>
-  </si>
-  <si>
-    <t>Corte Laser  OT4378,Recepcion corte laser OT4378</t>
-  </si>
-  <si>
-    <t>1216788240366987</t>
-  </si>
-  <si>
-    <t>Corte plasma  OT4378</t>
-  </si>
-  <si>
-    <t>Generacion OC Corte plasma  OT4378,Fabricación corte plasma  OT4378</t>
-  </si>
-  <si>
-    <t>1216788240366999</t>
-  </si>
-  <si>
-    <t>Corte plasma  OT4378,Fabricación corte plasma  OT4378</t>
-  </si>
-  <si>
-    <t>1216788240377532</t>
-  </si>
-  <si>
-    <t>Fabricación corte plasma  OT4378</t>
-  </si>
-  <si>
-    <t>Corte plasma  OT4378,Recepcion corte plasma OT4378</t>
-  </si>
-  <si>
-    <t>1216788240377549</t>
-  </si>
-  <si>
-    <t>Mecanizado OT4378</t>
-  </si>
-  <si>
-    <t>Generación OC mecanizado OT4378,Fabricación Mecanizado OT4378</t>
-  </si>
-  <si>
-    <t>1216788352775129</t>
-  </si>
-  <si>
-    <t>Mecanizado OT4378,Fabricación Mecanizado OT4378</t>
-  </si>
-  <si>
-    <t>1216788352775146</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado OT4378</t>
-  </si>
-  <si>
-    <t>Recepcion mecanizado OT4378,Mecanizado OT4378</t>
-  </si>
-  <si>
-    <t>1216788234970061</t>
-  </si>
-  <si>
-    <t>Fabricación externa OT4378</t>
-  </si>
-  <si>
-    <t>Rosemary Singh</t>
-  </si>
-  <si>
-    <t>rosemary.singh@zitron.com</t>
-  </si>
-  <si>
-    <t>Generacion Oc  OT4378,Armado OT4378,Control de calidad  OT4378</t>
-  </si>
-  <si>
-    <t>1216788147871096</t>
-  </si>
-  <si>
-    <t>Generacion Oc  OT4378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">propuesta fabricación externa ,propuesta fabricación externa </t>
-  </si>
-  <si>
-    <t>Fabricación externa OT4378,Armado OT4378</t>
-  </si>
-  <si>
-    <t>1216788055125022</t>
-  </si>
-  <si>
-    <t>Armado OT4378</t>
-  </si>
-  <si>
-    <t>Fabricación externa OT4378,Control de calidad  OT4378</t>
-  </si>
-  <si>
-    <t>1216788235053231</t>
-  </si>
-  <si>
-    <t>Control de calidad  OT4378</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>1216769310026586</t>
-  </si>
-  <si>
-    <t>Tableros</t>
-  </si>
-  <si>
-    <t>Eliana</t>
-  </si>
-  <si>
-    <t>ecarico@zitron.com</t>
-  </si>
-  <si>
-    <t>Generacion oc tableros ot 4379,Fabricacion tableros  ot 4379</t>
-  </si>
-  <si>
-    <t>1216769310026587</t>
-  </si>
-  <si>
-    <t>Fabricacion tableros  ot 4379,Tableros</t>
-  </si>
-  <si>
-    <t>1216769310026588</t>
-  </si>
-  <si>
-    <t>Fabricacion tableros  ot 4379</t>
-  </si>
-  <si>
-    <t>Tableros,Recepcion Tableros  ot 4379</t>
-  </si>
-  <si>
-    <t>1216788235053248</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>Check pruebas FAT OT4378,Plano Preliminar OT4378,Plano Definitivos OT4378,Check Planos OT4378</t>
-  </si>
-  <si>
-    <t>1216788235053260</t>
-  </si>
-  <si>
-    <t>Plano Preliminar OT4378</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,Plano Definitivos OT4378</t>
-  </si>
-  <si>
-    <t>1216788235072362</t>
-  </si>
-  <si>
-    <t>Plano Definitivos OT4378</t>
-  </si>
-  <si>
-    <t>Gonzalo Javier Dávila Bade</t>
-  </si>
-  <si>
-    <t>gonzalo.davila@zitron.com</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,Check Planos OT4378</t>
-  </si>
-  <si>
-    <t>1216788352823818</t>
-  </si>
-  <si>
-    <t>Propuesta Mecanizado OT4378,Propuesta Corte plasma  OT4378,propuesta Corte laser OT4378,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,Ingenieria y diseñoo:,Propuesta Fabricación externa OT4378</t>
-  </si>
-  <si>
-    <t>1216788055167269</t>
-  </si>
-  <si>
-    <t>Check pruebas FAT OT4378</t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A </t>
-  </si>
-  <si>
-    <t>1216788352861129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A </t>
-  </si>
-  <si>
-    <t>OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,Check pruebas FAT OT4378</t>
-  </si>
-  <si>
-    <t>1216788352861141</t>
-  </si>
-  <si>
-    <t>OT 4347 Preparación Materiales,Check pruebas FAT OT4378,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales,Preparación Materiales</t>
-  </si>
-  <si>
-    <t>1216788240544723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega </t>
-  </si>
-  <si>
-    <t>Recepcion mecanizado OT4378,Control de calidad Corte plasma OT4378,Control de calidad Mecanizado OT4378,Control de calidad corte Laser OT4378,Recepcion corte laser OT4378,Recepcion corte plasma OT4378</t>
-  </si>
-  <si>
-    <t>1216788240544735</t>
-  </si>
-  <si>
-    <t>Recepcion corte laser OT4378</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad corte Laser OT4378,Bodega </t>
   </si>
   <si>
     <t>1216788352896742</t>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46259.169307696764</v>
+        <v>46260.17450097222</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>106</v>
@@ -3100,8 +3100,8 @@
       <c r="R27" s="9">
         <v>46247</v>
       </c>
-      <c r="S27" s="12" t="s">
-        <v>111</v>
+      <c r="S27" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="T27" s="10">
         <v>0</v>
@@ -3112,7 +3112,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B28" s="5">
         <v>46225.58101144676</v>
@@ -3122,7 +3122,7 @@
         <v>46248.17134739584</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
@@ -3155,7 +3155,7 @@
         <v>88</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3171,7 +3171,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B29" s="9">
         <v>46225.581017233795</v>
@@ -3181,7 +3181,7 @@
         <v>46259.169309363424</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
@@ -3211,10 +3211,10 @@
         <v>106</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
@@ -3230,17 +3230,17 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B30" s="5">
         <v>46225.58102277778</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46259.16931034722</v>
+        <v>46260.1745009838</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
@@ -3270,7 +3270,7 @@
         <v>105</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="P30" s="6" t="s">
         <v>26</v>
@@ -3281,8 +3281,8 @@
       <c r="R30" s="5">
         <v>46247</v>
       </c>
-      <c r="S30" s="12" t="s">
-        <v>111</v>
+      <c r="S30" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
@@ -3293,7 +3293,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B31" s="9">
         <v>46225.58102737268</v>
@@ -3330,13 +3330,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O31" s="10" t="s">
         <v>93</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3346,7 +3346,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B32" s="5">
         <v>46225.581032222224</v>
@@ -3356,7 +3356,7 @@
         <v>46259.169311527774</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
@@ -3383,13 +3383,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>94</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3399,17 +3399,17 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B33" s="9">
         <v>46225.581037199074</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46259.16931252315</v>
+        <v>46260.17450096065</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
@@ -3439,7 +3439,7 @@
         <v>105</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="P33" s="10" t="s">
         <v>26</v>
@@ -3450,8 +3450,8 @@
       <c r="R33" s="9">
         <v>46247</v>
       </c>
-      <c r="S33" s="12" t="s">
-        <v>111</v>
+      <c r="S33" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="T33" s="10">
         <v>0</v>
@@ -3462,7 +3462,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B34" s="5">
         <v>46225.58104158565</v>
@@ -3499,13 +3499,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>99</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3515,7 +3515,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B35" s="9">
         <v>46225.5810464699</v>
@@ -3525,7 +3525,7 @@
         <v>46259.16931366899</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
@@ -3552,13 +3552,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="O35" s="10" t="s">
         <v>100</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -3568,7 +3568,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B36" s="5">
         <v>46225.58105121528</v>
@@ -3578,16 +3578,16 @@
         <v>46225.61316422454</v>
       </c>
       <c r="E36" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G36" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="F36" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G36" s="6" t="s">
+      <c r="H36" s="6" t="s">
         <v>136</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>137</v>
       </c>
       <c r="I36" s="5">
         <v>46247</v>
@@ -3608,7 +3608,7 @@
         <v>105</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3631,7 +3631,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B37" s="9">
         <v>46225.58109630787</v>
@@ -3641,16 +3641,16 @@
         <v>46255.62865305555</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="H37" s="10" t="s">
         <v>136</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>137</v>
       </c>
       <c r="I37" s="9">
         <v>46247</v>
@@ -3668,13 +3668,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O37" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="P37" s="10" t="s">
         <v>141</v>
-      </c>
-      <c r="P37" s="10" t="s">
-        <v>142</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3684,7 +3684,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B38" s="5">
         <v>46225.58110178241</v>
@@ -3694,16 +3694,16 @@
         <v>46225.613047719904</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>136</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>137</v>
       </c>
       <c r="I38" s="5">
         <v>46258</v>
@@ -3721,13 +3721,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3737,7 +3737,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B39" s="9">
         <v>46225.58110600694</v>
@@ -3747,16 +3747,16 @@
         <v>46225.613129363424</v>
       </c>
       <c r="E39" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G39" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="F39" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G39" s="10" t="s">
+      <c r="H39" s="10" t="s">
         <v>148</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>149</v>
       </c>
       <c r="I39" s="9">
         <v>46289</v>
@@ -3774,13 +3774,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
@@ -3790,7 +3790,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B40" s="5">
         <v>46225.59682005787</v>
@@ -3800,16 +3800,16 @@
         <v>46225.6133383912</v>
       </c>
       <c r="E40" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G40" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="F40" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G40" s="6" t="s">
+      <c r="H40" s="6" t="s">
         <v>152</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>153</v>
       </c>
       <c r="I40" s="5">
         <v>46233</v>
@@ -3830,7 +3830,7 @@
         <v>105</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>26</v>
@@ -3853,7 +3853,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B41" s="9">
         <v>46225.59686481481</v>
@@ -3869,10 +3869,10 @@
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="H41" s="10" t="s">
         <v>152</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>153</v>
       </c>
       <c r="I41" s="9">
         <v>46233</v>
@@ -3890,13 +3890,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O41" s="10" t="s">
         <v>102</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -3906,7 +3906,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B42" s="5">
         <v>46225.59692966435</v>
@@ -3916,16 +3916,16 @@
         <v>46225.613310636574</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="H42" s="6" t="s">
         <v>152</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>153</v>
       </c>
       <c r="I42" s="5">
         <v>46244</v>
@@ -3943,13 +3943,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>103</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -3959,7 +3959,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B43" s="9">
         <v>46225.58111748843</v>
@@ -3969,7 +3969,7 @@
         <v>46238.48696734954</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>25</v>
@@ -3993,7 +3993,7 @@
         <v>26</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4006,7 +4006,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B44" s="5">
         <v>46225.58112127315</v>
@@ -4018,16 +4018,16 @@
         <v>46235.20153063658</v>
       </c>
       <c r="E44" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G44" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="F44" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G44" s="6" t="s">
+      <c r="H44" s="6" t="s">
         <v>165</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>166</v>
       </c>
       <c r="I44" s="5">
         <v>46230</v>
@@ -4045,13 +4045,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>68</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q44" s="5">
         <v>46234</v>
@@ -4071,7 +4071,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B45" s="9">
         <v>46225.58112643519</v>
@@ -4083,16 +4083,16 @@
         <v>46242.202891875</v>
       </c>
       <c r="E45" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="F45" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G45" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="F45" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G45" s="10" t="s">
+      <c r="H45" s="10" t="s">
         <v>170</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>171</v>
       </c>
       <c r="I45" s="9">
         <v>46237</v>
@@ -4110,13 +4110,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q45" s="9">
         <v>46241</v>
@@ -4136,7 +4136,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B46" s="5">
         <v>46225.58113097222</v>
@@ -4154,10 +4154,10 @@
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="H46" s="6" t="s">
         <v>165</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>166</v>
       </c>
       <c r="I46" s="5">
         <v>46244</v>
@@ -4175,13 +4175,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q46" s="5">
         <v>46244</v>
@@ -4201,7 +4201,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B47" s="9">
         <v>46225.58114445602</v>
@@ -4211,16 +4211,16 @@
         <v>46225.61347256944</v>
       </c>
       <c r="E47" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="F47" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="F47" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G47" s="10" t="s">
+      <c r="H47" s="10" t="s">
         <v>177</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>178</v>
       </c>
       <c r="I47" s="9">
         <v>46290</v>
@@ -4238,13 +4238,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q47" s="9">
         <v>46290</v>
@@ -4264,7 +4264,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B48" s="5">
         <v>46225.58114871528</v>
@@ -4274,16 +4274,16 @@
         <v>46225.61551950232</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>177</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>178</v>
       </c>
       <c r="I48" s="5">
         <v>46290</v>
@@ -4301,13 +4301,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="O48" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="P48" s="6" t="s">
         <v>181</v>
-      </c>
-      <c r="P48" s="6" t="s">
-        <v>182</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4317,7 +4317,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B49" s="9">
         <v>46225.58115283565</v>
@@ -4327,16 +4327,16 @@
         <v>46225.615519513885</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="H49" s="10" t="s">
         <v>177</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>178</v>
       </c>
       <c r="I49" s="9">
         <v>46290</v>
@@ -4354,13 +4354,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q49" s="10"/>
       <c r="R49" s="10"/>
@@ -4370,7 +4370,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B50" s="5">
         <v>46225.581171631944</v>
@@ -4380,7 +4380,7 @@
         <v>46225.59181146991</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>25</v>
@@ -4404,7 +4404,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4417,26 +4417,26 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B51" s="9">
         <v>46225.58117489584</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46253.20084153935</v>
+        <v>46260.16932030093</v>
       </c>
       <c r="E51" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="F51" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G51" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="F51" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G51" s="10" t="s">
+      <c r="H51" s="10" t="s">
         <v>190</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>191</v>
       </c>
       <c r="I51" s="9">
         <v>46260</v>
@@ -4454,13 +4454,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Q51" s="9">
         <v>46260</v>
@@ -4469,7 +4469,7 @@
         <v>46260</v>
       </c>
       <c r="S51" s="12" t="s">
-        <v>111</v>
+        <v>192</v>
       </c>
       <c r="T51" s="10">
         <v>0</v>
@@ -4487,7 +4487,7 @@
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46253.20084106481</v>
+        <v>46260.169321504625</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>194</v>
@@ -4496,10 +4496,10 @@
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>190</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>191</v>
       </c>
       <c r="I52" s="5">
         <v>46260</v>
@@ -4517,10 +4517,10 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>195</v>
@@ -4532,7 +4532,7 @@
         <v>46260</v>
       </c>
       <c r="S52" s="12" t="s">
-        <v>111</v>
+        <v>192</v>
       </c>
       <c r="T52" s="6">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46253.200841157406</v>
+        <v>46260.16931856482</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>197</v>
@@ -4559,10 +4559,10 @@
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="H53" s="10" t="s">
         <v>190</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>191</v>
       </c>
       <c r="I53" s="9">
         <v>46260</v>
@@ -4580,10 +4580,10 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="P53" s="10" t="s">
         <v>198</v>
@@ -4595,7 +4595,7 @@
         <v>46260</v>
       </c>
       <c r="S53" s="12" t="s">
-        <v>111</v>
+        <v>192</v>
       </c>
       <c r="T53" s="10">
         <v>0</v>
@@ -4622,10 +4622,10 @@
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>148</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>149</v>
       </c>
       <c r="I54" s="5">
         <v>46261</v>
@@ -4643,10 +4643,10 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>201</v>
@@ -4658,7 +4658,7 @@
         <v>46261</v>
       </c>
       <c r="S54" s="12" t="s">
-        <v>111</v>
+        <v>192</v>
       </c>
       <c r="T54" s="6">
         <v>0</v>
@@ -4685,10 +4685,10 @@
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="H55" s="10" t="s">
         <v>148</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>149</v>
       </c>
       <c r="I55" s="9">
         <v>46261</v>
@@ -4706,7 +4706,7 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O55" s="10" t="s">
         <v>194</v>
@@ -4721,7 +4721,7 @@
         <v>46261</v>
       </c>
       <c r="S55" s="12" t="s">
-        <v>111</v>
+        <v>192</v>
       </c>
       <c r="T55" s="10">
         <v>0</v>
@@ -4748,10 +4748,10 @@
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>148</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>149</v>
       </c>
       <c r="I56" s="5">
         <v>46261</v>
@@ -4769,7 +4769,7 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>197</v>
@@ -4784,7 +4784,7 @@
         <v>46261</v>
       </c>
       <c r="S56" s="12" t="s">
-        <v>111</v>
+        <v>192</v>
       </c>
       <c r="T56" s="6">
         <v>0</v>
@@ -4894,7 +4894,7 @@
         <v>46262</v>
       </c>
       <c r="S58" s="12" t="s">
-        <v>111</v>
+        <v>192</v>
       </c>
       <c r="T58" s="6">
         <v>0</v>
@@ -4915,7 +4915,7 @@
         <v>46225.61435628472</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
@@ -4945,7 +4945,7 @@
         <v>208</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P59" s="10" t="s">
         <v>208</v>
@@ -4978,7 +4978,7 @@
         <v>46238.48696543981</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
@@ -5005,7 +5005,7 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>216</v>
@@ -5031,7 +5031,7 @@
         <v>46238.48696587963</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
@@ -5058,7 +5058,7 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O61" s="10" t="s">
         <v>219</v>
@@ -5090,10 +5090,10 @@
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>148</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>149</v>
       </c>
       <c r="I62" s="5">
         <v>46274</v>
@@ -5114,7 +5114,7 @@
         <v>208</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>208</v>
@@ -5147,16 +5147,16 @@
         <v>46238.486964502314</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="H63" s="10" t="s">
         <v>148</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>149</v>
       </c>
       <c r="I63" s="10"/>
       <c r="J63" s="9">
@@ -5198,16 +5198,16 @@
         <v>46238.48696504629</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>148</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>149</v>
       </c>
       <c r="I64" s="6"/>
       <c r="J64" s="5">
@@ -5302,10 +5302,10 @@
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>190</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>191</v>
       </c>
       <c r="I66" s="5">
         <v>46230</v>
@@ -5365,10 +5365,10 @@
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="H67" s="10" t="s">
         <v>190</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>191</v>
       </c>
       <c r="I67" s="9">
         <v>46230</v>
@@ -5428,10 +5428,10 @@
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>190</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>191</v>
       </c>
       <c r="I68" s="5">
         <v>46230</v>
@@ -5491,10 +5491,10 @@
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="H69" s="10" t="s">
         <v>190</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>191</v>
       </c>
       <c r="I69" s="9">
         <v>46293</v>
@@ -5515,7 +5515,7 @@
         <v>229</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="P69" s="10" t="s">
         <v>58</v>
@@ -5625,7 +5625,7 @@
         <v>241</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P71" s="10" t="s">
         <v>245</v>
@@ -5658,7 +5658,7 @@
         <v>46225.61483068287</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5688,7 +5688,7 @@
         <v>244</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>247</v>
@@ -5711,7 +5711,7 @@
         <v>46225.61482673611</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5741,7 +5741,7 @@
         <v>244</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P73" s="10" t="s">
         <v>249</v>
@@ -5827,7 +5827,7 @@
         <v>46238.48696328704</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -5880,7 +5880,7 @@
         <v>46238.486963877316</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5996,7 +5996,7 @@
         <v>46225.61518142361</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6047,7 +6047,7 @@
         <v>46225.615182291665</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6161,7 +6161,7 @@
         <v>46238.48696648148</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6214,7 +6214,7 @@
         <v>46238.48696707176</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6383,7 +6383,7 @@
         <v>46225.61551967592</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6434,7 +6434,7 @@
         <v>46225.61552056713</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6548,7 +6548,7 @@
         <v>46225.61568175926</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6578,7 +6578,7 @@
         <v>280</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>288</v>
@@ -6601,7 +6601,7 @@
         <v>46225.615682592594</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6631,7 +6631,7 @@
         <v>280</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P89" s="10" t="s">
         <v>288</v>
@@ -6764,7 +6764,7 @@
         <v>46225.61578579861</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6792,7 +6792,7 @@
         <v>294</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>300</v>
@@ -6815,7 +6815,7 @@
         <v>46225.61578274306</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -6845,7 +6845,7 @@
         <v>294</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P93" s="10" t="s">
         <v>300</v>
@@ -7031,7 +7031,7 @@
         <v>46225.615894421295</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7061,7 +7061,7 @@
         <v>307</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P97" s="10" t="s">
         <v>310</v>
@@ -7084,7 +7084,7 @@
         <v>46225.61589104167</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7114,7 +7114,7 @@
         <v>307</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>310</v>
@@ -7306,7 +7306,7 @@
         <v>46225.61600570602</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7334,7 +7334,7 @@
         <v>316</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>318</v>
@@ -7357,7 +7357,7 @@
         <v>46225.61600274306</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7385,7 +7385,7 @@
         <v>316</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P103" s="10" t="s">
         <v>318</v>
@@ -7577,7 +7577,7 @@
         <v>46225.61621090278</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
@@ -7605,7 +7605,7 @@
         <v>324</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P107" s="10" t="s">
         <v>327</v>
@@ -7628,7 +7628,7 @@
         <v>46225.61620709491</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7656,7 +7656,7 @@
         <v>324</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P108" s="6" t="s">
         <v>327</v>

--- a/data/50001580- CIA. RIO MINERALES.xlsx
+++ b/data/50001580- CIA. RIO MINERALES.xlsx
@@ -626,34 +626,34 @@
     <t xml:space="preserve">Control de calidad corte Laser OT4378,Bodega </t>
   </si>
   <si>
+    <t>1216788352896742</t>
+  </si>
+  <si>
+    <t>Recepcion corte plasma OT4378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Corte plasma OT4378,Bodega </t>
+  </si>
+  <si>
+    <t>1216788148149163</t>
+  </si>
+  <si>
+    <t>Recepcion mecanizado OT4378</t>
+  </si>
+  <si>
+    <t>Bodega ,Control de calidad Mecanizado OT4378</t>
+  </si>
+  <si>
+    <t>1216788148149185</t>
+  </si>
+  <si>
+    <t>Control de calidad corte Laser OT4378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,Bodega ,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A </t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1216788352896742</t>
-  </si>
-  <si>
-    <t>Recepcion corte plasma OT4378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Corte plasma OT4378,Bodega </t>
-  </si>
-  <si>
-    <t>1216788148149163</t>
-  </si>
-  <si>
-    <t>Recepcion mecanizado OT4378</t>
-  </si>
-  <si>
-    <t>Bodega ,Control de calidad Mecanizado OT4378</t>
-  </si>
-  <si>
-    <t>1216788148149185</t>
-  </si>
-  <si>
-    <t>Control de calidad corte Laser OT4378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,Bodega ,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A </t>
   </si>
   <si>
     <t>1216788235163161</t>
@@ -4424,7 +4424,7 @@
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46260.16932030093</v>
+        <v>46261.17149666666</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>188</v>
@@ -4468,8 +4468,8 @@
       <c r="R51" s="9">
         <v>46260</v>
       </c>
-      <c r="S51" s="12" t="s">
-        <v>192</v>
+      <c r="S51" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="T51" s="10">
         <v>0</v>
@@ -4480,17 +4480,17 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B52" s="5">
         <v>46225.58118028935</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46260.169321504625</v>
+        <v>46261.17149707176</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
@@ -4523,7 +4523,7 @@
         <v>123</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q52" s="5">
         <v>46260</v>
@@ -4531,8 +4531,8 @@
       <c r="R52" s="5">
         <v>46260</v>
       </c>
-      <c r="S52" s="12" t="s">
-        <v>192</v>
+      <c r="S52" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="T52" s="6">
         <v>0</v>
@@ -4543,17 +4543,17 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B53" s="9">
         <v>46225.58118576389</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46260.16931856482</v>
+        <v>46261.17149663194</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
@@ -4586,7 +4586,7 @@
         <v>131</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q53" s="9">
         <v>46260</v>
@@ -4594,8 +4594,8 @@
       <c r="R53" s="9">
         <v>46260</v>
       </c>
-      <c r="S53" s="12" t="s">
-        <v>192</v>
+      <c r="S53" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="T53" s="10">
         <v>0</v>
@@ -4606,17 +4606,17 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B54" s="5">
         <v>46225.58119107639</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46254.17217888889</v>
+        <v>46261.1687446875</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
@@ -4649,7 +4649,7 @@
         <v>188</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q54" s="5">
         <v>46261</v>
@@ -4658,7 +4658,7 @@
         <v>46261</v>
       </c>
       <c r="S54" s="12" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="T54" s="6">
         <v>0</v>
@@ -4676,7 +4676,7 @@
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46254.17217885416</v>
+        <v>46261.16874824074</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>203</v>
@@ -4709,7 +4709,7 @@
         <v>185</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="P55" s="10" t="s">
         <v>204</v>
@@ -4721,7 +4721,7 @@
         <v>46261</v>
       </c>
       <c r="S55" s="12" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="T55" s="10">
         <v>0</v>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46254.17217863426</v>
+        <v>46261.168747083335</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>206</v>
@@ -4772,10 +4772,10 @@
         <v>185</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q56" s="5">
         <v>46261</v>
@@ -4784,7 +4784,7 @@
         <v>46261</v>
       </c>
       <c r="S56" s="12" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="T56" s="6">
         <v>0</v>
@@ -4894,7 +4894,7 @@
         <v>46262</v>
       </c>
       <c r="S58" s="12" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="T58" s="6">
         <v>0</v>

--- a/data/50001580- CIA. RIO MINERALES.xlsx
+++ b/data/50001580- CIA. RIO MINERALES.xlsx
@@ -653,43 +653,43 @@
     <t xml:space="preserve">OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,Bodega ,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A </t>
   </si>
   <si>
+    <t>1216788235163161</t>
+  </si>
+  <si>
+    <t>Control de calidad Corte plasma OT4378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega ,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A </t>
+  </si>
+  <si>
+    <t>1216788148162531</t>
+  </si>
+  <si>
+    <t>Control de calidad Mecanizado OT4378</t>
+  </si>
+  <si>
+    <t>1216788148162553</t>
+  </si>
+  <si>
+    <t>Caldereria</t>
+  </si>
+  <si>
+    <t>Armado OT4378,Control de calidad Armado OT4378,Preparacion materiales OT4378</t>
+  </si>
+  <si>
+    <t>1216788240594883</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,Caldereria,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A </t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1216788235163161</t>
-  </si>
-  <si>
-    <t>Control de calidad Corte plasma OT4378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega ,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A </t>
-  </si>
-  <si>
-    <t>1216788148162531</t>
-  </si>
-  <si>
-    <t>Control de calidad Mecanizado OT4378</t>
-  </si>
-  <si>
-    <t>1216788148162553</t>
-  </si>
-  <si>
-    <t>Caldereria</t>
-  </si>
-  <si>
-    <t>Armado OT4378,Control de calidad Armado OT4378,Preparacion materiales OT4378</t>
-  </si>
-  <si>
-    <t>1216788240594883</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,Caldereria,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A </t>
   </si>
   <si>
     <t>1216788055231811</t>
@@ -4613,7 +4613,7 @@
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46261.1687446875</v>
+        <v>46262.17656298611</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>199</v>
@@ -4657,8 +4657,8 @@
       <c r="R54" s="5">
         <v>46261</v>
       </c>
-      <c r="S54" s="12" t="s">
-        <v>201</v>
+      <c r="S54" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="T54" s="6">
         <v>0</v>
@@ -4669,17 +4669,17 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B55" s="9">
         <v>46225.58119642361</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46261.16874824074</v>
+        <v>46262.1765628125</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
@@ -4712,7 +4712,7 @@
         <v>193</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q55" s="9">
         <v>46261</v>
@@ -4720,8 +4720,8 @@
       <c r="R55" s="9">
         <v>46261</v>
       </c>
-      <c r="S55" s="12" t="s">
-        <v>201</v>
+      <c r="S55" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="T55" s="10">
         <v>0</v>
@@ -4732,17 +4732,17 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B56" s="5">
         <v>46225.581201678244</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46261.168747083335</v>
+        <v>46262.17656298611</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
@@ -4783,8 +4783,8 @@
       <c r="R56" s="5">
         <v>46261</v>
       </c>
-      <c r="S56" s="12" t="s">
-        <v>201</v>
+      <c r="S56" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="T56" s="6">
         <v>0</v>
@@ -4795,7 +4795,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B57" s="9">
         <v>46225.58120702546</v>
@@ -4805,7 +4805,7 @@
         <v>46225.59190644676</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>25</v>
@@ -4829,7 +4829,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P57" s="10" t="s">
         <v>26</v>
@@ -4842,7 +4842,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B58" s="5">
         <v>46225.58121010417</v>
@@ -4858,10 +4858,10 @@
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>211</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>212</v>
       </c>
       <c r="I58" s="5">
         <v>46262</v>
@@ -4879,13 +4879,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>96</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q58" s="5">
         <v>46266</v>
@@ -4894,7 +4894,7 @@
         <v>46262</v>
       </c>
       <c r="S58" s="12" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="T58" s="6">
         <v>0</v>
@@ -4921,10 +4921,10 @@
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="H59" s="10" t="s">
         <v>211</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>212</v>
       </c>
       <c r="I59" s="9">
         <v>46267</v>
@@ -4942,13 +4942,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O59" s="10" t="s">
         <v>178</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Q59" s="9">
         <v>46273</v>
@@ -4984,10 +4984,10 @@
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>211</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>212</v>
       </c>
       <c r="I60" s="5">
         <v>46267</v>
@@ -5037,10 +5037,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="H61" s="10" t="s">
         <v>211</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>212</v>
       </c>
       <c r="I61" s="9">
         <v>46267</v>
@@ -5111,13 +5111,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>178</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Q62" s="5">
         <v>46274</v>
@@ -7249,10 +7249,10 @@
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="H101" s="10" t="s">
         <v>211</v>
-      </c>
-      <c r="H101" s="10" t="s">
-        <v>212</v>
       </c>
       <c r="I101" s="9">
         <v>46303</v>
@@ -7312,10 +7312,10 @@
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="H102" s="6" t="s">
         <v>211</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>212</v>
       </c>
       <c r="I102" s="6"/>
       <c r="J102" s="5">
@@ -7363,10 +7363,10 @@
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="H103" s="10" t="s">
         <v>211</v>
-      </c>
-      <c r="H103" s="10" t="s">
-        <v>212</v>
       </c>
       <c r="I103" s="10"/>
       <c r="J103" s="9">
@@ -7414,10 +7414,10 @@
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="H104" s="6" t="s">
         <v>211</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>212</v>
       </c>
       <c r="I104" s="5">
         <v>46303</v>
@@ -7467,10 +7467,10 @@
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="H105" s="10" t="s">
         <v>211</v>
-      </c>
-      <c r="H105" s="10" t="s">
-        <v>212</v>
       </c>
       <c r="I105" s="9">
         <v>46303</v>
@@ -7520,10 +7520,10 @@
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="H106" s="6" t="s">
         <v>211</v>
-      </c>
-      <c r="H106" s="6" t="s">
-        <v>212</v>
       </c>
       <c r="I106" s="5">
         <v>46304</v>
@@ -7583,10 +7583,10 @@
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="H107" s="10" t="s">
         <v>211</v>
-      </c>
-      <c r="H107" s="10" t="s">
-        <v>212</v>
       </c>
       <c r="I107" s="10"/>
       <c r="J107" s="9">
@@ -7634,10 +7634,10 @@
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="H108" s="6" t="s">
         <v>211</v>
-      </c>
-      <c r="H108" s="6" t="s">
-        <v>212</v>
       </c>
       <c r="I108" s="6"/>
       <c r="J108" s="5">
@@ -7685,10 +7685,10 @@
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="H109" s="10" t="s">
         <v>211</v>
-      </c>
-      <c r="H109" s="10" t="s">
-        <v>212</v>
       </c>
       <c r="I109" s="9">
         <v>46304</v>
@@ -7738,10 +7738,10 @@
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="H110" s="6" t="s">
         <v>211</v>
-      </c>
-      <c r="H110" s="6" t="s">
-        <v>212</v>
       </c>
       <c r="I110" s="5">
         <v>46304</v>

--- a/data/50001580- CIA. RIO MINERALES.xlsx
+++ b/data/50001580- CIA. RIO MINERALES.xlsx
@@ -4849,7 +4849,7 @@
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46259.18545266204</v>
+        <v>46266.16962159722</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>97</v>
@@ -4912,7 +4912,7 @@
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46225.61435628472</v>
+        <v>46266.18140545139</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>143</v>
@@ -4956,8 +4956,8 @@
       <c r="R59" s="9">
         <v>46267</v>
       </c>
-      <c r="S59" s="7" t="s">
-        <v>33</v>
+      <c r="S59" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="T59" s="10">
         <v>0</v>

--- a/data/50001580- CIA. RIO MINERALES.xlsx
+++ b/data/50001580- CIA. RIO MINERALES.xlsx
@@ -689,10 +689,10 @@
     <t xml:space="preserve">OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,Caldereria,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A </t>
   </si>
   <si>
+    <t>1216788055231811</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1216788055231811</t>
   </si>
   <si>
     <t>1216788055231828</t>
@@ -4849,7 +4849,7 @@
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46266.16962159722</v>
+        <v>46267.17196707176</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>97</v>
@@ -4893,8 +4893,8 @@
       <c r="R58" s="5">
         <v>46262</v>
       </c>
-      <c r="S58" s="12" t="s">
-        <v>213</v>
+      <c r="S58" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="T58" s="6">
         <v>0</v>
@@ -4905,7 +4905,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B59" s="9">
         <v>46225.581215474536</v>
@@ -4957,7 +4957,7 @@
         <v>46267</v>
       </c>
       <c r="S59" s="12" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="T59" s="10">
         <v>0</v>
@@ -5081,7 +5081,7 @@
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46225.61447392361</v>
+        <v>46267.17527064815</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>222</v>
@@ -5125,8 +5125,8 @@
       <c r="R62" s="5">
         <v>46274</v>
       </c>
-      <c r="S62" s="7" t="s">
-        <v>33</v>
+      <c r="S62" s="12" t="s">
+        <v>214</v>
       </c>
       <c r="T62" s="6">
         <v>0</v>

--- a/data/50001580- CIA. RIO MINERALES.xlsx
+++ b/data/50001580- CIA. RIO MINERALES.xlsx
@@ -4912,7 +4912,7 @@
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46266.18140545139</v>
+        <v>46273.16870916667</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>143</v>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46238.48696543981</v>
+        <v>46273.16871085648</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>180</v>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46238.48696587963</v>
+        <v>46273.16871189815</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>180</v>

--- a/data/50001580- CIA. RIO MINERALES.xlsx
+++ b/data/50001580- CIA. RIO MINERALES.xlsx
@@ -692,31 +692,31 @@
     <t>1216788055231811</t>
   </si>
   <si>
+    <t>1216788055231828</t>
+  </si>
+  <si>
+    <t>Control de calidad Mecanizado OT4378,Control de calidad corte Laser OT4378,Control de calidad Corte plasma OT4378,Check Planos OT4378,Preparacion materiales OT4378</t>
+  </si>
+  <si>
+    <t>OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,Armado OT4378</t>
+  </si>
+  <si>
+    <t>1216788240660101</t>
+  </si>
+  <si>
+    <t>Preparacion materiales OT4378,Control de calidad Mecanizado OT4378,Control de calidad corte Laser OT4378,Control de calidad Corte plasma OT4378,Check Planos OT4378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armado OT4378,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A </t>
+  </si>
+  <si>
+    <t>1216788148260237</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado OT4378</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1216788055231828</t>
-  </si>
-  <si>
-    <t>Control de calidad Mecanizado OT4378,Control de calidad corte Laser OT4378,Control de calidad Corte plasma OT4378,Check Planos OT4378,Preparacion materiales OT4378</t>
-  </si>
-  <si>
-    <t>OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,Armado OT4378</t>
-  </si>
-  <si>
-    <t>1216788240660101</t>
-  </si>
-  <si>
-    <t>Preparacion materiales OT4378,Control de calidad Mecanizado OT4378,Control de calidad corte Laser OT4378,Control de calidad Corte plasma OT4378,Check Planos OT4378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armado OT4378,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A </t>
-  </si>
-  <si>
-    <t>1216788148260237</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado OT4378</t>
   </si>
   <si>
     <t>1216788148260254</t>
@@ -4912,7 +4912,7 @@
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46273.16870916667</v>
+        <v>46274.1467808912</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>143</v>
@@ -4956,8 +4956,8 @@
       <c r="R59" s="9">
         <v>46267</v>
       </c>
-      <c r="S59" s="12" t="s">
-        <v>214</v>
+      <c r="S59" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="T59" s="10">
         <v>0</v>
@@ -4968,7 +4968,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B60" s="5">
         <v>46225.581219618056</v>
@@ -5008,10 +5008,10 @@
         <v>143</v>
       </c>
       <c r="O60" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="P60" s="6" t="s">
         <v>216</v>
-      </c>
-      <c r="P60" s="6" t="s">
-        <v>217</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5021,7 +5021,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B61" s="9">
         <v>46225.58123596065</v>
@@ -5061,10 +5061,10 @@
         <v>143</v>
       </c>
       <c r="O61" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="P61" s="10" t="s">
         <v>219</v>
-      </c>
-      <c r="P61" s="10" t="s">
-        <v>220</v>
       </c>
       <c r="Q61" s="10"/>
       <c r="R61" s="10"/>
@@ -5074,17 +5074,17 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B62" s="5">
         <v>46225.58129219907</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46267.17527064815</v>
+        <v>46274.16863295139</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
@@ -5126,7 +5126,7 @@
         <v>46274</v>
       </c>
       <c r="S62" s="12" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="T62" s="6">
         <v>0</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46238.486964502314</v>
+        <v>46274.168634444446</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>180</v>
@@ -5172,7 +5172,7 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O63" s="10" t="s">
         <v>224</v>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46238.48696504629</v>
+        <v>46274.168635671296</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>180</v>
@@ -5223,7 +5223,7 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O64" s="6" t="s">
         <v>224</v>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46232.62438273148</v>
+        <v>46274.139942662034</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>244</v>
@@ -5636,8 +5636,8 @@
       <c r="R71" s="9">
         <v>46275</v>
       </c>
-      <c r="S71" s="7" t="s">
-        <v>33</v>
+      <c r="S71" s="12" t="s">
+        <v>222</v>
       </c>
       <c r="T71" s="10">
         <v>0</v>

--- a/data/50001580- CIA. RIO MINERALES.xlsx
+++ b/data/50001580- CIA. RIO MINERALES.xlsx
@@ -204,25 +204,22 @@
     <t>Alta</t>
   </si>
   <si>
+    <t>1216769310026544</t>
+  </si>
+  <si>
+    <t>Revision Tableros ot 4379</t>
+  </si>
+  <si>
+    <t>sergio saavedra fernandez</t>
+  </si>
+  <si>
+    <t>sergio.saavedra@zitron.com</t>
+  </si>
+  <si>
+    <t>ot  4379 -  TABLERO YD 63 KW,ot 4379 -  TABLERO YD 63 KW</t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1216769310026544</t>
-  </si>
-  <si>
-    <t>Revision Tableros ot 4379</t>
-  </si>
-  <si>
-    <t>sergio saavedra fernandez</t>
-  </si>
-  <si>
-    <t>sergio.saavedra@zitron.com</t>
-  </si>
-  <si>
-    <t>ot  4379 -  TABLERO YD 63 KW,ot 4379 -  TABLERO YD 63 KW</t>
-  </si>
-  <si>
-    <t>Tarea sin iniciar</t>
   </si>
   <si>
     <t>1216769310026574</t>
@@ -360,6 +357,9 @@
   </si>
   <si>
     <t>Generacion oc tableros ot 4379</t>
+  </si>
+  <si>
+    <t>Tarea sin iniciar</t>
   </si>
   <si>
     <t>1216769310026536</t>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="C9" s="10"/>
       <c r="D9" s="9">
-        <v>46225.60046916667</v>
+        <v>46274.7341921412</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>45</v>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46231.20725755787</v>
+        <v>46274.73425525463</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>48</v>
@@ -2109,34 +2109,34 @@
         <v>52</v>
       </c>
       <c r="T10" s="6">
-        <v>0</v>
-      </c>
-      <c r="U10" s="12" t="s">
-        <v>53</v>
+        <v>1</v>
+      </c>
+      <c r="U10" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B11" s="9">
         <v>46225.58274704861</v>
       </c>
       <c r="C11" s="10"/>
       <c r="D11" s="9">
-        <v>46225.61217166667</v>
+        <v>46274.73486938658</v>
       </c>
       <c r="E11" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="F11" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G11" s="10" t="s">
+      <c r="H11" s="10" t="s">
         <v>56</v>
-      </c>
-      <c r="H11" s="10" t="s">
-        <v>57</v>
       </c>
       <c r="I11" s="9">
         <v>46294</v>
@@ -2157,7 +2157,7 @@
         <v>45</v>
       </c>
       <c r="O11" s="10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P11" s="10" t="s">
         <v>45</v>
@@ -2172,15 +2172,15 @@
         <v>33</v>
       </c>
       <c r="T11" s="10">
-        <v>0</v>
-      </c>
-      <c r="U11" s="11" t="s">
-        <v>59</v>
+        <v>0.2</v>
+      </c>
+      <c r="U11" s="12" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B12" s="5">
         <v>46225.59567834491</v>
@@ -2190,16 +2190,16 @@
         <v>46225.612248819445</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G12" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="H12" s="6" t="s">
         <v>56</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>57</v>
       </c>
       <c r="I12" s="5">
         <v>46294</v>
@@ -2217,13 +2217,13 @@
         <v>26</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O12" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="P12" s="6" t="s">
         <v>62</v>
-      </c>
-      <c r="P12" s="6" t="s">
-        <v>63</v>
       </c>
       <c r="Q12" s="6"/>
       <c r="R12" s="6"/>
@@ -2233,7 +2233,7 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B13" s="9">
         <v>46225.595835520835</v>
@@ -2243,16 +2243,16 @@
         <v>46225.61224515046</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G13" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="H13" s="10" t="s">
         <v>56</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>57</v>
       </c>
       <c r="I13" s="9">
         <v>46294</v>
@@ -2270,13 +2270,13 @@
         <v>26</v>
       </c>
       <c r="N13" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O13" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="P13" s="10" t="s">
         <v>62</v>
-      </c>
-      <c r="P13" s="10" t="s">
-        <v>63</v>
       </c>
       <c r="Q13" s="10"/>
       <c r="R13" s="10"/>
@@ -2286,7 +2286,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B14" s="5">
         <v>46225.58085679398</v>
@@ -2298,7 +2298,7 @@
         <v>46226.576112442126</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>25</v>
@@ -2322,7 +2322,7 @@
         <v>26</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P14" s="6" t="s">
         <v>26</v>
@@ -2339,7 +2339,7 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B15" s="9">
         <v>46225.58095215278</v>
@@ -2351,7 +2351,7 @@
         <v>46228.19449930555</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>26</v>
@@ -2372,19 +2372,19 @@
         <v>26</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M15" s="10" t="s">
         <v>26</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O15" s="10" t="s">
         <v>38</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q15" s="9">
         <v>46227</v>
@@ -2404,7 +2404,7 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B16" s="5">
         <v>46225.580861423616</v>
@@ -2414,7 +2414,7 @@
         <v>46225.59611458333</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>25</v>
@@ -2438,7 +2438,7 @@
         <v>26</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P16" s="6" t="s">
         <v>26</v>
@@ -2451,7 +2451,7 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B17" s="9">
         <v>46225.580958923616</v>
@@ -2461,16 +2461,16 @@
         <v>46237.5500087963</v>
       </c>
       <c r="E17" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="F17" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G17" s="10" t="s">
+      <c r="H17" s="10" t="s">
         <v>77</v>
-      </c>
-      <c r="H17" s="10" t="s">
-        <v>78</v>
       </c>
       <c r="I17" s="9">
         <v>46226</v>
@@ -2488,13 +2488,13 @@
         <v>26</v>
       </c>
       <c r="N17" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O17" s="10" t="s">
         <v>38</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q17" s="9">
         <v>46227</v>
@@ -2514,7 +2514,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B18" s="5">
         <v>46225.58096494213</v>
@@ -2524,16 +2524,16 @@
         <v>46237.550030706014</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="H18" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>78</v>
       </c>
       <c r="I18" s="5">
         <v>46226</v>
@@ -2551,13 +2551,13 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O18" s="6" t="s">
         <v>38</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Q18" s="5">
         <v>46227</v>
@@ -2577,7 +2577,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B19" s="9">
         <v>46225.58097109954</v>
@@ -2587,16 +2587,16 @@
         <v>46237.55005269676</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="H19" s="10" t="s">
         <v>77</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>78</v>
       </c>
       <c r="I19" s="9">
         <v>46226</v>
@@ -2614,13 +2614,13 @@
         <v>26</v>
       </c>
       <c r="N19" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O19" s="10" t="s">
         <v>38</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q19" s="9">
         <v>46227</v>
@@ -2640,7 +2640,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B20" s="5">
         <v>46225.58086628473</v>
@@ -2650,7 +2650,7 @@
         <v>46225.59619578704</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>25</v>
@@ -2674,7 +2674,7 @@
         <v>26</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P20" s="6" t="s">
         <v>26</v>
@@ -2687,7 +2687,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B21" s="9">
         <v>46225.580978240745</v>
@@ -2697,16 +2697,16 @@
         <v>46247.17789210648</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="H21" s="10" t="s">
         <v>77</v>
-      </c>
-      <c r="H21" s="10" t="s">
-        <v>78</v>
       </c>
       <c r="I21" s="9">
         <v>46245</v>
@@ -2724,13 +2724,13 @@
         <v>26</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="O21" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="P21" s="10" t="s">
         <v>90</v>
-      </c>
-      <c r="P21" s="10" t="s">
-        <v>91</v>
       </c>
       <c r="Q21" s="9">
         <v>46246</v>
@@ -2745,12 +2745,12 @@
         <v>0</v>
       </c>
       <c r="U21" s="12" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B22" s="5">
         <v>46225.5809840625</v>
@@ -2760,16 +2760,16 @@
         <v>46247.17788666667</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="H22" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>78</v>
       </c>
       <c r="I22" s="5">
         <v>46245</v>
@@ -2787,13 +2787,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q22" s="5">
         <v>46246</v>
@@ -2808,12 +2808,12 @@
         <v>0</v>
       </c>
       <c r="U22" s="12" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B23" s="9">
         <v>46225.58098827546</v>
@@ -2823,16 +2823,16 @@
         <v>46247.17788644676</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="H23" s="10" t="s">
         <v>77</v>
-      </c>
-      <c r="H23" s="10" t="s">
-        <v>78</v>
       </c>
       <c r="I23" s="9">
         <v>46245</v>
@@ -2850,13 +2850,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q23" s="9">
         <v>46246</v>
@@ -2871,12 +2871,12 @@
         <v>0</v>
       </c>
       <c r="U23" s="12" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B24" s="5">
         <v>46225.58100011574</v>
@@ -2886,16 +2886,16 @@
         <v>46247.17788643518</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="H24" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>78</v>
       </c>
       <c r="I24" s="5">
         <v>46245</v>
@@ -2913,13 +2913,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q24" s="5">
         <v>46246</v>
@@ -2934,12 +2934,12 @@
         <v>0</v>
       </c>
       <c r="U24" s="12" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B25" s="9">
         <v>46225.59619364583</v>
@@ -2949,16 +2949,16 @@
         <v>46233.168979988426</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="H25" s="10" t="s">
         <v>77</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>78</v>
       </c>
       <c r="I25" s="9">
         <v>46231</v>
@@ -2976,13 +2976,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="O25" s="10" t="s">
         <v>48</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Q25" s="9">
         <v>46232</v>
@@ -2997,7 +2997,7 @@
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
@@ -3107,7 +3107,7 @@
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
@@ -3152,7 +3152,7 @@
         <v>106</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P28" s="6" t="s">
         <v>113</v>
@@ -3166,7 +3166,7 @@
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
@@ -3225,7 +3225,7 @@
         <v>0</v>
       </c>
       <c r="U29" s="11" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
@@ -3288,7 +3288,7 @@
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
@@ -3303,7 +3303,7 @@
         <v>46248.17134908565</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
@@ -3333,7 +3333,7 @@
         <v>118</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P31" s="10" t="s">
         <v>121</v>
@@ -3386,7 +3386,7 @@
         <v>118</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>124</v>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="U33" s="11" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
@@ -3472,7 +3472,7 @@
         <v>46248.17135226852</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
@@ -3502,7 +3502,7 @@
         <v>126</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>129</v>
@@ -3555,7 +3555,7 @@
         <v>126</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>132</v>
@@ -3626,7 +3626,7 @@
         <v>0</v>
       </c>
       <c r="U36" s="11" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
@@ -3848,7 +3848,7 @@
         <v>0</v>
       </c>
       <c r="U40" s="11" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
@@ -3863,7 +3863,7 @@
         <v>46241.17189372685</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
@@ -3893,7 +3893,7 @@
         <v>150</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P41" s="10" t="s">
         <v>155</v>
@@ -3946,7 +3946,7 @@
         <v>150</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>158</v>
@@ -4048,7 +4048,7 @@
         <v>160</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>166</v>
@@ -4148,7 +4148,7 @@
         <v>46245.1918381713</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
@@ -4259,7 +4259,7 @@
         <v>0</v>
       </c>
       <c r="U47" s="11" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
@@ -4475,7 +4475,7 @@
         <v>0</v>
       </c>
       <c r="U51" s="11" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
@@ -4538,7 +4538,7 @@
         <v>0</v>
       </c>
       <c r="U52" s="11" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
@@ -4601,7 +4601,7 @@
         <v>0</v>
       </c>
       <c r="U53" s="11" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
@@ -4664,7 +4664,7 @@
         <v>0</v>
       </c>
       <c r="U54" s="11" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
@@ -4727,7 +4727,7 @@
         <v>0</v>
       </c>
       <c r="U55" s="11" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
@@ -4790,7 +4790,7 @@
         <v>0</v>
       </c>
       <c r="U56" s="11" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
@@ -4852,7 +4852,7 @@
         <v>46267.17196707176</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
@@ -4882,7 +4882,7 @@
         <v>207</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>212</v>
@@ -4900,7 +4900,7 @@
         <v>0</v>
       </c>
       <c r="U58" s="11" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
@@ -4963,7 +4963,7 @@
         <v>0</v>
       </c>
       <c r="U59" s="11" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
@@ -5132,7 +5132,7 @@
         <v>0</v>
       </c>
       <c r="U62" s="11" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
@@ -5326,7 +5326,7 @@
         <v>229</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>233</v>
@@ -5344,7 +5344,7 @@
         <v>0</v>
       </c>
       <c r="U66" s="11" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
@@ -5389,7 +5389,7 @@
         <v>229</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P67" s="10" t="s">
         <v>236</v>
@@ -5407,7 +5407,7 @@
         <v>0</v>
       </c>
       <c r="U67" s="11" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -5452,7 +5452,7 @@
         <v>229</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>233</v>
@@ -5470,7 +5470,7 @@
         <v>0</v>
       </c>
       <c r="U68" s="11" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
@@ -5485,7 +5485,7 @@
         <v>46225.61467041667</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
@@ -5518,7 +5518,7 @@
         <v>157</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q69" s="9">
         <v>46293</v>
@@ -5533,7 +5533,7 @@
         <v>0</v>
       </c>
       <c r="U69" s="11" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
@@ -5601,10 +5601,10 @@
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="H71" s="10" t="s">
         <v>77</v>
-      </c>
-      <c r="H71" s="10" t="s">
-        <v>78</v>
       </c>
       <c r="I71" s="9">
         <v>46275</v>
@@ -5643,7 +5643,7 @@
         <v>0</v>
       </c>
       <c r="U71" s="11" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
@@ -5664,10 +5664,10 @@
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>78</v>
       </c>
       <c r="I72" s="5">
         <v>46275</v>
@@ -5717,10 +5717,10 @@
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="H73" s="10" t="s">
         <v>77</v>
-      </c>
-      <c r="H73" s="10" t="s">
-        <v>78</v>
       </c>
       <c r="I73" s="9">
         <v>46275</v>
@@ -5770,10 +5770,10 @@
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>78</v>
       </c>
       <c r="I74" s="5">
         <v>46286</v>
@@ -5812,7 +5812,7 @@
         <v>0</v>
       </c>
       <c r="U74" s="11" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
@@ -5833,10 +5833,10 @@
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="H75" s="10" t="s">
         <v>77</v>
-      </c>
-      <c r="H75" s="10" t="s">
-        <v>78</v>
       </c>
       <c r="I75" s="9">
         <v>46286</v>
@@ -5886,10 +5886,10 @@
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>78</v>
       </c>
       <c r="I76" s="5">
         <v>46286</v>
@@ -5939,10 +5939,10 @@
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="H77" s="10" t="s">
         <v>77</v>
-      </c>
-      <c r="H77" s="10" t="s">
-        <v>78</v>
       </c>
       <c r="I77" s="9">
         <v>46287</v>
@@ -5981,7 +5981,7 @@
         <v>0</v>
       </c>
       <c r="U77" s="11" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
@@ -6002,10 +6002,10 @@
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="H78" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>78</v>
       </c>
       <c r="I78" s="6"/>
       <c r="J78" s="5">
@@ -6053,10 +6053,10 @@
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="H79" s="10" t="s">
         <v>77</v>
-      </c>
-      <c r="H79" s="10" t="s">
-        <v>78</v>
       </c>
       <c r="I79" s="10"/>
       <c r="J79" s="9">
@@ -6104,10 +6104,10 @@
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="H80" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>78</v>
       </c>
       <c r="I80" s="5">
         <v>46288</v>
@@ -6146,7 +6146,7 @@
         <v>0</v>
       </c>
       <c r="U80" s="11" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
@@ -6167,10 +6167,10 @@
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="H81" s="10" t="s">
         <v>77</v>
-      </c>
-      <c r="H81" s="10" t="s">
-        <v>78</v>
       </c>
       <c r="I81" s="9">
         <v>46288</v>
@@ -6220,10 +6220,10 @@
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="H82" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>78</v>
       </c>
       <c r="I82" s="5">
         <v>46288</v>
@@ -6273,10 +6273,10 @@
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="H83" s="10" t="s">
         <v>77</v>
-      </c>
-      <c r="H83" s="10" t="s">
-        <v>78</v>
       </c>
       <c r="I83" s="9">
         <v>46289</v>
@@ -6326,10 +6326,10 @@
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="H84" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>78</v>
       </c>
       <c r="I84" s="5">
         <v>46290</v>
@@ -6368,7 +6368,7 @@
         <v>0</v>
       </c>
       <c r="U84" s="11" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
@@ -6389,10 +6389,10 @@
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="H85" s="10" t="s">
         <v>77</v>
-      </c>
-      <c r="H85" s="10" t="s">
-        <v>78</v>
       </c>
       <c r="I85" s="10"/>
       <c r="J85" s="9">
@@ -6440,10 +6440,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="H86" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>78</v>
       </c>
       <c r="I86" s="6"/>
       <c r="J86" s="5">
@@ -6491,10 +6491,10 @@
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="H87" s="10" t="s">
         <v>77</v>
-      </c>
-      <c r="H87" s="10" t="s">
-        <v>78</v>
       </c>
       <c r="I87" s="9">
         <v>46293</v>
@@ -6533,7 +6533,7 @@
         <v>0</v>
       </c>
       <c r="U87" s="11" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
@@ -6554,10 +6554,10 @@
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="H88" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>78</v>
       </c>
       <c r="I88" s="5">
         <v>46293</v>
@@ -6607,10 +6607,10 @@
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="H89" s="10" t="s">
         <v>77</v>
-      </c>
-      <c r="H89" s="10" t="s">
-        <v>78</v>
       </c>
       <c r="I89" s="9">
         <v>46293</v>
@@ -6749,7 +6749,7 @@
         <v>0</v>
       </c>
       <c r="U91" s="11" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
@@ -6896,7 +6896,7 @@
         <v>294</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>304</v>
@@ -6947,7 +6947,7 @@
         <v>294</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="P95" s="10" t="s">
         <v>304</v>
@@ -6976,10 +6976,10 @@
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="H96" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>78</v>
       </c>
       <c r="I96" s="6"/>
       <c r="J96" s="5">
@@ -7016,7 +7016,7 @@
         <v>0</v>
       </c>
       <c r="U96" s="11" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
@@ -7037,10 +7037,10 @@
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="H97" s="10" t="s">
         <v>77</v>
-      </c>
-      <c r="H97" s="10" t="s">
-        <v>78</v>
       </c>
       <c r="I97" s="9">
         <v>46302</v>
@@ -7090,10 +7090,10 @@
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="H98" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>78</v>
       </c>
       <c r="I98" s="5">
         <v>46302</v>
@@ -7143,10 +7143,10 @@
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="H99" s="10" t="s">
         <v>77</v>
-      </c>
-      <c r="H99" s="10" t="s">
-        <v>78</v>
       </c>
       <c r="I99" s="9">
         <v>46302</v>
@@ -7196,10 +7196,10 @@
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="H100" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>78</v>
       </c>
       <c r="I100" s="5">
         <v>46302</v>
@@ -7291,7 +7291,7 @@
         <v>0</v>
       </c>
       <c r="U101" s="11" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
@@ -7562,7 +7562,7 @@
         <v>0</v>
       </c>
       <c r="U106" s="11" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
@@ -7880,7 +7880,7 @@
         <v>0</v>
       </c>
       <c r="U112" s="11" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
@@ -7943,7 +7943,7 @@
         <v>0</v>
       </c>
       <c r="U113" s="11" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001580- CIA. RIO MINERALES.xlsx
+++ b/data/50001580- CIA. RIO MINERALES.xlsx
@@ -716,76 +716,76 @@
     <t>Control de calidad Armado OT4378</t>
   </si>
   <si>
+    <t>1216788148260254</t>
+  </si>
+  <si>
+    <t>OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,Check Planos OT4378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Armado OT4378,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A </t>
+  </si>
+  <si>
+    <t>1216788235261927</t>
+  </si>
+  <si>
+    <t>OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,Control de calidad Armado OT4378</t>
+  </si>
+  <si>
+    <t>1216788235261949</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe OT4378,Recepcion Rodete OT4378,Recepcion motor OT4378</t>
+  </si>
+  <si>
+    <t>1216788148278105</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe OT4378</t>
+  </si>
+  <si>
+    <t>OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,Bodega:</t>
+  </si>
+  <si>
+    <t>1216788148278127</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete OT4378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega:,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A </t>
+  </si>
+  <si>
+    <t>1216788148289615</t>
+  </si>
+  <si>
+    <t>Recepcion motor OT4378</t>
+  </si>
+  <si>
+    <t>1216769310026593</t>
+  </si>
+  <si>
+    <t>1216788353013119</t>
+  </si>
+  <si>
+    <t>Montaje:</t>
+  </si>
+  <si>
+    <t>Montaje Alabe OT4378,Montaje Rodete OT4378,Revestimiento OT4378,Montaje motor OT4378</t>
+  </si>
+  <si>
+    <t>1216788353013131</t>
+  </si>
+  <si>
+    <t>Revestimiento OT4378</t>
+  </si>
+  <si>
+    <t>Montaje:,Montaje Alabe OT4378</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1216788148260254</t>
-  </si>
-  <si>
-    <t>OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,Check Planos OT4378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Armado OT4378,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A </t>
-  </si>
-  <si>
-    <t>1216788235261927</t>
-  </si>
-  <si>
-    <t>OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,Control de calidad Armado OT4378</t>
-  </si>
-  <si>
-    <t>1216788235261949</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe OT4378,Recepcion Rodete OT4378,Recepcion motor OT4378</t>
-  </si>
-  <si>
-    <t>1216788148278105</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe OT4378</t>
-  </si>
-  <si>
-    <t>OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,Bodega:</t>
-  </si>
-  <si>
-    <t>1216788148278127</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete OT4378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega:,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A </t>
-  </si>
-  <si>
-    <t>1216788148289615</t>
-  </si>
-  <si>
-    <t>Recepcion motor OT4378</t>
-  </si>
-  <si>
-    <t>1216769310026593</t>
-  </si>
-  <si>
-    <t>1216788353013119</t>
-  </si>
-  <si>
-    <t>Montaje:</t>
-  </si>
-  <si>
-    <t>Montaje Alabe OT4378,Montaje Rodete OT4378,Revestimiento OT4378,Montaje motor OT4378</t>
-  </si>
-  <si>
-    <t>1216788353013131</t>
-  </si>
-  <si>
-    <t>Revestimiento OT4378</t>
-  </si>
-  <si>
-    <t>Montaje:,Montaje Alabe OT4378</t>
   </si>
   <si>
     <t>1216788148296193</t>
@@ -5081,7 +5081,7 @@
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46274.16863295139</v>
+        <v>46275.15575423611</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>221</v>
@@ -5125,8 +5125,8 @@
       <c r="R62" s="5">
         <v>46274</v>
       </c>
-      <c r="S62" s="12" t="s">
-        <v>222</v>
+      <c r="S62" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="T62" s="6">
         <v>0</v>
@@ -5137,7 +5137,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B63" s="9">
         <v>46225.58129802083</v>
@@ -5175,10 +5175,10 @@
         <v>221</v>
       </c>
       <c r="O63" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="P63" s="10" t="s">
         <v>224</v>
-      </c>
-      <c r="P63" s="10" t="s">
-        <v>225</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5188,7 +5188,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B64" s="5">
         <v>46225.581304374995</v>
@@ -5226,10 +5226,10 @@
         <v>221</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5239,7 +5239,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B65" s="9">
         <v>46225.58131015046</v>
@@ -5249,7 +5249,7 @@
         <v>46225.59759329861</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>25</v>
@@ -5273,7 +5273,7 @@
         <v>26</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="P65" s="10" t="s">
         <v>26</v>
@@ -5286,7 +5286,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B66" s="5">
         <v>46225.58131376158</v>
@@ -5296,7 +5296,7 @@
         <v>46232.18544357639</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5323,13 +5323,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="O66" s="6" t="s">
         <v>75</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q66" s="5">
         <v>46231</v>
@@ -5349,7 +5349,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B67" s="9">
         <v>46225.58131929398</v>
@@ -5359,7 +5359,7 @@
         <v>46232.18544451389</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
@@ -5386,13 +5386,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="O67" s="10" t="s">
         <v>80</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Q67" s="9">
         <v>46231</v>
@@ -5412,7 +5412,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B68" s="5">
         <v>46225.58132505787</v>
@@ -5422,7 +5422,7 @@
         <v>46232.18544357639</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5449,13 +5449,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>83</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q68" s="5">
         <v>46231</v>
@@ -5475,7 +5475,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B69" s="9">
         <v>46225.597591134254</v>
@@ -5512,7 +5512,7 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="O69" s="10" t="s">
         <v>157</v>
@@ -5538,7 +5538,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B70" s="5">
         <v>46225.58133054398</v>
@@ -5548,7 +5548,7 @@
         <v>46232.67654627315</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>25</v>
@@ -5572,7 +5572,7 @@
         <v>26</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -5585,7 +5585,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B71" s="9">
         <v>46225.58133395833</v>
@@ -5595,7 +5595,7 @@
         <v>46274.139942662034</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
@@ -5622,13 +5622,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="O71" s="10" t="s">
         <v>178</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="Q71" s="9">
         <v>46281</v>
@@ -5637,7 +5637,7 @@
         <v>46275</v>
       </c>
       <c r="S71" s="12" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="T71" s="10">
         <v>0</v>
@@ -5685,7 +5685,7 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>180</v>
@@ -5738,7 +5738,7 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="O73" s="10" t="s">
         <v>180</v>
@@ -5791,7 +5791,7 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="O74" s="6" t="s">
         <v>252</v>
@@ -5960,7 +5960,7 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="O77" s="10" t="s">
         <v>260</v>
@@ -6125,7 +6125,7 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>268</v>
@@ -6294,7 +6294,7 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="O83" s="10" t="s">
         <v>267</v>
@@ -6347,7 +6347,7 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="O84" s="6" t="s">
         <v>279</v>
@@ -6512,7 +6512,7 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="O87" s="10" t="s">
         <v>286</v>
